--- a/AAII_Financials/Quarterly/HWKN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HWKN_QTR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Quarterly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Quarterly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="147" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
   <si>
     <t>HWKN</t>
   </si>
@@ -656,417 +656,430 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AF102"/>
+  <dimension ref="A5:AG102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="31" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="32" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E7" s="2">
         <v>45200</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45109</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45018</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>44927</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44836</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44745</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44654</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44556</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44465</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44374</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44283</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44192</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44101</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44010</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>43919</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43828</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43737</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43646</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43555</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43464</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43373</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43282</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43191</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43100</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43009</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>42918</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42827</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42736</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="8" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>208500</v>
+      </c>
+      <c r="E8" s="3">
         <v>236500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>251100</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>228100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>219200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>241200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>246500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>223000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>187100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>183300</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>181200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>163000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>142900</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>147800</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>143200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>132400</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>120400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>140000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>147300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>133100</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>128200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>145300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>149800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>127000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>118100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>125400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>133700</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>118600</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>112400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>121300</v>
       </c>
     </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>166200</v>
+      </c>
+      <c r="E9" s="3">
         <v>182600</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>199100</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>192400</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>182900</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>194800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>199800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>186700</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>153100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>146000</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>142300</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>131200</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>114700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>115000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>112200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>109800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>98900</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>112000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>118500</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>112400</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>107100</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>119600</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>121300</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>109200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>99200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>101300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>107700</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>96700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>91400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>94200</v>
       </c>
     </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>42300</v>
+      </c>
+      <c r="E10" s="3">
         <v>53900</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>52000</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>35700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>36300</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>46400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>46700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>36300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>34000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>37300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>38900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>31800</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>28200</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>32800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>31000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>22600</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>21500</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>28000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>28800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>20700</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>21100</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>25700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>28500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>17800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>18900</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>24100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>26000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>21900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>21000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>27100</v>
       </c>
     </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1099,8 +1112,9 @@
       <c r="AD11" s="3"/>
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG11" s="3"/>
+    </row>
+    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1191,8 +1205,11 @@
       <c r="AF12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1283,8 +1300,11 @@
       <c r="AF13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1336,17 +1356,17 @@
       <c r="S14" s="3">
         <v>0</v>
       </c>
-      <c r="T14" s="3" t="s">
-        <v>8</v>
+      <c r="T14" s="3">
+        <v>0</v>
       </c>
       <c r="U14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V14" s="3">
-        <v>0</v>
-      </c>
-      <c r="W14" s="3" t="s">
+      <c r="V14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
@@ -1354,11 +1374,11 @@
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
+      <c r="Z14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA14" s="3">
         <v>39100</v>
-      </c>
-      <c r="AA14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
@@ -1375,8 +1395,11 @@
       <c r="AF14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1467,8 +1490,11 @@
       <c r="AF15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:32" x14ac:dyDescent="0.2">
+      <c r="AG15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1498,192 +1524,199 @@
       <c r="AD16" s="3"/>
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
-    </row>
-    <row r="17" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG16" s="3"/>
+    </row>
+    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>190000</v>
+      </c>
+      <c r="E17" s="3">
         <v>203500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>218600</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>209700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>204000</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>214700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>218700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>207800</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>172800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>163700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>159100</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>150100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>132400</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>131200</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>127200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>124700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>113600</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>126900</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>133400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>127300</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>121400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>134500</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>136300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>163000</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>113400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>116100</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>123500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>111200</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>106400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>109100</v>
       </c>
     </row>
-    <row r="18" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>18500</v>
+      </c>
+      <c r="E18" s="3">
         <v>33000</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>32500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>18400</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>15200</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>26500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>27800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>15200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>14300</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>19600</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>22100</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>12900</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>10500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>16600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>16000</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>7700</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>6800</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>13100</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>13900</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>5800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>6800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>10800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>13500</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>-36000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>4700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>9300</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>10200</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>7400</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>6000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="19" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1716,76 +1749,77 @@
       <c r="AD19" s="3"/>
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
-    </row>
-    <row r="20" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG19" s="3"/>
+    </row>
+    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>800</v>
+      </c>
+      <c r="E20" s="3">
         <v>-300</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>400</v>
-      </c>
-      <c r="F20" s="3">
-        <v>500</v>
       </c>
       <c r="G20" s="3">
         <v>500</v>
       </c>
       <c r="H20" s="3">
+        <v>500</v>
+      </c>
+      <c r="I20" s="3">
         <v>-500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>100</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>200</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>300</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>400</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-1000</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-400</v>
-      </c>
-      <c r="T20" s="3">
-        <v>-600</v>
       </c>
       <c r="U20" s="3">
         <v>-600</v>
       </c>
       <c r="V20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="W20" s="3">
         <v>-500</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1200</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-700</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-900</v>
       </c>
       <c r="Z20" s="3">
         <v>-900</v>
@@ -1794,140 +1828,146 @@
         <v>-900</v>
       </c>
       <c r="AB20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-800</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-700</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-600</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>-700</v>
       </c>
       <c r="AF20" s="3">
         <v>-700</v>
       </c>
-    </row>
-    <row r="21" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG20" s="3">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>27700</v>
+      </c>
+      <c r="E21" s="3">
         <v>40100</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>39900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>26000</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>22700</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>32900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>33700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>21100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>20400</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>25700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>28300</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>19000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>16600</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>22500</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>21900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>12200</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>11800</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>17900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>18700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>10700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>11000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>15600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>18000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>-31200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>9300</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>14000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>15300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>12200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>10500</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="22" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E22" s="3">
         <v>700</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1100</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>900</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>400</v>
-      </c>
-      <c r="K22" s="3">
-        <v>300</v>
       </c>
       <c r="L22" s="3">
         <v>300</v>
@@ -1936,25 +1976,25 @@
         <v>300</v>
       </c>
       <c r="N22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="O22" s="3">
         <v>400</v>
       </c>
       <c r="P22" s="3">
+        <v>400</v>
+      </c>
+      <c r="Q22" s="3">
         <v>300</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>400</v>
-      </c>
-      <c r="R22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="S22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="T22" s="3">
-        <v>0</v>
+      <c r="T22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="U22" s="3">
         <v>0</v>
@@ -1992,192 +2032,201 @@
       <c r="AF22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>18200</v>
+      </c>
+      <c r="E23" s="3">
         <v>32000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>31700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>17500</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>14200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>24700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>26200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>14400</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>14100</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>19500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>22000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>12700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>10600</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>16600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>16000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>6800</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6300</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>12500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>13300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>5300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>5600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>10100</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>12500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>-36900</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>3800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>8500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>9500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>6800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5400</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="24" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E24" s="3">
         <v>8800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>6700</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6500</v>
-      </c>
-      <c r="J24" s="3">
-        <v>3900</v>
       </c>
       <c r="K24" s="3">
         <v>3900</v>
       </c>
       <c r="L24" s="3">
+        <v>3900</v>
+      </c>
+      <c r="M24" s="3">
         <v>5300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>5400</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>3600</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>2700</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>4400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4200</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2000</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>1800</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3500</v>
-      </c>
-      <c r="V24" s="3">
-        <v>1500</v>
       </c>
       <c r="W24" s="3">
         <v>1500</v>
       </c>
       <c r="X24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Y24" s="3">
         <v>2700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>1200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>-100</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>2600</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1800</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="25" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2268,192 +2317,201 @@
       <c r="AF25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E26" s="3">
         <v>23200</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>23400</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>11600</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>10700</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>18000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>19700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10200</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>14100</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>16600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>9100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>7900</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>12200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>11800</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>4800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4500</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>9300</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>9800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>3800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>7400</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>9100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>-38100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3900</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>5200</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>5800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>4200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3600</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="27" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E27" s="3">
         <v>23200</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>23400</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>11600</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>10700</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>18000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>19700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>10200</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>14100</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>16600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>9100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>7900</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>12200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>11800</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>4800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4500</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>9300</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>9800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>3800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>7400</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>9100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>-38100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3900</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>5200</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>5800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>4200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3600</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="28" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2544,8 +2602,11 @@
       <c r="AF28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2597,17 +2658,17 @@
       <c r="S29" s="3">
         <v>0</v>
       </c>
-      <c r="T29" s="3" t="s">
-        <v>8</v>
+      <c r="T29" s="3">
+        <v>0</v>
       </c>
       <c r="U29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V29" s="3">
-        <v>0</v>
-      </c>
-      <c r="W29" s="3" t="s">
+      <c r="V29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
@@ -2615,14 +2676,14 @@
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
+      <c r="Z29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AA29" s="3">
         <v>700</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AB29" s="3">
         <v>13200</v>
-      </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2636,8 +2697,11 @@
       <c r="AF29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2728,8 +2792,11 @@
       <c r="AF30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2820,76 +2887,79 @@
       <c r="AF31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-800</v>
+      </c>
+      <c r="E32" s="3">
         <v>300</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-400</v>
-      </c>
-      <c r="F32" s="3">
-        <v>-500</v>
       </c>
       <c r="G32" s="3">
         <v>-500</v>
       </c>
       <c r="H32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="I32" s="3">
         <v>500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-100</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-200</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-300</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-400</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>1000</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>400</v>
-      </c>
-      <c r="T32" s="3">
-        <v>600</v>
       </c>
       <c r="U32" s="3">
         <v>600</v>
       </c>
       <c r="V32" s="3">
+        <v>600</v>
+      </c>
+      <c r="W32" s="3">
         <v>500</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1200</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>700</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>900</v>
       </c>
       <c r="Z32" s="3">
         <v>900</v>
@@ -2898,114 +2968,120 @@
         <v>900</v>
       </c>
       <c r="AB32" s="3">
+        <v>900</v>
+      </c>
+      <c r="AC32" s="3">
         <v>800</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>700</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>600</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>700</v>
       </c>
       <c r="AF32" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="33" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG32" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E33" s="3">
         <v>23200</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>23400</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>11600</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>10700</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>18000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>19700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>10200</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>14100</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>16600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>9100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>7900</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>12200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>11800</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>4800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4500</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>9300</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>9800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>3800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>7400</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>9100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>-37400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>17100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>5200</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>5800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>4200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3600</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="34" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3096,197 +3172,206 @@
       <c r="AF34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E35" s="3">
         <v>23200</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>23400</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>11600</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>10700</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>18000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>19700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>10200</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>14100</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>16600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>9100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>7900</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>12200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>11800</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>4800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4500</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>9300</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>9800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>3800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>7400</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>9100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>-37400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>17100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>5200</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>5800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>4200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3600</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="37" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E38" s="2">
         <v>45200</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45109</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45018</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>44927</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44836</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44745</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44654</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44556</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44465</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44374</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44283</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44192</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44101</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44010</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>43919</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43828</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43737</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43646</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43555</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43464</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43373</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43282</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43191</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43100</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43009</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>42918</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42827</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42736</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="39" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3319,8 +3404,9 @@
       <c r="AD39" s="3"/>
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
-    </row>
-    <row r="40" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG39" s="3"/>
+    </row>
+    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3353,100 +3439,104 @@
       <c r="AD40" s="3"/>
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
-    </row>
-    <row r="41" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG40" s="3"/>
+    </row>
+    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5700</v>
+      </c>
+      <c r="E41" s="3">
         <v>11000</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7100</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7600</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>6100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>3900</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3500</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>23400</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6800</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>5200</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>8000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>4500</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4300</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>7300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4100</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5600</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>9200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>3800</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>2800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>6900</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>8400</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>16700</v>
       </c>
     </row>
-    <row r="42" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3537,376 +3627,391 @@
       <c r="AF42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>113000</v>
+      </c>
+      <c r="E43" s="3">
         <v>124800</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>138300</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>129300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>125500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>131400</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>138800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>122800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>102800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>90100</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>90900</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>90800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>77800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>74500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>69500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>67400</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>56700</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>65400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>69000</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>64500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>61500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>66400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>67900</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>66200</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>57900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>60000</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>62800</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>58600</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>53300</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>52800</v>
       </c>
     </row>
-    <row r="44" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>68800</v>
+      </c>
+      <c r="E44" s="3">
         <v>68500</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>76900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>88800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>101600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>113100</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>105000</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>95000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>76200</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>70300</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>67900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>63900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>64700</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>63200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>63400</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>54400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>57500</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>60800</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>58700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>60500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>67700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>67800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>66400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>59700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>62700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>65900</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>65600</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>51200</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>50300</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="45" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>7400</v>
+      </c>
+      <c r="E45" s="3">
         <v>3000</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>4100</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>6400</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>7100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>3200</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3900</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>6400</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>7000</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>2500</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3700</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>5400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>1700</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>4900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5600</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2800</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>4800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5200</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5700</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3500</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>4100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2500</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3300</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>5100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="46" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>195000</v>
+      </c>
+      <c r="E46" s="3">
         <v>207300</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>226500</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>232000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>240200</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>251600</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>253600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>227700</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>209500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>169700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>167800</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>163000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>155500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>142600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>140400</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>131000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>127000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>133100</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>138100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>139400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>142200</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>139900</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>142900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>135000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>133100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>132200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>134400</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>120900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>117000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>126400</v>
       </c>
     </row>
-    <row r="47" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -3997,192 +4102,201 @@
       <c r="AF47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>216900</v>
+      </c>
+      <c r="E48" s="3">
         <v>204200</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>201900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>196000</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>188900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>181000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>176400</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>172500</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>158400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>154200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>153700</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>156200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>147100</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>136000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>135800</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>135400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>134900</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>133900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>133500</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>118600</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>117600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>119400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>121700</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>123800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>125100</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>125900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>123000</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>121500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>120200</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>117900</v>
       </c>
     </row>
-    <row r="49" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>218200</v>
+      </c>
+      <c r="E49" s="3">
         <v>148900</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>148800</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>150500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>152300</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>154100</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>155800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>157600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>145500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>146100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>145500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>147100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>137400</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>138900</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>117800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>119100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>120400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>121600</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>122900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>124200</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>125400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>126800</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>128200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>129600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>170200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>171600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>173000</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>174400</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>175900</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>177600</v>
       </c>
     </row>
-    <row r="50" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4273,8 +4387,11 @@
       <c r="AF50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4365,100 +4482,106 @@
       <c r="AF51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13900</v>
+      </c>
+      <c r="E52" s="3">
         <v>15000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>14800</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>12500</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>10500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>7800</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7900</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>8000</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>6200</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>5600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5400</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>3800</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>4300</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4500</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3200</v>
-      </c>
-      <c r="X52" s="3">
-        <v>3800</v>
       </c>
       <c r="Y52" s="3">
         <v>3800</v>
       </c>
       <c r="Z52" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AA52" s="3">
         <v>2600</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>2400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2200</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3000</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>1700</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="53" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4549,100 +4672,106 @@
       <c r="AF53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>644000</v>
+      </c>
+      <c r="E54" s="3">
         <v>575300</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>592000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>590500</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>594000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>599300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>596400</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>567300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>521100</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>477800</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>475000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>472600</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>446000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>423100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>399500</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>389300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>386600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>393000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>399000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>385600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>388400</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>389800</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>396700</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>391000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>430700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>431900</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>433300</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>418600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>414700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>422900</v>
       </c>
     </row>
-    <row r="55" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4675,8 +4804,9 @@
       <c r="AD55" s="3"/>
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
-    </row>
-    <row r="56" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG55" s="3"/>
+    </row>
+    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4709,100 +4839,104 @@
       <c r="AD56" s="3"/>
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
-    </row>
-    <row r="57" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG56" s="3"/>
+    </row>
+    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>42900</v>
+      </c>
+      <c r="E57" s="3">
         <v>61200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>55600</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>53700</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>50600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>60900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>56400</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>66700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>44000</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>43000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>38100</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>37300</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>31200</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>32700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>31100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>34100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>26700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>29600</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>32000</v>
-      </c>
-      <c r="V57" s="3">
-        <v>29300</v>
       </c>
       <c r="W57" s="3">
         <v>29300</v>
       </c>
       <c r="X57" s="3">
+        <v>29300</v>
+      </c>
+      <c r="Y57" s="3">
         <v>35500</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>36700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>33400</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>28100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>26800</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>27900</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>29800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>21900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="58" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -4879,390 +5013,405 @@
         <v>9900</v>
       </c>
       <c r="AB58" s="3">
+        <v>9900</v>
+      </c>
+      <c r="AC58" s="3">
         <v>9200</v>
       </c>
-      <c r="AC58" s="3">
+      <c r="AD58" s="3">
         <v>8600</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>8000</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>7400</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="59" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>26900</v>
+      </c>
+      <c r="E59" s="3">
         <v>23400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>28800</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>27300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>24400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>20100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>21900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>24900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>21600</v>
-      </c>
-      <c r="L59" s="3">
-        <v>18600</v>
       </c>
       <c r="M59" s="3">
         <v>18600</v>
       </c>
       <c r="N59" s="3">
+        <v>18600</v>
+      </c>
+      <c r="O59" s="3">
         <v>23200</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>18000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>16100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>15700</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>14600</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14300</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>13800</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>16200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>13900</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>13500</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>10000</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>17300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>10600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>16400</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>8500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>17900</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>12700</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>18700</v>
       </c>
     </row>
-    <row r="60" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>79700</v>
+      </c>
+      <c r="E60" s="3">
         <v>94500</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>94300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>90900</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>84900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>90900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>88200</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>101500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>75500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>71500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>66500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>70500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>59000</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>58800</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>56700</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>62200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>51300</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>53900</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>55700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>55400</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>53100</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>58800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>56500</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>60600</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>48500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>52500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>45000</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>55700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>41900</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="61" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>109800</v>
+      </c>
+      <c r="E61" s="3">
         <v>49800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>78400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>101700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>120700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>130700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>149200</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>115600</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>105900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>73900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>85900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>88800</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>85800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>65800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>55800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>49800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>57700</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>64700</v>
-      </c>
-      <c r="U61" s="3">
-        <v>74700</v>
       </c>
       <c r="V61" s="3">
         <v>74700</v>
       </c>
       <c r="W61" s="3">
+        <v>74700</v>
+      </c>
+      <c r="X61" s="3">
         <v>80600</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>75800</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>90800</v>
       </c>
       <c r="Z61" s="3">
         <v>90800</v>
       </c>
       <c r="AA61" s="3">
+        <v>90800</v>
+      </c>
+      <c r="AB61" s="3">
         <v>104200</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>102700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>112200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>94600</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>105100</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>106900</v>
       </c>
     </row>
-    <row r="62" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>60800</v>
+      </c>
+      <c r="E62" s="3">
         <v>48400</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>48300</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>47900</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>47300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>46300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>45800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>47600</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>48000</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>48100</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>47400</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>48000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>44200</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>43900</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>43600</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>43900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>45400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>45000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>45200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>37700</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>37200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>37400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>37100</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>37400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>34700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>51100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>51500</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>50500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>50400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="63" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5353,8 +5502,11 @@
       <c r="AF63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5445,8 +5597,11 @@
       <c r="AF64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5537,100 +5692,106 @@
       <c r="AF65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>250300</v>
+      </c>
+      <c r="E66" s="3">
         <v>192600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>221000</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>240500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>252800</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>267900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>283100</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>264700</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>229500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>193500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>199800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>207300</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>189100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>168400</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>156000</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>155800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>154400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>163600</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>175600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>167700</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>170900</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>172000</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>184400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>188700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>187500</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>206200</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>208600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>200800</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>197400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>210100</v>
       </c>
     </row>
-    <row r="67" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5663,8 +5824,9 @@
       <c r="AD67" s="3"/>
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
-    </row>
-    <row r="68" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG67" s="3"/>
+    </row>
+    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5755,8 +5917,11 @@
       <c r="AF68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -5847,8 +6012,11 @@
       <c r="AF69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -5939,8 +6107,11 @@
       <c r="AF70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6031,100 +6202,106 @@
       <c r="AF71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>354100</v>
+      </c>
+      <c r="E72" s="3">
         <v>342500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>322700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>302400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>294000</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>286200</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>271100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>254400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>246800</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>239300</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>227900</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>213900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>207400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>202000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>192300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>182900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>180700</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>178600</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>171800</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>164400</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>163100</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>161400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>156400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>147200</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>189400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>172200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>171700</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>165900</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>166200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>162600</v>
       </c>
     </row>
-    <row r="73" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6215,8 +6392,11 @@
       <c r="AF73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6307,8 +6487,11 @@
       <c r="AF74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6399,100 +6582,106 @@
       <c r="AF75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>393800</v>
+      </c>
+      <c r="E76" s="3">
         <v>382700</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>371000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>350000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>341200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>331400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>313300</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>302600</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>291700</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>284300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>275200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>265200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>256900</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>254600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>243400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>233500</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>232200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>229400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>223400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>217900</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>217500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>217800</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>212300</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>202200</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>243300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>225700</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>224700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>217800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>217300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>212800</v>
       </c>
     </row>
-    <row r="77" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6583,197 +6772,206 @@
       <c r="AF77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:32" x14ac:dyDescent="0.2">
+      <c r="AG77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:32" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45291</v>
+      </c>
+      <c r="E80" s="2">
         <v>45200</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45109</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45018</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>44927</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44836</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44745</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44654</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44556</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44465</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44374</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44283</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44192</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44101</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44010</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>43919</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43828</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43737</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43646</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43555</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43464</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43373</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43282</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43191</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43100</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43009</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>42918</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42827</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42736</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="81" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>14900</v>
+      </c>
+      <c r="E81" s="3">
         <v>23200</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>23400</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>11600</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>10700</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>18000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>19700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>10200</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>14100</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>16600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>9100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>7900</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>12200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>11800</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>4800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4500</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>9300</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>9800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>3800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>7400</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>9100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>-37400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>17100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>5200</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>5800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>4200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3600</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="82" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -6806,55 +7004,56 @@
       <c r="AD82" s="3"/>
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
-    </row>
-    <row r="83" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG82" s="3"/>
+    </row>
+    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E83" s="3">
         <v>7400</v>
-      </c>
-      <c r="E83" s="3">
-        <v>7100</v>
       </c>
       <c r="F83" s="3">
         <v>7100</v>
       </c>
       <c r="G83" s="3">
+        <v>7100</v>
+      </c>
+      <c r="H83" s="3">
         <v>7000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6300</v>
-      </c>
-      <c r="K83" s="3">
-        <v>6000</v>
       </c>
       <c r="L83" s="3">
         <v>6000</v>
       </c>
       <c r="M83" s="3">
-        <v>5900</v>
+        <v>6000</v>
       </c>
       <c r="N83" s="3">
         <v>5900</v>
       </c>
       <c r="O83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="P83" s="3">
         <v>5700</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>5600</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5500</v>
-      </c>
-      <c r="R83" s="3">
-        <v>5400</v>
       </c>
       <c r="S83" s="3">
         <v>5400</v>
@@ -6872,34 +7071,37 @@
         <v>5400</v>
       </c>
       <c r="X83" s="3">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="Y83" s="3">
         <v>5500</v>
       </c>
       <c r="Z83" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AA83" s="3">
         <v>5600</v>
       </c>
-      <c r="AA83" s="3">
+      <c r="AB83" s="3">
         <v>5400</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>5500</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>5800</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>5400</v>
-      </c>
-      <c r="AE83" s="3">
-        <v>5200</v>
       </c>
       <c r="AF83" s="3">
         <v>5200</v>
       </c>
-    </row>
-    <row r="84" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG83" s="3">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -6990,8 +7192,11 @@
       <c r="AF84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7082,8 +7287,11 @@
       <c r="AF85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7174,8 +7382,11 @@
       <c r="AF86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7266,8 +7477,11 @@
       <c r="AF87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7358,100 +7572,106 @@
       <c r="AF88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>25000</v>
+      </c>
+      <c r="E89" s="3">
         <v>57800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>34900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>32900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>25700</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>28200</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>-9400</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>4100</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-1400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>25300</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>14800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>17200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>6500</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>18600</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>1600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>13900</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>17900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>17000</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>10100</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>17000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>6200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>18000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>6800</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>12800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>10100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>16400</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>-11900</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>13900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>2900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>13600</v>
       </c>
     </row>
-    <row r="90" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7484,100 +7704,104 @@
       <c r="AD90" s="3"/>
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
-    </row>
-    <row r="91" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG90" s="3"/>
+    </row>
+    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-9000</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-7900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-16000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11600</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-12800</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-8800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-4700</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-2200</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-5100</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-3300</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4900</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-9200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5400</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-3000</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-2400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3800</v>
-      </c>
-      <c r="AB91" s="3">
-        <v>-6600</v>
       </c>
       <c r="AC91" s="3">
         <v>-6600</v>
       </c>
       <c r="AD91" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="AE91" s="3">
         <v>-5800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-5600</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="92" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7668,8 +7892,11 @@
       <c r="AF92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7760,100 +7987,106 @@
       <c r="AF93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-86400</v>
+      </c>
+      <c r="E94" s="3">
         <v>-12100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-7800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-9300</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-11600</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-8800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-31700</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-10100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-5800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-2100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-23400</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-15000</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-28200</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-4800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-9100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5300</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-2900</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-1800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-3700</v>
-      </c>
-      <c r="AB94" s="3">
-        <v>-6500</v>
       </c>
       <c r="AC94" s="3">
         <v>-6500</v>
       </c>
       <c r="AD94" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="AE94" s="3">
         <v>-5700</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5500</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="95" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -7886,8 +8119,9 @@
       <c r="AD95" s="3"/>
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
-    </row>
-    <row r="96" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG95" s="3"/>
+    </row>
+    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -7895,37 +8129,37 @@
         <v>-3400</v>
       </c>
       <c r="E96" s="3">
-        <v>-3200</v>
+        <v>-3400</v>
       </c>
       <c r="F96" s="3">
         <v>-3200</v>
       </c>
       <c r="G96" s="3">
-        <v>-2900</v>
+        <v>-3200</v>
       </c>
       <c r="H96" s="3">
         <v>-2900</v>
       </c>
       <c r="I96" s="3">
-        <v>-3000</v>
+        <v>-2900</v>
       </c>
       <c r="J96" s="3">
         <v>-3000</v>
       </c>
       <c r="K96" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="L96" s="3">
         <v>-2700</v>
       </c>
-      <c r="L96" s="3">
+      <c r="M96" s="3">
         <v>-2800</v>
-      </c>
-      <c r="M96" s="3">
-        <v>-2600</v>
       </c>
       <c r="N96" s="3">
         <v>-2600</v>
       </c>
       <c r="O96" s="3">
-        <v>-2500</v>
+        <v>-2600</v>
       </c>
       <c r="P96" s="3">
         <v>-2500</v>
@@ -7937,49 +8171,52 @@
         <v>-2500</v>
       </c>
       <c r="S96" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="T96" s="3">
         <v>-2400</v>
       </c>
       <c r="U96" s="3">
-        <v>-2500</v>
+        <v>-2400</v>
       </c>
       <c r="V96" s="3">
         <v>-2500</v>
       </c>
       <c r="W96" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="X96" s="3">
         <v>-2400</v>
       </c>
       <c r="Y96" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="Z96" s="3">
         <v>-4700</v>
       </c>
-      <c r="Z96" s="3">
-        <v>0</v>
-      </c>
       <c r="AA96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-4500</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-4500</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8070,8 +8307,11 @@
       <c r="AF97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8162,8 +8402,11 @@
       <c r="AF98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8254,100 +8497,106 @@
       <c r="AF99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>56200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-41700</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-27600</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-22200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-11900</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-21400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>23400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>7600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>28100</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-17900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-10500</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>1200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>13400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>8300</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>3500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-11800</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-9400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-13800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-4600</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-9800</v>
       </c>
-      <c r="W100" s="3">
-        <v>0</v>
-      </c>
       <c r="X100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Y100" s="3">
         <v>-17400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-4300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-12800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-8900</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>14400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-9600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="101" spans="3:32" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8438,96 +8687,102 @@
       <c r="AF101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:32" x14ac:dyDescent="0.2">
+      <c r="AG101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-5200</v>
+      </c>
+      <c r="E102" s="3">
         <v>3900</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-500</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>2200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-2100</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-19900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>16600</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-5000</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>4800</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-3000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>3200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>1900</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3300</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1000</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-4100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-8300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-4600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HWKN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HWKN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="148" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
   <si>
     <t>HWKN</t>
   </si>
@@ -656,430 +656,443 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AG102"/>
+  <dimension ref="A5:AH102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E7" s="2">
         <v>45291</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45200</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45109</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45018</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>44927</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44836</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44745</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44654</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44556</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44465</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44374</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44283</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44192</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44101</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44010</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>43919</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43828</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43737</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43646</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43555</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43464</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43373</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43282</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43191</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43100</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43009</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>42918</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42827</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42736</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="8" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>223000</v>
+      </c>
+      <c r="E8" s="3">
         <v>208500</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>236500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>251100</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>228100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>219200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>241200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>246500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>223000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>187100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>183300</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>181200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>163000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>142900</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>147800</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>143200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>132400</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>120400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>140000</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>147300</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>133100</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>128200</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>145300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>149800</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>127000</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>118100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>125400</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>133700</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>118600</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>112400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>121300</v>
       </c>
     </row>
-    <row r="9" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>177500</v>
+      </c>
+      <c r="E9" s="3">
         <v>166200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>182600</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>199100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>192400</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>182900</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>194800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>199800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>186700</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>153100</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>146000</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>142300</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>131200</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>114700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>115000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>112200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>109800</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>98900</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>112000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>118500</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>112400</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>107100</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>119600</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>121300</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>109200</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>99200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>101300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>107700</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>96700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>91400</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>94200</v>
       </c>
     </row>
-    <row r="10" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>45500</v>
+      </c>
+      <c r="E10" s="3">
         <v>42300</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>53900</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>52000</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>35700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>36300</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>46400</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>46700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>36300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>34000</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>37300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>38900</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>31800</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>28200</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>32800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>31000</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>22600</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>21500</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>28000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>28800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>20700</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>21100</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>25700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>28500</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>17800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>18900</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>24100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>26000</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>21900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>21000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>27100</v>
       </c>
     </row>
-    <row r="11" spans="1:33" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1113,8 +1126,9 @@
       <c r="AE11" s="3"/>
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
-    </row>
-    <row r="12" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH11" s="3"/>
+    </row>
+    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1208,8 +1222,11 @@
       <c r="AG12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1303,8 +1320,11 @@
       <c r="AG13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1359,17 +1379,17 @@
       <c r="T14" s="3">
         <v>0</v>
       </c>
-      <c r="U14" s="3" t="s">
-        <v>8</v>
+      <c r="U14" s="3">
+        <v>0</v>
       </c>
       <c r="V14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W14" s="3">
-        <v>0</v>
-      </c>
-      <c r="X14" s="3" t="s">
+      <c r="W14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
@@ -1377,11 +1397,11 @@
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
+      <c r="AA14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB14" s="3">
         <v>39100</v>
-      </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
@@ -1398,8 +1418,11 @@
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1493,8 +1516,11 @@
       <c r="AG15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:33" x14ac:dyDescent="0.2">
+      <c r="AH15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1525,198 +1551,205 @@
       <c r="AE16" s="3"/>
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
-    </row>
-    <row r="17" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH16" s="3"/>
+    </row>
+    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>202900</v>
+      </c>
+      <c r="E17" s="3">
         <v>190000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>203500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>218600</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>209700</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>204000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>214700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>218700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>207800</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>172800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>163700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>159100</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>150100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>132400</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>131200</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>127200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>124700</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>113600</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>126900</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>133400</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>127300</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>121400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>134500</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>136300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>163000</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>113400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>116100</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>123500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>111200</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>106400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>109100</v>
       </c>
     </row>
-    <row r="18" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>20100</v>
+      </c>
+      <c r="E18" s="3">
         <v>18500</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>33000</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>32500</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>18400</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>15200</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>26500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>27800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>15200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>14300</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>19600</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>22100</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>12900</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>10500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>16600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>16000</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>7700</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>6800</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>13100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>13900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>5800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>6800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>10800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>13500</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>-36000</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>4700</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>9300</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>10200</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>7400</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>6000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="19" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1750,79 +1783,80 @@
       <c r="AE19" s="3"/>
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
-    </row>
-    <row r="20" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH19" s="3"/>
+    </row>
+    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>500</v>
+      </c>
+      <c r="E20" s="3">
         <v>800</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-300</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>400</v>
-      </c>
-      <c r="G20" s="3">
-        <v>500</v>
       </c>
       <c r="H20" s="3">
         <v>500</v>
       </c>
       <c r="I20" s="3">
+        <v>500</v>
+      </c>
+      <c r="J20" s="3">
         <v>-500</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-700</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>100</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>200</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-1000</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-400</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-600</v>
       </c>
       <c r="V20" s="3">
         <v>-600</v>
       </c>
       <c r="W20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="X20" s="3">
         <v>-500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-700</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-900</v>
       </c>
       <c r="AA20" s="3">
         <v>-900</v>
@@ -1831,117 +1865,123 @@
         <v>-900</v>
       </c>
       <c r="AC20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AD20" s="3">
         <v>-800</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-700</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-600</v>
-      </c>
-      <c r="AF20" s="3">
-        <v>-700</v>
       </c>
       <c r="AG20" s="3">
         <v>-700</v>
       </c>
-    </row>
-    <row r="21" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH20" s="3">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>29500</v>
+      </c>
+      <c r="E21" s="3">
         <v>27700</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>40100</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>39900</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>26000</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>22700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>32900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>33700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>21100</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>20400</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>25700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>28300</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>19000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>16600</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>22500</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>21900</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>12200</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>11800</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>17900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>18700</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>10700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>11000</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>15600</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>18000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>-31200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>9300</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>14000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>15300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>12200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>10500</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="22" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
@@ -1949,28 +1989,28 @@
         <v>1200</v>
       </c>
       <c r="E22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="F22" s="3">
         <v>700</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1100</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1400</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1500</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>900</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>400</v>
-      </c>
-      <c r="L22" s="3">
-        <v>300</v>
       </c>
       <c r="M22" s="3">
         <v>300</v>
@@ -1979,25 +2019,25 @@
         <v>300</v>
       </c>
       <c r="O22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="P22" s="3">
         <v>400</v>
       </c>
       <c r="Q22" s="3">
+        <v>400</v>
+      </c>
+      <c r="R22" s="3">
         <v>300</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>400</v>
-      </c>
-      <c r="S22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="T22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="U22" s="3">
-        <v>0</v>
+      <c r="U22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="V22" s="3">
         <v>0</v>
@@ -2035,198 +2075,207 @@
       <c r="AG22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>19300</v>
+      </c>
+      <c r="E23" s="3">
         <v>18200</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>32000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>31700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>17500</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>14200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>24700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>26200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>14400</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>14100</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>19500</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>22000</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>12700</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>10600</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>16600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>16000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>6800</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6300</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>12500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>13300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>5300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>10100</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>12500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>-36900</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>3800</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>8500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>9500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>6800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5400</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="24" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E24" s="3">
         <v>3300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8200</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5900</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>6700</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6500</v>
-      </c>
-      <c r="K24" s="3">
-        <v>3900</v>
       </c>
       <c r="L24" s="3">
         <v>3900</v>
       </c>
       <c r="M24" s="3">
+        <v>3900</v>
+      </c>
+      <c r="N24" s="3">
         <v>5300</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5400</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3600</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>2700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>4400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4200</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2000</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>1800</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>3300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3500</v>
-      </c>
-      <c r="W24" s="3">
-        <v>1500</v>
       </c>
       <c r="X24" s="3">
         <v>1500</v>
       </c>
       <c r="Y24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="Z24" s="3">
         <v>2700</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3400</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1200</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>-100</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>2600</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1800</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="25" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2320,198 +2369,207 @@
       <c r="AG25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E26" s="3">
         <v>14900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>23200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>23400</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>11600</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>10700</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>18000</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>19700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>14100</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>16600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>9100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>7900</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>12200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>11800</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>4800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4500</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>9300</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>9800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>3800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4100</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>7400</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>9100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>-38100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3900</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>5200</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3600</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="27" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E27" s="3">
         <v>14900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>23200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>23400</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>11600</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>10700</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>18000</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>19700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>10600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>10200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>14100</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>16600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>9100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>7900</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>12200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>11800</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>4800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4500</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>9300</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>9800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>3800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4100</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>7400</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>9100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>-38100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3900</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>5200</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>5800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3600</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="28" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2605,8 +2663,11 @@
       <c r="AG28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2661,17 +2722,17 @@
       <c r="T29" s="3">
         <v>0</v>
       </c>
-      <c r="U29" s="3" t="s">
-        <v>8</v>
+      <c r="U29" s="3">
+        <v>0</v>
       </c>
       <c r="V29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W29" s="3">
-        <v>0</v>
-      </c>
-      <c r="X29" s="3" t="s">
+      <c r="W29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
@@ -2679,14 +2740,14 @@
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
+      <c r="AA29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AB29" s="3">
         <v>700</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AC29" s="3">
         <v>13200</v>
-      </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2700,8 +2761,11 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2795,8 +2859,11 @@
       <c r="AG30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2890,79 +2957,82 @@
       <c r="AG31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E32" s="3">
         <v>-800</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>300</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-400</v>
-      </c>
-      <c r="G32" s="3">
-        <v>-500</v>
       </c>
       <c r="H32" s="3">
         <v>-500</v>
       </c>
       <c r="I32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="J32" s="3">
         <v>500</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>700</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-100</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-200</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>1000</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>400</v>
-      </c>
-      <c r="U32" s="3">
-        <v>600</v>
       </c>
       <c r="V32" s="3">
         <v>600</v>
       </c>
       <c r="W32" s="3">
+        <v>600</v>
+      </c>
+      <c r="X32" s="3">
         <v>500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1200</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>700</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>900</v>
       </c>
       <c r="AA32" s="3">
         <v>900</v>
@@ -2971,117 +3041,123 @@
         <v>900</v>
       </c>
       <c r="AC32" s="3">
+        <v>900</v>
+      </c>
+      <c r="AD32" s="3">
         <v>800</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>700</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>600</v>
-      </c>
-      <c r="AF32" s="3">
-        <v>700</v>
       </c>
       <c r="AG32" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="33" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH32" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E33" s="3">
         <v>14900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>23200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>23400</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>11600</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>10700</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>18000</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>19700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>10600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>10200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>14100</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>16600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>9100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>7900</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>12200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>11800</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>4800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4500</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>9300</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>9800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>3800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4100</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>7400</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>9100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>-37400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>17100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>5200</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>5800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>4200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>3600</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="34" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3175,203 +3251,212 @@
       <c r="AG34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E35" s="3">
         <v>14900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>23200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>23400</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>11600</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>10700</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>18000</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>19700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>10600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>10200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>14100</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>16600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>9100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>7900</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>12200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>11800</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>4800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4500</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>9300</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>9800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>3800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4100</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>7400</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>9100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>-37400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>17100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>5200</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>5800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>4200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>3600</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="37" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E38" s="2">
         <v>45291</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45200</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45109</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45018</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>44927</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44836</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44745</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44654</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44556</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44465</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44374</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44283</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44192</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44101</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44010</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>43919</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43828</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43737</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43646</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43555</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43464</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43373</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43282</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43191</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43100</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43009</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>42918</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42827</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42736</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="39" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3405,8 +3490,9 @@
       <c r="AE39" s="3"/>
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
-    </row>
-    <row r="40" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH39" s="3"/>
+    </row>
+    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3440,103 +3526,107 @@
       <c r="AE40" s="3"/>
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
-    </row>
-    <row r="41" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH40" s="3"/>
+    </row>
+    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7200</v>
+      </c>
+      <c r="E41" s="3">
         <v>5700</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>11000</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7600</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>6100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>3900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3500</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>23400</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6800</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>5200</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>8000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>4500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4300</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>7300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4100</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5600</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>9200</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4000</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7600</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>3800</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>2800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>6900</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>8400</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>16700</v>
       </c>
     </row>
-    <row r="42" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3630,388 +3720,403 @@
       <c r="AG42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>114500</v>
+      </c>
+      <c r="E43" s="3">
         <v>113000</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>124800</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>138300</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>129300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>125500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>131400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>138800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>122800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>102800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>90100</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>90900</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>90800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>77800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>74500</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>69500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>67400</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>56700</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>65400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>69000</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>64500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>61500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>66400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>67900</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>66200</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>57900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>60000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>62800</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>58600</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>53300</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>52800</v>
       </c>
     </row>
-    <row r="44" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>74600</v>
+      </c>
+      <c r="E44" s="3">
         <v>68800</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>68500</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>76900</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>88800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>101600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>113100</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>105000</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>95000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>76200</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>70300</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>67900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>63900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>64700</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>63200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>63400</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>54400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>57500</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>60800</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>58700</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>60500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>67700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>67800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>66400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>59700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>62700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>65900</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>65600</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>51200</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>50300</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="45" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>6600</v>
+      </c>
+      <c r="E45" s="3">
         <v>7400</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>3000</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>4100</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>6400</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>7100</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>3200</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3900</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>6400</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>7000</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>2500</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3700</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>5400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>1700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3100</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>4900</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5600</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2800</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5200</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3500</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4100</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>4800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3300</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>5100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="46" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>202800</v>
+      </c>
+      <c r="E46" s="3">
         <v>195000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>207300</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>226500</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>232000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>240200</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>251600</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>253600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>227700</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>209500</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>169700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>167800</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>163000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>155500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>142600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>140400</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>131000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>127000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>133100</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>138100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>139400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>142200</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>139900</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>142900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>135000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>133100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>132200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>134400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>120900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>117000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>126400</v>
       </c>
     </row>
-    <row r="47" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4105,198 +4210,207 @@
       <c r="AG47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>220600</v>
+      </c>
+      <c r="E48" s="3">
         <v>216900</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>204200</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>201900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>196000</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>188900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>181000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>176400</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>172500</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>158400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>154200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>153700</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>156200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>147100</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>136000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>135800</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>135400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>134900</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>133900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>133500</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>118600</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>117600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>119400</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>121700</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>123800</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>125100</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>125900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>123000</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>121500</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>120200</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>117900</v>
       </c>
     </row>
-    <row r="49" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>220000</v>
+      </c>
+      <c r="E49" s="3">
         <v>218200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>148900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>148800</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>150500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>152300</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>154100</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>155800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>157600</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>145500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>146100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>145500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>147100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>137400</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>138900</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>117800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>119100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>120400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>121600</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>122900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>124200</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>125400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>126800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>128200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>129600</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>170200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>171600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>173000</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>174400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>175900</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>177600</v>
       </c>
     </row>
-    <row r="50" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4390,8 +4504,11 @@
       <c r="AG50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4485,103 +4602,109 @@
       <c r="AG51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E52" s="3">
         <v>13900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>15000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>14800</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>12000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>10500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>7800</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7900</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>6200</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>5600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5400</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>3800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>4300</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4500</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3200</v>
-      </c>
-      <c r="Y52" s="3">
-        <v>3800</v>
       </c>
       <c r="Z52" s="3">
         <v>3800</v>
       </c>
       <c r="AA52" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AB52" s="3">
         <v>2600</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>2400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2200</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3000</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>1700</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="53" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4675,103 +4798,109 @@
       <c r="AG53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>657900</v>
+      </c>
+      <c r="E54" s="3">
         <v>644000</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>575300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>592000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>590500</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>594000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>599300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>596400</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>567300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>521100</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>477800</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>475000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>472600</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>446000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>423100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>399500</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>389300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>386600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>393000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>399000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>385600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>388400</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>389800</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>396700</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>391000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>430700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>431900</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>433300</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>418600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>414700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>422900</v>
       </c>
     </row>
-    <row r="55" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4805,8 +4934,9 @@
       <c r="AE55" s="3"/>
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
-    </row>
-    <row r="56" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH55" s="3"/>
+    </row>
+    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4840,103 +4970,107 @@
       <c r="AE56" s="3"/>
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
-    </row>
-    <row r="57" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH56" s="3"/>
+    </row>
+    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>56400</v>
+      </c>
+      <c r="E57" s="3">
         <v>42900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>61200</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>55600</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>53700</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>50600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>60900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>56400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>66700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>44000</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>43000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>38100</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>37300</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>31200</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>32700</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>31100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>34100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>26700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>29600</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>32000</v>
-      </c>
-      <c r="W57" s="3">
-        <v>29300</v>
       </c>
       <c r="X57" s="3">
         <v>29300</v>
       </c>
       <c r="Y57" s="3">
+        <v>29300</v>
+      </c>
+      <c r="Z57" s="3">
         <v>35500</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>36700</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>33400</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>28100</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>26800</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>27900</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>29800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>21900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="58" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5016,402 +5150,417 @@
         <v>9900</v>
       </c>
       <c r="AC58" s="3">
+        <v>9900</v>
+      </c>
+      <c r="AD58" s="3">
         <v>9200</v>
       </c>
-      <c r="AD58" s="3">
+      <c r="AE58" s="3">
         <v>8600</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>8000</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>7400</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="59" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>37000</v>
+      </c>
+      <c r="E59" s="3">
         <v>26900</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>23400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>28800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>27300</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>24400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>20100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>21900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>24900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21600</v>
-      </c>
-      <c r="M59" s="3">
-        <v>18600</v>
       </c>
       <c r="N59" s="3">
         <v>18600</v>
       </c>
       <c r="O59" s="3">
+        <v>18600</v>
+      </c>
+      <c r="P59" s="3">
         <v>23200</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>18000</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>16100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>15700</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>18200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>14600</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>14300</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>13800</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>16200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>13900</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>13500</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>10000</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>17300</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>10600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>16400</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>8500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>17900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>12700</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>18700</v>
       </c>
     </row>
-    <row r="60" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>103300</v>
+      </c>
+      <c r="E60" s="3">
         <v>79700</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>94500</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>94300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>90900</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>84900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>90900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>88200</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>101500</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>75500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>71500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>66500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>70500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>59000</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>58800</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>56700</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>62200</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>51300</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>53900</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>55700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>55400</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>53100</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>58800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>56500</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>60600</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>48500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>52500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>45000</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>55700</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>41900</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="61" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>88800</v>
+      </c>
+      <c r="E61" s="3">
         <v>109800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>49800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>78400</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>101700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>120700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>130700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>149200</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>115600</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>105900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>73900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>85900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>88800</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>85800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>65800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>55800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>49800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>57700</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>64700</v>
-      </c>
-      <c r="V61" s="3">
-        <v>74700</v>
       </c>
       <c r="W61" s="3">
         <v>74700</v>
       </c>
       <c r="X61" s="3">
+        <v>74700</v>
+      </c>
+      <c r="Y61" s="3">
         <v>80600</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>75800</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>90800</v>
       </c>
       <c r="AA61" s="3">
         <v>90800</v>
       </c>
       <c r="AB61" s="3">
+        <v>90800</v>
+      </c>
+      <c r="AC61" s="3">
         <v>104200</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>102700</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>112200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>94600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>105100</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>106900</v>
       </c>
     </row>
-    <row r="62" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E62" s="3">
         <v>60800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>48400</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>48300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>47900</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>47300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>46300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>45800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>47600</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>48000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>48100</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>47400</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>48000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>44200</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>43900</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>43600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>43900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>45400</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>45000</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>45200</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>37700</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>37200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>37400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>37100</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>37400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>34700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>51100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>51500</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>50500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>50400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="63" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5505,8 +5654,11 @@
       <c r="AG63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5600,8 +5752,11 @@
       <c r="AG64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5695,103 +5850,109 @@
       <c r="AG65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>251900</v>
+      </c>
+      <c r="E66" s="3">
         <v>250300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>192600</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>221000</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>240500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>252800</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>267900</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>283100</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>264700</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>229500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>193500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>199800</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>207300</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>189100</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>168400</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>156000</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>155800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>154400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>163600</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>175600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>167700</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>170900</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>172000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>184400</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>188700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>187500</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>206200</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>208600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>200800</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>197400</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>210100</v>
       </c>
     </row>
-    <row r="67" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5825,8 +5986,9 @@
       <c r="AE67" s="3"/>
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
-    </row>
-    <row r="68" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH67" s="3"/>
+    </row>
+    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -5920,8 +6082,11 @@
       <c r="AG68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6015,8 +6180,11 @@
       <c r="AG69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6110,8 +6278,11 @@
       <c r="AG70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6205,103 +6376,109 @@
       <c r="AG71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>364500</v>
+      </c>
+      <c r="E72" s="3">
         <v>354100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>342500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>322700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>302400</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>294000</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>286200</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>271100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>254400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>246800</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>239300</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>227900</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>213900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>207400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>202000</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>192300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>182900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>180700</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>178600</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>171800</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>164400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>163100</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>161400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>156400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>147200</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>189400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>172200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>171700</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>165900</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>166200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>162600</v>
       </c>
     </row>
-    <row r="73" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6395,8 +6572,11 @@
       <c r="AG73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6490,8 +6670,11 @@
       <c r="AG74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6585,103 +6768,109 @@
       <c r="AG75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>406000</v>
+      </c>
+      <c r="E76" s="3">
         <v>393800</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>382700</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>371000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>350000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>341200</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>331400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>313300</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>302600</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>291700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>284300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>275200</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>265200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>256900</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>254600</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>243400</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>233500</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>232200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>229400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>223400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>217900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>217500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>217800</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>212300</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>202200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>243300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>225700</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>224700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>217800</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>217300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>212800</v>
       </c>
     </row>
-    <row r="77" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6775,203 +6964,212 @@
       <c r="AG77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:33" x14ac:dyDescent="0.2">
+      <c r="AH77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:33" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45382</v>
+      </c>
+      <c r="E80" s="2">
         <v>45291</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45200</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45109</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45018</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>44927</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44836</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44745</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44654</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44556</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44465</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44374</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44283</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44192</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44101</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44010</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>43919</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43828</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43737</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43646</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43555</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43464</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43373</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43282</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43191</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43100</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43009</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>42918</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42827</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42736</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="81" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>13800</v>
+      </c>
+      <c r="E81" s="3">
         <v>14900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>23200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>23400</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>11600</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>10700</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>18000</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>19700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>10600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>10200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>14100</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>16600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>9100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>7900</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>12200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>11800</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>4800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4500</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>9300</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>9800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>3800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4100</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>7400</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>9100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>-37400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>17100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>5200</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>5800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>4200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>3600</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="82" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7005,58 +7203,59 @@
       <c r="AE82" s="3"/>
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
-    </row>
-    <row r="83" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH82" s="3"/>
+    </row>
+    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9000</v>
+      </c>
+      <c r="E83" s="3">
         <v>8300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7400</v>
-      </c>
-      <c r="F83" s="3">
-        <v>7100</v>
       </c>
       <c r="G83" s="3">
         <v>7100</v>
       </c>
       <c r="H83" s="3">
+        <v>7100</v>
+      </c>
+      <c r="I83" s="3">
         <v>7000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6300</v>
-      </c>
-      <c r="L83" s="3">
-        <v>6000</v>
       </c>
       <c r="M83" s="3">
         <v>6000</v>
       </c>
       <c r="N83" s="3">
-        <v>5900</v>
+        <v>6000</v>
       </c>
       <c r="O83" s="3">
         <v>5900</v>
       </c>
       <c r="P83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="Q83" s="3">
         <v>5700</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>5600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5500</v>
-      </c>
-      <c r="S83" s="3">
-        <v>5400</v>
       </c>
       <c r="T83" s="3">
         <v>5400</v>
@@ -7074,34 +7273,37 @@
         <v>5400</v>
       </c>
       <c r="Y83" s="3">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="Z83" s="3">
         <v>5500</v>
       </c>
       <c r="AA83" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AB83" s="3">
         <v>5600</v>
       </c>
-      <c r="AB83" s="3">
+      <c r="AC83" s="3">
         <v>5400</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>5500</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>5800</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>5400</v>
-      </c>
-      <c r="AF83" s="3">
-        <v>5200</v>
       </c>
       <c r="AG83" s="3">
         <v>5200</v>
       </c>
-    </row>
-    <row r="84" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH83" s="3">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7195,8 +7397,11 @@
       <c r="AG84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7290,8 +7495,11 @@
       <c r="AG85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7385,8 +7593,11 @@
       <c r="AG86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7480,8 +7691,11 @@
       <c r="AG87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7575,103 +7789,109 @@
       <c r="AG88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>41900</v>
+      </c>
+      <c r="E89" s="3">
         <v>25000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>57800</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>34900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>32900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>25700</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>28200</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>-9400</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>4100</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-1400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>25300</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>14800</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>17200</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>6500</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>18600</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>1600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>13900</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>17900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>17000</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>10100</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>17000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>6200</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>18000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>6800</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>12800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>10100</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>16400</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>-11900</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>13900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>2900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>13600</v>
       </c>
     </row>
-    <row r="90" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7705,103 +7925,107 @@
       <c r="AE90" s="3"/>
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
-    </row>
-    <row r="91" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH90" s="3"/>
+    </row>
+    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11900</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-9000</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-7900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-16000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11600</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-12800</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-8800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-4700</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-2200</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-7600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-5100</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-3300</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4900</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-9200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5400</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3800</v>
-      </c>
-      <c r="AC91" s="3">
-        <v>-6600</v>
       </c>
       <c r="AD91" s="3">
         <v>-6600</v>
       </c>
       <c r="AE91" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="AF91" s="3">
         <v>-5800</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-5600</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="92" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -7895,8 +8119,11 @@
       <c r="AG92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -7990,103 +8217,109 @@
       <c r="AG93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-16100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-86400</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-12100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-7800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-9300</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-11600</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-8800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11500</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-31700</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-10100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-5800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-2100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-23400</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-15000</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-28200</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-4800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-5100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-9100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5300</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-2900</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-1800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-3700</v>
-      </c>
-      <c r="AC94" s="3">
-        <v>-6500</v>
       </c>
       <c r="AD94" s="3">
         <v>-6500</v>
       </c>
       <c r="AE94" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="AF94" s="3">
         <v>-5700</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-5500</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="95" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8120,8 +8353,9 @@
       <c r="AE95" s="3"/>
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
-    </row>
-    <row r="96" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH95" s="3"/>
+    </row>
+    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8132,37 +8366,37 @@
         <v>-3400</v>
       </c>
       <c r="F96" s="3">
-        <v>-3200</v>
+        <v>-3400</v>
       </c>
       <c r="G96" s="3">
         <v>-3200</v>
       </c>
       <c r="H96" s="3">
-        <v>-2900</v>
+        <v>-3200</v>
       </c>
       <c r="I96" s="3">
         <v>-2900</v>
       </c>
       <c r="J96" s="3">
-        <v>-3000</v>
+        <v>-2900</v>
       </c>
       <c r="K96" s="3">
         <v>-3000</v>
       </c>
       <c r="L96" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="M96" s="3">
         <v>-2700</v>
       </c>
-      <c r="M96" s="3">
+      <c r="N96" s="3">
         <v>-2800</v>
-      </c>
-      <c r="N96" s="3">
-        <v>-2600</v>
       </c>
       <c r="O96" s="3">
         <v>-2600</v>
       </c>
       <c r="P96" s="3">
-        <v>-2500</v>
+        <v>-2600</v>
       </c>
       <c r="Q96" s="3">
         <v>-2500</v>
@@ -8174,49 +8408,52 @@
         <v>-2500</v>
       </c>
       <c r="T96" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="U96" s="3">
         <v>-2400</v>
       </c>
       <c r="V96" s="3">
-        <v>-2500</v>
+        <v>-2400</v>
       </c>
       <c r="W96" s="3">
         <v>-2500</v>
       </c>
       <c r="X96" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="Y96" s="3">
         <v>-2400</v>
       </c>
       <c r="Z96" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AA96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AA96" s="3">
-        <v>0</v>
-      </c>
       <c r="AB96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-4500</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8310,8 +8547,11 @@
       <c r="AG97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8405,8 +8645,11 @@
       <c r="AG98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8500,103 +8743,109 @@
       <c r="AG99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-24400</v>
+      </c>
+      <c r="E100" s="3">
         <v>56200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-41700</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-27600</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-22200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-11900</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-21400</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>23400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>7600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>28100</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-17900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-10500</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>1200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>13400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>8300</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>3500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-11800</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-9400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-13800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-4600</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-9800</v>
       </c>
-      <c r="X100" s="3">
-        <v>0</v>
-      </c>
       <c r="Y100" s="3">
+        <v>0</v>
+      </c>
+      <c r="Z100" s="3">
         <v>-17400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-4300</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-12800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-8900</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>14400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-9600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="101" spans="3:33" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8690,99 +8939,105 @@
       <c r="AG101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:33" x14ac:dyDescent="0.2">
+      <c r="AH101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-5200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>3900</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-500</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>2200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-2100</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-19900</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>16600</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>1600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2200</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-5000</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>4800</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-1400</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-3000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>3200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>1900</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3300</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1100</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>1000</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-4100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-8300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-4600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HWKN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HWKN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="149" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
   <si>
     <t>HWKN</t>
   </si>
@@ -656,443 +656,456 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AH102"/>
+  <dimension ref="A5:AI102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E7" s="2">
         <v>45382</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45291</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45200</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45109</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45018</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>44927</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44836</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44745</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44654</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44556</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44465</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44374</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44283</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44192</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44101</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44010</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>43919</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43828</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43737</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43646</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43555</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43464</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43373</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43282</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43191</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43100</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43009</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>42918</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42827</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42736</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="8" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>255900</v>
+      </c>
+      <c r="E8" s="3">
         <v>223000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>208500</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>236500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>251100</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>228100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>219200</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>241200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>246500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>223000</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>187100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>183300</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>181200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>163000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>142900</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>147800</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>143200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>132400</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>120400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>140000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>147300</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>133100</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>128200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>145300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>149800</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>127000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>118100</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>125400</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>133700</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>118600</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>112400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>121300</v>
       </c>
     </row>
-    <row r="9" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>191200</v>
+      </c>
+      <c r="E9" s="3">
         <v>177500</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>166200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>182600</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>199100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>192400</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>182900</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>194800</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>199800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>186700</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>153100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>146000</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>142300</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>131200</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>114700</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>115000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>112200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>109800</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>98900</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>112000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>118500</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>112400</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>107100</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>119600</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>121300</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>109200</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>99200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>101300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>107700</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>96700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>91400</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>94200</v>
       </c>
     </row>
-    <row r="10" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>64700</v>
+      </c>
+      <c r="E10" s="3">
         <v>45500</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>42300</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>53900</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>52000</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>35700</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>36300</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>46400</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>46700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>36300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>34000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>37300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>38900</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>31800</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>28200</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>32800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>31000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>22600</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>21500</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>28000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>28800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>20700</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>21100</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>25700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>28500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>17800</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>18900</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>24100</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>26000</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>21900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>21000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>27100</v>
       </c>
     </row>
-    <row r="11" spans="1:34" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1127,8 +1140,9 @@
       <c r="AF11" s="3"/>
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
-    </row>
-    <row r="12" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI11" s="3"/>
+    </row>
+    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1225,8 +1239,11 @@
       <c r="AH12" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="13" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI12" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1323,8 +1340,11 @@
       <c r="AH13" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="14" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI13" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1382,17 +1402,17 @@
       <c r="U14" s="3">
         <v>0</v>
       </c>
-      <c r="V14" s="3" t="s">
-        <v>8</v>
+      <c r="V14" s="3">
+        <v>0</v>
       </c>
       <c r="W14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y14" s="3" t="s">
+      <c r="X14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
@@ -1400,11 +1420,11 @@
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
+      <c r="AB14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC14" s="3">
         <v>39100</v>
-      </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
@@ -1421,8 +1441,11 @@
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="15" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
@@ -1519,8 +1542,11 @@
       <c r="AH15" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="16" spans="1:34" x14ac:dyDescent="0.2">
+      <c r="AI15" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1552,204 +1578,211 @@
       <c r="AF16" s="3"/>
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
-    </row>
-    <row r="17" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI16" s="3"/>
+    </row>
+    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>216100</v>
+      </c>
+      <c r="E17" s="3">
         <v>202900</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>190000</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>203500</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>218600</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>209700</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>204000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>214700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>218700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>207800</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>172800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>163700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>159100</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>150100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>132400</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>131200</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>127200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>124700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>113600</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>126900</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>133400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>127300</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>121400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>134500</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>136300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>163000</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>113400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>116100</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>123500</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>111200</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>106400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>109100</v>
       </c>
     </row>
-    <row r="18" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>39800</v>
+      </c>
+      <c r="E18" s="3">
         <v>20100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>18500</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>33000</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>32500</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>18400</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>15200</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>26500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>27800</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>15200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>14300</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>19600</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>22100</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>12900</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>10500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>16600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>16000</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>7700</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>6800</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>13100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>13900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>5800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>6800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>10800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>13500</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>-36000</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>4700</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>9300</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>10200</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>7400</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>6000</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="19" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1784,82 +1817,83 @@
       <c r="AF19" s="3"/>
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
-    </row>
-    <row r="20" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI19" s="3"/>
+    </row>
+    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>100</v>
+      </c>
+      <c r="E20" s="3">
         <v>500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>800</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-300</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>400</v>
-      </c>
-      <c r="H20" s="3">
-        <v>500</v>
       </c>
       <c r="I20" s="3">
         <v>500</v>
       </c>
       <c r="J20" s="3">
+        <v>500</v>
+      </c>
+      <c r="K20" s="3">
         <v>-500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-700</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>100</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>200</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>300</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>-1000</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>-400</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-600</v>
       </c>
       <c r="W20" s="3">
         <v>-600</v>
       </c>
       <c r="X20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Y20" s="3">
         <v>-500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-1200</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-700</v>
-      </c>
-      <c r="AA20" s="3">
-        <v>-900</v>
       </c>
       <c r="AB20" s="3">
         <v>-900</v>
@@ -1868,152 +1902,158 @@
         <v>-900</v>
       </c>
       <c r="AD20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-800</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-700</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-600</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>-700</v>
       </c>
       <c r="AH20" s="3">
         <v>-700</v>
       </c>
-    </row>
-    <row r="21" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI20" s="3">
+        <v>-700</v>
+      </c>
+    </row>
+    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>49300</v>
+      </c>
+      <c r="E21" s="3">
         <v>29500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>27700</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>40100</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>39900</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>26000</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>22700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>32900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>33700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>21100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>20400</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>25700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>28300</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>19000</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>16600</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>22500</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>21900</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>12200</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>11800</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>17900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>18700</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>10700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>11000</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>15600</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>18000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>-31200</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>9300</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>14000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>15300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>12200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>10500</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="22" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
-        <v>1200</v>
+        <v>1300</v>
       </c>
       <c r="E22" s="3">
         <v>1200</v>
       </c>
       <c r="F22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="G22" s="3">
         <v>700</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1100</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1500</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>900</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>400</v>
-      </c>
-      <c r="M22" s="3">
-        <v>300</v>
       </c>
       <c r="N22" s="3">
         <v>300</v>
@@ -2022,25 +2062,25 @@
         <v>300</v>
       </c>
       <c r="P22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="Q22" s="3">
         <v>400</v>
       </c>
       <c r="R22" s="3">
+        <v>400</v>
+      </c>
+      <c r="S22" s="3">
         <v>300</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>400</v>
-      </c>
-      <c r="T22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="U22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="V22" s="3">
-        <v>0</v>
+      <c r="V22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="W22" s="3">
         <v>0</v>
@@ -2078,204 +2118,213 @@
       <c r="AH22" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="23" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI22" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>38700</v>
+      </c>
+      <c r="E23" s="3">
         <v>19300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>18200</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>32000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>31700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>17500</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>14200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>24700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>26200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>14400</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>14100</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>19500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>22000</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>12700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>10600</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>16600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>16000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>6800</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6300</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>12500</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>13300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>5300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>10100</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>12500</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>-36900</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>3800</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>8500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>9500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>6800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>5400</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="24" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E24" s="3">
         <v>5500</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>3300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8200</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3500</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>6700</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6500</v>
-      </c>
-      <c r="L24" s="3">
-        <v>3900</v>
       </c>
       <c r="M24" s="3">
         <v>3900</v>
       </c>
       <c r="N24" s="3">
+        <v>3900</v>
+      </c>
+      <c r="O24" s="3">
         <v>5300</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5400</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3600</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>2700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>4400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4200</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2000</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>1800</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3300</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3500</v>
-      </c>
-      <c r="X24" s="3">
-        <v>1500</v>
       </c>
       <c r="Y24" s="3">
         <v>1500</v>
       </c>
       <c r="Z24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AA24" s="3">
         <v>2700</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3400</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1200</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>-100</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3300</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3700</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>2600</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>1800</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="25" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2372,204 +2421,213 @@
       <c r="AH25" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="26" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI25" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E26" s="3">
         <v>13800</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>14900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>23200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>23400</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>11600</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>10700</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>18000</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>19700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>10200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>14100</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>16600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>9100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>7900</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>12200</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>11800</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>4800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4500</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>9300</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>9800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>3800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4100</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>7400</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>9100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>-38100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>3900</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>5200</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>5800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3600</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="27" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E27" s="3">
         <v>13800</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>14900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>23200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>23400</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>11600</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>10700</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>18000</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>19700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>10600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>10200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>14100</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>16600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>9100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>7900</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>12200</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>11800</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>4800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4500</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>9300</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>9800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>3800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4100</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>7400</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>9100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>-38100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>3900</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>5200</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>5800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3600</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="28" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2666,8 +2724,11 @@
       <c r="AH28" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="29" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI28" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2725,17 +2786,17 @@
       <c r="U29" s="3">
         <v>0</v>
       </c>
-      <c r="V29" s="3" t="s">
-        <v>8</v>
+      <c r="V29" s="3">
+        <v>0</v>
       </c>
       <c r="W29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Y29" s="3" t="s">
+      <c r="X29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
@@ -2743,14 +2804,14 @@
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
+      <c r="AB29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AC29" s="3">
         <v>700</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AD29" s="3">
         <v>13200</v>
-      </c>
-      <c r="AD29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE29" s="3" t="s">
         <v>8</v>
@@ -2764,8 +2825,11 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-    </row>
-    <row r="30" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2862,8 +2926,11 @@
       <c r="AH30" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="31" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI30" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -2960,82 +3027,85 @@
       <c r="AH31" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="32" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI31" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="E32" s="3">
         <v>-500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>-800</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>300</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-400</v>
-      </c>
-      <c r="H32" s="3">
-        <v>-500</v>
       </c>
       <c r="I32" s="3">
         <v>-500</v>
       </c>
       <c r="J32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="K32" s="3">
         <v>500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>700</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-100</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>-200</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-300</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>1000</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>400</v>
-      </c>
-      <c r="V32" s="3">
-        <v>600</v>
       </c>
       <c r="W32" s="3">
         <v>600</v>
       </c>
       <c r="X32" s="3">
+        <v>600</v>
+      </c>
+      <c r="Y32" s="3">
         <v>500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>1200</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>700</v>
-      </c>
-      <c r="AA32" s="3">
-        <v>900</v>
       </c>
       <c r="AB32" s="3">
         <v>900</v>
@@ -3044,120 +3114,126 @@
         <v>900</v>
       </c>
       <c r="AD32" s="3">
+        <v>900</v>
+      </c>
+      <c r="AE32" s="3">
         <v>800</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>700</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>600</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>700</v>
       </c>
       <c r="AH32" s="3">
         <v>700</v>
       </c>
-    </row>
-    <row r="33" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI32" s="3">
+        <v>700</v>
+      </c>
+    </row>
+    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E33" s="3">
         <v>13800</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>14900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>23200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>23400</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>11600</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>10700</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>18000</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>19700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>10600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>10200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>14100</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>16600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>9100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>7900</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>12200</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>11800</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>4800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4500</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>9300</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>9800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>3800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4100</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>7400</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>9100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>-37400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>17100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>5200</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>5800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>4200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>3600</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="34" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3254,209 +3330,218 @@
       <c r="AH34" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="35" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI34" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E35" s="3">
         <v>13800</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>14900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>23200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>23400</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>11600</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>10700</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>18000</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>19700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>10600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>10200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>14100</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>16600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>9100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>7900</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>12200</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>11800</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>4800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4500</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>9300</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>9800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>3800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4100</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>7400</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>9100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>-37400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>17100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>5200</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>5800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>4200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>3600</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="37" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E38" s="2">
         <v>45382</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45291</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45200</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45109</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45018</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>44927</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44836</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44745</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44654</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44556</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44465</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44374</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44283</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44192</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44101</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44010</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>43919</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43828</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43737</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43646</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43555</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43464</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43373</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43282</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43191</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43100</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43009</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>42918</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42827</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42736</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="39" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3491,8 +3576,9 @@
       <c r="AF39" s="3"/>
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
-    </row>
-    <row r="40" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI39" s="3"/>
+    </row>
+    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3527,106 +3613,110 @@
       <c r="AF40" s="3"/>
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
-    </row>
-    <row r="41" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI40" s="3"/>
+    </row>
+    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E41" s="3">
         <v>7200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>5700</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>11000</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7600</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>6100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>3900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6000</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3500</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>23400</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6800</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>5200</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3000</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>8000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>4500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4300</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>7300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4100</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>5600</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>9200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4000</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>7600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>3800</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>2800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>6900</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>8400</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>16700</v>
       </c>
     </row>
-    <row r="42" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3723,400 +3813,415 @@
       <c r="AH42" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="43" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI42" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>126400</v>
+      </c>
+      <c r="E43" s="3">
         <v>114500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>113000</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>124800</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>138300</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>129300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>125500</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>131400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>138800</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>122800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>102800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>90100</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>90900</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>90800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>77800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>74500</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>69500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>67400</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>56700</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>65400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>69000</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>64500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>61500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>66400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>67900</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>66200</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>57900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>60000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>62800</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>58600</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>53300</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>52800</v>
       </c>
     </row>
-    <row r="44" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>81200</v>
+      </c>
+      <c r="E44" s="3">
         <v>74600</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>68800</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>68500</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>76900</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>88800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>101600</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>113100</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>105000</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>95000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>76200</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>70300</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>67900</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>63900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>64700</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>63200</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>63400</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>54400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>57500</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>60800</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>58700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>60500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>67700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>67800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>66400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>59700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>62700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>65900</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>65600</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>51200</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>50300</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="45" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
       <c r="D45" s="3">
+        <v>5500</v>
+      </c>
+      <c r="E45" s="3">
         <v>6600</v>
       </c>
-      <c r="E45" s="3">
+      <c r="F45" s="3">
         <v>7400</v>
       </c>
-      <c r="F45" s="3">
+      <c r="G45" s="3">
         <v>3000</v>
       </c>
-      <c r="G45" s="3">
+      <c r="H45" s="3">
         <v>4100</v>
       </c>
-      <c r="H45" s="3">
+      <c r="I45" s="3">
         <v>6400</v>
       </c>
-      <c r="I45" s="3">
+      <c r="J45" s="3">
         <v>7100</v>
       </c>
-      <c r="J45" s="3">
+      <c r="K45" s="3">
         <v>3200</v>
       </c>
-      <c r="K45" s="3">
+      <c r="L45" s="3">
         <v>3900</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>6400</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>7000</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>2500</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3700</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>5400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>5100</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>1700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>4900</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5600</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>2800</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4800</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5200</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>5700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>1700</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>3500</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>4100</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>4800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>2500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3300</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>4200</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>5100</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="46" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>222000</v>
+      </c>
+      <c r="E46" s="3">
         <v>202800</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>195000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>207300</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>226500</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>232000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>240200</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>251600</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>253600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>227700</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>209500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>169700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>167800</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>163000</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>155500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>142600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>140400</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>131000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>127000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>133100</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>138100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>139400</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>142200</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>139900</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>142900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>135000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>133100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>132200</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>134400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>120900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>117000</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>126400</v>
       </c>
     </row>
-    <row r="47" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
@@ -4213,204 +4318,213 @@
       <c r="AH47" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="48" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI47" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>225800</v>
+      </c>
+      <c r="E48" s="3">
         <v>220600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>216900</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>204200</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>201900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>196000</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>188900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>181000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>176400</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>172500</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>158400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>154200</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>153700</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>156200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>147100</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>136000</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>135800</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>135400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>134900</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>133900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>133500</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>118600</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>117600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>119400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>121700</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>123800</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>125100</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>125900</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>123000</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>121500</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>120200</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>117900</v>
       </c>
     </row>
-    <row r="49" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>238600</v>
+      </c>
+      <c r="E49" s="3">
         <v>220000</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>218200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>148900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>148800</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>150500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>152300</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>154100</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>155800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>157600</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>145500</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>146100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>145500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>147100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>137400</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>138900</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>117800</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>119100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>120400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>121600</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>122900</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>124200</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>125400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>126800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>128200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>129600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>170200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>171600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>173000</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>174400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>175900</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>177600</v>
       </c>
     </row>
-    <row r="50" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4507,8 +4621,11 @@
       <c r="AH50" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="51" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI50" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4605,106 +4722,112 @@
       <c r="AH51" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="52" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI51" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E52" s="3">
         <v>14500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>15000</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>14800</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12600</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>10500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>9500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>7800</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7900</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>6200</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>5600</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5400</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>3800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>4300</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4500</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3200</v>
-      </c>
-      <c r="Z52" s="3">
-        <v>3800</v>
       </c>
       <c r="AA52" s="3">
         <v>3800</v>
       </c>
       <c r="AB52" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AC52" s="3">
         <v>2600</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>2400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2200</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3000</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>1700</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1600</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="53" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4801,106 +4924,112 @@
       <c r="AH53" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="54" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI53" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>702700</v>
+      </c>
+      <c r="E54" s="3">
         <v>657900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>644000</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>575300</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>592000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>590500</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>594000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>599300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>596400</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>567300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>521100</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>477800</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>475000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>472600</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>446000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>423100</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>399500</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>389300</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>386600</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>393000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>399000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>385600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>388400</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>389800</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>396700</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>391000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>430700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>431900</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>433300</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>418600</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>414700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>422900</v>
       </c>
     </row>
-    <row r="55" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -4935,8 +5064,9 @@
       <c r="AF55" s="3"/>
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
-    </row>
-    <row r="56" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI55" s="3"/>
+    </row>
+    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -4971,106 +5101,110 @@
       <c r="AF56" s="3"/>
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
-    </row>
-    <row r="57" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI56" s="3"/>
+    </row>
+    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>47800</v>
+      </c>
+      <c r="E57" s="3">
         <v>56400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>42900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>61200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>55600</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>53700</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>50600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>60900</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>56400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>66700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>44000</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>43000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>38100</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>37300</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>31200</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>32700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>31100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>34100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>26700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>29600</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>32000</v>
-      </c>
-      <c r="X57" s="3">
-        <v>29300</v>
       </c>
       <c r="Y57" s="3">
         <v>29300</v>
       </c>
       <c r="Z57" s="3">
+        <v>29300</v>
+      </c>
+      <c r="AA57" s="3">
         <v>35500</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>36700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>33400</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>28100</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>26800</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>27900</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>29800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>21900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="58" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5153,414 +5287,429 @@
         <v>9900</v>
       </c>
       <c r="AD58" s="3">
+        <v>9900</v>
+      </c>
+      <c r="AE58" s="3">
         <v>9200</v>
       </c>
-      <c r="AE58" s="3">
+      <c r="AF58" s="3">
         <v>8600</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>8000</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>7400</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="59" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>40300</v>
+      </c>
+      <c r="E59" s="3">
         <v>37000</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>26900</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>23400</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>28800</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>27300</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>24400</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>20100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>21900</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>24900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>21600</v>
-      </c>
-      <c r="N59" s="3">
-        <v>18600</v>
       </c>
       <c r="O59" s="3">
         <v>18600</v>
       </c>
       <c r="P59" s="3">
+        <v>18600</v>
+      </c>
+      <c r="Q59" s="3">
         <v>23200</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>18000</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>16100</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>15700</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>18200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>14600</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>14300</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>13800</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>16200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>13900</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>13500</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>10000</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>17300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>10600</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>16400</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>8500</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>17900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>12700</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>18700</v>
       </c>
     </row>
-    <row r="60" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>98000</v>
+      </c>
+      <c r="E60" s="3">
         <v>103300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>79700</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>94500</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>94300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>90900</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>84900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>90900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>88200</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>101500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>75500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>71500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>66500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>70500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>59000</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>58800</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>56700</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>62200</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>51300</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>53900</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>55700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>55400</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>53100</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>58800</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>56500</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>60600</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>48500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>52500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>45000</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>55700</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>41900</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="61" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>123800</v>
+      </c>
+      <c r="E61" s="3">
         <v>88800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>109800</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>49800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>78400</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>101700</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>120700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>130700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>149200</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>115600</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>105900</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>73900</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>85900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>88800</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>85800</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>65800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>55800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>49800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>57700</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>64700</v>
-      </c>
-      <c r="W61" s="3">
-        <v>74700</v>
       </c>
       <c r="X61" s="3">
         <v>74700</v>
       </c>
       <c r="Y61" s="3">
+        <v>74700</v>
+      </c>
+      <c r="Z61" s="3">
         <v>80600</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>75800</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>90800</v>
       </c>
       <c r="AB61" s="3">
         <v>90800</v>
       </c>
       <c r="AC61" s="3">
+        <v>90800</v>
+      </c>
+      <c r="AD61" s="3">
         <v>104200</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>102700</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>112200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>94600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>105100</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>106900</v>
       </c>
     </row>
-    <row r="62" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>59700</v>
+      </c>
+      <c r="E62" s="3">
         <v>59800</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>60800</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>48400</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>48300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>47900</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>47300</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>46300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>45800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>47600</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>48000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>48100</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>47400</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>48000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>44200</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>43900</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>43600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>43900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>45400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>45000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>45200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>37700</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>37200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>37400</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>37100</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>37400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>34700</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>51100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>51500</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>50500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>50400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="63" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5657,8 +5806,11 @@
       <c r="AH63" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="64" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI63" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5755,8 +5907,11 @@
       <c r="AH64" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="65" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI64" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -5853,106 +6008,112 @@
       <c r="AH65" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="66" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI65" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>281500</v>
+      </c>
+      <c r="E66" s="3">
         <v>251900</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>250300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>192600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>221000</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>240500</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>252800</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>267900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>283100</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>264700</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>229500</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>193500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>199800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>207300</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>189100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>168400</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>156000</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>155800</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>154400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>163600</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>175600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>167700</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>170900</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>172000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>184400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>188700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>187500</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>206200</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>208600</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>200800</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>197400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>210100</v>
       </c>
     </row>
-    <row r="67" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -5987,8 +6148,9 @@
       <c r="AF67" s="3"/>
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
-    </row>
-    <row r="68" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI67" s="3"/>
+    </row>
+    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6085,8 +6247,11 @@
       <c r="AH68" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="69" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI68" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6183,8 +6348,11 @@
       <c r="AH69" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="70" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI69" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6281,8 +6449,11 @@
       <c r="AH70" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="71" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI70" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6379,106 +6550,112 @@
       <c r="AH71" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="72" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI71" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>390100</v>
+      </c>
+      <c r="E72" s="3">
         <v>364500</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>354100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>342500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>322700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>302400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>294000</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>286200</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>271100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>254400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>246800</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>239300</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>227900</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>213900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>207400</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>202000</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>192300</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>182900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>180700</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>178600</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>171800</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>164400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>163100</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>161400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>156400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>147200</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>189400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>172200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>171700</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>165900</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>166200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>162600</v>
       </c>
     </row>
-    <row r="73" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6575,8 +6752,11 @@
       <c r="AH73" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="74" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI73" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6673,8 +6853,11 @@
       <c r="AH74" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="75" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI74" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6771,106 +6954,112 @@
       <c r="AH75" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="76" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI75" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>421200</v>
+      </c>
+      <c r="E76" s="3">
         <v>406000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>393800</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>382700</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>371000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>350000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>341200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>331400</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>313300</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>302600</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>291700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>284300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>275200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>265200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>256900</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>254600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>243400</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>233500</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>232200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>229400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>223400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>217900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>217500</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>217800</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>212300</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>202200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>243300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>225700</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>224700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>217800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>217300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>212800</v>
       </c>
     </row>
-    <row r="77" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -6967,209 +7156,218 @@
       <c r="AH77" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="79" spans="2:34" x14ac:dyDescent="0.2">
+      <c r="AI77" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:34" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45473</v>
+      </c>
+      <c r="E80" s="2">
         <v>45382</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45291</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45200</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45109</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45018</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>44927</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44836</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44745</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44654</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44556</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44465</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44374</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44283</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44192</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44101</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44010</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>43919</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43828</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43737</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43646</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43555</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43464</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43373</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43282</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43191</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43100</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43009</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>42918</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42827</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42736</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="81" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>28900</v>
+      </c>
+      <c r="E81" s="3">
         <v>13800</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>14900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>23200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>23400</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>11600</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>10700</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>18000</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>19700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>10600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>10200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>14100</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>16600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>9100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>7900</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>12200</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>11800</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>4800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4500</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>9300</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>9800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>3800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4100</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>7400</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>9100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>-37400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>17100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>5200</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>5800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>4200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>3600</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="82" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7204,61 +7402,62 @@
       <c r="AF82" s="3"/>
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
-    </row>
-    <row r="83" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI82" s="3"/>
+    </row>
+    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E83" s="3">
         <v>9000</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7400</v>
-      </c>
-      <c r="G83" s="3">
-        <v>7100</v>
       </c>
       <c r="H83" s="3">
         <v>7100</v>
       </c>
       <c r="I83" s="3">
+        <v>7100</v>
+      </c>
+      <c r="J83" s="3">
         <v>7000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6300</v>
-      </c>
-      <c r="M83" s="3">
-        <v>6000</v>
       </c>
       <c r="N83" s="3">
         <v>6000</v>
       </c>
       <c r="O83" s="3">
-        <v>5900</v>
+        <v>6000</v>
       </c>
       <c r="P83" s="3">
         <v>5900</v>
       </c>
       <c r="Q83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="R83" s="3">
         <v>5700</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>5600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5500</v>
-      </c>
-      <c r="T83" s="3">
-        <v>5400</v>
       </c>
       <c r="U83" s="3">
         <v>5400</v>
@@ -7276,34 +7475,37 @@
         <v>5400</v>
       </c>
       <c r="Z83" s="3">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="AA83" s="3">
         <v>5500</v>
       </c>
       <c r="AB83" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AC83" s="3">
         <v>5600</v>
       </c>
-      <c r="AC83" s="3">
+      <c r="AD83" s="3">
         <v>5400</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>5500</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>5800</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>5400</v>
-      </c>
-      <c r="AG83" s="3">
-        <v>5200</v>
       </c>
       <c r="AH83" s="3">
         <v>5200</v>
       </c>
-    </row>
-    <row r="84" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI83" s="3">
+        <v>5200</v>
+      </c>
+    </row>
+    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7400,8 +7602,11 @@
       <c r="AH84" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="85" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI84" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7498,8 +7703,11 @@
       <c r="AH85" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="86" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI85" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7596,8 +7804,11 @@
       <c r="AH86" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="87" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI86" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7694,8 +7905,11 @@
       <c r="AH87" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="88" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI87" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -7792,106 +8006,112 @@
       <c r="AH88" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="89" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI88" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>17600</v>
+      </c>
+      <c r="E89" s="3">
         <v>41900</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>25000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>57800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>34900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>32900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>25700</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>28200</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>-9400</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>4100</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-1400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>25300</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>14800</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>17200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>6500</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>18600</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>1600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>13900</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>17900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>17000</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>10100</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>17000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>6200</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>18000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>6800</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>12800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>10100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>16400</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>-11900</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>13900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>2900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>13600</v>
       </c>
     </row>
-    <row r="90" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -7926,106 +8146,110 @@
       <c r="AF90" s="3"/>
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
-    </row>
-    <row r="91" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI90" s="3"/>
+    </row>
+    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11900</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-11300</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-9000</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-7900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-16000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11600</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-12800</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-8800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-4700</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-2200</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-7600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-5100</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-3300</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-4800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4900</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-9200</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5400</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3000</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3800</v>
-      </c>
-      <c r="AD91" s="3">
-        <v>-6600</v>
       </c>
       <c r="AE91" s="3">
         <v>-6600</v>
       </c>
       <c r="AF91" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="AG91" s="3">
         <v>-5800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-5600</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="92" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8122,8 +8346,11 @@
       <c r="AH92" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="93" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI92" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8220,106 +8447,112 @@
       <c r="AH93" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="94" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI93" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-35800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-16100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-86400</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-12100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-7800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-9300</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-11600</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-8800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11500</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-31700</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-10100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-5800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-2100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-23400</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-15000</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-28200</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-4800</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-9100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-2900</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-3700</v>
-      </c>
-      <c r="AD94" s="3">
-        <v>-6500</v>
       </c>
       <c r="AE94" s="3">
         <v>-6500</v>
       </c>
       <c r="AF94" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="AG94" s="3">
         <v>-5700</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-5500</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="95" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8354,8 +8587,9 @@
       <c r="AF95" s="3"/>
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
-    </row>
-    <row r="96" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI95" s="3"/>
+    </row>
+    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8369,37 +8603,37 @@
         <v>-3400</v>
       </c>
       <c r="G96" s="3">
-        <v>-3200</v>
+        <v>-3400</v>
       </c>
       <c r="H96" s="3">
         <v>-3200</v>
       </c>
       <c r="I96" s="3">
-        <v>-2900</v>
+        <v>-3200</v>
       </c>
       <c r="J96" s="3">
         <v>-2900</v>
       </c>
       <c r="K96" s="3">
-        <v>-3000</v>
+        <v>-2900</v>
       </c>
       <c r="L96" s="3">
         <v>-3000</v>
       </c>
       <c r="M96" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="N96" s="3">
         <v>-2700</v>
       </c>
-      <c r="N96" s="3">
+      <c r="O96" s="3">
         <v>-2800</v>
-      </c>
-      <c r="O96" s="3">
-        <v>-2600</v>
       </c>
       <c r="P96" s="3">
         <v>-2600</v>
       </c>
       <c r="Q96" s="3">
-        <v>-2500</v>
+        <v>-2600</v>
       </c>
       <c r="R96" s="3">
         <v>-2500</v>
@@ -8411,49 +8645,52 @@
         <v>-2500</v>
       </c>
       <c r="U96" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="V96" s="3">
         <v>-2400</v>
       </c>
       <c r="W96" s="3">
-        <v>-2500</v>
+        <v>-2400</v>
       </c>
       <c r="X96" s="3">
         <v>-2500</v>
       </c>
       <c r="Y96" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="Z96" s="3">
         <v>-2400</v>
       </c>
       <c r="AA96" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AB96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AB96" s="3">
-        <v>0</v>
-      </c>
       <c r="AC96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-4500</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-4500</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="97" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8550,8 +8787,11 @@
       <c r="AH97" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="98" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI97" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8648,8 +8888,11 @@
       <c r="AH98" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="99" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI98" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8746,106 +8989,112 @@
       <c r="AH99" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="100" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI99" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>20000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-24400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>56200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-41700</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-27600</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-22200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-11900</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-21400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>23400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>7600</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>28100</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-17900</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-10500</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>1200</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>13400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>8300</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>3500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-11800</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-9400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-13800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-4600</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-9800</v>
       </c>
-      <c r="Y100" s="3">
-        <v>0</v>
-      </c>
       <c r="Z100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AA100" s="3">
         <v>-17400</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-4300</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-12800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-8900</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>14400</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-9600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="101" spans="3:34" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -8942,102 +9191,108 @@
       <c r="AH101" s="3">
         <v>0</v>
       </c>
-    </row>
-    <row r="102" spans="3:34" x14ac:dyDescent="0.2">
+      <c r="AI101" s="3">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>1700</v>
+      </c>
+      <c r="E102" s="3">
         <v>1400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-5200</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>3900</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-500</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>2200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-2100</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-19900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>16600</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-5000</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>4800</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-1400</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-3000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>3200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1600</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>1900</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>3300</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>3900</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1000</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-4100</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-8300</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-4600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HWKN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HWKN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="150" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
   <si>
     <t>HWKN</t>
   </si>
@@ -656,456 +656,469 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AI102"/>
+  <dimension ref="A5:AJ102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="34" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="35" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45564</v>
+      </c>
+      <c r="E7" s="2">
         <v>45473</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45382</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45291</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45200</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45109</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45018</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>44927</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44836</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44745</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44654</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44556</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44465</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44374</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44283</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44192</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44101</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44010</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>43919</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43828</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43737</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43646</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43555</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43464</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43373</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43282</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43191</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43100</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43009</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>42918</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42827</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42736</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="8" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>247000</v>
+      </c>
+      <c r="E8" s="3">
         <v>255900</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>223000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>208500</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>236500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>251100</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>228100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>219200</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>241200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>246500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>223000</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>187100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>183300</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>181200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>163000</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>142900</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>147800</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>143200</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>132400</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>120400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>140000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>147300</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>133100</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>128200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>145300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>149800</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>127000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>118100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>125400</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>133700</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>118600</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>112400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>121300</v>
       </c>
     </row>
-    <row r="9" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>186800</v>
+      </c>
+      <c r="E9" s="3">
         <v>191200</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>177500</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>166200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>182600</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>199100</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>192400</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>182900</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>194800</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>199800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>186700</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>153100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>146000</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>142300</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>131200</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>114700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>115000</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>112200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>109800</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>98900</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>112000</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>118500</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>112400</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>107100</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>119600</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>121300</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>109200</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>99200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>101300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>107700</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>96700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>91400</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>94200</v>
       </c>
     </row>
-    <row r="10" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>60200</v>
+      </c>
+      <c r="E10" s="3">
         <v>64700</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>45500</v>
       </c>
-      <c r="F10" s="3">
-        <v>42300</v>
-      </c>
       <c r="G10" s="3">
+        <v>42200</v>
+      </c>
+      <c r="H10" s="3">
         <v>53900</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>52000</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>35700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>36300</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>46400</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>46700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>36300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>34000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>37300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>38900</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>31800</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>28200</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>32800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>31000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>22600</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>21500</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>28000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>28800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>20700</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>21100</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>25700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>28500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>17800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>18900</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>24100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>26000</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>21900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>21000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>27100</v>
       </c>
     </row>
-    <row r="11" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1141,8 +1154,9 @@
       <c r="AG11" s="3"/>
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
+      <c r="AJ11" s="3"/>
     </row>
-    <row r="12" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1242,8 +1256,11 @@
       <c r="AI12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1343,31 +1360,34 @@
       <c r="AI13" s="3">
         <v>0</v>
       </c>
+      <c r="AJ13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3">
-        <v>0</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0</v>
+      <c r="D14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="F14" s="3">
-        <v>0</v>
+        <v>-800</v>
       </c>
       <c r="G14" s="3">
-        <v>0</v>
-      </c>
-      <c r="H14" s="3">
-        <v>0</v>
-      </c>
-      <c r="I14" s="3">
-        <v>0</v>
-      </c>
-      <c r="J14" s="3">
-        <v>0</v>
+        <v>700</v>
+      </c>
+      <c r="H14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K14" s="3">
         <v>0</v>
@@ -1405,17 +1425,17 @@
       <c r="V14" s="3">
         <v>0</v>
       </c>
-      <c r="W14" s="3" t="s">
-        <v>8</v>
+      <c r="W14" s="3">
+        <v>0</v>
       </c>
       <c r="X14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y14" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z14" s="3" t="s">
+      <c r="Y14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
@@ -1423,11 +1443,11 @@
       <c r="AB14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC14" s="3">
+      <c r="AC14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD14" s="3">
         <v>39100</v>
-      </c>
-      <c r="AD14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AE14" s="3" t="s">
         <v>8</v>
@@ -1444,31 +1464,34 @@
       <c r="AI14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
-        <v>0</v>
+        <v>9900</v>
       </c>
       <c r="E15" s="3">
-        <v>0</v>
+        <v>9300</v>
       </c>
       <c r="F15" s="3">
-        <v>0</v>
+        <v>9000</v>
       </c>
       <c r="G15" s="3">
-        <v>0</v>
+        <v>8300</v>
       </c>
       <c r="H15" s="3">
-        <v>0</v>
+        <v>7400</v>
       </c>
       <c r="I15" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="J15" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="K15" s="3">
         <v>0</v>
@@ -1545,8 +1568,11 @@
       <c r="AI15" s="3">
         <v>0</v>
       </c>
+      <c r="AJ15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:35" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1579,210 +1605,217 @@
       <c r="AG16" s="3"/>
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
+      <c r="AJ16" s="3"/>
     </row>
-    <row r="17" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>213300</v>
+      </c>
+      <c r="E17" s="3">
         <v>216100</v>
       </c>
-      <c r="E17" s="3">
-        <v>202900</v>
-      </c>
       <c r="F17" s="3">
-        <v>190000</v>
+        <v>203700</v>
       </c>
       <c r="G17" s="3">
+        <v>189300</v>
+      </c>
+      <c r="H17" s="3">
         <v>203500</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>218600</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>209700</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>204000</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>214700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>218700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>207800</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>172800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>163700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>159100</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>150100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>132400</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>131200</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>127200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>124700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>113600</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>126900</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>133400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>127300</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>121400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>134500</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>136300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>163000</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>113400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>116100</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>123500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>111200</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>106400</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>109100</v>
       </c>
     </row>
-    <row r="18" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>33700</v>
+      </c>
+      <c r="E18" s="3">
         <v>39800</v>
       </c>
-      <c r="E18" s="3">
-        <v>20100</v>
-      </c>
       <c r="F18" s="3">
+        <v>19300</v>
+      </c>
+      <c r="G18" s="3">
+        <v>19200</v>
+      </c>
+      <c r="H18" s="3">
+        <v>33000</v>
+      </c>
+      <c r="I18" s="3">
+        <v>32500</v>
+      </c>
+      <c r="J18" s="3">
         <v>18500</v>
       </c>
-      <c r="G18" s="3">
-        <v>33000</v>
-      </c>
-      <c r="H18" s="3">
-        <v>32500</v>
-      </c>
-      <c r="I18" s="3">
-        <v>18400</v>
-      </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>15200</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>26500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>27800</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>15200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>14300</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>19600</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>22100</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>12900</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>10500</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>16600</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>16000</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>7700</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>6800</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>13100</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>13900</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>5800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>6800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>10800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>13500</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>-36000</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>4700</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>9300</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>10200</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>7400</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>6000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="19" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1818,85 +1851,86 @@
       <c r="AG19" s="3"/>
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
+      <c r="AJ19" s="3"/>
     </row>
-    <row r="20" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="E20" s="3">
+        <v>-200</v>
+      </c>
+      <c r="F20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="G20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="H20" s="3">
+        <v>300</v>
+      </c>
+      <c r="I20" s="3">
+        <v>-300</v>
+      </c>
+      <c r="J20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="K20" s="3">
+        <v>500</v>
+      </c>
+      <c r="L20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="M20" s="3">
+        <v>-700</v>
+      </c>
+      <c r="N20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="O20" s="3">
         <v>100</v>
       </c>
-      <c r="E20" s="3">
+      <c r="P20" s="3">
+        <v>200</v>
+      </c>
+      <c r="Q20" s="3">
+        <v>300</v>
+      </c>
+      <c r="R20" s="3">
+        <v>100</v>
+      </c>
+      <c r="S20" s="3">
         <v>500</v>
       </c>
-      <c r="F20" s="3">
-        <v>800</v>
-      </c>
-      <c r="G20" s="3">
-        <v>-300</v>
-      </c>
-      <c r="H20" s="3">
+      <c r="T20" s="3">
+        <v>300</v>
+      </c>
+      <c r="U20" s="3">
         <v>400</v>
       </c>
-      <c r="I20" s="3">
-        <v>500</v>
-      </c>
-      <c r="J20" s="3">
-        <v>500</v>
-      </c>
-      <c r="K20" s="3">
-        <v>-500</v>
-      </c>
-      <c r="L20" s="3">
-        <v>-700</v>
-      </c>
-      <c r="M20" s="3">
+      <c r="V20" s="3">
+        <v>-1000</v>
+      </c>
+      <c r="W20" s="3">
         <v>-400</v>
-      </c>
-      <c r="N20" s="3">
-        <v>100</v>
-      </c>
-      <c r="O20" s="3">
-        <v>200</v>
-      </c>
-      <c r="P20" s="3">
-        <v>300</v>
-      </c>
-      <c r="Q20" s="3">
-        <v>100</v>
-      </c>
-      <c r="R20" s="3">
-        <v>500</v>
-      </c>
-      <c r="S20" s="3">
-        <v>300</v>
-      </c>
-      <c r="T20" s="3">
-        <v>400</v>
-      </c>
-      <c r="U20" s="3">
-        <v>-1000</v>
-      </c>
-      <c r="V20" s="3">
-        <v>-400</v>
-      </c>
-      <c r="W20" s="3">
-        <v>-600</v>
       </c>
       <c r="X20" s="3">
         <v>-600</v>
       </c>
       <c r="Y20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="Z20" s="3">
         <v>-500</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-700</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>-900</v>
       </c>
       <c r="AC20" s="3">
         <v>-900</v>
@@ -1905,158 +1939,164 @@
         <v>-900</v>
       </c>
       <c r="AE20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-800</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-700</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-600</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>-700</v>
       </c>
       <c r="AI20" s="3">
         <v>-700</v>
       </c>
+      <c r="AJ20" s="3">
+        <v>-700</v>
+      </c>
     </row>
-    <row r="21" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>44300</v>
+      </c>
+      <c r="E21" s="3">
         <v>49300</v>
       </c>
-      <c r="E21" s="3">
-        <v>29500</v>
-      </c>
       <c r="F21" s="3">
-        <v>27700</v>
+        <v>28700</v>
       </c>
       <c r="G21" s="3">
+        <v>28400</v>
+      </c>
+      <c r="H21" s="3">
         <v>40100</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>39900</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>26000</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>22700</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>32900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>33700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>21100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>20400</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>25700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>28300</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>19000</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>16600</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>22500</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>21900</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>12200</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>11800</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>17900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>18700</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>10700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>11000</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>15600</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>18000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>-31200</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>9300</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>14000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>15300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>12200</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>10500</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="22" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1400</v>
+      </c>
+      <c r="E22" s="3">
         <v>1300</v>
-      </c>
-      <c r="E22" s="3">
-        <v>1200</v>
       </c>
       <c r="F22" s="3">
         <v>1200</v>
       </c>
       <c r="G22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="H22" s="3">
         <v>700</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1100</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1500</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>900</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>400</v>
-      </c>
-      <c r="N22" s="3">
-        <v>300</v>
       </c>
       <c r="O22" s="3">
         <v>300</v>
@@ -2065,25 +2105,25 @@
         <v>300</v>
       </c>
       <c r="Q22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="R22" s="3">
         <v>400</v>
       </c>
       <c r="S22" s="3">
+        <v>400</v>
+      </c>
+      <c r="T22" s="3">
         <v>300</v>
       </c>
-      <c r="T22" s="3">
+      <c r="U22" s="3">
         <v>400</v>
-      </c>
-      <c r="U22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="V22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="W22" s="3">
-        <v>0</v>
+      <c r="W22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="X22" s="3">
         <v>0</v>
@@ -2121,210 +2161,219 @@
       <c r="AI22" s="3">
         <v>0</v>
       </c>
+      <c r="AJ22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>33000</v>
+      </c>
+      <c r="E23" s="3">
         <v>38700</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>19300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>18200</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>32000</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>31700</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>17500</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>14200</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>24700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>26200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>14400</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>14100</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>19500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>22000</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>12700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>10600</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>16600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>16000</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>6800</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6300</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>12500</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>13300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>5300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>5600</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>10100</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>12500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>-36900</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>3800</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>8500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>9500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>6800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>5400</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="24" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>8900</v>
+      </c>
+      <c r="E24" s="3">
         <v>9800</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5500</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>3300</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>8800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8200</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>5900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>3500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>6700</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6500</v>
-      </c>
-      <c r="M24" s="3">
-        <v>3900</v>
       </c>
       <c r="N24" s="3">
         <v>3900</v>
       </c>
       <c r="O24" s="3">
+        <v>3900</v>
+      </c>
+      <c r="P24" s="3">
         <v>5300</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>5400</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>3600</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>2700</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>4400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4200</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2000</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>1800</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3300</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3500</v>
-      </c>
-      <c r="Y24" s="3">
-        <v>1500</v>
       </c>
       <c r="Z24" s="3">
         <v>1500</v>
       </c>
       <c r="AA24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AB24" s="3">
         <v>2700</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3400</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>1200</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>-100</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3300</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>2600</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1800</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="25" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2424,210 +2473,219 @@
       <c r="AI25" s="3">
         <v>0</v>
       </c>
+      <c r="AJ25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E26" s="3">
         <v>28900</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>13800</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>14900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>23200</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>23400</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>11600</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>10700</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>18000</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>19700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>10600</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10200</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>14100</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>16600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>9100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>7900</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>12200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>11800</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>4800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4500</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>9300</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>9800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>3800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4100</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>7400</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>9100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>-38100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3900</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>5200</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>5800</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>4200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>3600</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="27" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E27" s="3">
         <v>28900</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>13800</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>14900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>23200</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>23400</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>11600</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>10700</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>18000</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>19700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>10600</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>10200</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>14100</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>16600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>9100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>7900</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>12200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>11800</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>4800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4500</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>9300</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>9800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>3800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4100</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>7400</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>9100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>-38100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3900</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>5200</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>5800</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>4200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>3600</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="28" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2727,8 +2785,11 @@
       <c r="AI28" s="3">
         <v>0</v>
       </c>
+      <c r="AJ28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2789,17 +2850,17 @@
       <c r="V29" s="3">
         <v>0</v>
       </c>
-      <c r="W29" s="3" t="s">
-        <v>8</v>
+      <c r="W29" s="3">
+        <v>0</v>
       </c>
       <c r="X29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y29" s="3">
-        <v>0</v>
-      </c>
-      <c r="Z29" s="3" t="s">
+      <c r="Y29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
@@ -2807,14 +2868,14 @@
       <c r="AB29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC29" s="3">
+      <c r="AC29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AD29" s="3">
         <v>700</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AE29" s="3">
         <v>13200</v>
-      </c>
-      <c r="AE29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -2828,8 +2889,11 @@
       <c r="AI29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AJ29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2929,8 +2993,11 @@
       <c r="AI30" s="3">
         <v>0</v>
       </c>
+      <c r="AJ30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3030,85 +3097,88 @@
       <c r="AI31" s="3">
         <v>0</v>
       </c>
+      <c r="AJ31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>700</v>
+      </c>
+      <c r="E32" s="3">
+        <v>200</v>
+      </c>
+      <c r="F32" s="3">
+        <v>500</v>
+      </c>
+      <c r="G32" s="3">
+        <v>900</v>
+      </c>
+      <c r="H32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="I32" s="3">
+        <v>300</v>
+      </c>
+      <c r="J32" s="3">
+        <v>400</v>
+      </c>
+      <c r="K32" s="3">
+        <v>-500</v>
+      </c>
+      <c r="L32" s="3">
+        <v>500</v>
+      </c>
+      <c r="M32" s="3">
+        <v>700</v>
+      </c>
+      <c r="N32" s="3">
+        <v>400</v>
+      </c>
+      <c r="O32" s="3">
         <v>-100</v>
       </c>
-      <c r="E32" s="3">
+      <c r="P32" s="3">
+        <v>-200</v>
+      </c>
+      <c r="Q32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="R32" s="3">
+        <v>-100</v>
+      </c>
+      <c r="S32" s="3">
         <v>-500</v>
       </c>
-      <c r="F32" s="3">
-        <v>-800</v>
-      </c>
-      <c r="G32" s="3">
-        <v>300</v>
-      </c>
-      <c r="H32" s="3">
+      <c r="T32" s="3">
+        <v>-300</v>
+      </c>
+      <c r="U32" s="3">
         <v>-400</v>
       </c>
-      <c r="I32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="J32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="K32" s="3">
-        <v>500</v>
-      </c>
-      <c r="L32" s="3">
-        <v>700</v>
-      </c>
-      <c r="M32" s="3">
+      <c r="V32" s="3">
+        <v>1000</v>
+      </c>
+      <c r="W32" s="3">
         <v>400</v>
-      </c>
-      <c r="N32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="O32" s="3">
-        <v>-200</v>
-      </c>
-      <c r="P32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="Q32" s="3">
-        <v>-100</v>
-      </c>
-      <c r="R32" s="3">
-        <v>-500</v>
-      </c>
-      <c r="S32" s="3">
-        <v>-300</v>
-      </c>
-      <c r="T32" s="3">
-        <v>-400</v>
-      </c>
-      <c r="U32" s="3">
-        <v>1000</v>
-      </c>
-      <c r="V32" s="3">
-        <v>400</v>
-      </c>
-      <c r="W32" s="3">
-        <v>600</v>
       </c>
       <c r="X32" s="3">
         <v>600</v>
       </c>
       <c r="Y32" s="3">
+        <v>600</v>
+      </c>
+      <c r="Z32" s="3">
         <v>500</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1200</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>700</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>900</v>
       </c>
       <c r="AC32" s="3">
         <v>900</v>
@@ -3117,123 +3187,129 @@
         <v>900</v>
       </c>
       <c r="AE32" s="3">
+        <v>900</v>
+      </c>
+      <c r="AF32" s="3">
         <v>800</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>700</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>600</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>700</v>
       </c>
       <c r="AI32" s="3">
         <v>700</v>
       </c>
+      <c r="AJ32" s="3">
+        <v>700</v>
+      </c>
     </row>
-    <row r="33" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E33" s="3">
         <v>28900</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>13800</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>14900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>23200</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>23400</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>11600</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>10700</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>18000</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>19700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>10600</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>10200</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>14100</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>16600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>9100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>7900</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>12200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>11800</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>4800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4500</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>9300</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>9800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>3800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4100</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>7400</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>9100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>-37400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>17100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>5200</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>5800</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>4200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>3600</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="34" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3333,215 +3409,224 @@
       <c r="AI34" s="3">
         <v>0</v>
       </c>
+      <c r="AJ34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E35" s="3">
         <v>28900</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>13800</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>14900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>23200</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>23400</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>11600</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>10700</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>18000</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>19700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>10600</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>10200</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>14100</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>16600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>9100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>7900</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>12200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>11800</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>4800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4500</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>9300</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>9800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>3800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4100</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>7400</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>9100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>-37400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>17100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>5200</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>5800</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>4200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>3600</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="37" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45564</v>
+      </c>
+      <c r="E38" s="2">
         <v>45473</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45382</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45291</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45200</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45109</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45018</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>44927</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44836</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44745</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44654</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44556</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44465</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44374</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44283</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44192</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44101</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44010</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>43919</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43828</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43737</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43646</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43555</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43464</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43373</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43282</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43191</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43100</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43009</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>42918</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42827</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42736</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="39" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3577,8 +3662,9 @@
       <c r="AG39" s="3"/>
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
+      <c r="AJ39" s="3"/>
     </row>
-    <row r="40" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3614,109 +3700,113 @@
       <c r="AG40" s="3"/>
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
+      <c r="AJ40" s="3"/>
     </row>
-    <row r="41" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>7500</v>
+      </c>
+      <c r="E41" s="3">
         <v>8900</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7200</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5700</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>11000</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7100</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7600</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>6100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>3900</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3500</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>23400</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6800</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>5200</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>8000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>4500</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4300</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>7300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4100</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>5600</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>9200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>7300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4000</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>5200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>7600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>3800</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>2800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>6900</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>8400</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>16700</v>
       </c>
     </row>
-    <row r="42" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3816,435 +3906,450 @@
       <c r="AI42" s="3">
         <v>0</v>
       </c>
+      <c r="AJ42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>115200</v>
+      </c>
+      <c r="E43" s="3">
         <v>126400</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>114500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>113000</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>124800</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>138300</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>129300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>125500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>131400</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>138800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>122800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>102800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>90100</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>90900</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>90800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>77800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>74500</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>69500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>67400</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>56700</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>65400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>69000</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>64500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>61500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>66400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>67900</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>66200</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>57900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>60000</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>62800</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>58600</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>53300</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>52800</v>
       </c>
     </row>
-    <row r="44" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>81600</v>
+      </c>
+      <c r="E44" s="3">
         <v>81200</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>74600</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>68800</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>68500</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>76900</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>88800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>101600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>113100</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>105000</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>95000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>76200</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>70300</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>67900</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>63900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>64700</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>63200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>63400</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>54400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>57500</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>60800</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>58700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>60500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>67700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>67800</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>66400</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>59700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>62700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>65900</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>65600</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>51200</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>50300</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="45" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
-      <c r="D45" s="3">
-        <v>5500</v>
-      </c>
-      <c r="E45" s="3">
-        <v>6600</v>
-      </c>
-      <c r="F45" s="3">
-        <v>7400</v>
-      </c>
-      <c r="G45" s="3">
-        <v>3000</v>
-      </c>
-      <c r="H45" s="3">
+      <c r="D45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="K45" s="3">
+        <v>7100</v>
+      </c>
+      <c r="L45" s="3">
+        <v>3200</v>
+      </c>
+      <c r="M45" s="3">
+        <v>3900</v>
+      </c>
+      <c r="N45" s="3">
+        <v>6400</v>
+      </c>
+      <c r="O45" s="3">
+        <v>7000</v>
+      </c>
+      <c r="P45" s="3">
+        <v>2500</v>
+      </c>
+      <c r="Q45" s="3">
+        <v>3700</v>
+      </c>
+      <c r="R45" s="3">
+        <v>5400</v>
+      </c>
+      <c r="S45" s="3">
+        <v>5100</v>
+      </c>
+      <c r="T45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="U45" s="3">
+        <v>3100</v>
+      </c>
+      <c r="V45" s="3">
+        <v>4900</v>
+      </c>
+      <c r="W45" s="3">
+        <v>5600</v>
+      </c>
+      <c r="X45" s="3">
+        <v>2800</v>
+      </c>
+      <c r="Y45" s="3">
+        <v>4800</v>
+      </c>
+      <c r="Z45" s="3">
+        <v>5200</v>
+      </c>
+      <c r="AA45" s="3">
+        <v>5700</v>
+      </c>
+      <c r="AB45" s="3">
+        <v>1700</v>
+      </c>
+      <c r="AC45" s="3">
+        <v>3500</v>
+      </c>
+      <c r="AD45" s="3">
         <v>4100</v>
       </c>
-      <c r="I45" s="3">
-        <v>6400</v>
-      </c>
-      <c r="J45" s="3">
-        <v>7100</v>
-      </c>
-      <c r="K45" s="3">
-        <v>3200</v>
-      </c>
-      <c r="L45" s="3">
-        <v>3900</v>
-      </c>
-      <c r="M45" s="3">
-        <v>6400</v>
-      </c>
-      <c r="N45" s="3">
-        <v>7000</v>
-      </c>
-      <c r="O45" s="3">
+      <c r="AE45" s="3">
+        <v>4800</v>
+      </c>
+      <c r="AF45" s="3">
         <v>2500</v>
       </c>
-      <c r="P45" s="3">
-        <v>3700</v>
-      </c>
-      <c r="Q45" s="3">
-        <v>5400</v>
-      </c>
-      <c r="R45" s="3">
+      <c r="AG45" s="3">
+        <v>3300</v>
+      </c>
+      <c r="AH45" s="3">
+        <v>4200</v>
+      </c>
+      <c r="AI45" s="3">
         <v>5100</v>
       </c>
-      <c r="S45" s="3">
-        <v>1700</v>
-      </c>
-      <c r="T45" s="3">
-        <v>3100</v>
-      </c>
-      <c r="U45" s="3">
-        <v>4900</v>
-      </c>
-      <c r="V45" s="3">
-        <v>5600</v>
-      </c>
-      <c r="W45" s="3">
-        <v>2800</v>
-      </c>
-      <c r="X45" s="3">
-        <v>4800</v>
-      </c>
-      <c r="Y45" s="3">
-        <v>5200</v>
-      </c>
-      <c r="Z45" s="3">
-        <v>5700</v>
-      </c>
-      <c r="AA45" s="3">
-        <v>1700</v>
-      </c>
-      <c r="AB45" s="3">
-        <v>3500</v>
-      </c>
-      <c r="AC45" s="3">
-        <v>4100</v>
-      </c>
-      <c r="AD45" s="3">
-        <v>4800</v>
-      </c>
-      <c r="AE45" s="3">
+      <c r="AJ45" s="3">
         <v>2500</v>
       </c>
-      <c r="AF45" s="3">
-        <v>3300</v>
-      </c>
-      <c r="AG45" s="3">
-        <v>4200</v>
-      </c>
-      <c r="AH45" s="3">
-        <v>5100</v>
-      </c>
-      <c r="AI45" s="3">
-        <v>2500</v>
-      </c>
     </row>
-    <row r="46" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>209900</v>
+      </c>
+      <c r="E46" s="3">
         <v>222000</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>202800</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>195000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>207300</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>226500</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>232000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>240200</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>251600</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>253600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>227700</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>209500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>169700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>167800</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>163000</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>155500</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>142600</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>140400</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>131000</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>127000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>133100</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>138100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>139400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>142200</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>139900</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>142900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>135000</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>133100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>132200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>134400</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>120900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>117000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>126400</v>
       </c>
     </row>
-    <row r="47" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
-        <v>0</v>
+        <v>2300</v>
       </c>
       <c r="E47" s="3">
-        <v>0</v>
+        <v>4100</v>
       </c>
       <c r="F47" s="3">
-        <v>0</v>
+        <v>4300</v>
       </c>
       <c r="G47" s="3">
-        <v>0</v>
+        <v>3700</v>
       </c>
       <c r="H47" s="3">
-        <v>0</v>
+        <v>5500</v>
       </c>
       <c r="I47" s="3">
-        <v>0</v>
+        <v>5100</v>
       </c>
       <c r="J47" s="3">
-        <v>0</v>
+        <v>4000</v>
       </c>
       <c r="K47" s="3">
         <v>0</v>
@@ -4321,210 +4426,219 @@
       <c r="AI47" s="3">
         <v>0</v>
       </c>
+      <c r="AJ47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>229500</v>
+      </c>
+      <c r="E48" s="3">
         <v>225800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>220600</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>216900</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>204200</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>201900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>196000</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>188900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>181000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>176400</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>172500</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>158400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>154200</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>153700</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>156200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>147100</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>136000</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>135800</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>135400</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>134900</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>133900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>133500</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>118600</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>117600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>119400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>121700</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>123800</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>125100</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>125900</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>123000</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>121500</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>120200</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>117900</v>
       </c>
     </row>
-    <row r="49" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>235500</v>
+      </c>
+      <c r="E49" s="3">
         <v>238600</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>220000</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>218200</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>148900</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>148800</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>150500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>152300</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>154100</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>155800</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>157600</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>145500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>146100</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>145500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>147100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>137400</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>138900</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>117800</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>119100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>120400</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>121600</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>122900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>124200</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>125400</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>126800</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>128200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>129600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>170200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>171600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>173000</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>174400</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>175900</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>177600</v>
       </c>
     </row>
-    <row r="50" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4624,8 +4738,11 @@
       <c r="AI50" s="3">
         <v>0</v>
       </c>
+      <c r="AJ50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4725,109 +4842,115 @@
       <c r="AI51" s="3">
         <v>0</v>
       </c>
+      <c r="AJ51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
-        <v>16300</v>
+        <v>12600</v>
       </c>
       <c r="E52" s="3">
-        <v>14500</v>
+        <v>12200</v>
       </c>
       <c r="F52" s="3">
-        <v>13900</v>
+        <v>10200</v>
       </c>
       <c r="G52" s="3">
-        <v>15000</v>
+        <v>10200</v>
       </c>
       <c r="H52" s="3">
-        <v>14800</v>
+        <v>9500</v>
       </c>
       <c r="I52" s="3">
-        <v>12000</v>
+        <v>9700</v>
       </c>
       <c r="J52" s="3">
+        <v>8000</v>
+      </c>
+      <c r="K52" s="3">
         <v>12500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12600</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>10500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>7800</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7900</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>8000</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>6200</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>5600</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5400</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>3800</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>4300</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4500</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>3400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3200</v>
-      </c>
-      <c r="AA52" s="3">
-        <v>3800</v>
       </c>
       <c r="AB52" s="3">
         <v>3800</v>
       </c>
       <c r="AC52" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AD52" s="3">
         <v>2600</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>2400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2200</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3000</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>1700</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="53" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -4927,109 +5050,115 @@
       <c r="AI53" s="3">
         <v>0</v>
       </c>
+      <c r="AJ53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>689700</v>
+      </c>
+      <c r="E54" s="3">
         <v>702700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>657900</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>644000</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>575300</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>592000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>590500</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>594000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>599300</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>596400</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>567300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>521100</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>477800</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>475000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>472600</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>446000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>423100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>399500</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>389300</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>386600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>393000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>399000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>385600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>388400</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>389800</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>396700</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>391000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>430700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>431900</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>433300</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>418600</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>414700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>422900</v>
       </c>
     </row>
-    <row r="55" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5065,8 +5194,9 @@
       <c r="AG55" s="3"/>
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
+      <c r="AJ55" s="3"/>
     </row>
-    <row r="56" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5102,109 +5232,113 @@
       <c r="AG56" s="3"/>
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
+      <c r="AJ56" s="3"/>
     </row>
-    <row r="57" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>51000</v>
+      </c>
+      <c r="E57" s="3">
         <v>47800</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>56400</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>42900</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>61200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>55600</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>53700</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>50600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>60900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>56400</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>66700</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>44000</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>43000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>38100</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>37300</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>31200</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>32700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>31100</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>34100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>26700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>29600</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>32000</v>
-      </c>
-      <c r="Y57" s="3">
-        <v>29300</v>
       </c>
       <c r="Z57" s="3">
         <v>29300</v>
       </c>
       <c r="AA57" s="3">
+        <v>29300</v>
+      </c>
+      <c r="AB57" s="3">
         <v>35500</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>36700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>33400</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>28100</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>26800</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>27900</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>29800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>21900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="58" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5215,7 +5349,7 @@
         <v>9900</v>
       </c>
       <c r="F58" s="3">
-        <v>9900</v>
+        <v>12400</v>
       </c>
       <c r="G58" s="3">
         <v>9900</v>
@@ -5290,426 +5424,441 @@
         <v>9900</v>
       </c>
       <c r="AE58" s="3">
+        <v>9900</v>
+      </c>
+      <c r="AF58" s="3">
         <v>9200</v>
       </c>
-      <c r="AF58" s="3">
+      <c r="AG58" s="3">
         <v>8600</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>8000</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>7400</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="59" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>40300</v>
+        <v>11100</v>
       </c>
       <c r="E59" s="3">
-        <v>37000</v>
+        <v>20100</v>
       </c>
       <c r="F59" s="3">
-        <v>26900</v>
+        <v>7300</v>
       </c>
       <c r="G59" s="3">
-        <v>23400</v>
+        <v>9200</v>
       </c>
       <c r="H59" s="3">
-        <v>28800</v>
+        <v>10900</v>
       </c>
       <c r="I59" s="3">
-        <v>27300</v>
+        <v>18100</v>
       </c>
       <c r="J59" s="3">
+        <v>10000</v>
+      </c>
+      <c r="K59" s="3">
         <v>24400</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>20100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>21900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>24900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>21600</v>
-      </c>
-      <c r="O59" s="3">
-        <v>18600</v>
       </c>
       <c r="P59" s="3">
         <v>18600</v>
       </c>
       <c r="Q59" s="3">
+        <v>18600</v>
+      </c>
+      <c r="R59" s="3">
         <v>23200</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>18000</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>16100</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>15700</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>18200</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>14600</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>14300</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>13800</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>16200</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>13900</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>13500</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>10000</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>17300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>10600</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>16400</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>8500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>17900</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>12700</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>18700</v>
       </c>
     </row>
-    <row r="60" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>92300</v>
+      </c>
+      <c r="E60" s="3">
         <v>98000</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>103300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>79700</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>94500</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>94300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>90900</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>84900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>90900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>88200</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>101500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>75500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>71500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>66500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>70500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>59000</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>58800</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>56700</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>62200</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>51300</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>53900</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>55700</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>55400</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>53100</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>58800</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>56500</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>60600</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>48500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>52500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>45000</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>55700</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>41900</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="61" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
-        <v>123800</v>
+        <v>103500</v>
       </c>
       <c r="E61" s="3">
+        <v>133700</v>
+      </c>
+      <c r="F61" s="3">
+        <v>98300</v>
+      </c>
+      <c r="G61" s="3">
+        <v>120900</v>
+      </c>
+      <c r="H61" s="3">
+        <v>59300</v>
+      </c>
+      <c r="I61" s="3">
+        <v>88000</v>
+      </c>
+      <c r="J61" s="3">
+        <v>110400</v>
+      </c>
+      <c r="K61" s="3">
+        <v>120700</v>
+      </c>
+      <c r="L61" s="3">
+        <v>130700</v>
+      </c>
+      <c r="M61" s="3">
+        <v>149200</v>
+      </c>
+      <c r="N61" s="3">
+        <v>115600</v>
+      </c>
+      <c r="O61" s="3">
+        <v>105900</v>
+      </c>
+      <c r="P61" s="3">
+        <v>73900</v>
+      </c>
+      <c r="Q61" s="3">
+        <v>85900</v>
+      </c>
+      <c r="R61" s="3">
         <v>88800</v>
       </c>
-      <c r="F61" s="3">
-        <v>109800</v>
-      </c>
-      <c r="G61" s="3">
+      <c r="S61" s="3">
+        <v>85800</v>
+      </c>
+      <c r="T61" s="3">
+        <v>65800</v>
+      </c>
+      <c r="U61" s="3">
+        <v>55800</v>
+      </c>
+      <c r="V61" s="3">
         <v>49800</v>
       </c>
-      <c r="H61" s="3">
-        <v>78400</v>
-      </c>
-      <c r="I61" s="3">
-        <v>101700</v>
-      </c>
-      <c r="J61" s="3">
-        <v>120700</v>
-      </c>
-      <c r="K61" s="3">
-        <v>130700</v>
-      </c>
-      <c r="L61" s="3">
-        <v>149200</v>
-      </c>
-      <c r="M61" s="3">
-        <v>115600</v>
-      </c>
-      <c r="N61" s="3">
-        <v>105900</v>
-      </c>
-      <c r="O61" s="3">
-        <v>73900</v>
-      </c>
-      <c r="P61" s="3">
-        <v>85900</v>
-      </c>
-      <c r="Q61" s="3">
-        <v>88800</v>
-      </c>
-      <c r="R61" s="3">
-        <v>85800</v>
-      </c>
-      <c r="S61" s="3">
-        <v>65800</v>
-      </c>
-      <c r="T61" s="3">
-        <v>55800</v>
-      </c>
-      <c r="U61" s="3">
-        <v>49800</v>
-      </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>57700</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>64700</v>
-      </c>
-      <c r="X61" s="3">
-        <v>74700</v>
       </c>
       <c r="Y61" s="3">
         <v>74700</v>
       </c>
       <c r="Z61" s="3">
+        <v>74700</v>
+      </c>
+      <c r="AA61" s="3">
         <v>80600</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>75800</v>
-      </c>
-      <c r="AB61" s="3">
-        <v>90800</v>
       </c>
       <c r="AC61" s="3">
         <v>90800</v>
       </c>
       <c r="AD61" s="3">
+        <v>90800</v>
+      </c>
+      <c r="AE61" s="3">
         <v>104200</v>
       </c>
-      <c r="AE61" s="3">
+      <c r="AF61" s="3">
         <v>102700</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>112200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>94600</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>105100</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>106900</v>
       </c>
     </row>
-    <row r="62" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
-        <v>59700</v>
+        <v>25200</v>
       </c>
       <c r="E62" s="3">
-        <v>59800</v>
+        <v>24100</v>
       </c>
       <c r="F62" s="3">
-        <v>60800</v>
+        <v>24300</v>
       </c>
       <c r="G62" s="3">
-        <v>48400</v>
+        <v>22400</v>
       </c>
       <c r="H62" s="3">
-        <v>48300</v>
+        <v>11000</v>
       </c>
       <c r="I62" s="3">
-        <v>47900</v>
+        <v>10800</v>
       </c>
       <c r="J62" s="3">
+        <v>11500</v>
+      </c>
+      <c r="K62" s="3">
         <v>47300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>46300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>45800</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>47600</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>48000</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>48100</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>47400</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>48000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>44200</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>43900</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>43600</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>43900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>45400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>45000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>45200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>37700</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>37200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>37400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>37100</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>37400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>34700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>51100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>51500</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>50500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>50400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="63" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5809,8 +5958,11 @@
       <c r="AI63" s="3">
         <v>0</v>
       </c>
+      <c r="AJ63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -5910,8 +6062,11 @@
       <c r="AI64" s="3">
         <v>0</v>
       </c>
+      <c r="AJ64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6011,109 +6166,115 @@
       <c r="AI65" s="3">
         <v>0</v>
       </c>
+      <c r="AJ65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>246300</v>
+      </c>
+      <c r="E66" s="3">
         <v>281500</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>251900</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>250300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>192600</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>221000</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>240500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>252800</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>267900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>283100</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>264700</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>229500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>193500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>199800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>207300</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>189100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>168400</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>156000</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>155800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>154400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>163600</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>175600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>167700</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>170900</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>172000</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>184400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>188700</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>187500</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>206200</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>208600</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>200800</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>197400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>210100</v>
       </c>
     </row>
-    <row r="67" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6149,8 +6310,9 @@
       <c r="AG67" s="3"/>
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
+      <c r="AJ67" s="3"/>
     </row>
-    <row r="68" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6250,8 +6412,11 @@
       <c r="AI68" s="3">
         <v>0</v>
       </c>
+      <c r="AJ68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6351,8 +6516,11 @@
       <c r="AI69" s="3">
         <v>0</v>
       </c>
+      <c r="AJ69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6452,8 +6620,11 @@
       <c r="AI70" s="3">
         <v>0</v>
       </c>
+      <c r="AJ70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6553,109 +6724,115 @@
       <c r="AI71" s="3">
         <v>0</v>
       </c>
+      <c r="AJ71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>410400</v>
+      </c>
+      <c r="E72" s="3">
         <v>390100</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>364500</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>354100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>342500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>322700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>302400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>294000</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>286200</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>271100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>254400</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>246800</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>239300</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>227900</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>213900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>207400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>202000</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>192300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>182900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>180700</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>178600</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>171800</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>164400</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>163100</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>161400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>156400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>147200</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>189400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>172200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>171700</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>165900</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>166200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>162600</v>
       </c>
     </row>
-    <row r="73" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6755,8 +6932,11 @@
       <c r="AI73" s="3">
         <v>0</v>
       </c>
+      <c r="AJ73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -6856,8 +7036,11 @@
       <c r="AI74" s="3">
         <v>0</v>
       </c>
+      <c r="AJ74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -6957,109 +7140,115 @@
       <c r="AI75" s="3">
         <v>0</v>
       </c>
+      <c r="AJ75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>443400</v>
+      </c>
+      <c r="E76" s="3">
         <v>421200</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>406000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>393800</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>382700</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>371000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>350000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>341200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>331400</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>313300</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>302600</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>291700</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>284300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>275200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>265200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>256900</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>254600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>243400</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>233500</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>232200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>229400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>223400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>217900</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>217500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>217800</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>212300</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>202200</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>243300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>225700</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>224700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>217800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>217300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>212800</v>
       </c>
     </row>
-    <row r="77" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7159,215 +7348,224 @@
       <c r="AI77" s="3">
         <v>0</v>
       </c>
+      <c r="AJ77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:35" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45564</v>
+      </c>
+      <c r="E80" s="2">
         <v>45473</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45382</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45291</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45200</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45109</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45018</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>44927</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44836</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44745</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44654</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44556</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44465</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44374</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44283</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44192</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44101</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44010</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>43919</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43828</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43737</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43646</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43555</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43464</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43373</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43282</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43191</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43100</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43009</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>42918</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42827</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42736</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="81" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>24100</v>
+      </c>
+      <c r="E81" s="3">
         <v>28900</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>13800</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>14900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>23200</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>23400</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>11600</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>10700</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>18000</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>19700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>10600</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>10200</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>14100</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>16600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>9100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>7900</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>12200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>11800</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>4800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4500</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>9300</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>9800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>3800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4100</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>7400</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>9100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>-37400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>17100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>5200</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>5800</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>4200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>3600</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="82" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7403,64 +7601,65 @@
       <c r="AG82" s="3"/>
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
+      <c r="AJ82" s="3"/>
     </row>
-    <row r="83" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
-        <v>9300</v>
+        <v>7400</v>
       </c>
       <c r="E83" s="3">
-        <v>9000</v>
+        <v>7100</v>
       </c>
       <c r="F83" s="3">
-        <v>8300</v>
+        <v>200</v>
       </c>
       <c r="G83" s="3">
-        <v>7400</v>
+        <v>7000</v>
       </c>
       <c r="H83" s="3">
-        <v>7100</v>
+        <v>6800</v>
       </c>
       <c r="I83" s="3">
-        <v>7100</v>
+        <v>6600</v>
       </c>
       <c r="J83" s="3">
+        <v>6300</v>
+      </c>
+      <c r="K83" s="3">
         <v>7000</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6800</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6600</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6300</v>
-      </c>
-      <c r="N83" s="3">
-        <v>6000</v>
       </c>
       <c r="O83" s="3">
         <v>6000</v>
       </c>
       <c r="P83" s="3">
-        <v>5900</v>
+        <v>6000</v>
       </c>
       <c r="Q83" s="3">
         <v>5900</v>
       </c>
       <c r="R83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="S83" s="3">
         <v>5700</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>5600</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>5500</v>
-      </c>
-      <c r="U83" s="3">
-        <v>5400</v>
       </c>
       <c r="V83" s="3">
         <v>5400</v>
@@ -7478,34 +7677,37 @@
         <v>5400</v>
       </c>
       <c r="AA83" s="3">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="AB83" s="3">
         <v>5500</v>
       </c>
       <c r="AC83" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AD83" s="3">
         <v>5600</v>
       </c>
-      <c r="AD83" s="3">
+      <c r="AE83" s="3">
         <v>5400</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>5500</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>5800</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>5400</v>
-      </c>
-      <c r="AH83" s="3">
-        <v>5200</v>
       </c>
       <c r="AI83" s="3">
         <v>5200</v>
       </c>
+      <c r="AJ83" s="3">
+        <v>5200</v>
+      </c>
     </row>
-    <row r="84" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7605,8 +7807,11 @@
       <c r="AI84" s="3">
         <v>0</v>
       </c>
+      <c r="AJ84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7706,8 +7911,11 @@
       <c r="AI85" s="3">
         <v>0</v>
       </c>
+      <c r="AJ85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -7807,8 +8015,11 @@
       <c r="AI86" s="3">
         <v>0</v>
       </c>
+      <c r="AJ86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -7908,8 +8119,11 @@
       <c r="AI87" s="3">
         <v>0</v>
       </c>
+      <c r="AJ87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8009,109 +8223,115 @@
       <c r="AI88" s="3">
         <v>0</v>
       </c>
+      <c r="AJ88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>41600</v>
+      </c>
+      <c r="E89" s="3">
         <v>17600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>41900</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>25000</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>57800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>34900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>32900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>25700</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>28200</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>-9400</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>4100</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-1400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>25300</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>14800</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>17200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>6500</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>18600</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>1600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>13900</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>17900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>17000</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>10100</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>17000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>6200</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>18000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>6800</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>12800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>10100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>16400</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>-11900</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>13900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>2900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>13600</v>
       </c>
     </row>
-    <row r="90" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8147,8 +8367,9 @@
       <c r="AG90" s="3"/>
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
+      <c r="AJ90" s="3"/>
     </row>
-    <row r="91" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
@@ -8156,100 +8377,103 @@
         <v>-10600</v>
       </c>
       <c r="E91" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="F91" s="3">
         <v>-11900</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11300</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-9000</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-7900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-16000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-11600</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-9000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-12800</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-8800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-4700</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-2200</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-7600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-5100</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-3300</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4900</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-9200</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5400</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-3800</v>
-      </c>
-      <c r="AE91" s="3">
-        <v>-6600</v>
       </c>
       <c r="AF91" s="3">
         <v>-6600</v>
       </c>
       <c r="AG91" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="AH91" s="3">
         <v>-5800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-5600</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="92" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8349,8 +8573,11 @@
       <c r="AI92" s="3">
         <v>0</v>
       </c>
+      <c r="AJ92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8450,109 +8677,115 @@
       <c r="AI93" s="3">
         <v>0</v>
       </c>
+      <c r="AJ93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-10500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-35800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-16100</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-86400</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-12100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-7800</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-9300</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-11600</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-8800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11500</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-31700</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-10100</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-5800</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-23400</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-15000</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-28200</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-4800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-9100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-3700</v>
-      </c>
-      <c r="AE94" s="3">
-        <v>-6500</v>
       </c>
       <c r="AF94" s="3">
         <v>-6500</v>
       </c>
       <c r="AG94" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="AH94" s="3">
         <v>-5700</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-5500</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="95" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8588,55 +8821,56 @@
       <c r="AG95" s="3"/>
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
+      <c r="AJ95" s="3"/>
     </row>
-    <row r="96" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
       <c r="D96" s="3">
-        <v>-3400</v>
+        <v>3800</v>
       </c>
       <c r="E96" s="3">
-        <v>-3400</v>
+        <v>3400</v>
       </c>
       <c r="F96" s="3">
-        <v>-3400</v>
+        <v>3400</v>
       </c>
       <c r="G96" s="3">
-        <v>-3400</v>
+        <v>3400</v>
       </c>
       <c r="H96" s="3">
-        <v>-3200</v>
+        <v>3400</v>
       </c>
       <c r="I96" s="3">
-        <v>-3200</v>
+        <v>3200</v>
       </c>
       <c r="J96" s="3">
-        <v>-2900</v>
+        <v>3200</v>
       </c>
       <c r="K96" s="3">
         <v>-2900</v>
       </c>
       <c r="L96" s="3">
-        <v>-3000</v>
+        <v>-2900</v>
       </c>
       <c r="M96" s="3">
         <v>-3000</v>
       </c>
       <c r="N96" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="O96" s="3">
         <v>-2700</v>
       </c>
-      <c r="O96" s="3">
+      <c r="P96" s="3">
         <v>-2800</v>
-      </c>
-      <c r="P96" s="3">
-        <v>-2600</v>
       </c>
       <c r="Q96" s="3">
         <v>-2600</v>
       </c>
       <c r="R96" s="3">
-        <v>-2500</v>
+        <v>-2600</v>
       </c>
       <c r="S96" s="3">
         <v>-2500</v>
@@ -8648,49 +8882,52 @@
         <v>-2500</v>
       </c>
       <c r="V96" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="W96" s="3">
         <v>-2400</v>
       </c>
       <c r="X96" s="3">
-        <v>-2500</v>
+        <v>-2400</v>
       </c>
       <c r="Y96" s="3">
         <v>-2500</v>
       </c>
       <c r="Z96" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="AA96" s="3">
         <v>-2400</v>
       </c>
       <c r="AB96" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AC96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AC96" s="3">
-        <v>0</v>
-      </c>
       <c r="AD96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-4500</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI96" s="3">
+      <c r="AJ96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -8790,8 +9027,11 @@
       <c r="AI97" s="3">
         <v>0</v>
       </c>
+      <c r="AJ97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -8891,8 +9131,11 @@
       <c r="AI98" s="3">
         <v>0</v>
       </c>
+      <c r="AJ98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -8992,132 +9235,138 @@
       <c r="AI99" s="3">
         <v>0</v>
       </c>
+      <c r="AJ99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-32500</v>
+      </c>
+      <c r="E100" s="3">
         <v>20000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-24400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>56200</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-41700</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-27600</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-22200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-11900</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-21400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>23400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>7600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>28100</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-17900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-10500</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>1200</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>13400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>8300</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>3500</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-11800</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-9400</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-13800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-4600</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-9800</v>
       </c>
-      <c r="Z100" s="3">
-        <v>0</v>
-      </c>
       <c r="AA100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AB100" s="3">
         <v>-17400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-4300</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-12800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-8900</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>14400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-9600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="101" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
-      <c r="D101" s="3">
-        <v>0</v>
-      </c>
-      <c r="E101" s="3">
-        <v>0</v>
-      </c>
-      <c r="F101" s="3">
-        <v>0</v>
-      </c>
-      <c r="G101" s="3">
-        <v>0</v>
-      </c>
-      <c r="H101" s="3">
-        <v>0</v>
-      </c>
-      <c r="I101" s="3">
-        <v>0</v>
-      </c>
-      <c r="J101" s="3">
-        <v>0</v>
+      <c r="D101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="F101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="H101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I101" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="J101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="K101" s="3">
         <v>0</v>
@@ -9194,105 +9443,111 @@
       <c r="AI101" s="3">
         <v>0</v>
       </c>
+      <c r="AJ101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:35" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E102" s="3">
         <v>1700</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-5200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>3900</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-500</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>2200</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-2100</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2500</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-19900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>16600</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-5000</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>4800</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-1400</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>200</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-3000</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>3200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-1600</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>1900</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>3300</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>3900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1000</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-4100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-8300</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-4600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HWKN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HWKN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
   <si>
     <t>HWKN</t>
   </si>
@@ -656,469 +656,481 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AJ102"/>
+  <dimension ref="A5:AK102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="11" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="35" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="36" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E7" s="2">
         <v>45564</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45473</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45382</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45291</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45200</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45109</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45018</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>44927</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44836</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44745</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44654</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44556</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44465</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44374</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44283</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44192</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44101</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44010</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>43919</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43828</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43737</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43646</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43555</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43464</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43373</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43282</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43191</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43100</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43009</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>42918</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42827</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42736</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="8" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>226200</v>
+      </c>
+      <c r="E8" s="3">
         <v>247000</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>255900</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>223000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>208500</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>236500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>251100</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>228100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>219200</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>241200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>246500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>223000</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>187100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>183300</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>181200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>163000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>142900</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>147800</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>143200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>132400</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>120400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>140000</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>147300</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>133100</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>128200</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>145300</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>149800</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>127000</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>118100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>125400</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>133700</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>118600</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>112400</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>121300</v>
       </c>
     </row>
-    <row r="9" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>177800</v>
+      </c>
+      <c r="E9" s="3">
         <v>186800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>191200</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>177500</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>166200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>182600</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>199100</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>192400</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>182900</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>194800</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>199800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>186700</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>153100</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>146000</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>142300</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>131200</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>114700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>115000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>112200</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>109800</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>98900</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>112000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>118500</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>112400</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>107100</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>119600</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>121300</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>109200</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>99200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>101300</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>107700</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>96700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>91400</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>94200</v>
       </c>
     </row>
-    <row r="10" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>48400</v>
+      </c>
+      <c r="E10" s="3">
         <v>60200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>64700</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>45500</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>42200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>53900</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>52000</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>35700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>36300</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>46400</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>46700</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>36300</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>34000</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>37300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>38900</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>31800</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>28200</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>32800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>31000</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>22600</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>21500</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>28000</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>28800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>20700</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>21100</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>25700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>28500</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>17800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>18900</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>24100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>26000</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>21900</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>21000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>27100</v>
       </c>
     </row>
-    <row r="11" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1155,8 +1167,9 @@
       <c r="AH11" s="3"/>
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
+      <c r="AK11" s="3"/>
     </row>
-    <row r="12" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1259,8 +1272,11 @@
       <c r="AJ12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1363,8 +1379,11 @@
       <c r="AJ13" s="3">
         <v>0</v>
       </c>
+      <c r="AK13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1374,11 +1393,11 @@
       <c r="E14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="F14" s="3">
+      <c r="F14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="G14" s="3">
         <v>-800</v>
-      </c>
-      <c r="G14" s="3">
-        <v>700</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1389,8 +1408,8 @@
       <c r="J14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K14" s="3">
-        <v>0</v>
+      <c r="K14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L14" s="3">
         <v>0</v>
@@ -1428,17 +1447,17 @@
       <c r="W14" s="3">
         <v>0</v>
       </c>
-      <c r="X14" s="3" t="s">
-        <v>8</v>
+      <c r="X14" s="3">
+        <v>0</v>
       </c>
       <c r="Y14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA14" s="3" t="s">
+      <c r="Z14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AA14" s="3">
+        <v>0</v>
       </c>
       <c r="AB14" s="3" t="s">
         <v>8</v>
@@ -1446,11 +1465,11 @@
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
+      <c r="AD14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE14" s="3">
         <v>39100</v>
-      </c>
-      <c r="AE14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
@@ -1467,34 +1486,37 @@
       <c r="AJ14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E15" s="3">
         <v>9900</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>9300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>9000</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>8300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>7400</v>
-      </c>
-      <c r="I15" s="3">
-        <v>7100</v>
       </c>
       <c r="J15" s="3">
         <v>7100</v>
       </c>
       <c r="K15" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="L15" s="3">
         <v>0</v>
@@ -1571,8 +1593,11 @@
       <c r="AJ15" s="3">
         <v>0</v>
       </c>
+      <c r="AK15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:36" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1606,216 +1631,223 @@
       <c r="AH16" s="3"/>
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
+      <c r="AK16" s="3"/>
     </row>
-    <row r="17" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>205100</v>
+      </c>
+      <c r="E17" s="3">
         <v>213300</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>216100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>203700</v>
       </c>
-      <c r="G17" s="3">
-        <v>189300</v>
-      </c>
       <c r="H17" s="3">
+        <v>190000</v>
+      </c>
+      <c r="I17" s="3">
         <v>203500</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>218600</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>209700</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>204000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>214700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>218700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>207800</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>172800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>163700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>159100</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>150100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>132400</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>131200</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>127200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>124700</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>113600</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>126900</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>133400</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>127300</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>121400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>134500</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>136300</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>163000</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>113400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>116100</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>123500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>111200</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>106400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>109100</v>
       </c>
     </row>
-    <row r="18" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E18" s="3">
         <v>33700</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>39800</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>19300</v>
       </c>
-      <c r="G18" s="3">
-        <v>19200</v>
-      </c>
       <c r="H18" s="3">
+        <v>18500</v>
+      </c>
+      <c r="I18" s="3">
         <v>33000</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>32500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>18500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>15200</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>26500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>27800</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>15200</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>14300</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>19600</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>22100</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>12900</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>10500</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>16600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>16000</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>7700</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>6800</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>13100</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>13900</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>5800</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>6800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>10800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>13500</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>-36000</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>4700</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>9300</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>10200</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>7400</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>6000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="19" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1852,88 +1884,89 @@
       <c r="AH19" s="3"/>
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
+      <c r="AK19" s="3"/>
     </row>
-    <row r="20" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-400</v>
+      </c>
+      <c r="E20" s="3">
         <v>-700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-200</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-500</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-900</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>300</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-400</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-700</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>100</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>200</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>300</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>100</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>500</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>300</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>400</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>-1000</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-400</v>
-      </c>
-      <c r="X20" s="3">
-        <v>-600</v>
       </c>
       <c r="Y20" s="3">
         <v>-600</v>
       </c>
       <c r="Z20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AA20" s="3">
         <v>-500</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-700</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>-900</v>
       </c>
       <c r="AD20" s="3">
         <v>-900</v>
@@ -1942,164 +1975,170 @@
         <v>-900</v>
       </c>
       <c r="AF20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AG20" s="3">
         <v>-800</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-700</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-600</v>
-      </c>
-      <c r="AI20" s="3">
-        <v>-700</v>
       </c>
       <c r="AJ20" s="3">
         <v>-700</v>
       </c>
+      <c r="AK20" s="3">
+        <v>-700</v>
+      </c>
     </row>
-    <row r="21" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>31600</v>
+      </c>
+      <c r="E21" s="3">
         <v>44300</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>49300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>28700</v>
       </c>
-      <c r="G21" s="3">
-        <v>28400</v>
-      </c>
       <c r="H21" s="3">
+        <v>27700</v>
+      </c>
+      <c r="I21" s="3">
         <v>40100</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>39900</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>26000</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>22700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>32900</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>33700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>21100</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>20400</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>25700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>28300</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>19000</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>16600</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>22500</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>21900</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>12200</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>11800</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>17900</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>18700</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>10700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>11000</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>15600</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>18000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>-31200</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>9300</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>14000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>15300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>12200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>10500</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="22" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="E22" s="3">
         <v>1400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1300</v>
-      </c>
-      <c r="F22" s="3">
-        <v>1200</v>
       </c>
       <c r="G22" s="3">
         <v>1200</v>
       </c>
       <c r="H22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="I22" s="3">
         <v>700</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1100</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1400</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1500</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>900</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>400</v>
-      </c>
-      <c r="O22" s="3">
-        <v>300</v>
       </c>
       <c r="P22" s="3">
         <v>300</v>
@@ -2108,25 +2147,25 @@
         <v>300</v>
       </c>
       <c r="R22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="S22" s="3">
         <v>400</v>
       </c>
       <c r="T22" s="3">
+        <v>400</v>
+      </c>
+      <c r="U22" s="3">
         <v>300</v>
       </c>
-      <c r="U22" s="3">
+      <c r="V22" s="3">
         <v>400</v>
-      </c>
-      <c r="V22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="W22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="X22" s="3">
-        <v>0</v>
+      <c r="X22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Y22" s="3">
         <v>0</v>
@@ -2164,216 +2203,225 @@
       <c r="AJ22" s="3">
         <v>0</v>
       </c>
+      <c r="AK22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>20300</v>
+      </c>
+      <c r="E23" s="3">
         <v>33000</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>38700</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>19300</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>18200</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>32000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>31700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>17500</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>14200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>24700</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>26200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>14400</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>14100</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>19500</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>22000</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>12700</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>10600</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>16600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>16000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>6800</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6300</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>12500</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>13300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>5300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5600</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>10100</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>12500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>-36900</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>3800</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>8500</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>9500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>6800</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>5400</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="24" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E24" s="3">
         <v>8900</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>9800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>5500</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>3300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8800</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8200</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5900</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>6700</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6500</v>
-      </c>
-      <c r="N24" s="3">
-        <v>3900</v>
       </c>
       <c r="O24" s="3">
         <v>3900</v>
       </c>
       <c r="P24" s="3">
+        <v>3900</v>
+      </c>
+      <c r="Q24" s="3">
         <v>5300</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>5400</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>3600</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>2700</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>4400</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>4200</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>2000</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>1800</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>3300</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3500</v>
-      </c>
-      <c r="Z24" s="3">
-        <v>1500</v>
       </c>
       <c r="AA24" s="3">
         <v>1500</v>
       </c>
       <c r="AB24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AC24" s="3">
         <v>2700</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3400</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>1200</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>-100</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>3300</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>2600</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1800</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="25" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2476,216 +2524,225 @@
       <c r="AJ25" s="3">
         <v>0</v>
       </c>
+      <c r="AK25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E26" s="3">
         <v>24100</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>28900</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>13800</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>14900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>23200</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>23400</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>11600</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>10700</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>18000</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>19700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>10600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10200</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>14100</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>16600</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>9100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>7900</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>12200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>11800</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>4800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4500</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>9300</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>9800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>3800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4100</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>7400</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>9100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>-38100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3900</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>5200</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>5800</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>4200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="27" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E27" s="3">
         <v>24100</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>28900</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>13800</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>14900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>23200</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>23400</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>11600</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>10700</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>18000</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>19700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>10600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10200</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>14100</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>16600</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>9100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>7900</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>12200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>11800</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>4800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4500</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>9300</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>9800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>3800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4100</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>7400</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>9100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>-38100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3900</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>5200</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>5800</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>4200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="28" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2788,8 +2845,11 @@
       <c r="AJ28" s="3">
         <v>0</v>
       </c>
+      <c r="AK28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2853,17 +2913,17 @@
       <c r="W29" s="3">
         <v>0</v>
       </c>
-      <c r="X29" s="3" t="s">
-        <v>8</v>
+      <c r="X29" s="3">
+        <v>0</v>
       </c>
       <c r="Y29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AA29" s="3" t="s">
+      <c r="Z29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AA29" s="3">
+        <v>0</v>
       </c>
       <c r="AB29" s="3" t="s">
         <v>8</v>
@@ -2871,14 +2931,14 @@
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
+      <c r="AD29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AE29" s="3">
         <v>700</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AF29" s="3">
         <v>13200</v>
-      </c>
-      <c r="AF29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -2892,8 +2952,11 @@
       <c r="AJ29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AK29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -2996,8 +3059,11 @@
       <c r="AJ30" s="3">
         <v>0</v>
       </c>
+      <c r="AK30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3100,88 +3166,91 @@
       <c r="AJ31" s="3">
         <v>0</v>
       </c>
+      <c r="AK31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>400</v>
+      </c>
+      <c r="E32" s="3">
         <v>700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>200</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>500</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>900</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>-300</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>400</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>-500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>700</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-100</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-200</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-300</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-100</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-500</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-300</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-400</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>1000</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>400</v>
-      </c>
-      <c r="X32" s="3">
-        <v>600</v>
       </c>
       <c r="Y32" s="3">
         <v>600</v>
       </c>
       <c r="Z32" s="3">
+        <v>600</v>
+      </c>
+      <c r="AA32" s="3">
         <v>500</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1200</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>700</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>900</v>
       </c>
       <c r="AD32" s="3">
         <v>900</v>
@@ -3190,126 +3259,132 @@
         <v>900</v>
       </c>
       <c r="AF32" s="3">
+        <v>900</v>
+      </c>
+      <c r="AG32" s="3">
         <v>800</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>700</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>600</v>
-      </c>
-      <c r="AI32" s="3">
-        <v>700</v>
       </c>
       <c r="AJ32" s="3">
         <v>700</v>
       </c>
+      <c r="AK32" s="3">
+        <v>700</v>
+      </c>
     </row>
-    <row r="33" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E33" s="3">
         <v>24100</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>28900</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>13800</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>14900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>23200</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>23400</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>11600</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>10700</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>18000</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>19700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>10600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>10200</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>14100</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>16600</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>9100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>7900</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>12200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>11800</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>4800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4500</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>9300</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>9800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>3800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4100</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>7400</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>9100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>-37400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>17100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>5200</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>5800</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>4200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="34" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3412,221 +3487,230 @@
       <c r="AJ34" s="3">
         <v>0</v>
       </c>
+      <c r="AK34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E35" s="3">
         <v>24100</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>28900</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>13800</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>14900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>23200</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>23400</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>11600</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>10700</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>18000</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>19700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>10600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>10200</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>14100</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>16600</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>9100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>7900</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>12200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>11800</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>4800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4500</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>9300</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>9800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>3800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4100</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>7400</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>9100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>-37400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>17100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>5200</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>5800</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>4200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="37" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E38" s="2">
         <v>45564</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45473</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45382</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45291</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45200</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45109</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45018</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>44927</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44836</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44745</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44654</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44556</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44465</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44374</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44283</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44192</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44101</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44010</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>43919</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43828</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43737</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43646</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43555</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43464</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43373</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43282</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43191</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43100</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43009</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>42918</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42827</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42736</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="39" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3663,8 +3747,9 @@
       <c r="AH39" s="3"/>
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
+      <c r="AK39" s="3"/>
     </row>
-    <row r="40" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3701,112 +3786,116 @@
       <c r="AH40" s="3"/>
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
+      <c r="AK40" s="3"/>
     </row>
-    <row r="41" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E41" s="3">
         <v>7500</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8900</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7200</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5700</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>11000</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7100</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7600</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>6100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>3900</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3500</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>23400</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6800</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>5200</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>8000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3200</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>4500</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4300</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>7300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4100</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>5600</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>9200</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4000</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5200</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>7600</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>3800</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>2800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>6900</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>8400</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>16700</v>
       </c>
     </row>
-    <row r="42" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -3909,112 +3998,118 @@
       <c r="AJ42" s="3">
         <v>0</v>
       </c>
+      <c r="AK42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>111500</v>
+      </c>
+      <c r="E43" s="3">
         <v>115200</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>126400</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>114500</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>113000</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>124800</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>138300</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>129300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>125500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>131400</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>138800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>122800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>102800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>90100</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>90900</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>90800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>77800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>74500</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>69500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>67400</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>56700</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>65400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>69000</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>64500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>61500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>66400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>67900</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>66200</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>57900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>60000</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>62800</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>58600</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>53300</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>52800</v>
       </c>
     </row>
-    <row r="44" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
@@ -4022,103 +4117,106 @@
         <v>81600</v>
       </c>
       <c r="E44" s="3">
+        <v>81600</v>
+      </c>
+      <c r="F44" s="3">
         <v>81200</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>74600</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>68800</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>68500</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>76900</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>88800</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>101600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>113100</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>105000</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>95000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>76200</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>70300</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>67900</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>63900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>64700</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>63200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>63400</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>54400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>57500</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>60800</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>58700</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>60500</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>67700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>67800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>66400</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>59700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>62700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>65900</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>65600</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>51200</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>50300</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="45" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4143,217 +4241,223 @@
       <c r="J45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K45" s="3">
+      <c r="K45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="L45" s="3">
         <v>7100</v>
       </c>
-      <c r="L45" s="3">
+      <c r="M45" s="3">
         <v>3200</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3900</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>6400</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>7000</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>2500</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3700</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>5400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5100</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>1700</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>4900</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5600</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>2800</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>4800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>5200</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>5700</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>1700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>3500</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4100</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4800</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>2500</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3300</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>4200</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>5100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="46" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>210400</v>
+      </c>
+      <c r="E46" s="3">
         <v>209900</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>222000</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>202800</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>195000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>207300</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>226500</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>232000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>240200</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>251600</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>253600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>227700</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>209500</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>169700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>167800</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>163000</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>155500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>142600</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>140400</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>131000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>127000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>133100</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>138100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>139400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>142200</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>139900</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>142900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>135000</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>133100</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>132200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>134400</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>120900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>117000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>126400</v>
       </c>
     </row>
-    <row r="47" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>3200</v>
+      </c>
+      <c r="E47" s="3">
         <v>2300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>4100</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3700</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>5500</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4000</v>
       </c>
-      <c r="K47" s="3">
-        <v>0</v>
-      </c>
       <c r="L47" s="3">
         <v>0</v>
       </c>
@@ -4429,216 +4533,225 @@
       <c r="AJ47" s="3">
         <v>0</v>
       </c>
+      <c r="AK47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>233500</v>
+      </c>
+      <c r="E48" s="3">
         <v>229500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>225800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>220600</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>216900</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>204200</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>201900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>196000</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>188900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>181000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>176400</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>172500</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>158400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>154200</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>153700</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>156200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>147100</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>136000</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>135800</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>135400</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>134900</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>133900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>133500</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>118600</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>117600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>119400</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>121700</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>123800</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>125100</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>125900</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>123000</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>121500</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>120200</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>117900</v>
       </c>
     </row>
-    <row r="49" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>247200</v>
+      </c>
+      <c r="E49" s="3">
         <v>235500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>238600</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>220000</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>218200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>148900</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>148800</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>150500</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>152300</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>154100</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>155800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>157600</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>145500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>146100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>145500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>147100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>137400</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>138900</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>117800</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>119100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>120400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>121600</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>122900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>124200</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>125400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>126800</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>128200</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>129600</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>170200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>171600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>173000</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>174400</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>175900</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>177600</v>
       </c>
     </row>
-    <row r="50" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4741,8 +4854,11 @@
       <c r="AJ50" s="3">
         <v>0</v>
       </c>
+      <c r="AK50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4845,112 +4961,118 @@
       <c r="AJ51" s="3">
         <v>0</v>
       </c>
+      <c r="AK51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>13000</v>
+      </c>
+      <c r="E52" s="3">
         <v>12600</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12200</v>
-      </c>
-      <c r="F52" s="3">
-        <v>10200</v>
       </c>
       <c r="G52" s="3">
         <v>10200</v>
       </c>
       <c r="H52" s="3">
+        <v>10200</v>
+      </c>
+      <c r="I52" s="3">
         <v>9500</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>9700</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>8000</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>12500</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12600</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>10500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>7800</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7900</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>8000</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>6200</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>5600</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5400</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>3800</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>4300</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4400</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4500</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3200</v>
-      </c>
-      <c r="AB52" s="3">
-        <v>3800</v>
       </c>
       <c r="AC52" s="3">
         <v>3800</v>
       </c>
       <c r="AD52" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AE52" s="3">
         <v>2600</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>2400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2200</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>3000</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>1700</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="53" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5053,112 +5175,118 @@
       <c r="AJ53" s="3">
         <v>0</v>
       </c>
+      <c r="AK53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>707200</v>
+      </c>
+      <c r="E54" s="3">
         <v>689700</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>702700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>657900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>644000</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>575300</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>592000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>590500</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>594000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>599300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>596400</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>567300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>521100</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>477800</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>475000</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>472600</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>446000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>423100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>399500</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>389300</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>386600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>393000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>399000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>385600</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>388400</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>389800</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>396700</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>391000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>430700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>431900</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>433300</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>418600</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>414700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>422900</v>
       </c>
     </row>
-    <row r="55" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5195,8 +5323,9 @@
       <c r="AH55" s="3"/>
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
+      <c r="AK55" s="3"/>
     </row>
-    <row r="56" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5233,112 +5362,116 @@
       <c r="AH56" s="3"/>
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
+      <c r="AK56" s="3"/>
     </row>
-    <row r="57" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>39900</v>
+      </c>
+      <c r="E57" s="3">
         <v>51000</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>47800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>56400</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>42900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>61200</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>55600</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>53700</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>50600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>60900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>56400</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>66700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>44000</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>43000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>38100</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>37300</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>31200</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>32700</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>31100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>34100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>26700</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>29600</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>32000</v>
-      </c>
-      <c r="Z57" s="3">
-        <v>29300</v>
       </c>
       <c r="AA57" s="3">
         <v>29300</v>
       </c>
       <c r="AB57" s="3">
+        <v>29300</v>
+      </c>
+      <c r="AC57" s="3">
         <v>35500</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>36700</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>33400</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>28100</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>26800</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>27900</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>29800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>21900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="58" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5349,10 +5482,10 @@
         <v>9900</v>
       </c>
       <c r="F58" s="3">
+        <v>9900</v>
+      </c>
+      <c r="G58" s="3">
         <v>12400</v>
-      </c>
-      <c r="G58" s="3">
-        <v>9900</v>
       </c>
       <c r="H58" s="3">
         <v>9900</v>
@@ -5427,438 +5560,453 @@
         <v>9900</v>
       </c>
       <c r="AF58" s="3">
+        <v>9900</v>
+      </c>
+      <c r="AG58" s="3">
         <v>9200</v>
       </c>
-      <c r="AG58" s="3">
+      <c r="AH58" s="3">
         <v>8600</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>8000</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>7400</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="59" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>8400</v>
+      </c>
+      <c r="E59" s="3">
         <v>11100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>20100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>7300</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>9200</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>10900</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>18100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10000</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>24400</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>20100</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>21900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>24900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>21600</v>
-      </c>
-      <c r="P59" s="3">
-        <v>18600</v>
       </c>
       <c r="Q59" s="3">
         <v>18600</v>
       </c>
       <c r="R59" s="3">
+        <v>18600</v>
+      </c>
+      <c r="S59" s="3">
         <v>23200</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>18000</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>16100</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>15700</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>18200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>14600</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>14300</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>13800</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>16200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>13900</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>13500</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>10000</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>17300</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>10600</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>16400</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>8500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>17900</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>12700</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>18700</v>
       </c>
     </row>
-    <row r="60" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>84300</v>
+      </c>
+      <c r="E60" s="3">
         <v>92300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>98000</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>103300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>79700</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>94500</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>94300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>90900</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>84900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>90900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>88200</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>101500</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>75500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>71500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>66500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>70500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>59000</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>58800</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>56700</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>62200</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>51300</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>53900</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>55700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>55400</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>53100</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>58800</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>56500</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>60600</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>48500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>52500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>45000</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>55700</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>41900</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="61" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>114500</v>
+      </c>
+      <c r="E61" s="3">
         <v>103500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>133700</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>98300</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>120900</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>59300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>88000</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>110400</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>120700</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>130700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>149200</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>115600</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>105900</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>73900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>85900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>88800</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>85800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>65800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>55800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>49800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>57700</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>64700</v>
-      </c>
-      <c r="Y61" s="3">
-        <v>74700</v>
       </c>
       <c r="Z61" s="3">
         <v>74700</v>
       </c>
       <c r="AA61" s="3">
+        <v>74700</v>
+      </c>
+      <c r="AB61" s="3">
         <v>80600</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>75800</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>90800</v>
       </c>
       <c r="AD61" s="3">
         <v>90800</v>
       </c>
       <c r="AE61" s="3">
+        <v>90800</v>
+      </c>
+      <c r="AF61" s="3">
         <v>104200</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>102700</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>112200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>94600</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>105100</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>106900</v>
       </c>
     </row>
-    <row r="62" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>26100</v>
+      </c>
+      <c r="E62" s="3">
         <v>25200</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>24100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>24300</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>22400</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>11000</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>10800</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11500</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>47300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>46300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>45800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>47600</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>48000</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>48100</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>47400</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>48000</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>44200</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>43900</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>43600</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>43900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>45400</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>45000</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>45200</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>37700</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>37200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>37400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>37100</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>37400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>34700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>51100</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>51500</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>50500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>50400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="63" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -5961,8 +6109,11 @@
       <c r="AJ63" s="3">
         <v>0</v>
       </c>
+      <c r="AK63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6065,8 +6216,11 @@
       <c r="AJ64" s="3">
         <v>0</v>
       </c>
+      <c r="AK64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6169,112 +6323,118 @@
       <c r="AJ65" s="3">
         <v>0</v>
       </c>
+      <c r="AK65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>250300</v>
+      </c>
+      <c r="E66" s="3">
         <v>246300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>281500</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>251900</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>250300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>192600</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>221000</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>240500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>252800</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>267900</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>283100</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>264700</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>229500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>193500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>199800</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>207300</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>189100</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>168400</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>156000</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>155800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>154400</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>163600</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>175600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>167700</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>170900</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>172000</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>184400</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>188700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>187500</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>206200</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>208600</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>200800</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>197400</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>210100</v>
       </c>
     </row>
-    <row r="67" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6311,8 +6471,9 @@
       <c r="AH67" s="3"/>
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
+      <c r="AK67" s="3"/>
     </row>
-    <row r="68" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6415,8 +6576,11 @@
       <c r="AJ68" s="3">
         <v>0</v>
       </c>
+      <c r="AK68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6519,8 +6683,11 @@
       <c r="AJ69" s="3">
         <v>0</v>
       </c>
+      <c r="AK69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6623,8 +6790,11 @@
       <c r="AJ70" s="3">
         <v>0</v>
       </c>
+      <c r="AK70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6727,112 +6897,118 @@
       <c r="AJ71" s="3">
         <v>0</v>
       </c>
+      <c r="AK71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>421700</v>
+      </c>
+      <c r="E72" s="3">
         <v>410400</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>390100</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>364500</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>354100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>342500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>322700</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>302400</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>294000</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>286200</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>271100</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>254400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>246800</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>239300</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>227900</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>213900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>207400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>202000</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>192300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>182900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>180700</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>178600</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>171800</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>164400</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>163100</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>161400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>156400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>147200</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>189400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>172200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>171700</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>165900</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>166200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>162600</v>
       </c>
     </row>
-    <row r="73" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -6935,8 +7111,11 @@
       <c r="AJ73" s="3">
         <v>0</v>
       </c>
+      <c r="AK73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7039,8 +7218,11 @@
       <c r="AJ74" s="3">
         <v>0</v>
       </c>
+      <c r="AK74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7143,112 +7325,118 @@
       <c r="AJ75" s="3">
         <v>0</v>
       </c>
+      <c r="AK75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>457000</v>
+      </c>
+      <c r="E76" s="3">
         <v>443400</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>421200</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>406000</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>393800</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>382700</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>371000</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>350000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>341200</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>331400</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>313300</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>302600</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>291700</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>284300</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>275200</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>265200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>256900</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>254600</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>243400</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>233500</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>232200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>229400</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>223400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>217900</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>217500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>217800</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>212300</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>202200</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>243300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>225700</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>224700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>217800</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>217300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>212800</v>
       </c>
     </row>
-    <row r="77" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7351,221 +7539,230 @@
       <c r="AJ77" s="3">
         <v>0</v>
       </c>
+      <c r="AK77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:36" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45655</v>
+      </c>
+      <c r="E80" s="2">
         <v>45564</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45473</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45382</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45291</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45200</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45109</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45018</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>44927</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44836</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44745</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44654</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44556</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44465</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44374</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44283</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44192</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44101</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44010</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>43919</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43828</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43737</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43646</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43555</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43464</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43373</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43282</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43191</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43100</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43009</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>42918</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42827</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42736</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="81" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E81" s="3">
         <v>24100</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>28900</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>13800</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>14900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>23200</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>23400</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>11600</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>10700</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>18000</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>19700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>10600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>10200</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>14100</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>16600</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>9100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>7900</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>12200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>11800</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>4800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4500</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>9300</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>9800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>3800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4100</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>7400</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>9100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>-37400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>17100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>5200</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>5800</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>4200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>3600</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="82" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7602,67 +7799,68 @@
       <c r="AH82" s="3"/>
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
+      <c r="AK82" s="3"/>
     </row>
-    <row r="83" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>8300</v>
+      </c>
+      <c r="E83" s="3">
         <v>7400</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7100</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>200</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7000</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>6800</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6600</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6300</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6300</v>
-      </c>
-      <c r="O83" s="3">
-        <v>6000</v>
       </c>
       <c r="P83" s="3">
         <v>6000</v>
       </c>
       <c r="Q83" s="3">
-        <v>5900</v>
+        <v>6000</v>
       </c>
       <c r="R83" s="3">
         <v>5900</v>
       </c>
       <c r="S83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="T83" s="3">
         <v>5700</v>
       </c>
-      <c r="T83" s="3">
+      <c r="U83" s="3">
         <v>5600</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>5500</v>
-      </c>
-      <c r="V83" s="3">
-        <v>5400</v>
       </c>
       <c r="W83" s="3">
         <v>5400</v>
@@ -7680,34 +7878,37 @@
         <v>5400</v>
       </c>
       <c r="AB83" s="3">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="AC83" s="3">
         <v>5500</v>
       </c>
       <c r="AD83" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AE83" s="3">
         <v>5600</v>
       </c>
-      <c r="AE83" s="3">
+      <c r="AF83" s="3">
         <v>5400</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>5500</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>5800</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>5400</v>
-      </c>
-      <c r="AI83" s="3">
-        <v>5200</v>
       </c>
       <c r="AJ83" s="3">
         <v>5200</v>
       </c>
+      <c r="AK83" s="3">
+        <v>5200</v>
+      </c>
     </row>
-    <row r="84" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -7810,8 +8011,11 @@
       <c r="AJ84" s="3">
         <v>0</v>
       </c>
+      <c r="AK84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -7914,8 +8118,11 @@
       <c r="AJ85" s="3">
         <v>0</v>
       </c>
+      <c r="AK85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8018,8 +8225,11 @@
       <c r="AJ86" s="3">
         <v>0</v>
       </c>
+      <c r="AK86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8122,8 +8332,11 @@
       <c r="AJ87" s="3">
         <v>0</v>
       </c>
+      <c r="AK87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8226,112 +8439,118 @@
       <c r="AJ88" s="3">
         <v>0</v>
       </c>
+      <c r="AK88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>21000</v>
+      </c>
+      <c r="E89" s="3">
         <v>41600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>17600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>41900</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>25000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>57800</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>34900</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>32900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>25700</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>28200</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>-9400</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>4100</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-1400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>25300</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>14800</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>17200</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>6500</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>18600</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>1600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>13900</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>17900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>17000</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>10100</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>17000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>6200</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>18000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>6800</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>12800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>10100</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>16400</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>-11900</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>13900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>2900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>13600</v>
       </c>
     </row>
-    <row r="90" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8368,112 +8587,116 @@
       <c r="AH90" s="3"/>
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
+      <c r="AK90" s="3"/>
     </row>
-    <row r="91" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
-        <v>-10600</v>
+        <v>-8700</v>
       </c>
       <c r="E91" s="3">
         <v>-10600</v>
       </c>
       <c r="F91" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="G91" s="3">
         <v>-11900</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11300</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-9000</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-7900</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-16000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11600</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-12800</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-8800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-4700</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-2200</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-7600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-5100</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-3300</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4800</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-5100</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5300</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-4900</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-9200</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5400</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3800</v>
-      </c>
-      <c r="AF91" s="3">
-        <v>-6600</v>
       </c>
       <c r="AG91" s="3">
         <v>-6600</v>
       </c>
       <c r="AH91" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="AI91" s="3">
         <v>-5800</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-5600</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="92" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8576,8 +8799,11 @@
       <c r="AJ92" s="3">
         <v>0</v>
       </c>
+      <c r="AK92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8680,112 +8906,118 @@
       <c r="AJ93" s="3">
         <v>0</v>
       </c>
+      <c r="AK93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-26500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-10500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-35800</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-16100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-86400</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-12100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-7800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-9300</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-11600</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-8800</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11500</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-31700</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-10100</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-5800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-2100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-23400</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-15000</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-28200</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-4800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-5100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5200</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-4800</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-9100</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5300</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-3700</v>
-      </c>
-      <c r="AF94" s="3">
-        <v>-6500</v>
       </c>
       <c r="AG94" s="3">
         <v>-6500</v>
       </c>
       <c r="AH94" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="AI94" s="3">
         <v>-5700</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-5500</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="95" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -8822,8 +9054,9 @@
       <c r="AH95" s="3"/>
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
+      <c r="AK95" s="3"/>
     </row>
-    <row r="96" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -8831,7 +9064,7 @@
         <v>3800</v>
       </c>
       <c r="E96" s="3">
-        <v>3400</v>
+        <v>3800</v>
       </c>
       <c r="F96" s="3">
         <v>3400</v>
@@ -8843,37 +9076,37 @@
         <v>3400</v>
       </c>
       <c r="I96" s="3">
-        <v>3200</v>
+        <v>3400</v>
       </c>
       <c r="J96" s="3">
         <v>3200</v>
       </c>
       <c r="K96" s="3">
-        <v>-2900</v>
+        <v>3200</v>
       </c>
       <c r="L96" s="3">
         <v>-2900</v>
       </c>
       <c r="M96" s="3">
-        <v>-3000</v>
+        <v>-2900</v>
       </c>
       <c r="N96" s="3">
         <v>-3000</v>
       </c>
       <c r="O96" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="P96" s="3">
         <v>-2700</v>
       </c>
-      <c r="P96" s="3">
+      <c r="Q96" s="3">
         <v>-2800</v>
-      </c>
-      <c r="Q96" s="3">
-        <v>-2600</v>
       </c>
       <c r="R96" s="3">
         <v>-2600</v>
       </c>
       <c r="S96" s="3">
-        <v>-2500</v>
+        <v>-2600</v>
       </c>
       <c r="T96" s="3">
         <v>-2500</v>
@@ -8885,49 +9118,52 @@
         <v>-2500</v>
       </c>
       <c r="W96" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="X96" s="3">
         <v>-2400</v>
       </c>
       <c r="Y96" s="3">
-        <v>-2500</v>
+        <v>-2400</v>
       </c>
       <c r="Z96" s="3">
         <v>-2500</v>
       </c>
       <c r="AA96" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="AB96" s="3">
         <v>-2400</v>
       </c>
       <c r="AC96" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AD96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AD96" s="3">
-        <v>0</v>
-      </c>
       <c r="AE96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-4500</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-4500</v>
       </c>
-      <c r="AJ96" s="3">
+      <c r="AK96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9030,8 +9266,11 @@
       <c r="AJ97" s="3">
         <v>0</v>
       </c>
+      <c r="AK97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9134,8 +9373,11 @@
       <c r="AJ98" s="3">
         <v>0</v>
       </c>
+      <c r="AK98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9238,112 +9480,118 @@
       <c r="AJ99" s="3">
         <v>0</v>
       </c>
+      <c r="AK99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>6200</v>
+      </c>
+      <c r="E100" s="3">
         <v>-32500</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>20000</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-24400</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>56200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-41700</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-27600</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-22200</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-11900</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-21400</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>23400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>7600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>28100</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-17900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-10500</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>1200</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>13400</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>8300</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>3500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-11800</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-9400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-13800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-4600</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-9800</v>
       </c>
-      <c r="AA100" s="3">
-        <v>0</v>
-      </c>
       <c r="AB100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AC100" s="3">
         <v>-17400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-4300</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-12800</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-8900</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>14400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-9600</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="101" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9368,8 +9616,8 @@
       <c r="J101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="K101" s="3">
-        <v>0</v>
+      <c r="K101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="L101" s="3">
         <v>0</v>
@@ -9446,108 +9694,114 @@
       <c r="AJ101" s="3">
         <v>0</v>
       </c>
+      <c r="AK101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:36" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>800</v>
+      </c>
+      <c r="E102" s="3">
         <v>-1400</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>1700</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-5200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>3900</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-500</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>2200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-2100</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-19900</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>16600</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>1600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2200</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-5000</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>4800</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-1400</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-3000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>3200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1600</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-3600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>1900</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3300</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>200</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>3900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>1000</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-4100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-8300</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-4600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HWKN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HWKN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="175" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
   <si>
     <t>HWKN</t>
   </si>
@@ -656,481 +656,494 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AK102"/>
+  <dimension ref="A5:AL102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="12" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="17" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="36" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="37" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E7" s="2">
         <v>45655</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45564</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45473</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45382</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45291</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45200</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45109</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45018</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>44927</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44836</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44745</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44654</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44556</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44465</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44374</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44283</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44192</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44101</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44010</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>43919</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43828</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43737</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43646</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43555</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43464</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43373</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43282</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43191</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43100</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43009</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>42918</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42827</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42736</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="8" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>245300</v>
+      </c>
+      <c r="E8" s="3">
         <v>226200</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>247000</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>255900</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>223000</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>208500</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>236500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>251100</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>228100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>219200</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>241200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>246500</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>223000</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>187100</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>183300</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>181200</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>163000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>142900</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>147800</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>143200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>132400</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>120400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>140000</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>147300</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>133100</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>128200</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>145300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>149800</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>127000</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>118100</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>125400</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>133700</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>118600</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>112400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>121300</v>
       </c>
     </row>
-    <row r="9" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>193100</v>
+      </c>
+      <c r="E9" s="3">
         <v>177800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>186800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>191200</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>177500</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>166200</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>182600</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>199100</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>192400</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>182900</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>194800</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>199800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>186700</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>153100</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>146000</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>142300</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>131200</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>114700</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>115000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>112200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>109800</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>98900</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>112000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>118500</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>112400</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>107100</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>119600</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>121300</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>109200</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>99200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>101300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>107700</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>96700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>91400</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>94200</v>
       </c>
     </row>
-    <row r="10" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>52200</v>
+      </c>
+      <c r="E10" s="3">
         <v>48400</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>60200</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>64700</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>45500</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>42200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>53900</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>52000</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>35700</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>36300</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>46400</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>46700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>36300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>34000</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>37300</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>38900</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>31800</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>28200</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>32800</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>31000</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>22600</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>21500</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>28000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>28800</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>20700</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>21100</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>25700</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>28500</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>17800</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>18900</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>24100</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>26000</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>21900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>21000</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>27100</v>
       </c>
     </row>
-    <row r="11" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1168,8 +1181,9 @@
       <c r="AI11" s="3"/>
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
+      <c r="AL11" s="3"/>
     </row>
-    <row r="12" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1275,8 +1289,11 @@
       <c r="AK12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1382,8 +1399,11 @@
       <c r="AK13" s="3">
         <v>0</v>
       </c>
+      <c r="AL13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1396,8 +1416,8 @@
       <c r="F14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="G14" s="3">
-        <v>-800</v>
+      <c r="G14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="H14" s="3" t="s">
         <v>8</v>
@@ -1411,8 +1431,8 @@
       <c r="K14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L14" s="3">
-        <v>0</v>
+      <c r="L14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M14" s="3">
         <v>0</v>
@@ -1450,17 +1470,17 @@
       <c r="X14" s="3">
         <v>0</v>
       </c>
-      <c r="Y14" s="3" t="s">
-        <v>8</v>
+      <c r="Y14" s="3">
+        <v>0</v>
       </c>
       <c r="Z14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB14" s="3" t="s">
+      <c r="AA14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
@@ -1468,11 +1488,11 @@
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
+      <c r="AE14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF14" s="3">
         <v>39100</v>
-      </c>
-      <c r="AF14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
@@ -1489,37 +1509,40 @@
       <c r="AK14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E15" s="3">
         <v>10100</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>9900</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>9300</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>9000</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>8300</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>7400</v>
-      </c>
-      <c r="J15" s="3">
-        <v>7100</v>
       </c>
       <c r="K15" s="3">
         <v>7100</v>
       </c>
       <c r="L15" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="M15" s="3">
         <v>0</v>
@@ -1596,8 +1619,11 @@
       <c r="AK15" s="3">
         <v>0</v>
       </c>
+      <c r="AL15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:37" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1632,222 +1658,229 @@
       <c r="AI16" s="3"/>
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
+      <c r="AL16" s="3"/>
     </row>
-    <row r="17" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>220700</v>
+      </c>
+      <c r="E17" s="3">
         <v>205100</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>213300</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>216100</v>
       </c>
-      <c r="G17" s="3">
-        <v>203700</v>
-      </c>
       <c r="H17" s="3">
+        <v>202900</v>
+      </c>
+      <c r="I17" s="3">
         <v>190000</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>203500</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>218600</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>209700</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>204000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>214700</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>218700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>207800</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>172800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>163700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>159100</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>150100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>132400</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>131200</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>127200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>124700</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>113600</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>126900</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>133400</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>127300</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>121400</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>134500</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>136300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>163000</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>113400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>116100</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>123500</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>111200</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>106400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>109100</v>
       </c>
     </row>
-    <row r="18" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>24600</v>
+      </c>
+      <c r="E18" s="3">
         <v>21100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>33700</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>39800</v>
       </c>
-      <c r="G18" s="3">
-        <v>19300</v>
-      </c>
       <c r="H18" s="3">
+        <v>20100</v>
+      </c>
+      <c r="I18" s="3">
         <v>18500</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>33000</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>32500</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>18500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>15200</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>26500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>27800</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>15200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>14300</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>19600</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>22100</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>12900</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>10500</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>16600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>16000</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>7700</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>6800</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>13100</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>13900</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>5800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>6800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>10800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>13500</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>-36000</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>4700</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>9300</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>10200</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>7400</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>6000</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="19" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1885,91 +1918,92 @@
       <c r="AI19" s="3"/>
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
+      <c r="AL19" s="3"/>
     </row>
-    <row r="20" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-400</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-200</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-500</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-900</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>300</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-400</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>500</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-700</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>100</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>200</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>300</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>500</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>400</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>-1000</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-400</v>
-      </c>
-      <c r="Y20" s="3">
-        <v>-600</v>
       </c>
       <c r="Z20" s="3">
         <v>-600</v>
       </c>
       <c r="AA20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AB20" s="3">
         <v>-500</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-700</v>
-      </c>
-      <c r="AD20" s="3">
-        <v>-900</v>
       </c>
       <c r="AE20" s="3">
         <v>-900</v>
@@ -1978,170 +2012,176 @@
         <v>-900</v>
       </c>
       <c r="AG20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AH20" s="3">
         <v>-800</v>
       </c>
-      <c r="AH20" s="3">
+      <c r="AI20" s="3">
         <v>-700</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-600</v>
-      </c>
-      <c r="AJ20" s="3">
-        <v>-700</v>
       </c>
       <c r="AK20" s="3">
         <v>-700</v>
       </c>
+      <c r="AL20" s="3">
+        <v>-700</v>
+      </c>
     </row>
-    <row r="21" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>34500</v>
+      </c>
+      <c r="E21" s="3">
         <v>31600</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>44300</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>49300</v>
       </c>
-      <c r="G21" s="3">
-        <v>28700</v>
-      </c>
       <c r="H21" s="3">
+        <v>29500</v>
+      </c>
+      <c r="I21" s="3">
         <v>27700</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>40100</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>39900</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>26000</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>22700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>32900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>33700</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>21100</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>20400</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>25700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>28300</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>19000</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>16600</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>22500</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>21900</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>12200</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>11800</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>17900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>18700</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>10700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>11000</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>15600</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>18000</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>-31200</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>9300</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>14000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>15300</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>12200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>10500</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="22" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>1500</v>
+      </c>
+      <c r="E22" s="3">
         <v>1200</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1400</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1300</v>
-      </c>
-      <c r="G22" s="3">
-        <v>1200</v>
       </c>
       <c r="H22" s="3">
         <v>1200</v>
       </c>
       <c r="I22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="J22" s="3">
         <v>700</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1100</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1400</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1500</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1400</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>900</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>400</v>
-      </c>
-      <c r="P22" s="3">
-        <v>300</v>
       </c>
       <c r="Q22" s="3">
         <v>300</v>
@@ -2150,25 +2190,25 @@
         <v>300</v>
       </c>
       <c r="S22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="T22" s="3">
         <v>400</v>
       </c>
       <c r="U22" s="3">
+        <v>400</v>
+      </c>
+      <c r="V22" s="3">
         <v>300</v>
       </c>
-      <c r="V22" s="3">
+      <c r="W22" s="3">
         <v>400</v>
-      </c>
-      <c r="W22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="X22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Y22" s="3">
-        <v>0</v>
+      <c r="Y22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Z22" s="3">
         <v>0</v>
@@ -2206,222 +2246,231 @@
       <c r="AK22" s="3">
         <v>0</v>
       </c>
+      <c r="AL22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>22400</v>
+      </c>
+      <c r="E23" s="3">
         <v>20300</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>33000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>38700</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>19300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>18200</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>32000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>31700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>17500</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>14200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>24700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>26200</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>14400</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>14100</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>19500</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>22000</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>12700</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>10600</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>16600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>16000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>6800</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6300</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>12500</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>13300</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>5300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>5600</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>10100</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>12500</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>-36900</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>3800</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>8500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>9500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>6800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>5400</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="24" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>6100</v>
+      </c>
+      <c r="E24" s="3">
         <v>5300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8900</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>9800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5500</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>3300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>8200</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5900</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3500</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>6700</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6500</v>
-      </c>
-      <c r="O24" s="3">
-        <v>3900</v>
       </c>
       <c r="P24" s="3">
         <v>3900</v>
       </c>
       <c r="Q24" s="3">
+        <v>3900</v>
+      </c>
+      <c r="R24" s="3">
         <v>5300</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>5400</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>3600</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>2700</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>4400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4200</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2000</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>1800</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>3300</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3500</v>
-      </c>
-      <c r="AA24" s="3">
-        <v>1500</v>
       </c>
       <c r="AB24" s="3">
         <v>1500</v>
       </c>
       <c r="AC24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AD24" s="3">
         <v>2700</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3400</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>1200</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>-100</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3300</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>3700</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>2600</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>1800</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="25" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2527,222 +2576,231 @@
       <c r="AK25" s="3">
         <v>0</v>
       </c>
+      <c r="AL25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E26" s="3">
         <v>15000</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>24100</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>28900</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>13800</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>14900</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>23200</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>23400</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>11600</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>10700</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>18000</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>19700</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>10200</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>14100</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>16600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>9100</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>7900</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>12200</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>11800</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>4800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4500</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>9300</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>9800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>3800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4100</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>7400</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>9100</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>-38100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>3900</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>5200</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>5800</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>3600</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="27" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E27" s="3">
         <v>15000</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>24100</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>28900</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>13800</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>14900</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>23200</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>23400</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>11600</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>10700</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>18000</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>19700</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>10200</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>14100</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>16600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>9100</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>7900</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>12200</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>11800</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>4800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4500</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>9300</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>9800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>3800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4100</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>7400</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>9100</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>-38100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>3900</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>5200</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>5800</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>3600</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="28" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2848,8 +2906,11 @@
       <c r="AK28" s="3">
         <v>0</v>
       </c>
+      <c r="AL28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2916,17 +2977,17 @@
       <c r="X29" s="3">
         <v>0</v>
       </c>
-      <c r="Y29" s="3" t="s">
-        <v>8</v>
+      <c r="Y29" s="3">
+        <v>0</v>
       </c>
       <c r="Z29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AA29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AB29" s="3" t="s">
+      <c r="AA29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
@@ -2934,14 +2995,14 @@
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
+      <c r="AE29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AF29" s="3">
         <v>700</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AG29" s="3">
         <v>13200</v>
-      </c>
-      <c r="AG29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH29" s="3" t="s">
         <v>8</v>
@@ -2955,8 +3016,11 @@
       <c r="AK29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AL29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3062,8 +3126,11 @@
       <c r="AK30" s="3">
         <v>0</v>
       </c>
+      <c r="AL30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3169,91 +3236,94 @@
       <c r="AK31" s="3">
         <v>0</v>
       </c>
+      <c r="AL31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E32" s="3">
         <v>400</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>200</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>500</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>900</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>-300</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>400</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-500</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>700</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-100</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-200</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-300</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-500</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-400</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>1000</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>400</v>
-      </c>
-      <c r="Y32" s="3">
-        <v>600</v>
       </c>
       <c r="Z32" s="3">
         <v>600</v>
       </c>
       <c r="AA32" s="3">
+        <v>600</v>
+      </c>
+      <c r="AB32" s="3">
         <v>500</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>1200</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>700</v>
-      </c>
-      <c r="AD32" s="3">
-        <v>900</v>
       </c>
       <c r="AE32" s="3">
         <v>900</v>
@@ -3262,129 +3332,135 @@
         <v>900</v>
       </c>
       <c r="AG32" s="3">
+        <v>900</v>
+      </c>
+      <c r="AH32" s="3">
         <v>800</v>
       </c>
-      <c r="AH32" s="3">
+      <c r="AI32" s="3">
         <v>700</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>600</v>
-      </c>
-      <c r="AJ32" s="3">
-        <v>700</v>
       </c>
       <c r="AK32" s="3">
         <v>700</v>
       </c>
+      <c r="AL32" s="3">
+        <v>700</v>
+      </c>
     </row>
-    <row r="33" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E33" s="3">
         <v>15000</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>24100</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>28900</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>13800</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>14900</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>23200</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>23400</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>11600</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>10700</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>18000</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>19700</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>10600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>10200</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>14100</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>16600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>9100</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>7900</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>12200</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>11800</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>4800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4500</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>9300</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>9800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>3800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>4100</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>7400</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>9100</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>-37400</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>17100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>5200</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>5800</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>3600</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="34" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3490,227 +3566,236 @@
       <c r="AK34" s="3">
         <v>0</v>
       </c>
+      <c r="AL34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E35" s="3">
         <v>15000</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>24100</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>28900</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>13800</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>14900</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>23200</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>23400</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>11600</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>10700</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>18000</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>19700</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>10600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>10200</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>14100</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>16600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>9100</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>7900</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>12200</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>11800</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>4800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4500</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>9300</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>9800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>3800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>4100</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>7400</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>9100</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>-37400</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>17100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>5200</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>5800</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>3600</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="37" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E38" s="2">
         <v>45655</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45564</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45473</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45382</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45291</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45200</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45109</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45018</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>44927</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44836</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44745</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44654</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44556</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44465</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44374</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44283</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44192</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44101</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44010</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>43919</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43828</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43737</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43646</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43555</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43464</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43373</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43282</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43191</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43100</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43009</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>42918</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42827</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42736</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="39" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3748,8 +3833,9 @@
       <c r="AI39" s="3"/>
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
+      <c r="AL39" s="3"/>
     </row>
-    <row r="40" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3787,115 +3873,119 @@
       <c r="AI40" s="3"/>
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
+      <c r="AL40" s="3"/>
     </row>
-    <row r="41" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>5100</v>
+      </c>
+      <c r="E41" s="3">
         <v>8300</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>7500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>8900</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>7200</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>5700</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>11000</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7100</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7600</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>6100</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>3900</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>6000</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>3500</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>23400</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6800</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>5200</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3000</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>8000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>3200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>4500</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4300</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>7300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4100</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>5600</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>9200</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4000</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5000</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>7600</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>3800</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>2800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>6900</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>8400</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>16700</v>
       </c>
     </row>
-    <row r="42" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4001,222 +4091,231 @@
       <c r="AK42" s="3">
         <v>0</v>
       </c>
+      <c r="AL42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>134700</v>
+      </c>
+      <c r="E43" s="3">
         <v>111500</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>115200</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>126400</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>114500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>113000</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>124800</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>138300</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>129300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>125500</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>131400</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>138800</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>122800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>102800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>90100</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>90900</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>90800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>77800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>74500</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>69500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>67400</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>56700</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>65400</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>69000</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>64500</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>61500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>66400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>67900</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>66200</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>57900</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>60000</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>62800</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>58600</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>53300</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>52800</v>
       </c>
     </row>
-    <row r="44" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
-        <v>81600</v>
+        <v>83500</v>
       </c>
       <c r="E44" s="3">
         <v>81600</v>
       </c>
       <c r="F44" s="3">
+        <v>81600</v>
+      </c>
+      <c r="G44" s="3">
         <v>81200</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>74600</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>68800</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>68500</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>76900</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>88800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>101600</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>113100</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>105000</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>95000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>76200</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>70300</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>67900</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>63900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>64700</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>63200</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>63400</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>54400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>57500</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>60800</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>58700</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>60500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>67700</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>67800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>66400</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>59700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>62700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>65900</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>65600</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>51200</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>50300</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="45" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4244,223 +4343,229 @@
       <c r="K45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L45" s="3">
+      <c r="L45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="M45" s="3">
         <v>7100</v>
       </c>
-      <c r="M45" s="3">
+      <c r="N45" s="3">
         <v>3200</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3900</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>6400</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>7000</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>2500</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3700</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>5400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5100</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>1700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3100</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>4900</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5600</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>2800</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>4800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>5200</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>5700</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>1700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>3500</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>4100</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>4800</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>2500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3300</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>5100</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="46" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>230700</v>
+      </c>
+      <c r="E46" s="3">
         <v>210400</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>209900</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>222000</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>202800</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>195000</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>207300</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>226500</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>232000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>240200</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>251600</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>253600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>227700</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>209500</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>169700</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>167800</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>163000</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>155500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>142600</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>140400</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>131000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>127000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>133100</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>138100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>139400</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>142200</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>139900</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>142900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>135000</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>133100</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>132200</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>134400</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>120900</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>117000</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>126400</v>
       </c>
     </row>
-    <row r="47" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>2400</v>
+      </c>
+      <c r="E47" s="3">
         <v>3200</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>2300</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>4100</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4300</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>3700</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>5500</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4000</v>
       </c>
-      <c r="L47" s="3">
-        <v>0</v>
-      </c>
       <c r="M47" s="3">
         <v>0</v>
       </c>
@@ -4536,222 +4641,231 @@
       <c r="AK47" s="3">
         <v>0</v>
       </c>
+      <c r="AL47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>238700</v>
+      </c>
+      <c r="E48" s="3">
         <v>233500</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>229500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>225800</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>220600</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>216900</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>204200</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>201900</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>196000</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>188900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>181000</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>176400</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>172500</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>158400</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>154200</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>153700</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>156200</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>147100</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>136000</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>135800</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>135400</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>134900</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>133900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>133500</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>118600</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>117600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>119400</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>121700</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>123800</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>125100</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>125900</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>123000</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>121500</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>120200</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>117900</v>
       </c>
     </row>
-    <row r="49" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>285500</v>
+      </c>
+      <c r="E49" s="3">
         <v>247200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>235500</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>238600</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>220000</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>218200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>148900</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>148800</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>150500</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>152300</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>154100</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>155800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>157600</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>145500</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>146100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>145500</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>147100</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>137400</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>138900</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>117800</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>119100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>120400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>121600</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>122900</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>124200</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>125400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>126800</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>128200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>129600</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>170200</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>171600</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>173000</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>174400</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>175900</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>177600</v>
       </c>
     </row>
-    <row r="50" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4857,8 +4971,11 @@
       <c r="AK50" s="3">
         <v>0</v>
       </c>
+      <c r="AL50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -4964,115 +5081,121 @@
       <c r="AK51" s="3">
         <v>0</v>
       </c>
+      <c r="AL51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>12500</v>
+      </c>
+      <c r="E52" s="3">
         <v>13000</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>12600</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12200</v>
-      </c>
-      <c r="G52" s="3">
-        <v>10200</v>
       </c>
       <c r="H52" s="3">
         <v>10200</v>
       </c>
       <c r="I52" s="3">
+        <v>10200</v>
+      </c>
+      <c r="J52" s="3">
         <v>9500</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>9700</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>8000</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>12500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12600</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>10500</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>9500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>7800</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7900</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>8000</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>6200</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6000</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>5600</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5400</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>3800</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>4300</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4500</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3400</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3200</v>
-      </c>
-      <c r="AC52" s="3">
-        <v>3800</v>
       </c>
       <c r="AD52" s="3">
         <v>3800</v>
       </c>
       <c r="AE52" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AF52" s="3">
         <v>2600</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>2400</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2200</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>3000</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>1700</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1600</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="53" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5178,115 +5301,121 @@
       <c r="AK53" s="3">
         <v>0</v>
       </c>
+      <c r="AL53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>769900</v>
+      </c>
+      <c r="E54" s="3">
         <v>707200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>689700</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>702700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>657900</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>644000</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>575300</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>592000</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>590500</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>594000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>599300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>596400</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>567300</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>521100</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>477800</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>475000</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>472600</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>446000</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>423100</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>399500</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>389300</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>386600</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>393000</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>399000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>385600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>388400</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>389800</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>396700</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>391000</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>430700</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>431900</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>433300</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>418600</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>414700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>422900</v>
       </c>
     </row>
-    <row r="55" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5324,8 +5453,9 @@
       <c r="AI55" s="3"/>
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
+      <c r="AL55" s="3"/>
     </row>
-    <row r="56" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5363,120 +5493,124 @@
       <c r="AI56" s="3"/>
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
+      <c r="AL56" s="3"/>
     </row>
-    <row r="57" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>61200</v>
+      </c>
+      <c r="E57" s="3">
         <v>39900</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>51000</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>47800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>56400</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>42900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>61200</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>55600</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>53700</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>50600</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>60900</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>56400</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>66700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>44000</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>43000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>38100</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>37300</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>31200</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>32700</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>31100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>34100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>26700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>29600</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>32000</v>
-      </c>
-      <c r="AA57" s="3">
-        <v>29300</v>
       </c>
       <c r="AB57" s="3">
         <v>29300</v>
       </c>
       <c r="AC57" s="3">
+        <v>29300</v>
+      </c>
+      <c r="AD57" s="3">
         <v>35500</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>36700</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>33400</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>28100</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>26800</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>27900</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>29800</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>21900</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="58" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>9900</v>
+        <v>12800</v>
       </c>
       <c r="E58" s="3">
         <v>9900</v>
@@ -5485,7 +5619,7 @@
         <v>9900</v>
       </c>
       <c r="G58" s="3">
-        <v>12400</v>
+        <v>9900</v>
       </c>
       <c r="H58" s="3">
         <v>9900</v>
@@ -5563,450 +5697,465 @@
         <v>9900</v>
       </c>
       <c r="AG58" s="3">
+        <v>9900</v>
+      </c>
+      <c r="AH58" s="3">
         <v>9200</v>
       </c>
-      <c r="AH58" s="3">
+      <c r="AI58" s="3">
         <v>8600</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>8000</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>7400</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="59" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>5800</v>
+      </c>
+      <c r="E59" s="3">
         <v>8400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>20100</v>
       </c>
-      <c r="G59" s="3">
-        <v>7300</v>
-      </c>
       <c r="H59" s="3">
+        <v>9800</v>
+      </c>
+      <c r="I59" s="3">
         <v>9200</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>10900</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>18100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>10000</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>24400</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>20100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>21900</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>24900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>21600</v>
-      </c>
-      <c r="Q59" s="3">
-        <v>18600</v>
       </c>
       <c r="R59" s="3">
         <v>18600</v>
       </c>
       <c r="S59" s="3">
+        <v>18600</v>
+      </c>
+      <c r="T59" s="3">
         <v>23200</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>18000</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>16100</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>15700</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>18200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>14600</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>14300</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>13800</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>16200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>13900</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>13500</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>10000</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>17300</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>10600</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>16400</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>8500</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>17900</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>12700</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>18700</v>
       </c>
     </row>
-    <row r="60" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>107100</v>
+      </c>
+      <c r="E60" s="3">
         <v>84300</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>92300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>98000</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>103300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>79700</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>94500</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>94300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>90900</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>84900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>90900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>88200</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>101500</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>75500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>71500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>66500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>70500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>59000</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>58800</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>56700</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>62200</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>51300</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>53900</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>55700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>55400</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>53100</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>58800</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>56500</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>60600</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>48500</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>52500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>45000</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>55700</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>41900</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="61" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>149800</v>
+      </c>
+      <c r="E61" s="3">
         <v>114500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>103500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>133700</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>98300</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>120900</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>59300</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>88000</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>110400</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>120700</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>130700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>149200</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>115600</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>105900</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>73900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>85900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>88800</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>85800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>65800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>55800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>49800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>57700</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>64700</v>
-      </c>
-      <c r="Z61" s="3">
-        <v>74700</v>
       </c>
       <c r="AA61" s="3">
         <v>74700</v>
       </c>
       <c r="AB61" s="3">
+        <v>74700</v>
+      </c>
+      <c r="AC61" s="3">
         <v>80600</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>75800</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>90800</v>
       </c>
       <c r="AE61" s="3">
         <v>90800</v>
       </c>
       <c r="AF61" s="3">
+        <v>90800</v>
+      </c>
+      <c r="AG61" s="3">
         <v>104200</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>102700</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>112200</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>94600</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>105100</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>106900</v>
       </c>
     </row>
-    <row r="62" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>27100</v>
+      </c>
+      <c r="E62" s="3">
         <v>26100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>25200</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>24100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>24300</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>22400</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>11000</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>10800</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>11500</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>47300</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>46300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>45800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>47600</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>48000</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>48100</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>47400</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>48000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>44200</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>43900</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>43600</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>43900</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>45400</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>45000</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>45200</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>37700</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>37200</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>37400</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>37100</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>37400</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>34700</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>51100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>51500</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>50500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>50400</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="63" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6112,8 +6261,11 @@
       <c r="AK63" s="3">
         <v>0</v>
       </c>
+      <c r="AL63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6219,8 +6371,11 @@
       <c r="AK64" s="3">
         <v>0</v>
       </c>
+      <c r="AL64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6326,115 +6481,121 @@
       <c r="AK65" s="3">
         <v>0</v>
       </c>
+      <c r="AL65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>309600</v>
+      </c>
+      <c r="E66" s="3">
         <v>250300</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>246300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>281500</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>251900</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>250300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>192600</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>221000</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>240500</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>252800</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>267900</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>283100</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>264700</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>229500</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>193500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>199800</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>207300</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>189100</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>168400</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>156000</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>155800</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>154400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>163600</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>175600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>167700</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>170900</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>172000</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>184400</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>188700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>187500</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>206200</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>208600</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>200800</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>197400</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>210100</v>
       </c>
     </row>
-    <row r="67" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6472,8 +6633,9 @@
       <c r="AI67" s="3"/>
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
+      <c r="AL67" s="3"/>
     </row>
-    <row r="68" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6579,8 +6741,11 @@
       <c r="AK68" s="3">
         <v>0</v>
       </c>
+      <c r="AL68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6686,8 +6851,11 @@
       <c r="AK69" s="3">
         <v>0</v>
       </c>
+      <c r="AL69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6793,8 +6961,11 @@
       <c r="AK70" s="3">
         <v>0</v>
       </c>
+      <c r="AL70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -6900,115 +7071,121 @@
       <c r="AK71" s="3">
         <v>0</v>
       </c>
+      <c r="AL71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>434300</v>
+      </c>
+      <c r="E72" s="3">
         <v>421700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>410400</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>390100</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>364500</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>354100</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>342500</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>322700</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>302400</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>294000</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>286200</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>271100</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>254400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>246800</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>239300</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>227900</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>213900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>207400</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>202000</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>192300</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>182900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>180700</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>178600</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>171800</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>164400</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>163100</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>161400</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>156400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>147200</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>189400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>172200</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>171700</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>165900</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>166200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>162600</v>
       </c>
     </row>
-    <row r="73" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7114,8 +7291,11 @@
       <c r="AK73" s="3">
         <v>0</v>
       </c>
+      <c r="AL73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7221,8 +7401,11 @@
       <c r="AK74" s="3">
         <v>0</v>
       </c>
+      <c r="AL74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7328,115 +7511,121 @@
       <c r="AK75" s="3">
         <v>0</v>
       </c>
+      <c r="AL75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>460300</v>
+      </c>
+      <c r="E76" s="3">
         <v>457000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>443400</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>421200</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>406000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>393800</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>382700</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>371000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>350000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>341200</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>331400</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>313300</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>302600</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>291700</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>284300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>275200</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>265200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>256900</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>254600</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>243400</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>233500</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>232200</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>229400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>223400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>217900</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>217500</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>217800</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>212300</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>202200</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>243300</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>225700</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>224700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>217800</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>217300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>212800</v>
       </c>
     </row>
-    <row r="77" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7542,227 +7731,236 @@
       <c r="AK77" s="3">
         <v>0</v>
       </c>
+      <c r="AL77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:37" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45746</v>
+      </c>
+      <c r="E80" s="2">
         <v>45655</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45564</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45473</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45382</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45291</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45200</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45109</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45018</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>44927</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44836</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44745</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44654</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44556</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44465</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44374</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44283</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44192</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44101</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44010</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>43919</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43828</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43737</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43646</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43555</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43464</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43373</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43282</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43191</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43100</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43009</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>42918</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42827</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42736</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="81" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>16300</v>
+      </c>
+      <c r="E81" s="3">
         <v>15000</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>24100</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>28900</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>13800</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>14900</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>23200</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>23400</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>11600</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>10700</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>18000</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>19700</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>10600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>10200</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>14100</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>16600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>9100</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>7900</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>12200</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>11800</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>4800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4500</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>9300</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>9800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>3800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>4100</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>7400</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>9100</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>-37400</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>17100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>5200</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>5800</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>4200</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>3600</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="82" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7800,70 +7998,71 @@
       <c r="AI82" s="3"/>
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
+      <c r="AL82" s="3"/>
     </row>
-    <row r="83" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>500</v>
+      </c>
+      <c r="E83" s="3">
         <v>8300</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>7400</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7100</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>200</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7000</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>6800</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6600</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6300</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6300</v>
-      </c>
-      <c r="P83" s="3">
-        <v>6000</v>
       </c>
       <c r="Q83" s="3">
         <v>6000</v>
       </c>
       <c r="R83" s="3">
-        <v>5900</v>
+        <v>6000</v>
       </c>
       <c r="S83" s="3">
         <v>5900</v>
       </c>
       <c r="T83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="U83" s="3">
         <v>5700</v>
       </c>
-      <c r="U83" s="3">
+      <c r="V83" s="3">
         <v>5600</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>5500</v>
-      </c>
-      <c r="W83" s="3">
-        <v>5400</v>
       </c>
       <c r="X83" s="3">
         <v>5400</v>
@@ -7881,34 +8080,37 @@
         <v>5400</v>
       </c>
       <c r="AC83" s="3">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="AD83" s="3">
         <v>5500</v>
       </c>
       <c r="AE83" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AF83" s="3">
         <v>5600</v>
       </c>
-      <c r="AF83" s="3">
+      <c r="AG83" s="3">
         <v>5400</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>5500</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>5800</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>5400</v>
-      </c>
-      <c r="AJ83" s="3">
-        <v>5200</v>
       </c>
       <c r="AK83" s="3">
         <v>5200</v>
       </c>
+      <c r="AL83" s="3">
+        <v>5200</v>
+      </c>
     </row>
-    <row r="84" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8014,8 +8216,11 @@
       <c r="AK84" s="3">
         <v>0</v>
       </c>
+      <c r="AL84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8121,8 +8326,11 @@
       <c r="AK85" s="3">
         <v>0</v>
       </c>
+      <c r="AL85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8228,8 +8436,11 @@
       <c r="AK86" s="3">
         <v>0</v>
       </c>
+      <c r="AL86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8335,8 +8546,11 @@
       <c r="AK87" s="3">
         <v>0</v>
       </c>
+      <c r="AL87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8442,115 +8656,121 @@
       <c r="AK88" s="3">
         <v>0</v>
       </c>
+      <c r="AL88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>30800</v>
+      </c>
+      <c r="E89" s="3">
         <v>21000</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>41600</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>17600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>41900</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>25000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>57800</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>34900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>32900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>25700</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>28200</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>-9400</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>4100</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>-1400</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>25300</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>14800</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>17200</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>6500</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>18600</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>1600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>13900</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>17900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>17000</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>10100</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>17000</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>6200</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>18000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>6800</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>12800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>10100</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>16400</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>-11900</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>13900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>2900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>13600</v>
       </c>
     </row>
-    <row r="90" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8588,115 +8808,119 @@
       <c r="AI90" s="3"/>
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
+      <c r="AL90" s="3"/>
     </row>
-    <row r="91" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-11100</v>
+      </c>
+      <c r="E91" s="3">
         <v>-8700</v>
-      </c>
-      <c r="E91" s="3">
-        <v>-10600</v>
       </c>
       <c r="F91" s="3">
         <v>-10600</v>
       </c>
       <c r="G91" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="H91" s="3">
         <v>-11900</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-11300</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-9000</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-7900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-16000</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11600</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-11600</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-12800</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-4700</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-2200</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-7600</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-5100</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-3300</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-4800</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4900</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-9200</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5400</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3800</v>
-      </c>
-      <c r="AG91" s="3">
-        <v>-6600</v>
       </c>
       <c r="AH91" s="3">
         <v>-6600</v>
       </c>
       <c r="AI91" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="AJ91" s="3">
         <v>-5800</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-5600</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="92" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -8802,8 +9026,11 @@
       <c r="AK92" s="3">
         <v>0</v>
       </c>
+      <c r="AL92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -8909,115 +9136,121 @@
       <c r="AK93" s="3">
         <v>0</v>
       </c>
+      <c r="AL93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-55100</v>
+      </c>
+      <c r="E94" s="3">
         <v>-26500</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-10500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-35800</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-16100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-86400</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-12100</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-7800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-9300</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-11600</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-8800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-11500</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-31700</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-10100</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-5800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-2100</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-23400</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-15000</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-28200</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-4800</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-5100</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-9100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5300</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-3700</v>
-      </c>
-      <c r="AG94" s="3">
-        <v>-6500</v>
       </c>
       <c r="AH94" s="3">
         <v>-6500</v>
       </c>
       <c r="AI94" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="AJ94" s="3">
         <v>-5700</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-5500</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="95" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9055,8 +9288,9 @@
       <c r="AI95" s="3"/>
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
+      <c r="AL95" s="3"/>
     </row>
-    <row r="96" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9067,7 +9301,7 @@
         <v>3800</v>
       </c>
       <c r="F96" s="3">
-        <v>3400</v>
+        <v>3800</v>
       </c>
       <c r="G96" s="3">
         <v>3400</v>
@@ -9079,37 +9313,37 @@
         <v>3400</v>
       </c>
       <c r="J96" s="3">
-        <v>3200</v>
+        <v>3400</v>
       </c>
       <c r="K96" s="3">
         <v>3200</v>
       </c>
       <c r="L96" s="3">
-        <v>-2900</v>
+        <v>3200</v>
       </c>
       <c r="M96" s="3">
         <v>-2900</v>
       </c>
       <c r="N96" s="3">
-        <v>-3000</v>
+        <v>-2900</v>
       </c>
       <c r="O96" s="3">
         <v>-3000</v>
       </c>
       <c r="P96" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="Q96" s="3">
         <v>-2700</v>
       </c>
-      <c r="Q96" s="3">
+      <c r="R96" s="3">
         <v>-2800</v>
-      </c>
-      <c r="R96" s="3">
-        <v>-2600</v>
       </c>
       <c r="S96" s="3">
         <v>-2600</v>
       </c>
       <c r="T96" s="3">
-        <v>-2500</v>
+        <v>-2600</v>
       </c>
       <c r="U96" s="3">
         <v>-2500</v>
@@ -9121,49 +9355,52 @@
         <v>-2500</v>
       </c>
       <c r="X96" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="Y96" s="3">
         <v>-2400</v>
       </c>
       <c r="Z96" s="3">
-        <v>-2500</v>
+        <v>-2400</v>
       </c>
       <c r="AA96" s="3">
         <v>-2500</v>
       </c>
       <c r="AB96" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="AC96" s="3">
         <v>-2400</v>
       </c>
       <c r="AD96" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AE96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AE96" s="3">
-        <v>0</v>
-      </c>
       <c r="AF96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AG96" s="3">
-        <v>0</v>
-      </c>
       <c r="AH96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-4500</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-4500</v>
       </c>
-      <c r="AK96" s="3">
+      <c r="AL96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9269,8 +9506,11 @@
       <c r="AK97" s="3">
         <v>0</v>
       </c>
+      <c r="AL97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9376,8 +9616,11 @@
       <c r="AK98" s="3">
         <v>0</v>
       </c>
+      <c r="AL98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9483,115 +9726,121 @@
       <c r="AK99" s="3">
         <v>0</v>
       </c>
+      <c r="AL99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>21100</v>
+      </c>
+      <c r="E100" s="3">
         <v>6200</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-32500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>20000</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>-24400</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>56200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-41700</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-27600</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-22200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-11900</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-21400</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>23400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>7600</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>28100</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-17900</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-10500</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>1200</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>13400</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>8300</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>3500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>-11800</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-9400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-13800</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-4600</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-9800</v>
       </c>
-      <c r="AB100" s="3">
-        <v>0</v>
-      </c>
       <c r="AC100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AD100" s="3">
         <v>-17400</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-4300</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-12800</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-8900</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>14400</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-9600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="101" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9619,8 +9868,8 @@
       <c r="K101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="L101" s="3">
-        <v>0</v>
+      <c r="L101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="M101" s="3">
         <v>0</v>
@@ -9697,111 +9946,117 @@
       <c r="AK101" s="3">
         <v>0</v>
       </c>
+      <c r="AL101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:37" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-3200</v>
+      </c>
+      <c r="E102" s="3">
         <v>800</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-1400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>1700</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1400</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-5200</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>3900</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>-500</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>2200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-2100</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>2500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>-19900</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>16600</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>1600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2200</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-5000</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>4800</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>-1400</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-3000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>3200</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1600</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>1900</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3300</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>200</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>3900</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>1000</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-4100</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-8300</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-4600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HWKN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HWKN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="180" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="184" uniqueCount="92">
   <si>
     <t>HWKN</t>
   </si>
@@ -656,494 +656,507 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AL102"/>
+  <dimension ref="A5:AM102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="13" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="18" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="20" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="32" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="37" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="19" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="21" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="23" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="25" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="27" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="29" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="31" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="33" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="38" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:39" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:39" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>45837</v>
+      </c>
+      <c r="E7" s="2">
         <v>45746</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45655</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45564</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45473</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45382</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45291</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45200</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45109</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45018</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>44927</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>44836</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44745</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44654</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44556</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44465</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44374</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44283</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44192</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44101</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44010</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>43919</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>43828</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43737</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43646</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43555</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43464</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43373</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43282</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43191</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43100</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43009</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>42918</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>42827</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42736</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="8" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>293300</v>
+      </c>
+      <c r="E8" s="3">
         <v>245300</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>226200</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>247000</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>255900</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>223000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>208500</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>236500</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>251100</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>228100</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>219200</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>241200</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>246500</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>223000</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>187100</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>183300</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>181200</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>163000</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>142900</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>147800</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>143200</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>132400</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>120400</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>140000</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>147300</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>133100</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>128200</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>145300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>149800</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>127000</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>118100</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>125400</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>133700</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>118600</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>112400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>121300</v>
       </c>
     </row>
-    <row r="9" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>220900</v>
+      </c>
+      <c r="E9" s="3">
         <v>193100</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>177800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>186800</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>191200</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>177500</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>166200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>182600</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>199100</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>192400</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>182900</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>194800</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>199800</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>186700</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>153100</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>146000</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>142300</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>131200</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>114700</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>115000</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>112200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>109800</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>98900</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>112000</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>118500</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>112400</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>107100</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>119600</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>121300</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>109200</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>99200</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>101300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>107700</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>96700</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>91400</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>94200</v>
       </c>
     </row>
-    <row r="10" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>72400</v>
+      </c>
+      <c r="E10" s="3">
         <v>52200</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>48400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>60200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>64700</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>45500</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>42200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>53900</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>52000</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>35700</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>36300</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>46400</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>46700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>36300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>34000</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>37300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>38900</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>31800</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>28200</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>32800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>31000</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>22600</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>21500</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>28000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>28800</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>20700</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>21100</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>25700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>28500</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>17800</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>18900</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>24100</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>26000</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>21900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>21000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>27100</v>
       </c>
     </row>
-    <row r="11" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1182,8 +1195,9 @@
       <c r="AJ11" s="3"/>
       <c r="AK11" s="3"/>
       <c r="AL11" s="3"/>
+      <c r="AM11" s="3"/>
     </row>
-    <row r="12" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1292,8 +1306,11 @@
       <c r="AL12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1402,8 +1419,11 @@
       <c r="AL13" s="3">
         <v>0</v>
       </c>
+      <c r="AM13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
@@ -1434,8 +1454,8 @@
       <c r="L14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M14" s="3">
-        <v>0</v>
+      <c r="M14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N14" s="3">
         <v>0</v>
@@ -1473,17 +1493,17 @@
       <c r="Y14" s="3">
         <v>0</v>
       </c>
-      <c r="Z14" s="3" t="s">
-        <v>8</v>
+      <c r="Z14" s="3">
+        <v>0</v>
       </c>
       <c r="AA14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC14" s="3" t="s">
+      <c r="AB14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
@@ -1491,11 +1511,11 @@
       <c r="AE14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF14" s="3">
+      <c r="AF14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG14" s="3">
         <v>39100</v>
-      </c>
-      <c r="AG14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AH14" s="3" t="s">
         <v>8</v>
@@ -1512,40 +1532,43 @@
       <c r="AL14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:39" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>12300</v>
+      </c>
+      <c r="E15" s="3">
         <v>10600</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>10100</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>9900</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>9300</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>9000</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>8300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>7400</v>
-      </c>
-      <c r="K15" s="3">
-        <v>7100</v>
       </c>
       <c r="L15" s="3">
         <v>7100</v>
       </c>
       <c r="M15" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="N15" s="3">
         <v>0</v>
@@ -1622,8 +1645,11 @@
       <c r="AL15" s="3">
         <v>0</v>
       </c>
+      <c r="AM15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:38" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:39" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1659,228 +1685,235 @@
       <c r="AJ16" s="3"/>
       <c r="AK16" s="3"/>
       <c r="AL16" s="3"/>
+      <c r="AM16" s="3"/>
     </row>
-    <row r="17" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>251900</v>
+      </c>
+      <c r="E17" s="3">
         <v>220700</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>205100</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>213300</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>216100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>202900</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>190000</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>203500</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>218600</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>209700</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>204000</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>214700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>218700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>207800</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>172800</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>163700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>159100</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>150100</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>132400</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>131200</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>127200</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>124700</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>113600</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>126900</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>133400</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>127300</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>121400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>134500</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>136300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>163000</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>113400</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>116100</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>123500</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>111200</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>106400</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>109100</v>
       </c>
     </row>
-    <row r="18" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>41300</v>
+      </c>
+      <c r="E18" s="3">
         <v>24600</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>21100</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>33700</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>39800</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>20100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>18500</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>33000</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>32500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>18500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>15200</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>26500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>27800</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>15200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>14300</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>19600</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>22100</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>12900</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>10500</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>16600</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>16000</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>7700</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>6800</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>13100</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>13900</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>5800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>6800</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>10800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>13500</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>-36000</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>4700</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>9300</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>10200</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>7400</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>6000</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="19" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1919,94 +1952,95 @@
       <c r="AJ19" s="3"/>
       <c r="AK19" s="3"/>
       <c r="AL19" s="3"/>
+      <c r="AM19" s="3"/>
     </row>
-    <row r="20" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="E20" s="3">
         <v>600</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-400</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-700</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-200</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-500</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-900</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>300</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-300</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-400</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>500</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-500</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-700</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-400</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>100</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>200</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>300</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>500</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>400</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>-1000</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>-400</v>
-      </c>
-      <c r="Z20" s="3">
-        <v>-600</v>
       </c>
       <c r="AA20" s="3">
         <v>-600</v>
       </c>
       <c r="AB20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AC20" s="3">
         <v>-500</v>
       </c>
-      <c r="AC20" s="3">
+      <c r="AD20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AD20" s="3">
+      <c r="AE20" s="3">
         <v>-700</v>
-      </c>
-      <c r="AE20" s="3">
-        <v>-900</v>
       </c>
       <c r="AF20" s="3">
         <v>-900</v>
@@ -2015,176 +2049,182 @@
         <v>-900</v>
       </c>
       <c r="AH20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AI20" s="3">
         <v>-800</v>
       </c>
-      <c r="AI20" s="3">
+      <c r="AJ20" s="3">
         <v>-700</v>
       </c>
-      <c r="AJ20" s="3">
+      <c r="AK20" s="3">
         <v>-600</v>
-      </c>
-      <c r="AK20" s="3">
-        <v>-700</v>
       </c>
       <c r="AL20" s="3">
         <v>-700</v>
       </c>
+      <c r="AM20" s="3">
+        <v>-700</v>
+      </c>
     </row>
-    <row r="21" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>54600</v>
+      </c>
+      <c r="E21" s="3">
         <v>34500</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>31600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>44300</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>49300</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>29500</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>27700</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>40100</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>39900</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>26000</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>22700</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>32900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>33700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>21100</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>20400</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>25700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>28300</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>19000</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>16600</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>22500</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>21900</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>12200</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>11800</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>17900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>18700</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>10700</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>11000</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>15600</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>18000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>-31200</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>9300</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>14000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>15300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>12200</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>10500</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="22" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3300</v>
+      </c>
+      <c r="E22" s="3">
         <v>1500</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>1200</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1400</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1300</v>
-      </c>
-      <c r="H22" s="3">
-        <v>1200</v>
       </c>
       <c r="I22" s="3">
         <v>1200</v>
       </c>
       <c r="J22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="K22" s="3">
         <v>700</v>
       </c>
-      <c r="K22" s="3">
+      <c r="L22" s="3">
         <v>1100</v>
       </c>
-      <c r="L22" s="3">
+      <c r="M22" s="3">
         <v>1400</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1500</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>900</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>400</v>
-      </c>
-      <c r="Q22" s="3">
-        <v>300</v>
       </c>
       <c r="R22" s="3">
         <v>300</v>
@@ -2193,25 +2233,25 @@
         <v>300</v>
       </c>
       <c r="T22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="U22" s="3">
         <v>400</v>
       </c>
       <c r="V22" s="3">
+        <v>400</v>
+      </c>
+      <c r="W22" s="3">
         <v>300</v>
       </c>
-      <c r="W22" s="3">
+      <c r="X22" s="3">
         <v>400</v>
-      </c>
-      <c r="X22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="Y22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="Z22" s="3">
-        <v>0</v>
+      <c r="Z22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AA22" s="3">
         <v>0</v>
@@ -2249,228 +2289,237 @@
       <c r="AL22" s="3">
         <v>0</v>
       </c>
+      <c r="AM22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>39000</v>
+      </c>
+      <c r="E23" s="3">
         <v>22400</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>20300</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>33000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>38700</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>19300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>18200</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>32000</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>31700</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>17500</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>14200</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>24700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>26200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>14400</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>14100</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>19500</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>22000</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>12700</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>10600</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>16600</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>16000</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>6800</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>6300</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>12500</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>13300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>5300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>5600</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>10100</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>12500</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>-36900</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>3800</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>8500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>9500</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>6800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>5400</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="24" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E24" s="3">
         <v>6100</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>5300</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>8900</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>9800</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5500</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>3300</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>8800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>8200</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>5900</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>3500</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>6700</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>6500</v>
-      </c>
-      <c r="P24" s="3">
-        <v>3900</v>
       </c>
       <c r="Q24" s="3">
         <v>3900</v>
       </c>
       <c r="R24" s="3">
+        <v>3900</v>
+      </c>
+      <c r="S24" s="3">
         <v>5300</v>
       </c>
-      <c r="S24" s="3">
+      <c r="T24" s="3">
         <v>5400</v>
       </c>
-      <c r="T24" s="3">
+      <c r="U24" s="3">
         <v>3600</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>2700</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>4400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>4200</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2000</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>1800</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>3300</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>3500</v>
-      </c>
-      <c r="AB24" s="3">
-        <v>1500</v>
       </c>
       <c r="AC24" s="3">
         <v>1500</v>
       </c>
       <c r="AD24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AE24" s="3">
         <v>2700</v>
       </c>
-      <c r="AE24" s="3">
+      <c r="AF24" s="3">
         <v>3400</v>
       </c>
-      <c r="AF24" s="3">
+      <c r="AG24" s="3">
         <v>1200</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>-100</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>3300</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>3700</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>2600</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>1800</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="25" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2579,228 +2628,237 @@
       <c r="AL25" s="3">
         <v>0</v>
       </c>
+      <c r="AM25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E26" s="3">
         <v>16300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>15000</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>24100</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>28900</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>13800</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>14900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>23200</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>23400</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>11600</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>10700</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>18000</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>19700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>10600</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>10200</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>14100</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>16600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>9100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>7900</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>12200</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>11800</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>4800</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>4500</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>9300</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>9800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>3800</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>4100</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>7400</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>9100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>-38100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>3900</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>5200</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>4200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>3600</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="27" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E27" s="3">
         <v>16300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>15000</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>24100</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>28900</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>13800</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>14900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>23200</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>23400</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>11600</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>10700</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>18000</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>19700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>10600</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>10200</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>14100</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>16600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>9100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>7900</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>12200</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>11800</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>4800</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>4500</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>9300</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>9800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>3800</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>4100</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>7400</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>9100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>-38100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>3900</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>5200</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>4200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>3600</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="28" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -2909,8 +2967,11 @@
       <c r="AL28" s="3">
         <v>0</v>
       </c>
+      <c r="AM28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -2980,17 +3041,17 @@
       <c r="Y29" s="3">
         <v>0</v>
       </c>
-      <c r="Z29" s="3" t="s">
-        <v>8</v>
+      <c r="Z29" s="3">
+        <v>0</v>
       </c>
       <c r="AA29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AC29" s="3" t="s">
+      <c r="AB29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
@@ -2998,14 +3059,14 @@
       <c r="AE29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AF29" s="3">
+      <c r="AF29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AG29" s="3">
         <v>700</v>
       </c>
-      <c r="AG29" s="3">
+      <c r="AH29" s="3">
         <v>13200</v>
-      </c>
-      <c r="AH29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AI29" s="3" t="s">
         <v>8</v>
@@ -3019,8 +3080,11 @@
       <c r="AL29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AM29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3129,8 +3193,11 @@
       <c r="AL30" s="3">
         <v>0</v>
       </c>
+      <c r="AM30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3239,94 +3306,97 @@
       <c r="AL31" s="3">
         <v>0</v>
       </c>
+      <c r="AM31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>900</v>
+      </c>
+      <c r="E32" s="3">
         <v>-600</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>400</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>700</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>200</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>500</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>900</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>-300</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>300</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>400</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-500</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>500</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>700</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>400</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>-100</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>-200</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-300</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-500</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-400</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>1000</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>400</v>
-      </c>
-      <c r="Z32" s="3">
-        <v>600</v>
       </c>
       <c r="AA32" s="3">
         <v>600</v>
       </c>
       <c r="AB32" s="3">
+        <v>600</v>
+      </c>
+      <c r="AC32" s="3">
         <v>500</v>
       </c>
-      <c r="AC32" s="3">
+      <c r="AD32" s="3">
         <v>1200</v>
       </c>
-      <c r="AD32" s="3">
+      <c r="AE32" s="3">
         <v>700</v>
-      </c>
-      <c r="AE32" s="3">
-        <v>900</v>
       </c>
       <c r="AF32" s="3">
         <v>900</v>
@@ -3335,132 +3405,138 @@
         <v>900</v>
       </c>
       <c r="AH32" s="3">
+        <v>900</v>
+      </c>
+      <c r="AI32" s="3">
         <v>800</v>
       </c>
-      <c r="AI32" s="3">
+      <c r="AJ32" s="3">
         <v>700</v>
       </c>
-      <c r="AJ32" s="3">
+      <c r="AK32" s="3">
         <v>600</v>
-      </c>
-      <c r="AK32" s="3">
-        <v>700</v>
       </c>
       <c r="AL32" s="3">
         <v>700</v>
       </c>
+      <c r="AM32" s="3">
+        <v>700</v>
+      </c>
     </row>
-    <row r="33" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E33" s="3">
         <v>16300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>15000</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>24100</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>28900</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>13800</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>14900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>23200</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>23400</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>11600</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>10700</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>18000</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>19700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>10600</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>10200</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>14100</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>16600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>9100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>7900</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>12200</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>11800</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>4800</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>4500</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>9300</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>9800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>3800</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>4100</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>7400</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>9100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>-37400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>17100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>5200</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>4200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>3600</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="34" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3569,233 +3645,242 @@
       <c r="AL34" s="3">
         <v>0</v>
       </c>
+      <c r="AM34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E35" s="3">
         <v>16300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>15000</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>24100</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>28900</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>13800</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>14900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>23200</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>23400</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>11600</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>10700</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>18000</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>19700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>10600</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>10200</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>14100</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>16600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>9100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>7900</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>12200</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>11800</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>4800</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>4500</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>9300</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>9800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>3800</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>4100</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>7400</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>9100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>-37400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>17100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>5200</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>4200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>3600</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="37" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>45837</v>
+      </c>
+      <c r="E38" s="2">
         <v>45746</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45655</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45564</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45473</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45382</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45291</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45200</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45109</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45018</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>44927</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>44836</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44745</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44654</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44556</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44465</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44374</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44283</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44192</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44101</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44010</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>43919</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>43828</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43737</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43646</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43555</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43464</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43373</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43282</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43191</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43100</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43009</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>42918</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>42827</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42736</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="39" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -3834,8 +3919,9 @@
       <c r="AJ39" s="3"/>
       <c r="AK39" s="3"/>
       <c r="AL39" s="3"/>
+      <c r="AM39" s="3"/>
     </row>
-    <row r="40" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -3874,118 +3960,122 @@
       <c r="AJ40" s="3"/>
       <c r="AK40" s="3"/>
       <c r="AL40" s="3"/>
+      <c r="AM40" s="3"/>
     </row>
-    <row r="41" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E41" s="3">
         <v>5100</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>8300</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>7500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8900</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7200</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>5700</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>11000</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7100</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>7600</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>6100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>3900</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6000</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3500</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>23400</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6800</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>5200</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>3000</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>8000</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>4500</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>4300</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>7300</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4100</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>5600</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>9200</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>7300</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>4000</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>5200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>5000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>7600</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>3800</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>2800</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>6900</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>8400</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>16700</v>
       </c>
     </row>
-    <row r="42" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4094,228 +4184,237 @@
       <c r="AL42" s="3">
         <v>0</v>
       </c>
+      <c r="AM42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>140100</v>
+      </c>
+      <c r="E43" s="3">
         <v>134700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>111500</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>115200</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>126400</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>114500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>113000</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>124800</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>138300</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>129300</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>125500</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>131400</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>138800</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>122800</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>102800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>90100</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>90900</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>90800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>77800</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>74500</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>69500</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>67400</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>56700</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>65400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>69000</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>64500</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>61500</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>66400</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>67900</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>66200</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>57900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>60000</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>62800</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>58600</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>53300</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>52800</v>
       </c>
     </row>
-    <row r="44" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>95700</v>
+      </c>
+      <c r="E44" s="3">
         <v>83500</v>
-      </c>
-      <c r="E44" s="3">
-        <v>81600</v>
       </c>
       <c r="F44" s="3">
         <v>81600</v>
       </c>
       <c r="G44" s="3">
+        <v>81600</v>
+      </c>
+      <c r="H44" s="3">
         <v>81200</v>
       </c>
-      <c r="H44" s="3">
+      <c r="I44" s="3">
         <v>74600</v>
       </c>
-      <c r="I44" s="3">
+      <c r="J44" s="3">
         <v>68800</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>68500</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>76900</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>88800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>101600</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>113100</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>105000</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>95000</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>76200</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>70300</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>67900</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>63900</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>64700</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>63200</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>63400</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>54400</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>57500</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>60800</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>58700</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>60500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>67700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>67800</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>66400</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>59700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>62700</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>65900</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>65600</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>51200</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>50300</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="45" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4346,229 +4445,235 @@
       <c r="L45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M45" s="3">
+      <c r="M45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="N45" s="3">
         <v>7100</v>
       </c>
-      <c r="N45" s="3">
+      <c r="O45" s="3">
         <v>3200</v>
       </c>
-      <c r="O45" s="3">
+      <c r="P45" s="3">
         <v>3900</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>6400</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>7000</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>2500</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>3700</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>5400</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>5100</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>1700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>3100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>4900</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>5600</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>2800</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4800</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>5200</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>5700</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>1700</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>3500</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>4100</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>4800</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>2500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>3300</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>4200</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>5100</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="46" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>256400</v>
+      </c>
+      <c r="E46" s="3">
         <v>230700</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>210400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>209900</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>222000</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>202800</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>195000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>207300</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>226500</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>232000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>240200</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>251600</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>253600</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>227700</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>209500</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>169700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>167800</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>163000</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>155500</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>142600</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>140400</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>131000</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>127000</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>133100</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>138100</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>139400</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>142200</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>139900</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>142900</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>135000</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>133100</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>132200</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>134400</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>120900</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>117000</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>126400</v>
       </c>
     </row>
-    <row r="47" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1900</v>
+      </c>
+      <c r="E47" s="3">
         <v>2400</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>3200</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2300</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>4100</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>4300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>3700</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>5500</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>5100</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>4000</v>
       </c>
-      <c r="M47" s="3">
-        <v>0</v>
-      </c>
       <c r="N47" s="3">
         <v>0</v>
       </c>
@@ -4644,228 +4749,237 @@
       <c r="AL47" s="3">
         <v>0</v>
       </c>
+      <c r="AM47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>256500</v>
+      </c>
+      <c r="E48" s="3">
         <v>238700</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>233500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>229500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>225800</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>220600</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>216900</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>204200</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>201900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>196000</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>188900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>181000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>176400</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>172500</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>158400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>154200</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>153700</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>156200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>147100</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>136000</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>135800</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>135400</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>134900</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>133900</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>133500</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>118600</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>117600</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>119400</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>121700</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>123800</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>125100</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>125900</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>123000</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>121500</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>120200</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>117900</v>
       </c>
     </row>
-    <row r="49" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>458900</v>
+      </c>
+      <c r="E49" s="3">
         <v>285500</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>247200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>235500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>238600</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>220000</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>218200</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>148900</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>148800</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>150500</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>152300</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>154100</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>155800</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>157600</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>145500</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>146100</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>145500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>147100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>137400</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>138900</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>117800</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>119100</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>120400</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>121600</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>122900</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>124200</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>125400</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>126800</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>128200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>129600</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>170200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>171600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>173000</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>174400</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>175900</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>177600</v>
       </c>
     </row>
-    <row r="50" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -4974,8 +5088,11 @@
       <c r="AL50" s="3">
         <v>0</v>
       </c>
+      <c r="AM50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5084,118 +5201,124 @@
       <c r="AL51" s="3">
         <v>0</v>
       </c>
+      <c r="AM51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E52" s="3">
         <v>12500</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>13000</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12600</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>12200</v>
-      </c>
-      <c r="H52" s="3">
-        <v>10200</v>
       </c>
       <c r="I52" s="3">
         <v>10200</v>
       </c>
       <c r="J52" s="3">
+        <v>10200</v>
+      </c>
+      <c r="K52" s="3">
         <v>9500</v>
       </c>
-      <c r="K52" s="3">
+      <c r="L52" s="3">
         <v>9700</v>
       </c>
-      <c r="L52" s="3">
+      <c r="M52" s="3">
         <v>8000</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>12500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>12600</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>10500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>9500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>7800</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>7900</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>8000</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>6200</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>6000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>5600</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>5400</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>3800</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>4300</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>4400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4500</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>3400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>3200</v>
-      </c>
-      <c r="AD52" s="3">
-        <v>3800</v>
       </c>
       <c r="AE52" s="3">
         <v>3800</v>
       </c>
       <c r="AF52" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AG52" s="3">
         <v>2600</v>
       </c>
-      <c r="AG52" s="3">
+      <c r="AH52" s="3">
         <v>2400</v>
       </c>
-      <c r="AH52" s="3">
+      <c r="AI52" s="3">
         <v>2200</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>3000</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>1700</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>1600</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="53" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5304,118 +5427,124 @@
       <c r="AL53" s="3">
         <v>0</v>
       </c>
+      <c r="AM53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>988300</v>
+      </c>
+      <c r="E54" s="3">
         <v>769900</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>707200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>689700</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>702700</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>657900</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>644000</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>575300</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>592000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>590500</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>594000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>599300</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>596400</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>567300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>521100</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>477800</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>475000</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>472600</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>446000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>423100</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>399500</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>389300</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>386600</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>393000</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>399000</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>385600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>388400</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>389800</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>396700</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>391000</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>430700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>431900</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>433300</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>418600</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>414700</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>422900</v>
       </c>
     </row>
-    <row r="55" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5454,8 +5583,9 @@
       <c r="AJ55" s="3"/>
       <c r="AK55" s="3"/>
       <c r="AL55" s="3"/>
+      <c r="AM55" s="3"/>
     </row>
-    <row r="56" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5494,126 +5624,130 @@
       <c r="AJ56" s="3"/>
       <c r="AK56" s="3"/>
       <c r="AL56" s="3"/>
+      <c r="AM56" s="3"/>
     </row>
-    <row r="57" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>62800</v>
+      </c>
+      <c r="E57" s="3">
         <v>61200</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>39900</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>51000</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>47800</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>56400</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>42900</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>61200</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>55600</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>53700</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>50600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>60900</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>56400</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>66700</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>44000</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>43000</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>38100</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>37300</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>31200</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>32700</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>31100</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>34100</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>26700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>29600</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>32000</v>
-      </c>
-      <c r="AB57" s="3">
-        <v>29300</v>
       </c>
       <c r="AC57" s="3">
         <v>29300</v>
       </c>
       <c r="AD57" s="3">
+        <v>29300</v>
+      </c>
+      <c r="AE57" s="3">
         <v>35500</v>
       </c>
-      <c r="AE57" s="3">
+      <c r="AF57" s="3">
         <v>36700</v>
       </c>
-      <c r="AF57" s="3">
+      <c r="AG57" s="3">
         <v>33400</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>28100</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>26800</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>27900</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>29800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>21900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="58" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
+        <v>9800</v>
+      </c>
+      <c r="E58" s="3">
         <v>12800</v>
-      </c>
-      <c r="E58" s="3">
-        <v>9900</v>
       </c>
       <c r="F58" s="3">
         <v>9900</v>
@@ -5700,462 +5834,477 @@
         <v>9900</v>
       </c>
       <c r="AH58" s="3">
+        <v>9900</v>
+      </c>
+      <c r="AI58" s="3">
         <v>9200</v>
       </c>
-      <c r="AI58" s="3">
+      <c r="AJ58" s="3">
         <v>8600</v>
       </c>
-      <c r="AJ58" s="3">
+      <c r="AK58" s="3">
         <v>8000</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>7400</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="59" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>16200</v>
+      </c>
+      <c r="E59" s="3">
         <v>5800</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>8400</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>11100</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>20100</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>9800</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>9200</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>10900</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>18100</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10000</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>24400</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>20100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>21900</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>24900</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>21600</v>
-      </c>
-      <c r="R59" s="3">
-        <v>18600</v>
       </c>
       <c r="S59" s="3">
         <v>18600</v>
       </c>
       <c r="T59" s="3">
+        <v>18600</v>
+      </c>
+      <c r="U59" s="3">
         <v>23200</v>
       </c>
-      <c r="U59" s="3">
+      <c r="V59" s="3">
         <v>18000</v>
       </c>
-      <c r="V59" s="3">
+      <c r="W59" s="3">
         <v>16100</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>15700</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>18200</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>14600</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>14300</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>13800</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>16200</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>13900</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>13500</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>10000</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>17300</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>10600</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>16400</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>8500</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>17900</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>12700</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>18700</v>
       </c>
     </row>
-    <row r="60" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>110900</v>
+      </c>
+      <c r="E60" s="3">
         <v>107100</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>84300</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>92300</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>98000</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>103300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>79700</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>94500</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>94300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>90900</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>84900</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>90900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>88200</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>101500</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>75500</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>71500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>66500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>70500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>59000</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>58800</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>56700</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>62200</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>51300</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>53900</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>55700</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>55400</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>53100</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>58800</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>56500</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>60600</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>48500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>52500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>45000</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>55700</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>41900</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="61" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>298900</v>
+      </c>
+      <c r="E61" s="3">
         <v>149800</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>114500</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>103500</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>133700</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>98300</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>120900</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>59300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>88000</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>110400</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>120700</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>130700</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>149200</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>115600</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>105900</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>73900</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>85900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>88800</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>85800</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>65800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>55800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>49800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>57700</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>64700</v>
-      </c>
-      <c r="AA61" s="3">
-        <v>74700</v>
       </c>
       <c r="AB61" s="3">
         <v>74700</v>
       </c>
       <c r="AC61" s="3">
+        <v>74700</v>
+      </c>
+      <c r="AD61" s="3">
         <v>80600</v>
       </c>
-      <c r="AD61" s="3">
+      <c r="AE61" s="3">
         <v>75800</v>
-      </c>
-      <c r="AE61" s="3">
-        <v>90800</v>
       </c>
       <c r="AF61" s="3">
         <v>90800</v>
       </c>
       <c r="AG61" s="3">
+        <v>90800</v>
+      </c>
+      <c r="AH61" s="3">
         <v>104200</v>
       </c>
-      <c r="AH61" s="3">
+      <c r="AI61" s="3">
         <v>102700</v>
       </c>
-      <c r="AI61" s="3">
+      <c r="AJ61" s="3">
         <v>112200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>94600</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>105100</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>106900</v>
       </c>
     </row>
-    <row r="62" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>68600</v>
+      </c>
+      <c r="E62" s="3">
         <v>27100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>26100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>25200</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>24100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>24300</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>22400</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>11000</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>10800</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11500</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>47300</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>46300</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>45800</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>47600</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>48000</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>48100</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>47400</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>48000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>44200</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>43900</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>43600</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>43900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>45400</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>45000</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>45200</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>37700</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>37200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>37400</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>37100</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>37400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>34700</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>51100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>51500</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>50500</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>50400</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="63" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6264,8 +6413,11 @@
       <c r="AL63" s="3">
         <v>0</v>
       </c>
+      <c r="AM63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6374,8 +6526,11 @@
       <c r="AL64" s="3">
         <v>0</v>
       </c>
+      <c r="AM64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6484,118 +6639,124 @@
       <c r="AL65" s="3">
         <v>0</v>
       </c>
+      <c r="AM65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>503700</v>
+      </c>
+      <c r="E66" s="3">
         <v>309600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>250300</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>246300</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>281500</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>251900</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>250300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>192600</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>221000</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>240500</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>252800</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>267900</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>283100</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>264700</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>229500</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>193500</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>199800</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>207300</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>189100</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>168400</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>156000</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>155800</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>154400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>163600</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>175600</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>167700</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>170900</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>172000</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>184400</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>188700</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>187500</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>206200</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>208600</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>200800</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>197400</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>210100</v>
       </c>
     </row>
-    <row r="67" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6634,8 +6795,9 @@
       <c r="AJ67" s="3"/>
       <c r="AK67" s="3"/>
       <c r="AL67" s="3"/>
+      <c r="AM67" s="3"/>
     </row>
-    <row r="68" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -6744,8 +6906,11 @@
       <c r="AL68" s="3">
         <v>0</v>
       </c>
+      <c r="AM68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -6854,8 +7019,11 @@
       <c r="AL69" s="3">
         <v>0</v>
       </c>
+      <c r="AM69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -6964,8 +7132,11 @@
       <c r="AL70" s="3">
         <v>0</v>
       </c>
+      <c r="AM70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7074,118 +7245,124 @@
       <c r="AL71" s="3">
         <v>0</v>
       </c>
+      <c r="AM71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>459700</v>
+      </c>
+      <c r="E72" s="3">
         <v>434300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>421700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>410400</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>390100</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>364500</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>354100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>342500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>322700</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>302400</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>294000</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>286200</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>271100</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>254400</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>246800</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>239300</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>227900</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>213900</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>207400</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>202000</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>192300</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>182900</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>180700</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>178600</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>171800</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>164400</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>163100</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>161400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>156400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>147200</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>189400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>172200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>171700</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>165900</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>166200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>162600</v>
       </c>
     </row>
-    <row r="73" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7294,8 +7471,11 @@
       <c r="AL73" s="3">
         <v>0</v>
       </c>
+      <c r="AM73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7404,8 +7584,11 @@
       <c r="AL74" s="3">
         <v>0</v>
       </c>
+      <c r="AM74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7514,118 +7697,124 @@
       <c r="AL75" s="3">
         <v>0</v>
       </c>
+      <c r="AM75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>484600</v>
+      </c>
+      <c r="E76" s="3">
         <v>460300</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>457000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>443400</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>421200</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>406000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>393800</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>382700</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>371000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>350000</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>341200</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>331400</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>313300</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>302600</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>291700</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>284300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>275200</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>265200</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>256900</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>254600</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>243400</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>233500</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>232200</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>229400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>223400</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>217900</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>217500</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>217800</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>212300</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>202200</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>243300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>225700</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>224700</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>217800</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>217300</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>212800</v>
       </c>
     </row>
-    <row r="77" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -7734,233 +7923,242 @@
       <c r="AL77" s="3">
         <v>0</v>
       </c>
+      <c r="AM77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:39" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:38" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:39" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>45837</v>
+      </c>
+      <c r="E80" s="2">
         <v>45746</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45655</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45564</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45473</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45382</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45291</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45200</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45109</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45018</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>44927</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>44836</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44745</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44654</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44556</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44465</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44374</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44283</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44192</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44101</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44010</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>43919</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>43828</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43737</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43646</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43555</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43464</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43373</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43282</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43191</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43100</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43009</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>42918</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>42827</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42736</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="81" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>29200</v>
+      </c>
+      <c r="E81" s="3">
         <v>16300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>15000</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>24100</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>28900</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>13800</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>14900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>23200</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>23400</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>11600</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>10700</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>18000</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>19700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>10600</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>10200</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>14100</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>16600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>9100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>7900</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>12200</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>11800</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>4800</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>4500</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>9300</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>9800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>3800</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>4100</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>7400</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>9100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>-37400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>17100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>5200</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>4200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>3600</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="82" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -7999,73 +8197,74 @@
       <c r="AJ82" s="3"/>
       <c r="AK82" s="3"/>
       <c r="AL82" s="3"/>
+      <c r="AM82" s="3"/>
     </row>
-    <row r="83" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>9300</v>
+      </c>
+      <c r="E83" s="3">
         <v>500</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>8300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>7400</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>7100</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>200</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7000</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>6800</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>6600</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6300</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>7000</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6800</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6600</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6300</v>
-      </c>
-      <c r="Q83" s="3">
-        <v>6000</v>
       </c>
       <c r="R83" s="3">
         <v>6000</v>
       </c>
       <c r="S83" s="3">
-        <v>5900</v>
+        <v>6000</v>
       </c>
       <c r="T83" s="3">
         <v>5900</v>
       </c>
       <c r="U83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="V83" s="3">
         <v>5700</v>
       </c>
-      <c r="V83" s="3">
+      <c r="W83" s="3">
         <v>5600</v>
       </c>
-      <c r="W83" s="3">
+      <c r="X83" s="3">
         <v>5500</v>
-      </c>
-      <c r="X83" s="3">
-        <v>5400</v>
       </c>
       <c r="Y83" s="3">
         <v>5400</v>
@@ -8083,34 +8282,37 @@
         <v>5400</v>
       </c>
       <c r="AD83" s="3">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="AE83" s="3">
         <v>5500</v>
       </c>
       <c r="AF83" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AG83" s="3">
         <v>5600</v>
       </c>
-      <c r="AG83" s="3">
+      <c r="AH83" s="3">
         <v>5400</v>
       </c>
-      <c r="AH83" s="3">
+      <c r="AI83" s="3">
         <v>5500</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>5800</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>5400</v>
-      </c>
-      <c r="AK83" s="3">
-        <v>5200</v>
       </c>
       <c r="AL83" s="3">
         <v>5200</v>
       </c>
+      <c r="AM83" s="3">
+        <v>5200</v>
+      </c>
     </row>
-    <row r="84" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8219,8 +8421,11 @@
       <c r="AL84" s="3">
         <v>0</v>
       </c>
+      <c r="AM84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8329,8 +8534,11 @@
       <c r="AL85" s="3">
         <v>0</v>
       </c>
+      <c r="AM85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8439,8 +8647,11 @@
       <c r="AL86" s="3">
         <v>0</v>
       </c>
+      <c r="AM86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8549,8 +8760,11 @@
       <c r="AL87" s="3">
         <v>0</v>
       </c>
+      <c r="AM87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -8659,118 +8873,124 @@
       <c r="AL88" s="3">
         <v>0</v>
       </c>
+      <c r="AM88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>31500</v>
+      </c>
+      <c r="E89" s="3">
         <v>30800</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>21000</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>41600</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>17600</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>41900</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>25000</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>57800</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>34900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>32900</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>25700</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>28200</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>-9400</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>4100</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-1400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>25300</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>14800</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>17200</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>6500</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>18600</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>1600</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>13900</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>17900</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>17000</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>10100</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>17000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>6200</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>18000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>6800</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>12800</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>10100</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>16400</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>-11900</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>13900</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>2900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>13600</v>
       </c>
     </row>
-    <row r="90" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -8809,118 +9029,122 @@
       <c r="AJ90" s="3"/>
       <c r="AK90" s="3"/>
       <c r="AL90" s="3"/>
+      <c r="AM90" s="3"/>
     </row>
-    <row r="91" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-13500</v>
+      </c>
+      <c r="E91" s="3">
         <v>-11100</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-8700</v>
-      </c>
-      <c r="F91" s="3">
-        <v>-10600</v>
       </c>
       <c r="G91" s="3">
         <v>-10600</v>
       </c>
       <c r="H91" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="I91" s="3">
         <v>-11900</v>
       </c>
-      <c r="I91" s="3">
+      <c r="J91" s="3">
         <v>-11300</v>
       </c>
-      <c r="J91" s="3">
+      <c r="K91" s="3">
         <v>-9000</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-7900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-16000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-11600</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-9000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-12800</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-8800</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-4700</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-2200</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-7600</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-5100</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-3300</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-4800</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-5300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4900</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-9200</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-5400</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-3800</v>
-      </c>
-      <c r="AH91" s="3">
-        <v>-6600</v>
       </c>
       <c r="AI91" s="3">
         <v>-6600</v>
       </c>
       <c r="AJ91" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="AK91" s="3">
         <v>-5800</v>
       </c>
-      <c r="AK91" s="3">
+      <c r="AL91" s="3">
         <v>-5600</v>
       </c>
-      <c r="AL91" s="3">
+      <c r="AM91" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="92" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9029,8 +9253,11 @@
       <c r="AL92" s="3">
         <v>0</v>
       </c>
+      <c r="AM92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9139,118 +9366,124 @@
       <c r="AL93" s="3">
         <v>0</v>
       </c>
+      <c r="AM93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-164500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-55100</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-26500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-10500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-35800</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-16100</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-86400</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-12100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-7800</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-9300</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-11600</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-8800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11500</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-31700</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-10100</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-5800</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-2100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-23400</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-15000</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-28200</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-4800</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-5200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-9100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-3700</v>
-      </c>
-      <c r="AH94" s="3">
-        <v>-6500</v>
       </c>
       <c r="AI94" s="3">
         <v>-6500</v>
       </c>
       <c r="AJ94" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="AK94" s="3">
         <v>-5700</v>
       </c>
-      <c r="AK94" s="3">
+      <c r="AL94" s="3">
         <v>-5500</v>
       </c>
-      <c r="AL94" s="3">
+      <c r="AM94" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="95" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9289,8 +9522,9 @@
       <c r="AJ95" s="3"/>
       <c r="AK95" s="3"/>
       <c r="AL95" s="3"/>
+      <c r="AM95" s="3"/>
     </row>
-    <row r="96" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9304,7 +9538,7 @@
         <v>3800</v>
       </c>
       <c r="G96" s="3">
-        <v>3400</v>
+        <v>3800</v>
       </c>
       <c r="H96" s="3">
         <v>3400</v>
@@ -9316,37 +9550,37 @@
         <v>3400</v>
       </c>
       <c r="K96" s="3">
-        <v>3200</v>
+        <v>3400</v>
       </c>
       <c r="L96" s="3">
         <v>3200</v>
       </c>
       <c r="M96" s="3">
-        <v>-2900</v>
+        <v>3200</v>
       </c>
       <c r="N96" s="3">
         <v>-2900</v>
       </c>
       <c r="O96" s="3">
-        <v>-3000</v>
+        <v>-2900</v>
       </c>
       <c r="P96" s="3">
         <v>-3000</v>
       </c>
       <c r="Q96" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="R96" s="3">
         <v>-2700</v>
       </c>
-      <c r="R96" s="3">
+      <c r="S96" s="3">
         <v>-2800</v>
-      </c>
-      <c r="S96" s="3">
-        <v>-2600</v>
       </c>
       <c r="T96" s="3">
         <v>-2600</v>
       </c>
       <c r="U96" s="3">
-        <v>-2500</v>
+        <v>-2600</v>
       </c>
       <c r="V96" s="3">
         <v>-2500</v>
@@ -9358,49 +9592,52 @@
         <v>-2500</v>
       </c>
       <c r="Y96" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="Z96" s="3">
         <v>-2400</v>
       </c>
       <c r="AA96" s="3">
-        <v>-2500</v>
+        <v>-2400</v>
       </c>
       <c r="AB96" s="3">
         <v>-2500</v>
       </c>
       <c r="AC96" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="AD96" s="3">
         <v>-2400</v>
       </c>
       <c r="AE96" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AF96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AF96" s="3">
-        <v>0</v>
-      </c>
       <c r="AG96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-4500</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-4500</v>
       </c>
-      <c r="AL96" s="3">
+      <c r="AM96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9509,8 +9746,11 @@
       <c r="AL97" s="3">
         <v>0</v>
       </c>
+      <c r="AM97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -9619,8 +9859,11 @@
       <c r="AL98" s="3">
         <v>0</v>
       </c>
+      <c r="AM98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -9729,118 +9972,124 @@
       <c r="AL99" s="3">
         <v>0</v>
       </c>
+      <c r="AM99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>142500</v>
+      </c>
+      <c r="E100" s="3">
         <v>21100</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>6200</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>-32500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>20000</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-24400</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>56200</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-41700</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-27600</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-22200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-11900</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-21400</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>23400</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>7600</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>28100</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>-17900</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>-10500</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>1200</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>13400</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>8300</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>3500</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>-11800</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>-9400</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-13800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-4600</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-9800</v>
       </c>
-      <c r="AC100" s="3">
-        <v>0</v>
-      </c>
       <c r="AD100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AE100" s="3">
         <v>-17400</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-4300</v>
       </c>
-      <c r="AF100" s="3">
+      <c r="AG100" s="3">
         <v>-12800</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-2600</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-8900</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>14400</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-9600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="101" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -9871,8 +10120,8 @@
       <c r="L101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="M101" s="3">
-        <v>0</v>
+      <c r="M101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="N101" s="3">
         <v>0</v>
@@ -9949,114 +10198,120 @@
       <c r="AL101" s="3">
         <v>0</v>
       </c>
+      <c r="AM101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:38" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:39" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>9400</v>
+      </c>
+      <c r="E102" s="3">
         <v>-3200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>800</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-1400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>1700</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>1400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-5200</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>3900</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-500</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>1400</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>2200</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-2100</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2500</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-19900</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>16600</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>1600</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>2200</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>-5000</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>4800</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-1400</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>200</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-3000</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>3200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3600</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>1900</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>3300</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>200</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>3900</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>1000</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-4100</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-8300</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-4600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HWKN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HWKN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="188" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
   <si>
     <t>HWKN</t>
   </si>
@@ -656,520 +656,532 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AN102"/>
+  <dimension ref="A5:AO102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="15" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="16" max="16" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="20" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="21" max="21" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="24" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="28" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="29" max="29" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="32" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="33" max="33" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="39" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="40" max="40" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="17" max="17" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="34" max="34" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="40" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="41" max="41" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E7" s="2">
         <v>45928</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45837</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45746</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45655</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45564</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45473</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45382</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45291</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45200</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45109</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45018</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>44927</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44836</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44745</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44654</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44556</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44465</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44374</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44283</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44192</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44101</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44010</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>43919</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43828</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43737</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43646</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43555</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43464</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43373</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43282</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43191</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43009</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>42918</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42827</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42736</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="8" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>244100</v>
+      </c>
+      <c r="E8" s="3">
         <v>280400</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>293300</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>245300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>226200</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>247000</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>255900</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>223000</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>208500</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>236500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>251100</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>228100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>219200</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>241200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>246500</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>223000</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>187100</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>183300</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>181200</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>163000</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>142900</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>147800</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>143200</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>132400</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>120400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>140000</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>147300</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>133100</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>128200</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>145300</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>149800</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>127000</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>118100</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>125400</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>133700</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>118600</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>112400</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>121300</v>
       </c>
     </row>
-    <row r="9" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>193300</v>
+      </c>
+      <c r="E9" s="3">
         <v>212800</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>220900</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>193100</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>177800</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>186800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>191200</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>177500</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>166200</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>182600</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>199100</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>192400</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>182900</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>194800</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>199800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>186700</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>153100</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>146000</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>142300</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>131200</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>114700</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>115000</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>112200</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>109800</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>98900</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>112000</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>118500</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>112400</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>107100</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>119600</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>121300</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>109200</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>99200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>101300</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>107700</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>96700</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>91400</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>94200</v>
       </c>
     </row>
-    <row r="10" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>50800</v>
+      </c>
+      <c r="E10" s="3">
         <v>67600</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>72400</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>52200</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>48400</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>60200</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>64700</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>45500</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>42200</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>53900</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>52000</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>35700</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>36300</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>46400</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>46700</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>36300</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>34000</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>37300</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>38900</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>31800</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>28200</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>32800</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>31000</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>22600</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>21500</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>28000</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>28800</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>20700</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>21100</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>25700</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>28500</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>17800</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>18900</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>24100</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>26000</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>21900</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>21000</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>27100</v>
       </c>
     </row>
-    <row r="11" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1210,8 +1222,9 @@
       <c r="AL11" s="3"/>
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
+      <c r="AO11" s="3"/>
     </row>
-    <row r="12" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1326,8 +1339,11 @@
       <c r="AN12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1442,13 +1458,16 @@
       <c r="AN13" s="3">
         <v>0</v>
       </c>
+      <c r="AO13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
+      <c r="D14" s="3">
+        <v>500</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>8</v>
@@ -1480,8 +1499,8 @@
       <c r="N14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O14" s="3">
-        <v>0</v>
+      <c r="O14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P14" s="3">
         <v>0</v>
@@ -1519,17 +1538,17 @@
       <c r="AA14" s="3">
         <v>0</v>
       </c>
-      <c r="AB14" s="3" t="s">
-        <v>8</v>
+      <c r="AB14" s="3">
+        <v>0</v>
       </c>
       <c r="AC14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE14" s="3" t="s">
+      <c r="AD14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AE14" s="3">
+        <v>0</v>
       </c>
       <c r="AF14" s="3" t="s">
         <v>8</v>
@@ -1537,11 +1556,11 @@
       <c r="AG14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH14" s="3">
+      <c r="AH14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI14" s="3">
         <v>39100</v>
-      </c>
-      <c r="AI14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AJ14" s="3" t="s">
         <v>8</v>
@@ -1558,46 +1577,49 @@
       <c r="AN14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>2300</v>
+      </c>
+      <c r="E15" s="3">
         <v>13300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>12300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>10600</v>
       </c>
-      <c r="G15" s="3">
+      <c r="H15" s="3">
         <v>10100</v>
       </c>
-      <c r="H15" s="3">
+      <c r="I15" s="3">
         <v>9900</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>9300</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>9000</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>8300</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>7400</v>
-      </c>
-      <c r="M15" s="3">
-        <v>7100</v>
       </c>
       <c r="N15" s="3">
         <v>7100</v>
       </c>
       <c r="O15" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="P15" s="3">
         <v>0</v>
@@ -1674,8 +1696,11 @@
       <c r="AN15" s="3">
         <v>0</v>
       </c>
+      <c r="AO15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:40" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1713,240 +1738,247 @@
       <c r="AL16" s="3"/>
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
+      <c r="AO16" s="3"/>
     </row>
-    <row r="17" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>221000</v>
+      </c>
+      <c r="E17" s="3">
         <v>246500</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>251900</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>220700</v>
       </c>
-      <c r="G17" s="3">
+      <c r="H17" s="3">
         <v>205100</v>
       </c>
-      <c r="H17" s="3">
+      <c r="I17" s="3">
         <v>213300</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>216100</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>202900</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>190000</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>203500</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>218600</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>209700</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>204000</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>214700</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>218700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>207800</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>172800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>163700</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>159100</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>150100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>132400</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>131200</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>127200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>124700</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>113600</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>126900</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>133400</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>127300</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>121400</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>134500</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>136300</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>163000</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>113400</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>116100</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>123500</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>111200</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>106400</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>109100</v>
       </c>
     </row>
-    <row r="18" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>23100</v>
+      </c>
+      <c r="E18" s="3">
         <v>33900</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>41300</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>24600</v>
       </c>
-      <c r="G18" s="3">
+      <c r="H18" s="3">
         <v>21100</v>
       </c>
-      <c r="H18" s="3">
+      <c r="I18" s="3">
         <v>33700</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>39800</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>20100</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>18500</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>33000</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>32500</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>18500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>15200</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>26500</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>27800</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>15200</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>14300</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>19600</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>22100</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>12900</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>10500</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>16600</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>16000</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>7700</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>6800</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>13100</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>13900</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>5800</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>6800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>10800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>13500</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>-36000</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>4700</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>9300</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>10200</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>7400</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>6000</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="19" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -1987,100 +2019,101 @@
       <c r="AL19" s="3"/>
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
+      <c r="AO19" s="3"/>
     </row>
-    <row r="20" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>-500</v>
+      </c>
+      <c r="E20" s="3">
         <v>-700</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-900</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>600</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>-400</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-700</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-200</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-500</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-900</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>300</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>-300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-400</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>500</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>-500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-700</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-400</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>100</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>200</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>300</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>100</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>500</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>300</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>400</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-400</v>
-      </c>
-      <c r="AB20" s="3">
-        <v>-600</v>
       </c>
       <c r="AC20" s="3">
         <v>-600</v>
       </c>
       <c r="AD20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AE20" s="3">
         <v>-500</v>
       </c>
-      <c r="AE20" s="3">
+      <c r="AF20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-700</v>
-      </c>
-      <c r="AG20" s="3">
-        <v>-900</v>
       </c>
       <c r="AH20" s="3">
         <v>-900</v>
@@ -2089,188 +2122,194 @@
         <v>-900</v>
       </c>
       <c r="AJ20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AK20" s="3">
         <v>-800</v>
       </c>
-      <c r="AK20" s="3">
+      <c r="AL20" s="3">
         <v>-700</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-600</v>
-      </c>
-      <c r="AM20" s="3">
-        <v>-700</v>
       </c>
       <c r="AN20" s="3">
         <v>-700</v>
       </c>
+      <c r="AO20" s="3">
+        <v>-700</v>
+      </c>
     </row>
-    <row r="21" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>25800</v>
+      </c>
+      <c r="E21" s="3">
         <v>47900</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>54600</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>34500</v>
       </c>
-      <c r="G21" s="3">
+      <c r="H21" s="3">
         <v>31600</v>
       </c>
-      <c r="H21" s="3">
+      <c r="I21" s="3">
         <v>44300</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>49300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>29500</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>27700</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>40100</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>39900</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>26000</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>22700</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>32900</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>33700</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>21100</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>20400</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>25700</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>28300</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>19000</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>16600</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>22500</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>21900</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>12200</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>11800</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>17900</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>18700</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>10700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>11000</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>15600</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>18000</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>-31200</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>9300</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>14000</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>15300</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>12200</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>10500</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="22" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3400</v>
+      </c>
+      <c r="E22" s="3">
         <v>3800</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3300</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>1500</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1200</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1400</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1300</v>
-      </c>
-      <c r="J22" s="3">
-        <v>1200</v>
       </c>
       <c r="K22" s="3">
         <v>1200</v>
       </c>
       <c r="L22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="M22" s="3">
         <v>700</v>
       </c>
-      <c r="M22" s="3">
+      <c r="N22" s="3">
         <v>1100</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1400</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1500</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1400</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>900</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>400</v>
-      </c>
-      <c r="S22" s="3">
-        <v>300</v>
       </c>
       <c r="T22" s="3">
         <v>300</v>
@@ -2279,25 +2318,25 @@
         <v>300</v>
       </c>
       <c r="V22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="W22" s="3">
         <v>400</v>
       </c>
       <c r="X22" s="3">
+        <v>400</v>
+      </c>
+      <c r="Y22" s="3">
         <v>300</v>
       </c>
-      <c r="Y22" s="3">
+      <c r="Z22" s="3">
         <v>400</v>
-      </c>
-      <c r="Z22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AA22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AB22" s="3">
-        <v>0</v>
+      <c r="AB22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AC22" s="3">
         <v>0</v>
@@ -2335,240 +2374,249 @@
       <c r="AN22" s="3">
         <v>0</v>
       </c>
+      <c r="AO22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>19600</v>
+      </c>
+      <c r="E23" s="3">
         <v>30800</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>39000</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>22400</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>20300</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>33000</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>38700</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>19300</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>18200</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>32000</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>31700</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>17500</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>14200</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>24700</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>26200</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>14400</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>14100</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>19500</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>22000</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>12700</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>10600</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>16600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>16000</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>6800</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6300</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>12500</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>13300</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>5300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5600</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>10100</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>12500</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>-36900</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>3800</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>8500</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>9500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>6800</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>5400</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="24" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>5300</v>
+      </c>
+      <c r="E24" s="3">
         <v>8200</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>9800</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>6100</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>5300</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>8900</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>9800</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>5500</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>3300</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>8800</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8200</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>5900</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>3500</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>6700</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6500</v>
-      </c>
-      <c r="R24" s="3">
-        <v>3900</v>
       </c>
       <c r="S24" s="3">
         <v>3900</v>
       </c>
       <c r="T24" s="3">
+        <v>3900</v>
+      </c>
+      <c r="U24" s="3">
         <v>5300</v>
       </c>
-      <c r="U24" s="3">
+      <c r="V24" s="3">
         <v>5400</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>3600</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>2700</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>4400</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4200</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>2000</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>1800</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>3300</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3500</v>
-      </c>
-      <c r="AD24" s="3">
-        <v>1500</v>
       </c>
       <c r="AE24" s="3">
         <v>1500</v>
       </c>
       <c r="AF24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AG24" s="3">
         <v>2700</v>
       </c>
-      <c r="AG24" s="3">
+      <c r="AH24" s="3">
         <v>3400</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>1200</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>-100</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>3300</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>3700</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>2600</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>1800</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="25" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2683,240 +2731,249 @@
       <c r="AN25" s="3">
         <v>0</v>
       </c>
+      <c r="AO25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E26" s="3">
         <v>22600</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>29200</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>16300</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>15000</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>24100</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>28900</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>13800</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>14900</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>23200</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>23400</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>11600</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>10700</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>18000</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>19700</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>10600</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>10200</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>14100</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>16600</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>9100</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>7900</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>12200</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>11800</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>4800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4500</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>9300</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>9800</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>3800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>4100</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>7400</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>9100</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>-38100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>3900</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>5200</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>5800</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>4200</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>3600</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="27" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E27" s="3">
         <v>22600</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>29200</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>16300</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>15000</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>24100</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>28900</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>13800</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>14900</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>23200</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>23400</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>11600</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>10700</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>18000</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>19700</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>10600</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>10200</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>14100</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>16600</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>9100</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>7900</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>12200</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>11800</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>4800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4500</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>9300</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>9800</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>3800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>4100</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>7400</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>9100</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>-38100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>3900</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>5200</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>5800</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>4200</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>3600</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="28" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3031,8 +3088,11 @@
       <c r="AN28" s="3">
         <v>0</v>
       </c>
+      <c r="AO28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3108,17 +3168,17 @@
       <c r="AA29" s="3">
         <v>0</v>
       </c>
-      <c r="AB29" s="3" t="s">
-        <v>8</v>
+      <c r="AB29" s="3">
+        <v>0</v>
       </c>
       <c r="AC29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AD29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AE29" s="3" t="s">
+      <c r="AD29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AE29" s="3">
+        <v>0</v>
       </c>
       <c r="AF29" s="3" t="s">
         <v>8</v>
@@ -3126,14 +3186,14 @@
       <c r="AG29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AH29" s="3">
+      <c r="AH29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AI29" s="3">
         <v>700</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AJ29" s="3">
         <v>13200</v>
-      </c>
-      <c r="AJ29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK29" s="3" t="s">
         <v>8</v>
@@ -3147,8 +3207,11 @@
       <c r="AN29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AO29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3263,8 +3326,11 @@
       <c r="AN30" s="3">
         <v>0</v>
       </c>
+      <c r="AO30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3379,100 +3445,103 @@
       <c r="AN31" s="3">
         <v>0</v>
       </c>
+      <c r="AO31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>500</v>
+      </c>
+      <c r="E32" s="3">
         <v>700</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>900</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>-600</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>400</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>700</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>200</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>500</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>900</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>-300</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>400</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>-500</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>700</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>400</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>-100</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-200</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-300</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-100</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-500</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-300</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-400</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>1000</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>400</v>
-      </c>
-      <c r="AB32" s="3">
-        <v>600</v>
       </c>
       <c r="AC32" s="3">
         <v>600</v>
       </c>
       <c r="AD32" s="3">
+        <v>600</v>
+      </c>
+      <c r="AE32" s="3">
         <v>500</v>
       </c>
-      <c r="AE32" s="3">
+      <c r="AF32" s="3">
         <v>1200</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>700</v>
-      </c>
-      <c r="AG32" s="3">
-        <v>900</v>
       </c>
       <c r="AH32" s="3">
         <v>900</v>
@@ -3481,138 +3550,144 @@
         <v>900</v>
       </c>
       <c r="AJ32" s="3">
+        <v>900</v>
+      </c>
+      <c r="AK32" s="3">
         <v>800</v>
       </c>
-      <c r="AK32" s="3">
+      <c r="AL32" s="3">
         <v>700</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>600</v>
-      </c>
-      <c r="AM32" s="3">
-        <v>700</v>
       </c>
       <c r="AN32" s="3">
         <v>700</v>
       </c>
+      <c r="AO32" s="3">
+        <v>700</v>
+      </c>
     </row>
-    <row r="33" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E33" s="3">
         <v>22600</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>29200</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>16300</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>15000</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>24100</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>28900</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>13800</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>14900</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>23200</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>23400</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>11600</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>10700</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>18000</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>19700</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>10600</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>10200</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>14100</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>16600</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>9100</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>7900</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>12200</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>11800</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>4800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4500</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>9300</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>9800</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>3800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>4100</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>7400</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>9100</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>-37400</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>17100</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>5200</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>5800</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>4200</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>3600</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="34" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3727,245 +3802,254 @@
       <c r="AN34" s="3">
         <v>0</v>
       </c>
+      <c r="AO34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E35" s="3">
         <v>22600</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>29200</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>16300</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>15000</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>24100</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>28900</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>13800</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>14900</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>23200</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>23400</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>11600</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>10700</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>18000</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>19700</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>10600</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>10200</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>14100</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>16600</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>9100</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>7900</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>12200</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>11800</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>4800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4500</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>9300</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>9800</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>3800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>4100</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>7400</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>9100</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>-37400</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>17100</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>5200</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>5800</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>4200</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>3600</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="37" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E38" s="2">
         <v>45928</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45837</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45746</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45655</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45564</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45473</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45382</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45291</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45200</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45109</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45018</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>44927</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44836</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44745</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44654</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44556</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44465</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44374</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44283</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44192</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44101</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44010</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>43919</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43828</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43737</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43646</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43555</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43464</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43373</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43282</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43191</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43009</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>42918</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42827</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42736</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="39" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4006,8 +4090,9 @@
       <c r="AL39" s="3"/>
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
+      <c r="AO39" s="3"/>
     </row>
-    <row r="40" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4048,124 +4133,128 @@
       <c r="AL40" s="3"/>
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
+      <c r="AO40" s="3"/>
     </row>
-    <row r="41" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>8200</v>
+      </c>
+      <c r="E41" s="3">
         <v>10400</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>14500</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>5100</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>8300</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>7500</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>8900</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>7200</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>5700</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>11000</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>7100</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7600</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>6100</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>3900</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>6000</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>3500</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>23400</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>6800</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>5200</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>3000</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>8000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>3200</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>4500</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4300</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>7300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>4100</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>5600</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>9200</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>7300</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>4000</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>5200</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5000</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>7600</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>3800</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>2800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>6900</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>8400</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>16700</v>
       </c>
     </row>
-    <row r="42" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4280,240 +4369,249 @@
       <c r="AN42" s="3">
         <v>0</v>
       </c>
+      <c r="AO42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>123700</v>
+      </c>
+      <c r="E43" s="3">
         <v>131100</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>140100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>134700</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>111500</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>115200</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>126400</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>114500</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>113000</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>124800</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>138300</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>129300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>125500</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>131400</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>138800</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>122800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>102800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>90100</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>90900</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>90800</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>77800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>74500</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>69500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>67400</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>56700</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>65400</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>69000</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>64500</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>61500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>66400</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>67900</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>66200</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>57900</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>60000</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>62800</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>58600</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>53300</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>52800</v>
       </c>
     </row>
-    <row r="44" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>85900</v>
+      </c>
+      <c r="E44" s="3">
         <v>92900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>95700</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>83500</v>
-      </c>
-      <c r="G44" s="3">
-        <v>81600</v>
       </c>
       <c r="H44" s="3">
         <v>81600</v>
       </c>
       <c r="I44" s="3">
+        <v>81600</v>
+      </c>
+      <c r="J44" s="3">
         <v>81200</v>
       </c>
-      <c r="J44" s="3">
+      <c r="K44" s="3">
         <v>74600</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>68800</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>68500</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>76900</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>88800</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>101600</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>113100</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>105000</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>95000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>76200</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>70300</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>67900</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>63900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>64700</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>63200</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>63400</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>54400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>57500</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>60800</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>58700</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>60500</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>67700</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>67800</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>66400</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>59700</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>62700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>65900</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>65600</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>51200</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>50300</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="45" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4550,241 +4648,247 @@
       <c r="N45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O45" s="3">
+      <c r="O45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="P45" s="3">
         <v>7100</v>
       </c>
-      <c r="P45" s="3">
+      <c r="Q45" s="3">
         <v>3200</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3900</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>6400</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>7000</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>2500</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>3700</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>5400</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5100</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>1700</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>3100</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>4900</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>5600</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>2800</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>4800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>5200</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>5700</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>1700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>3500</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>4100</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>4800</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>2500</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>3300</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>4200</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>5100</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="46" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>228200</v>
+      </c>
+      <c r="E46" s="3">
         <v>239600</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>256400</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>230700</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>210400</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>209900</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>222000</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>202800</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>195000</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>207300</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>226500</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>232000</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>240200</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>251600</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>253600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>227700</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>209500</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>169700</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>167800</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>163000</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>155500</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>142600</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>140400</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>131000</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>127000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>133100</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>138100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>139400</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>142200</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>139900</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>142900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>135000</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>133100</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>132200</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>134400</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>120900</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>117000</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>126400</v>
       </c>
     </row>
-    <row r="47" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
       <c r="D47" s="3">
+        <v>1300</v>
+      </c>
+      <c r="E47" s="3">
         <v>1600</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1900</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>2400</v>
       </c>
-      <c r="G47" s="3">
+      <c r="H47" s="3">
         <v>3200</v>
       </c>
-      <c r="H47" s="3">
+      <c r="I47" s="3">
         <v>2300</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>4100</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4300</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>3700</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>5500</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5100</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>4000</v>
       </c>
-      <c r="O47" s="3">
-        <v>0</v>
-      </c>
       <c r="P47" s="3">
         <v>0</v>
       </c>
@@ -4860,240 +4964,249 @@
       <c r="AN47" s="3">
         <v>0</v>
       </c>
+      <c r="AO47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>270600</v>
+      </c>
+      <c r="E48" s="3">
         <v>264800</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>256500</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>238700</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>233500</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>229500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>225800</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>220600</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>216900</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>204200</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>201900</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>196000</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>188900</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>181000</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>176400</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>172500</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>158400</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>154200</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>153700</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>156200</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>147100</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>136000</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>135800</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>135400</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>134900</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>133900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>133500</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>118600</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>117600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>119400</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>121700</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>123800</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>125100</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>125900</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>123000</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>121500</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>120200</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>117900</v>
       </c>
     </row>
-    <row r="49" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>461400</v>
+      </c>
+      <c r="E49" s="3">
         <v>463200</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>458900</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>285500</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>247200</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>235500</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>238600</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>220000</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>218200</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>148900</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>148800</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>150500</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>152300</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>154100</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>155800</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>157600</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>145500</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>146100</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>145500</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>147100</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>137400</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>138900</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>117800</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>119100</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>120400</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>121600</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>122900</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>124200</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>125400</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>126800</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>128200</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>129600</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>170200</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>171600</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>173000</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>174400</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>175900</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>177600</v>
       </c>
     </row>
-    <row r="50" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5208,8 +5321,11 @@
       <c r="AN50" s="3">
         <v>0</v>
       </c>
+      <c r="AO50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5324,124 +5440,130 @@
       <c r="AN51" s="3">
         <v>0</v>
       </c>
+      <c r="AO51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
       <c r="D52" s="3">
+        <v>15000</v>
+      </c>
+      <c r="E52" s="3">
         <v>14900</v>
       </c>
-      <c r="E52" s="3">
+      <c r="F52" s="3">
         <v>14500</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>12500</v>
       </c>
-      <c r="G52" s="3">
+      <c r="H52" s="3">
         <v>13000</v>
       </c>
-      <c r="H52" s="3">
+      <c r="I52" s="3">
         <v>12600</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12200</v>
-      </c>
-      <c r="J52" s="3">
-        <v>10200</v>
       </c>
       <c r="K52" s="3">
         <v>10200</v>
       </c>
       <c r="L52" s="3">
+        <v>10200</v>
+      </c>
+      <c r="M52" s="3">
         <v>9500</v>
       </c>
-      <c r="M52" s="3">
+      <c r="N52" s="3">
         <v>9700</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>8000</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>12500</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>12600</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>10500</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>9500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>7800</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7900</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>8000</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>6200</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6000</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>5600</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5400</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>3800</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>4300</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4400</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4500</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>3400</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3200</v>
-      </c>
-      <c r="AF52" s="3">
-        <v>3800</v>
       </c>
       <c r="AG52" s="3">
         <v>3800</v>
       </c>
       <c r="AH52" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AI52" s="3">
         <v>2600</v>
       </c>
-      <c r="AI52" s="3">
+      <c r="AJ52" s="3">
         <v>2400</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2200</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>3000</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>1700</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1600</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="53" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5556,124 +5678,130 @@
       <c r="AN53" s="3">
         <v>0</v>
       </c>
+      <c r="AO53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>976500</v>
+      </c>
+      <c r="E54" s="3">
         <v>984200</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>988300</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>769900</v>
       </c>
-      <c r="G54" s="3">
+      <c r="H54" s="3">
         <v>707200</v>
       </c>
-      <c r="H54" s="3">
+      <c r="I54" s="3">
         <v>689700</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>702700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>657900</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>644000</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>575300</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>592000</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>590500</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>594000</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>599300</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>596400</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>567300</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>521100</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>477800</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>475000</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>472600</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>446000</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>423100</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>399500</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>389300</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>386600</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>393000</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>399000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>385600</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>388400</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>389800</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>396700</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>391000</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>430700</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>431900</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>433300</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>418600</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>414700</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>422900</v>
       </c>
     </row>
-    <row r="55" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5714,8 +5842,9 @@
       <c r="AL55" s="3"/>
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
+      <c r="AO55" s="3"/>
     </row>
-    <row r="56" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5756,124 +5885,128 @@
       <c r="AL56" s="3"/>
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
+      <c r="AO56" s="3"/>
     </row>
-    <row r="57" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>46400</v>
+      </c>
+      <c r="E57" s="3">
         <v>55300</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>62800</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>61200</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>39900</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>51000</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>47800</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>56400</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>42900</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>61200</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>55600</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>53700</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>50600</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>60900</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>56400</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>66700</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>44000</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>43000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>38100</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>37300</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>31200</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>32700</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>31100</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>34100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>26700</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>29600</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>32000</v>
-      </c>
-      <c r="AD57" s="3">
-        <v>29300</v>
       </c>
       <c r="AE57" s="3">
         <v>29300</v>
       </c>
       <c r="AF57" s="3">
+        <v>29300</v>
+      </c>
+      <c r="AG57" s="3">
         <v>35500</v>
       </c>
-      <c r="AG57" s="3">
+      <c r="AH57" s="3">
         <v>36700</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>33400</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>28100</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>26800</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>27900</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>29800</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>21900</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="58" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
@@ -5884,10 +6017,10 @@
         <v>9800</v>
       </c>
       <c r="F58" s="3">
+        <v>9800</v>
+      </c>
+      <c r="G58" s="3">
         <v>12800</v>
-      </c>
-      <c r="G58" s="3">
-        <v>9900</v>
       </c>
       <c r="H58" s="3">
         <v>9900</v>
@@ -5974,486 +6107,501 @@
         <v>9900</v>
       </c>
       <c r="AJ58" s="3">
+        <v>9900</v>
+      </c>
+      <c r="AK58" s="3">
         <v>9200</v>
       </c>
-      <c r="AK58" s="3">
+      <c r="AL58" s="3">
         <v>8600</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>8000</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>7400</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="59" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>12400</v>
+      </c>
+      <c r="E59" s="3">
         <v>11100</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>16200</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>5800</v>
       </c>
-      <c r="G59" s="3">
+      <c r="H59" s="3">
         <v>8400</v>
       </c>
-      <c r="H59" s="3">
+      <c r="I59" s="3">
         <v>11100</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>20100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>9800</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9200</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>10900</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>18100</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>10000</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>24400</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>20100</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>21900</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>24900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>21600</v>
-      </c>
-      <c r="T59" s="3">
-        <v>18600</v>
       </c>
       <c r="U59" s="3">
         <v>18600</v>
       </c>
       <c r="V59" s="3">
+        <v>18600</v>
+      </c>
+      <c r="W59" s="3">
         <v>23200</v>
       </c>
-      <c r="W59" s="3">
+      <c r="X59" s="3">
         <v>18000</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>16100</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>15700</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>18200</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>14600</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>14300</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>13800</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>16200</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>13900</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>13500</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>10000</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>17300</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>10600</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>16400</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>8500</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>17900</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>12700</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>18700</v>
       </c>
     </row>
-    <row r="60" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>97200</v>
+      </c>
+      <c r="E60" s="3">
         <v>98600</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>110900</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>107100</v>
       </c>
-      <c r="G60" s="3">
+      <c r="H60" s="3">
         <v>84300</v>
       </c>
-      <c r="H60" s="3">
+      <c r="I60" s="3">
         <v>92300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>98000</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>103300</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>79700</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>94500</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>94300</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>90900</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>84900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>90900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>88200</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>101500</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>75500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>71500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>66500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>70500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>59000</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>58800</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>56700</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>62200</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>51300</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>53900</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>55700</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>55400</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>53100</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>58800</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>56500</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>60600</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>48500</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>52500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>45000</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>55700</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>41900</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="61" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>268500</v>
+      </c>
+      <c r="E61" s="3">
         <v>283400</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>298900</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>149800</v>
       </c>
-      <c r="G61" s="3">
+      <c r="H61" s="3">
         <v>114500</v>
       </c>
-      <c r="H61" s="3">
+      <c r="I61" s="3">
         <v>103500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>133700</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>98300</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>120900</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>59300</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>88000</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>110400</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>120700</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>130700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>149200</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>115600</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>105900</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>73900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>85900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>88800</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>85800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>65800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>55800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>49800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>57700</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>64700</v>
-      </c>
-      <c r="AC61" s="3">
-        <v>74700</v>
       </c>
       <c r="AD61" s="3">
         <v>74700</v>
       </c>
       <c r="AE61" s="3">
+        <v>74700</v>
+      </c>
+      <c r="AF61" s="3">
         <v>80600</v>
       </c>
-      <c r="AF61" s="3">
+      <c r="AG61" s="3">
         <v>75800</v>
-      </c>
-      <c r="AG61" s="3">
-        <v>90800</v>
       </c>
       <c r="AH61" s="3">
         <v>90800</v>
       </c>
       <c r="AI61" s="3">
+        <v>90800</v>
+      </c>
+      <c r="AJ61" s="3">
         <v>104200</v>
       </c>
-      <c r="AJ61" s="3">
+      <c r="AK61" s="3">
         <v>102700</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>112200</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>94600</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>105100</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>106900</v>
       </c>
     </row>
-    <row r="62" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>67100</v>
+      </c>
+      <c r="E62" s="3">
         <v>70100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>68600</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>27100</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>26100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>25200</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>24100</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>24300</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>22400</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>11000</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>10800</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>11500</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>47300</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>46300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>45800</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>47600</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>48000</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>48100</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>47400</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>48000</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>44200</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>43900</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>43600</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>43900</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>45400</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>45000</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>45200</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>37700</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>37200</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>37400</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>37100</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>37400</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>34700</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>51100</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>51500</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>50500</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>50400</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="63" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6568,8 +6716,11 @@
       <c r="AN63" s="3">
         <v>0</v>
       </c>
+      <c r="AO63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6684,8 +6835,11 @@
       <c r="AN64" s="3">
         <v>0</v>
       </c>
+      <c r="AO64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6800,124 +6954,130 @@
       <c r="AN65" s="3">
         <v>0</v>
       </c>
+      <c r="AO65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>457600</v>
+      </c>
+      <c r="E66" s="3">
         <v>477200</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>503700</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>309600</v>
       </c>
-      <c r="G66" s="3">
+      <c r="H66" s="3">
         <v>250300</v>
       </c>
-      <c r="H66" s="3">
+      <c r="I66" s="3">
         <v>246300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>281500</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>251900</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>250300</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>192600</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>221000</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>240500</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>252800</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>267900</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>283100</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>264700</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>229500</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>193500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>199800</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>207300</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>189100</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>168400</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>156000</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>155800</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>154400</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>163600</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>175600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>167700</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>170900</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>172000</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>184400</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>188700</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>187500</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>206200</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>208600</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>200800</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>197400</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>210100</v>
       </c>
     </row>
-    <row r="67" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -6958,8 +7118,9 @@
       <c r="AL67" s="3"/>
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
+      <c r="AO67" s="3"/>
     </row>
-    <row r="68" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7074,8 +7235,11 @@
       <c r="AN68" s="3">
         <v>0</v>
       </c>
+      <c r="AO68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7190,8 +7354,11 @@
       <c r="AN69" s="3">
         <v>0</v>
       </c>
+      <c r="AO69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7306,8 +7473,11 @@
       <c r="AN70" s="3">
         <v>0</v>
       </c>
+      <c r="AO70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7422,124 +7592,130 @@
       <c r="AN71" s="3">
         <v>0</v>
       </c>
+      <c r="AO71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>488700</v>
+      </c>
+      <c r="E72" s="3">
         <v>478300</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>459700</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>434300</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>421700</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>410400</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>390100</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>364500</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>354100</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>342500</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>322700</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>302400</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>294000</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>286200</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>271100</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>254400</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>246800</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>239300</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>227900</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>213900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>207400</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>202000</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>192300</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>182900</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>180700</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>178600</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>171800</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>164400</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>163100</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>161400</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>156400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>147200</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>189400</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>172200</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>171700</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>165900</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>166200</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>162600</v>
       </c>
     </row>
-    <row r="73" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7654,8 +7830,11 @@
       <c r="AN73" s="3">
         <v>0</v>
       </c>
+      <c r="AO73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7770,8 +7949,11 @@
       <c r="AN74" s="3">
         <v>0</v>
       </c>
+      <c r="AO74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -7886,124 +8068,130 @@
       <c r="AN75" s="3">
         <v>0</v>
       </c>
+      <c r="AO75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>518900</v>
+      </c>
+      <c r="E76" s="3">
         <v>507000</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>484600</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>460300</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>457000</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>443400</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>421200</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>406000</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>393800</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>382700</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>371000</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>350000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>341200</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>331400</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>313300</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>302600</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>291700</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>284300</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>275200</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>265200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>256900</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>254600</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>243400</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>233500</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>232200</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>229400</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>223400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>217900</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>217500</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>217800</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>212300</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>202200</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>243300</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>225700</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>224700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>217800</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>217300</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>212800</v>
       </c>
     </row>
-    <row r="77" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8118,245 +8306,254 @@
       <c r="AN77" s="3">
         <v>0</v>
       </c>
+      <c r="AO77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:40" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46019</v>
+      </c>
+      <c r="E80" s="2">
         <v>45928</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45837</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45746</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45655</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45564</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45473</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45382</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45291</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45200</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45109</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45018</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>44927</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44836</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44745</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44654</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44556</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44465</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44374</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44283</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44192</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44101</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44010</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>43919</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43828</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43737</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43646</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43555</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43464</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43373</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43282</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43191</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43100</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43009</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>42918</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42827</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42736</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="81" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>14300</v>
+      </c>
+      <c r="E81" s="3">
         <v>22600</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>29200</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>16300</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>15000</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>24100</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>28900</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>13800</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>14900</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>23200</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>23400</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>11600</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>10700</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>18000</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>19700</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>10600</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>10200</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>14100</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>16600</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>9100</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>7900</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>12200</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>11800</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>4800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4500</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>9300</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>9800</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>3800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>4100</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>7400</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>9100</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>-37400</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>17100</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>5200</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>5800</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>4200</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>3600</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="82" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8397,79 +8594,80 @@
       <c r="AL82" s="3"/>
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
+      <c r="AO82" s="3"/>
     </row>
-    <row r="83" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10100</v>
+      </c>
+      <c r="E83" s="3">
         <v>9900</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>9300</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>500</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>8300</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>7400</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7100</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>200</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>7000</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>6800</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6600</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6300</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>7000</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>6800</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6600</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>6300</v>
-      </c>
-      <c r="S83" s="3">
-        <v>6000</v>
       </c>
       <c r="T83" s="3">
         <v>6000</v>
       </c>
       <c r="U83" s="3">
-        <v>5900</v>
+        <v>6000</v>
       </c>
       <c r="V83" s="3">
         <v>5900</v>
       </c>
       <c r="W83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="X83" s="3">
         <v>5700</v>
       </c>
-      <c r="X83" s="3">
+      <c r="Y83" s="3">
         <v>5600</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>5500</v>
-      </c>
-      <c r="Z83" s="3">
-        <v>5400</v>
       </c>
       <c r="AA83" s="3">
         <v>5400</v>
@@ -8487,34 +8685,37 @@
         <v>5400</v>
       </c>
       <c r="AF83" s="3">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="AG83" s="3">
         <v>5500</v>
       </c>
       <c r="AH83" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AI83" s="3">
         <v>5600</v>
       </c>
-      <c r="AI83" s="3">
+      <c r="AJ83" s="3">
         <v>5400</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>5500</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>5800</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>5400</v>
-      </c>
-      <c r="AM83" s="3">
-        <v>5200</v>
       </c>
       <c r="AN83" s="3">
         <v>5200</v>
       </c>
+      <c r="AO83" s="3">
+        <v>5200</v>
+      </c>
     </row>
-    <row r="84" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8629,8 +8830,11 @@
       <c r="AN84" s="3">
         <v>0</v>
       </c>
+      <c r="AO84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8745,8 +8949,11 @@
       <c r="AN85" s="3">
         <v>0</v>
       </c>
+      <c r="AO85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -8861,8 +9068,11 @@
       <c r="AN86" s="3">
         <v>0</v>
       </c>
+      <c r="AO86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -8977,8 +9187,11 @@
       <c r="AN87" s="3">
         <v>0</v>
       </c>
+      <c r="AO87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9093,124 +9306,130 @@
       <c r="AN88" s="3">
         <v>0</v>
       </c>
+      <c r="AO88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>35600</v>
+      </c>
+      <c r="E89" s="3">
         <v>39500</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>31500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>30800</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>21000</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>41600</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>17600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>41900</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>25000</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>57800</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>34900</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>32900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>25700</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>28200</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>-9400</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>4100</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>-1400</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>25300</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>14800</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>17200</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>6500</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>18600</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>1600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>13900</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>17900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>17000</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>10100</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>17000</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>6200</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>18000</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>6800</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>12800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>10100</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>16400</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>-11900</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>13900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>2900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>13600</v>
       </c>
     </row>
-    <row r="90" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9251,124 +9470,128 @@
       <c r="AL90" s="3"/>
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
+      <c r="AO90" s="3"/>
     </row>
-    <row r="91" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-14300</v>
+      </c>
+      <c r="E91" s="3">
         <v>-10800</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-13500</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-11100</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-8700</v>
-      </c>
-      <c r="H91" s="3">
-        <v>-10600</v>
       </c>
       <c r="I91" s="3">
         <v>-10600</v>
       </c>
       <c r="J91" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="K91" s="3">
         <v>-11900</v>
       </c>
-      <c r="K91" s="3">
+      <c r="L91" s="3">
         <v>-11300</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-9000</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-7900</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-16000</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-11600</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-9000</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-11600</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-12800</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-8800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-4700</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-2200</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-7600</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-5100</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-3300</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-4900</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-9200</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-5400</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-3800</v>
-      </c>
-      <c r="AJ91" s="3">
-        <v>-6600</v>
       </c>
       <c r="AK91" s="3">
         <v>-6600</v>
       </c>
       <c r="AL91" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="AM91" s="3">
         <v>-5800</v>
       </c>
-      <c r="AM91" s="3">
+      <c r="AN91" s="3">
         <v>-5600</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="92" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9483,8 +9706,11 @@
       <c r="AN92" s="3">
         <v>0</v>
       </c>
+      <c r="AO92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9599,124 +9825,130 @@
       <c r="AN93" s="3">
         <v>0</v>
       </c>
+      <c r="AO93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-18800</v>
+      </c>
+      <c r="E94" s="3">
         <v>-21300</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-164500</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-55100</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-26500</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-10500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-35800</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-16100</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-86400</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-12100</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-7800</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-9300</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-11600</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-8800</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-11500</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-31700</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-10100</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-5800</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-2100</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-23400</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-15000</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-28200</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-4800</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-5100</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-4800</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-9100</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-5300</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-3700</v>
-      </c>
-      <c r="AJ94" s="3">
-        <v>-6500</v>
       </c>
       <c r="AK94" s="3">
         <v>-6500</v>
       </c>
       <c r="AL94" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="AM94" s="3">
         <v>-5700</v>
       </c>
-      <c r="AM94" s="3">
+      <c r="AN94" s="3">
         <v>-5500</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="95" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9757,8 +9989,9 @@
       <c r="AL95" s="3"/>
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
+      <c r="AO95" s="3"/>
     </row>
-    <row r="96" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -9766,7 +9999,7 @@
         <v>4000</v>
       </c>
       <c r="E96" s="3">
-        <v>3800</v>
+        <v>4000</v>
       </c>
       <c r="F96" s="3">
         <v>3800</v>
@@ -9778,7 +10011,7 @@
         <v>3800</v>
       </c>
       <c r="I96" s="3">
-        <v>3400</v>
+        <v>3800</v>
       </c>
       <c r="J96" s="3">
         <v>3400</v>
@@ -9790,37 +10023,37 @@
         <v>3400</v>
       </c>
       <c r="M96" s="3">
-        <v>3200</v>
+        <v>3400</v>
       </c>
       <c r="N96" s="3">
         <v>3200</v>
       </c>
       <c r="O96" s="3">
-        <v>-2900</v>
+        <v>3200</v>
       </c>
       <c r="P96" s="3">
         <v>-2900</v>
       </c>
       <c r="Q96" s="3">
-        <v>-3000</v>
+        <v>-2900</v>
       </c>
       <c r="R96" s="3">
         <v>-3000</v>
       </c>
       <c r="S96" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="T96" s="3">
         <v>-2700</v>
       </c>
-      <c r="T96" s="3">
+      <c r="U96" s="3">
         <v>-2800</v>
-      </c>
-      <c r="U96" s="3">
-        <v>-2600</v>
       </c>
       <c r="V96" s="3">
         <v>-2600</v>
       </c>
       <c r="W96" s="3">
-        <v>-2500</v>
+        <v>-2600</v>
       </c>
       <c r="X96" s="3">
         <v>-2500</v>
@@ -9832,49 +10065,52 @@
         <v>-2500</v>
       </c>
       <c r="AA96" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="AB96" s="3">
         <v>-2400</v>
       </c>
       <c r="AC96" s="3">
-        <v>-2500</v>
+        <v>-2400</v>
       </c>
       <c r="AD96" s="3">
         <v>-2500</v>
       </c>
       <c r="AE96" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="AF96" s="3">
         <v>-2400</v>
       </c>
       <c r="AG96" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AH96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AH96" s="3">
-        <v>0</v>
-      </c>
       <c r="AI96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AJ96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AJ96" s="3">
-        <v>0</v>
-      </c>
       <c r="AK96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AL96" s="3">
         <v>-4500</v>
       </c>
-      <c r="AL96" s="3">
-        <v>0</v>
-      </c>
       <c r="AM96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AN96" s="3">
         <v>-4500</v>
       </c>
-      <c r="AN96" s="3">
+      <c r="AO96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -9989,8 +10225,11 @@
       <c r="AN97" s="3">
         <v>0</v>
       </c>
+      <c r="AO97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10105,8 +10344,11 @@
       <c r="AN98" s="3">
         <v>0</v>
       </c>
+      <c r="AO98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10221,124 +10463,130 @@
       <c r="AN99" s="3">
         <v>0</v>
       </c>
+      <c r="AO99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-19000</v>
+      </c>
+      <c r="E100" s="3">
         <v>-22400</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>142500</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>21100</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>6200</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>-32500</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>20000</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>-24400</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>56200</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>-41700</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-27600</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-22200</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-11900</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-21400</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>23400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>7600</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>28100</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>-17900</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-10500</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>1200</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>13400</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>8300</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>3500</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>-11800</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-9400</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-13800</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-4600</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-9800</v>
       </c>
-      <c r="AE100" s="3">
-        <v>0</v>
-      </c>
       <c r="AF100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AG100" s="3">
         <v>-17400</v>
       </c>
-      <c r="AG100" s="3">
+      <c r="AH100" s="3">
         <v>-4300</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-12800</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-8900</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>14400</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>-9600</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="101" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10375,8 +10623,8 @@
       <c r="N101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="O101" s="3">
-        <v>0</v>
+      <c r="O101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="P101" s="3">
         <v>0</v>
@@ -10453,120 +10701,126 @@
       <c r="AN101" s="3">
         <v>0</v>
       </c>
+      <c r="AO101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:40" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-2200</v>
+      </c>
+      <c r="E102" s="3">
         <v>-4100</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>9400</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>-3200</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>800</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>-1400</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>1700</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1400</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>-5200</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>3900</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>-500</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>1400</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>2200</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>-2100</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>2500</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>-19900</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>16600</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>1600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>2200</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>-5000</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>4800</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>-1400</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>200</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>-3000</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>3200</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-3600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>1900</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>3300</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>200</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>3900</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>1000</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>-4100</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-8300</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-4600</v>
       </c>
     </row>

--- a/AAII_Financials/Quarterly/HWKN_QTR_FIN.xlsx
+++ b/AAII_Financials/Quarterly/HWKN_QTR_FIN.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="191" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="195" uniqueCount="92">
   <si>
     <t>HWKN</t>
   </si>
@@ -656,532 +656,545 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet2"/>
-  <dimension ref="A5:AO102"/>
+  <dimension ref="A5:AP102"/>
   <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.2"/>
   <cols>
     <col min="1" max="1" width="8.7109375" style="1" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="26.85546875" style="1" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="69.140625" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="9" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="15" max="16" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="18" max="18" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="19" max="19" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="20" max="21" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="22" max="22" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="23" max="23" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="24" max="25" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="26" max="26" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="27" max="27" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="28" max="29" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="30" max="30" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
-    <col min="31" max="31" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="32" max="33" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="34" max="34" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="35" max="35" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="36" max="36" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="37" max="37" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="38" max="38" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="39" max="40" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
-    <col min="41" max="41" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
-    <col min="42" max="16384" width="9.140625" style="1"/>
+    <col min="4" max="4" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="5" max="6" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="16" max="17" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="18" max="18" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="19" max="19" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="20" max="20" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="21" max="22" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="23" max="23" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="24" max="24" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="25" max="26" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="27" max="27" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="28" max="28" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="29" max="30" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="31" max="31" width="14.42578125" style="1" bestFit="1" customWidth="1"/>
+    <col min="32" max="32" width="14.85546875" style="1" bestFit="1" customWidth="1"/>
+    <col min="33" max="34" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="35" max="35" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="36" max="36" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="37" max="37" width="14.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="38" max="38" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="39" max="39" width="11.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="40" max="41" width="12.7109375" style="1" bestFit="1" customWidth="1"/>
+    <col min="42" max="42" width="12.5703125" style="1" bestFit="1" customWidth="1"/>
+    <col min="43" max="16384" width="9.140625" style="1"/>
   </cols>
   <sheetData>
-    <row r="5" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:42" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:42" x14ac:dyDescent="0.2">
       <c r="B6" s="1" t="s">
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C7" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D7" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E7" s="2">
         <v>46019</v>
       </c>
-      <c r="E7" s="2">
+      <c r="F7" s="2">
         <v>45928</v>
       </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>45837</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>45746</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>45655</v>
       </c>
-      <c r="I7" s="2">
+      <c r="J7" s="2">
         <v>45564</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>45473</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>45382</v>
       </c>
-      <c r="L7" s="2">
+      <c r="M7" s="2">
         <v>45291</v>
       </c>
-      <c r="M7" s="2">
+      <c r="N7" s="2">
         <v>45200</v>
       </c>
-      <c r="N7" s="2">
+      <c r="O7" s="2">
         <v>45109</v>
       </c>
-      <c r="O7" s="2">
+      <c r="P7" s="2">
         <v>45018</v>
       </c>
-      <c r="P7" s="2">
+      <c r="Q7" s="2">
         <v>44927</v>
       </c>
-      <c r="Q7" s="2">
+      <c r="R7" s="2">
         <v>44836</v>
       </c>
-      <c r="R7" s="2">
+      <c r="S7" s="2">
         <v>44745</v>
       </c>
-      <c r="S7" s="2">
+      <c r="T7" s="2">
         <v>44654</v>
       </c>
-      <c r="T7" s="2">
+      <c r="U7" s="2">
         <v>44556</v>
       </c>
-      <c r="U7" s="2">
+      <c r="V7" s="2">
         <v>44465</v>
       </c>
-      <c r="V7" s="2">
+      <c r="W7" s="2">
         <v>44374</v>
       </c>
-      <c r="W7" s="2">
+      <c r="X7" s="2">
         <v>44283</v>
       </c>
-      <c r="X7" s="2">
+      <c r="Y7" s="2">
         <v>44192</v>
       </c>
-      <c r="Y7" s="2">
+      <c r="Z7" s="2">
         <v>44101</v>
       </c>
-      <c r="Z7" s="2">
+      <c r="AA7" s="2">
         <v>44010</v>
       </c>
-      <c r="AA7" s="2">
+      <c r="AB7" s="2">
         <v>43919</v>
       </c>
-      <c r="AB7" s="2">
+      <c r="AC7" s="2">
         <v>43828</v>
       </c>
-      <c r="AC7" s="2">
+      <c r="AD7" s="2">
         <v>43737</v>
       </c>
-      <c r="AD7" s="2">
+      <c r="AE7" s="2">
         <v>43646</v>
       </c>
-      <c r="AE7" s="2">
+      <c r="AF7" s="2">
         <v>43555</v>
       </c>
-      <c r="AF7" s="2">
+      <c r="AG7" s="2">
         <v>43464</v>
       </c>
-      <c r="AG7" s="2">
+      <c r="AH7" s="2">
         <v>43373</v>
       </c>
-      <c r="AH7" s="2">
+      <c r="AI7" s="2">
         <v>43282</v>
       </c>
-      <c r="AI7" s="2">
+      <c r="AJ7" s="2">
         <v>43191</v>
       </c>
-      <c r="AJ7" s="2">
+      <c r="AK7" s="2">
         <v>43100</v>
       </c>
-      <c r="AK7" s="2">
+      <c r="AL7" s="2">
         <v>43009</v>
       </c>
-      <c r="AL7" s="2">
+      <c r="AM7" s="2">
         <v>42918</v>
       </c>
-      <c r="AM7" s="2">
+      <c r="AN7" s="2">
         <v>42827</v>
       </c>
-      <c r="AN7" s="2">
+      <c r="AO7" s="2">
         <v>42736</v>
       </c>
-      <c r="AO7" s="2">
+      <c r="AP7" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="8" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C8" s="1" t="s">
         <v>3</v>
       </c>
       <c r="D8" s="3">
+        <v>265900</v>
+      </c>
+      <c r="E8" s="3">
         <v>244100</v>
       </c>
-      <c r="E8" s="3">
+      <c r="F8" s="3">
         <v>280400</v>
       </c>
-      <c r="F8" s="3">
+      <c r="G8" s="3">
         <v>293300</v>
       </c>
-      <c r="G8" s="3">
+      <c r="H8" s="3">
         <v>245300</v>
       </c>
-      <c r="H8" s="3">
+      <c r="I8" s="3">
         <v>226200</v>
       </c>
-      <c r="I8" s="3">
+      <c r="J8" s="3">
         <v>247000</v>
       </c>
-      <c r="J8" s="3">
+      <c r="K8" s="3">
         <v>255900</v>
       </c>
-      <c r="K8" s="3">
+      <c r="L8" s="3">
         <v>223000</v>
       </c>
-      <c r="L8" s="3">
+      <c r="M8" s="3">
         <v>208500</v>
       </c>
-      <c r="M8" s="3">
+      <c r="N8" s="3">
         <v>236500</v>
       </c>
-      <c r="N8" s="3">
+      <c r="O8" s="3">
         <v>251100</v>
       </c>
-      <c r="O8" s="3">
+      <c r="P8" s="3">
         <v>228100</v>
       </c>
-      <c r="P8" s="3">
+      <c r="Q8" s="3">
         <v>219200</v>
       </c>
-      <c r="Q8" s="3">
+      <c r="R8" s="3">
         <v>241200</v>
       </c>
-      <c r="R8" s="3">
+      <c r="S8" s="3">
         <v>246500</v>
       </c>
-      <c r="S8" s="3">
+      <c r="T8" s="3">
         <v>223000</v>
       </c>
-      <c r="T8" s="3">
+      <c r="U8" s="3">
         <v>187100</v>
       </c>
-      <c r="U8" s="3">
+      <c r="V8" s="3">
         <v>183300</v>
       </c>
-      <c r="V8" s="3">
+      <c r="W8" s="3">
         <v>181200</v>
       </c>
-      <c r="W8" s="3">
+      <c r="X8" s="3">
         <v>163000</v>
       </c>
-      <c r="X8" s="3">
+      <c r="Y8" s="3">
         <v>142900</v>
       </c>
-      <c r="Y8" s="3">
+      <c r="Z8" s="3">
         <v>147800</v>
       </c>
-      <c r="Z8" s="3">
+      <c r="AA8" s="3">
         <v>143200</v>
       </c>
-      <c r="AA8" s="3">
+      <c r="AB8" s="3">
         <v>132400</v>
       </c>
-      <c r="AB8" s="3">
+      <c r="AC8" s="3">
         <v>120400</v>
       </c>
-      <c r="AC8" s="3">
+      <c r="AD8" s="3">
         <v>140000</v>
       </c>
-      <c r="AD8" s="3">
+      <c r="AE8" s="3">
         <v>147300</v>
       </c>
-      <c r="AE8" s="3">
+      <c r="AF8" s="3">
         <v>133100</v>
       </c>
-      <c r="AF8" s="3">
+      <c r="AG8" s="3">
         <v>128200</v>
       </c>
-      <c r="AG8" s="3">
+      <c r="AH8" s="3">
         <v>145300</v>
       </c>
-      <c r="AH8" s="3">
+      <c r="AI8" s="3">
         <v>149800</v>
       </c>
-      <c r="AI8" s="3">
+      <c r="AJ8" s="3">
         <v>127000</v>
       </c>
-      <c r="AJ8" s="3">
+      <c r="AK8" s="3">
         <v>118100</v>
       </c>
-      <c r="AK8" s="3">
+      <c r="AL8" s="3">
         <v>125400</v>
       </c>
-      <c r="AL8" s="3">
+      <c r="AM8" s="3">
         <v>133700</v>
       </c>
-      <c r="AM8" s="3">
+      <c r="AN8" s="3">
         <v>118600</v>
       </c>
-      <c r="AN8" s="3">
+      <c r="AO8" s="3">
         <v>112400</v>
       </c>
-      <c r="AO8" s="3">
+      <c r="AP8" s="3">
         <v>121300</v>
       </c>
     </row>
-    <row r="9" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C9" s="1" t="s">
         <v>4</v>
       </c>
       <c r="D9" s="3">
+        <v>211700</v>
+      </c>
+      <c r="E9" s="3">
         <v>193300</v>
       </c>
-      <c r="E9" s="3">
+      <c r="F9" s="3">
         <v>212800</v>
       </c>
-      <c r="F9" s="3">
+      <c r="G9" s="3">
         <v>220900</v>
       </c>
-      <c r="G9" s="3">
+      <c r="H9" s="3">
         <v>193100</v>
       </c>
-      <c r="H9" s="3">
+      <c r="I9" s="3">
         <v>177800</v>
       </c>
-      <c r="I9" s="3">
+      <c r="J9" s="3">
         <v>186800</v>
       </c>
-      <c r="J9" s="3">
+      <c r="K9" s="3">
         <v>191200</v>
       </c>
-      <c r="K9" s="3">
+      <c r="L9" s="3">
         <v>177500</v>
       </c>
-      <c r="L9" s="3">
+      <c r="M9" s="3">
         <v>166200</v>
       </c>
-      <c r="M9" s="3">
+      <c r="N9" s="3">
         <v>182600</v>
       </c>
-      <c r="N9" s="3">
+      <c r="O9" s="3">
         <v>199100</v>
       </c>
-      <c r="O9" s="3">
+      <c r="P9" s="3">
         <v>192400</v>
       </c>
-      <c r="P9" s="3">
+      <c r="Q9" s="3">
         <v>182900</v>
       </c>
-      <c r="Q9" s="3">
+      <c r="R9" s="3">
         <v>194800</v>
       </c>
-      <c r="R9" s="3">
+      <c r="S9" s="3">
         <v>199800</v>
       </c>
-      <c r="S9" s="3">
+      <c r="T9" s="3">
         <v>186700</v>
       </c>
-      <c r="T9" s="3">
+      <c r="U9" s="3">
         <v>153100</v>
       </c>
-      <c r="U9" s="3">
+      <c r="V9" s="3">
         <v>146000</v>
       </c>
-      <c r="V9" s="3">
+      <c r="W9" s="3">
         <v>142300</v>
       </c>
-      <c r="W9" s="3">
+      <c r="X9" s="3">
         <v>131200</v>
       </c>
-      <c r="X9" s="3">
+      <c r="Y9" s="3">
         <v>114700</v>
       </c>
-      <c r="Y9" s="3">
+      <c r="Z9" s="3">
         <v>115000</v>
       </c>
-      <c r="Z9" s="3">
+      <c r="AA9" s="3">
         <v>112200</v>
       </c>
-      <c r="AA9" s="3">
+      <c r="AB9" s="3">
         <v>109800</v>
       </c>
-      <c r="AB9" s="3">
+      <c r="AC9" s="3">
         <v>98900</v>
       </c>
-      <c r="AC9" s="3">
+      <c r="AD9" s="3">
         <v>112000</v>
       </c>
-      <c r="AD9" s="3">
+      <c r="AE9" s="3">
         <v>118500</v>
       </c>
-      <c r="AE9" s="3">
+      <c r="AF9" s="3">
         <v>112400</v>
       </c>
-      <c r="AF9" s="3">
+      <c r="AG9" s="3">
         <v>107100</v>
       </c>
-      <c r="AG9" s="3">
+      <c r="AH9" s="3">
         <v>119600</v>
       </c>
-      <c r="AH9" s="3">
+      <c r="AI9" s="3">
         <v>121300</v>
       </c>
-      <c r="AI9" s="3">
+      <c r="AJ9" s="3">
         <v>109200</v>
       </c>
-      <c r="AJ9" s="3">
+      <c r="AK9" s="3">
         <v>99200</v>
       </c>
-      <c r="AK9" s="3">
+      <c r="AL9" s="3">
         <v>101300</v>
       </c>
-      <c r="AL9" s="3">
+      <c r="AM9" s="3">
         <v>107700</v>
       </c>
-      <c r="AM9" s="3">
+      <c r="AN9" s="3">
         <v>96700</v>
       </c>
-      <c r="AN9" s="3">
+      <c r="AO9" s="3">
         <v>91400</v>
       </c>
-      <c r="AO9" s="3">
+      <c r="AP9" s="3">
         <v>94200</v>
       </c>
     </row>
-    <row r="10" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C10" s="1" t="s">
         <v>5</v>
       </c>
       <c r="D10" s="3">
+        <v>54200</v>
+      </c>
+      <c r="E10" s="3">
         <v>50800</v>
       </c>
-      <c r="E10" s="3">
+      <c r="F10" s="3">
         <v>67600</v>
       </c>
-      <c r="F10" s="3">
+      <c r="G10" s="3">
         <v>72400</v>
       </c>
-      <c r="G10" s="3">
+      <c r="H10" s="3">
         <v>52200</v>
       </c>
-      <c r="H10" s="3">
+      <c r="I10" s="3">
         <v>48400</v>
       </c>
-      <c r="I10" s="3">
+      <c r="J10" s="3">
         <v>60200</v>
       </c>
-      <c r="J10" s="3">
+      <c r="K10" s="3">
         <v>64700</v>
       </c>
-      <c r="K10" s="3">
+      <c r="L10" s="3">
         <v>45500</v>
       </c>
-      <c r="L10" s="3">
+      <c r="M10" s="3">
         <v>42200</v>
       </c>
-      <c r="M10" s="3">
+      <c r="N10" s="3">
         <v>53900</v>
       </c>
-      <c r="N10" s="3">
+      <c r="O10" s="3">
         <v>52000</v>
       </c>
-      <c r="O10" s="3">
+      <c r="P10" s="3">
         <v>35700</v>
       </c>
-      <c r="P10" s="3">
+      <c r="Q10" s="3">
         <v>36300</v>
       </c>
-      <c r="Q10" s="3">
+      <c r="R10" s="3">
         <v>46400</v>
       </c>
-      <c r="R10" s="3">
+      <c r="S10" s="3">
         <v>46700</v>
       </c>
-      <c r="S10" s="3">
+      <c r="T10" s="3">
         <v>36300</v>
       </c>
-      <c r="T10" s="3">
+      <c r="U10" s="3">
         <v>34000</v>
       </c>
-      <c r="U10" s="3">
+      <c r="V10" s="3">
         <v>37300</v>
       </c>
-      <c r="V10" s="3">
+      <c r="W10" s="3">
         <v>38900</v>
       </c>
-      <c r="W10" s="3">
+      <c r="X10" s="3">
         <v>31800</v>
       </c>
-      <c r="X10" s="3">
+      <c r="Y10" s="3">
         <v>28200</v>
       </c>
-      <c r="Y10" s="3">
+      <c r="Z10" s="3">
         <v>32800</v>
       </c>
-      <c r="Z10" s="3">
+      <c r="AA10" s="3">
         <v>31000</v>
       </c>
-      <c r="AA10" s="3">
+      <c r="AB10" s="3">
         <v>22600</v>
       </c>
-      <c r="AB10" s="3">
+      <c r="AC10" s="3">
         <v>21500</v>
       </c>
-      <c r="AC10" s="3">
+      <c r="AD10" s="3">
         <v>28000</v>
       </c>
-      <c r="AD10" s="3">
+      <c r="AE10" s="3">
         <v>28800</v>
       </c>
-      <c r="AE10" s="3">
+      <c r="AF10" s="3">
         <v>20700</v>
       </c>
-      <c r="AF10" s="3">
+      <c r="AG10" s="3">
         <v>21100</v>
       </c>
-      <c r="AG10" s="3">
+      <c r="AH10" s="3">
         <v>25700</v>
       </c>
-      <c r="AH10" s="3">
+      <c r="AI10" s="3">
         <v>28500</v>
       </c>
-      <c r="AI10" s="3">
+      <c r="AJ10" s="3">
         <v>17800</v>
       </c>
-      <c r="AJ10" s="3">
+      <c r="AK10" s="3">
         <v>18900</v>
       </c>
-      <c r="AK10" s="3">
+      <c r="AL10" s="3">
         <v>24100</v>
       </c>
-      <c r="AL10" s="3">
+      <c r="AM10" s="3">
         <v>26000</v>
       </c>
-      <c r="AM10" s="3">
+      <c r="AN10" s="3">
         <v>21900</v>
       </c>
-      <c r="AN10" s="3">
+      <c r="AO10" s="3">
         <v>21000</v>
       </c>
-      <c r="AO10" s="3">
+      <c r="AP10" s="3">
         <v>27100</v>
       </c>
     </row>
-    <row r="11" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C11" s="1" t="s">
         <v>6</v>
       </c>
@@ -1223,8 +1236,9 @@
       <c r="AM11" s="3"/>
       <c r="AN11" s="3"/>
       <c r="AO11" s="3"/>
+      <c r="AP11" s="3"/>
     </row>
-    <row r="12" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C12" s="1" t="s">
         <v>7</v>
       </c>
@@ -1342,8 +1356,11 @@
       <c r="AO12" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP12" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="13" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C13" s="1" t="s">
         <v>9</v>
       </c>
@@ -1461,16 +1478,19 @@
       <c r="AO13" s="3">
         <v>0</v>
       </c>
+      <c r="AP13" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="14" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C14" s="1" t="s">
         <v>10</v>
       </c>
       <c r="D14" s="3">
+        <v>-1400</v>
+      </c>
+      <c r="E14" s="3">
         <v>500</v>
-      </c>
-      <c r="E14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="F14" s="3" t="s">
         <v>8</v>
@@ -1478,8 +1498,8 @@
       <c r="G14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="H14" s="3" t="s">
-        <v>8</v>
+      <c r="H14" s="3">
+        <v>300</v>
       </c>
       <c r="I14" s="3" t="s">
         <v>8</v>
@@ -1502,8 +1522,8 @@
       <c r="O14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P14" s="3">
-        <v>0</v>
+      <c r="P14" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q14" s="3">
         <v>0</v>
@@ -1541,17 +1561,17 @@
       <c r="AB14" s="3">
         <v>0</v>
       </c>
-      <c r="AC14" s="3" t="s">
-        <v>8</v>
+      <c r="AC14" s="3">
+        <v>0</v>
       </c>
       <c r="AD14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE14" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF14" s="3" t="s">
+      <c r="AE14" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AF14" s="3">
+        <v>0</v>
       </c>
       <c r="AG14" s="3" t="s">
         <v>8</v>
@@ -1559,11 +1579,11 @@
       <c r="AH14" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI14" s="3">
+      <c r="AI14" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ14" s="3">
         <v>39100</v>
-      </c>
-      <c r="AJ14" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AK14" s="3" t="s">
         <v>8</v>
@@ -1580,49 +1600,52 @@
       <c r="AO14" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP14" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="15" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:42" x14ac:dyDescent="0.2">
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
       <c r="D15" s="3">
+        <v>14500</v>
+      </c>
+      <c r="E15" s="3">
         <v>2300</v>
       </c>
-      <c r="E15" s="3">
+      <c r="F15" s="3">
         <v>13300</v>
       </c>
-      <c r="F15" s="3">
+      <c r="G15" s="3">
         <v>12300</v>
       </c>
-      <c r="G15" s="3">
-        <v>10600</v>
-      </c>
       <c r="H15" s="3">
+        <v>12800</v>
+      </c>
+      <c r="I15" s="3">
         <v>10100</v>
       </c>
-      <c r="I15" s="3">
+      <c r="J15" s="3">
         <v>9900</v>
       </c>
-      <c r="J15" s="3">
+      <c r="K15" s="3">
         <v>9300</v>
       </c>
-      <c r="K15" s="3">
+      <c r="L15" s="3">
         <v>9000</v>
       </c>
-      <c r="L15" s="3">
+      <c r="M15" s="3">
         <v>8300</v>
       </c>
-      <c r="M15" s="3">
+      <c r="N15" s="3">
         <v>7400</v>
-      </c>
-      <c r="N15" s="3">
-        <v>7100</v>
       </c>
       <c r="O15" s="3">
         <v>7100</v>
       </c>
       <c r="P15" s="3">
-        <v>0</v>
+        <v>7100</v>
       </c>
       <c r="Q15" s="3">
         <v>0</v>
@@ -1699,8 +1722,11 @@
       <c r="AO15" s="3">
         <v>0</v>
       </c>
+      <c r="AP15" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="16" spans="1:41" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:42" x14ac:dyDescent="0.2">
       <c r="D16" s="3"/>
       <c r="E16" s="3"/>
       <c r="F16" s="3"/>
@@ -1739,246 +1765,253 @@
       <c r="AM16" s="3"/>
       <c r="AN16" s="3"/>
       <c r="AO16" s="3"/>
+      <c r="AP16" s="3"/>
     </row>
-    <row r="17" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="17" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
       <c r="D17" s="3">
+        <v>243900</v>
+      </c>
+      <c r="E17" s="3">
         <v>221000</v>
       </c>
-      <c r="E17" s="3">
+      <c r="F17" s="3">
         <v>246500</v>
       </c>
-      <c r="F17" s="3">
+      <c r="G17" s="3">
         <v>251900</v>
       </c>
-      <c r="G17" s="3">
-        <v>220700</v>
-      </c>
       <c r="H17" s="3">
+        <v>220400</v>
+      </c>
+      <c r="I17" s="3">
         <v>205100</v>
       </c>
-      <c r="I17" s="3">
+      <c r="J17" s="3">
         <v>213300</v>
       </c>
-      <c r="J17" s="3">
+      <c r="K17" s="3">
         <v>216100</v>
       </c>
-      <c r="K17" s="3">
+      <c r="L17" s="3">
         <v>202900</v>
       </c>
-      <c r="L17" s="3">
+      <c r="M17" s="3">
         <v>190000</v>
       </c>
-      <c r="M17" s="3">
+      <c r="N17" s="3">
         <v>203500</v>
       </c>
-      <c r="N17" s="3">
+      <c r="O17" s="3">
         <v>218600</v>
       </c>
-      <c r="O17" s="3">
+      <c r="P17" s="3">
         <v>209700</v>
       </c>
-      <c r="P17" s="3">
+      <c r="Q17" s="3">
         <v>204000</v>
       </c>
-      <c r="Q17" s="3">
+      <c r="R17" s="3">
         <v>214700</v>
       </c>
-      <c r="R17" s="3">
+      <c r="S17" s="3">
         <v>218700</v>
       </c>
-      <c r="S17" s="3">
+      <c r="T17" s="3">
         <v>207800</v>
       </c>
-      <c r="T17" s="3">
+      <c r="U17" s="3">
         <v>172800</v>
       </c>
-      <c r="U17" s="3">
+      <c r="V17" s="3">
         <v>163700</v>
       </c>
-      <c r="V17" s="3">
+      <c r="W17" s="3">
         <v>159100</v>
       </c>
-      <c r="W17" s="3">
+      <c r="X17" s="3">
         <v>150100</v>
       </c>
-      <c r="X17" s="3">
+      <c r="Y17" s="3">
         <v>132400</v>
       </c>
-      <c r="Y17" s="3">
+      <c r="Z17" s="3">
         <v>131200</v>
       </c>
-      <c r="Z17" s="3">
+      <c r="AA17" s="3">
         <v>127200</v>
       </c>
-      <c r="AA17" s="3">
+      <c r="AB17" s="3">
         <v>124700</v>
       </c>
-      <c r="AB17" s="3">
+      <c r="AC17" s="3">
         <v>113600</v>
       </c>
-      <c r="AC17" s="3">
+      <c r="AD17" s="3">
         <v>126900</v>
       </c>
-      <c r="AD17" s="3">
+      <c r="AE17" s="3">
         <v>133400</v>
       </c>
-      <c r="AE17" s="3">
+      <c r="AF17" s="3">
         <v>127300</v>
       </c>
-      <c r="AF17" s="3">
+      <c r="AG17" s="3">
         <v>121400</v>
       </c>
-      <c r="AG17" s="3">
+      <c r="AH17" s="3">
         <v>134500</v>
       </c>
-      <c r="AH17" s="3">
+      <c r="AI17" s="3">
         <v>136300</v>
       </c>
-      <c r="AI17" s="3">
+      <c r="AJ17" s="3">
         <v>163000</v>
       </c>
-      <c r="AJ17" s="3">
+      <c r="AK17" s="3">
         <v>113400</v>
       </c>
-      <c r="AK17" s="3">
+      <c r="AL17" s="3">
         <v>116100</v>
       </c>
-      <c r="AL17" s="3">
+      <c r="AM17" s="3">
         <v>123500</v>
       </c>
-      <c r="AM17" s="3">
+      <c r="AN17" s="3">
         <v>111200</v>
       </c>
-      <c r="AN17" s="3">
+      <c r="AO17" s="3">
         <v>106400</v>
       </c>
-      <c r="AO17" s="3">
+      <c r="AP17" s="3">
         <v>109100</v>
       </c>
     </row>
-    <row r="18" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="18" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
       <c r="D18" s="3">
+        <v>22100</v>
+      </c>
+      <c r="E18" s="3">
         <v>23100</v>
       </c>
-      <c r="E18" s="3">
+      <c r="F18" s="3">
         <v>33900</v>
       </c>
-      <c r="F18" s="3">
+      <c r="G18" s="3">
         <v>41300</v>
       </c>
-      <c r="G18" s="3">
-        <v>24600</v>
-      </c>
       <c r="H18" s="3">
+        <v>24900</v>
+      </c>
+      <c r="I18" s="3">
         <v>21100</v>
       </c>
-      <c r="I18" s="3">
+      <c r="J18" s="3">
         <v>33700</v>
       </c>
-      <c r="J18" s="3">
+      <c r="K18" s="3">
         <v>39800</v>
       </c>
-      <c r="K18" s="3">
+      <c r="L18" s="3">
         <v>20100</v>
       </c>
-      <c r="L18" s="3">
+      <c r="M18" s="3">
         <v>18500</v>
       </c>
-      <c r="M18" s="3">
+      <c r="N18" s="3">
         <v>33000</v>
       </c>
-      <c r="N18" s="3">
+      <c r="O18" s="3">
         <v>32500</v>
       </c>
-      <c r="O18" s="3">
+      <c r="P18" s="3">
         <v>18500</v>
       </c>
-      <c r="P18" s="3">
+      <c r="Q18" s="3">
         <v>15200</v>
       </c>
-      <c r="Q18" s="3">
+      <c r="R18" s="3">
         <v>26500</v>
       </c>
-      <c r="R18" s="3">
+      <c r="S18" s="3">
         <v>27800</v>
       </c>
-      <c r="S18" s="3">
+      <c r="T18" s="3">
         <v>15200</v>
       </c>
-      <c r="T18" s="3">
+      <c r="U18" s="3">
         <v>14300</v>
       </c>
-      <c r="U18" s="3">
+      <c r="V18" s="3">
         <v>19600</v>
       </c>
-      <c r="V18" s="3">
+      <c r="W18" s="3">
         <v>22100</v>
       </c>
-      <c r="W18" s="3">
+      <c r="X18" s="3">
         <v>12900</v>
       </c>
-      <c r="X18" s="3">
+      <c r="Y18" s="3">
         <v>10500</v>
       </c>
-      <c r="Y18" s="3">
+      <c r="Z18" s="3">
         <v>16600</v>
       </c>
-      <c r="Z18" s="3">
+      <c r="AA18" s="3">
         <v>16000</v>
       </c>
-      <c r="AA18" s="3">
+      <c r="AB18" s="3">
         <v>7700</v>
       </c>
-      <c r="AB18" s="3">
+      <c r="AC18" s="3">
         <v>6800</v>
       </c>
-      <c r="AC18" s="3">
+      <c r="AD18" s="3">
         <v>13100</v>
       </c>
-      <c r="AD18" s="3">
+      <c r="AE18" s="3">
         <v>13900</v>
       </c>
-      <c r="AE18" s="3">
+      <c r="AF18" s="3">
         <v>5800</v>
       </c>
-      <c r="AF18" s="3">
+      <c r="AG18" s="3">
         <v>6800</v>
       </c>
-      <c r="AG18" s="3">
+      <c r="AH18" s="3">
         <v>10800</v>
       </c>
-      <c r="AH18" s="3">
+      <c r="AI18" s="3">
         <v>13500</v>
       </c>
-      <c r="AI18" s="3">
+      <c r="AJ18" s="3">
         <v>-36000</v>
       </c>
-      <c r="AJ18" s="3">
+      <c r="AK18" s="3">
         <v>4700</v>
       </c>
-      <c r="AK18" s="3">
+      <c r="AL18" s="3">
         <v>9300</v>
       </c>
-      <c r="AL18" s="3">
+      <c r="AM18" s="3">
         <v>10200</v>
       </c>
-      <c r="AM18" s="3">
+      <c r="AN18" s="3">
         <v>7400</v>
       </c>
-      <c r="AN18" s="3">
+      <c r="AO18" s="3">
         <v>6000</v>
       </c>
-      <c r="AO18" s="3">
+      <c r="AP18" s="3">
         <v>12200</v>
       </c>
     </row>
-    <row r="19" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="19" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C19" s="1" t="s">
         <v>14</v>
       </c>
@@ -2020,103 +2053,104 @@
       <c r="AM19" s="3"/>
       <c r="AN19" s="3"/>
       <c r="AO19" s="3"/>
+      <c r="AP19" s="3"/>
     </row>
-    <row r="20" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="20" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
       <c r="D20" s="3">
+        <v>600</v>
+      </c>
+      <c r="E20" s="3">
         <v>-500</v>
       </c>
-      <c r="E20" s="3">
+      <c r="F20" s="3">
         <v>-700</v>
       </c>
-      <c r="F20" s="3">
+      <c r="G20" s="3">
         <v>-900</v>
       </c>
-      <c r="G20" s="3">
+      <c r="H20" s="3">
         <v>600</v>
       </c>
-      <c r="H20" s="3">
+      <c r="I20" s="3">
         <v>-400</v>
       </c>
-      <c r="I20" s="3">
+      <c r="J20" s="3">
         <v>-700</v>
       </c>
-      <c r="J20" s="3">
+      <c r="K20" s="3">
         <v>-200</v>
       </c>
-      <c r="K20" s="3">
+      <c r="L20" s="3">
         <v>-500</v>
       </c>
-      <c r="L20" s="3">
+      <c r="M20" s="3">
         <v>-900</v>
       </c>
-      <c r="M20" s="3">
+      <c r="N20" s="3">
         <v>300</v>
       </c>
-      <c r="N20" s="3">
+      <c r="O20" s="3">
         <v>-300</v>
       </c>
-      <c r="O20" s="3">
+      <c r="P20" s="3">
         <v>-400</v>
       </c>
-      <c r="P20" s="3">
+      <c r="Q20" s="3">
         <v>500</v>
       </c>
-      <c r="Q20" s="3">
+      <c r="R20" s="3">
         <v>-500</v>
       </c>
-      <c r="R20" s="3">
+      <c r="S20" s="3">
         <v>-700</v>
       </c>
-      <c r="S20" s="3">
+      <c r="T20" s="3">
         <v>-400</v>
       </c>
-      <c r="T20" s="3">
+      <c r="U20" s="3">
         <v>100</v>
       </c>
-      <c r="U20" s="3">
+      <c r="V20" s="3">
         <v>200</v>
       </c>
-      <c r="V20" s="3">
+      <c r="W20" s="3">
         <v>300</v>
       </c>
-      <c r="W20" s="3">
+      <c r="X20" s="3">
         <v>100</v>
       </c>
-      <c r="X20" s="3">
+      <c r="Y20" s="3">
         <v>500</v>
       </c>
-      <c r="Y20" s="3">
+      <c r="Z20" s="3">
         <v>300</v>
       </c>
-      <c r="Z20" s="3">
+      <c r="AA20" s="3">
         <v>400</v>
       </c>
-      <c r="AA20" s="3">
+      <c r="AB20" s="3">
         <v>-1000</v>
       </c>
-      <c r="AB20" s="3">
+      <c r="AC20" s="3">
         <v>-400</v>
-      </c>
-      <c r="AC20" s="3">
-        <v>-600</v>
       </c>
       <c r="AD20" s="3">
         <v>-600</v>
       </c>
       <c r="AE20" s="3">
+        <v>-600</v>
+      </c>
+      <c r="AF20" s="3">
         <v>-500</v>
       </c>
-      <c r="AF20" s="3">
+      <c r="AG20" s="3">
         <v>-1200</v>
       </c>
-      <c r="AG20" s="3">
+      <c r="AH20" s="3">
         <v>-700</v>
-      </c>
-      <c r="AH20" s="3">
-        <v>-900</v>
       </c>
       <c r="AI20" s="3">
         <v>-900</v>
@@ -2125,194 +2159,200 @@
         <v>-900</v>
       </c>
       <c r="AK20" s="3">
+        <v>-900</v>
+      </c>
+      <c r="AL20" s="3">
         <v>-800</v>
       </c>
-      <c r="AL20" s="3">
+      <c r="AM20" s="3">
         <v>-700</v>
       </c>
-      <c r="AM20" s="3">
+      <c r="AN20" s="3">
         <v>-600</v>
-      </c>
-      <c r="AN20" s="3">
-        <v>-700</v>
       </c>
       <c r="AO20" s="3">
         <v>-700</v>
       </c>
+      <c r="AP20" s="3">
+        <v>-700</v>
+      </c>
     </row>
-    <row r="21" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="21" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
       <c r="D21" s="3">
+        <v>36000</v>
+      </c>
+      <c r="E21" s="3">
         <v>25800</v>
       </c>
-      <c r="E21" s="3">
+      <c r="F21" s="3">
         <v>47900</v>
       </c>
-      <c r="F21" s="3">
+      <c r="G21" s="3">
         <v>54600</v>
       </c>
-      <c r="G21" s="3">
-        <v>34500</v>
-      </c>
       <c r="H21" s="3">
+        <v>37100</v>
+      </c>
+      <c r="I21" s="3">
         <v>31600</v>
       </c>
-      <c r="I21" s="3">
+      <c r="J21" s="3">
         <v>44300</v>
       </c>
-      <c r="J21" s="3">
+      <c r="K21" s="3">
         <v>49300</v>
       </c>
-      <c r="K21" s="3">
+      <c r="L21" s="3">
         <v>29500</v>
       </c>
-      <c r="L21" s="3">
+      <c r="M21" s="3">
         <v>27700</v>
       </c>
-      <c r="M21" s="3">
+      <c r="N21" s="3">
         <v>40100</v>
       </c>
-      <c r="N21" s="3">
+      <c r="O21" s="3">
         <v>39900</v>
       </c>
-      <c r="O21" s="3">
+      <c r="P21" s="3">
         <v>26000</v>
       </c>
-      <c r="P21" s="3">
+      <c r="Q21" s="3">
         <v>22700</v>
       </c>
-      <c r="Q21" s="3">
+      <c r="R21" s="3">
         <v>32900</v>
       </c>
-      <c r="R21" s="3">
+      <c r="S21" s="3">
         <v>33700</v>
       </c>
-      <c r="S21" s="3">
+      <c r="T21" s="3">
         <v>21100</v>
       </c>
-      <c r="T21" s="3">
+      <c r="U21" s="3">
         <v>20400</v>
       </c>
-      <c r="U21" s="3">
+      <c r="V21" s="3">
         <v>25700</v>
       </c>
-      <c r="V21" s="3">
+      <c r="W21" s="3">
         <v>28300</v>
       </c>
-      <c r="W21" s="3">
+      <c r="X21" s="3">
         <v>19000</v>
       </c>
-      <c r="X21" s="3">
+      <c r="Y21" s="3">
         <v>16600</v>
       </c>
-      <c r="Y21" s="3">
+      <c r="Z21" s="3">
         <v>22500</v>
       </c>
-      <c r="Z21" s="3">
+      <c r="AA21" s="3">
         <v>21900</v>
       </c>
-      <c r="AA21" s="3">
+      <c r="AB21" s="3">
         <v>12200</v>
       </c>
-      <c r="AB21" s="3">
+      <c r="AC21" s="3">
         <v>11800</v>
       </c>
-      <c r="AC21" s="3">
+      <c r="AD21" s="3">
         <v>17900</v>
       </c>
-      <c r="AD21" s="3">
+      <c r="AE21" s="3">
         <v>18700</v>
       </c>
-      <c r="AE21" s="3">
+      <c r="AF21" s="3">
         <v>10700</v>
       </c>
-      <c r="AF21" s="3">
+      <c r="AG21" s="3">
         <v>11000</v>
       </c>
-      <c r="AG21" s="3">
+      <c r="AH21" s="3">
         <v>15600</v>
       </c>
-      <c r="AH21" s="3">
+      <c r="AI21" s="3">
         <v>18000</v>
       </c>
-      <c r="AI21" s="3">
+      <c r="AJ21" s="3">
         <v>-31200</v>
       </c>
-      <c r="AJ21" s="3">
+      <c r="AK21" s="3">
         <v>9300</v>
       </c>
-      <c r="AK21" s="3">
+      <c r="AL21" s="3">
         <v>14000</v>
       </c>
-      <c r="AL21" s="3">
+      <c r="AM21" s="3">
         <v>15300</v>
       </c>
-      <c r="AM21" s="3">
+      <c r="AN21" s="3">
         <v>12200</v>
       </c>
-      <c r="AN21" s="3">
+      <c r="AO21" s="3">
         <v>10500</v>
       </c>
-      <c r="AO21" s="3">
+      <c r="AP21" s="3">
         <v>16800</v>
       </c>
     </row>
-    <row r="22" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="22" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C22" s="1" t="s">
         <v>17</v>
       </c>
       <c r="D22" s="3">
+        <v>3000</v>
+      </c>
+      <c r="E22" s="3">
         <v>3400</v>
       </c>
-      <c r="E22" s="3">
+      <c r="F22" s="3">
         <v>3800</v>
       </c>
-      <c r="F22" s="3">
+      <c r="G22" s="3">
         <v>3300</v>
       </c>
-      <c r="G22" s="3">
+      <c r="H22" s="3">
         <v>1500</v>
       </c>
-      <c r="H22" s="3">
+      <c r="I22" s="3">
         <v>1200</v>
       </c>
-      <c r="I22" s="3">
+      <c r="J22" s="3">
         <v>1400</v>
       </c>
-      <c r="J22" s="3">
+      <c r="K22" s="3">
         <v>1300</v>
-      </c>
-      <c r="K22" s="3">
-        <v>1200</v>
       </c>
       <c r="L22" s="3">
         <v>1200</v>
       </c>
       <c r="M22" s="3">
+        <v>1200</v>
+      </c>
+      <c r="N22" s="3">
         <v>700</v>
       </c>
-      <c r="N22" s="3">
+      <c r="O22" s="3">
         <v>1100</v>
       </c>
-      <c r="O22" s="3">
+      <c r="P22" s="3">
         <v>1400</v>
       </c>
-      <c r="P22" s="3">
+      <c r="Q22" s="3">
         <v>1500</v>
       </c>
-      <c r="Q22" s="3">
+      <c r="R22" s="3">
         <v>1400</v>
       </c>
-      <c r="R22" s="3">
+      <c r="S22" s="3">
         <v>900</v>
       </c>
-      <c r="S22" s="3">
+      <c r="T22" s="3">
         <v>400</v>
-      </c>
-      <c r="T22" s="3">
-        <v>300</v>
       </c>
       <c r="U22" s="3">
         <v>300</v>
@@ -2321,25 +2361,25 @@
         <v>300</v>
       </c>
       <c r="W22" s="3">
-        <v>400</v>
+        <v>300</v>
       </c>
       <c r="X22" s="3">
         <v>400</v>
       </c>
       <c r="Y22" s="3">
+        <v>400</v>
+      </c>
+      <c r="Z22" s="3">
         <v>300</v>
       </c>
-      <c r="Z22" s="3">
+      <c r="AA22" s="3">
         <v>400</v>
-      </c>
-      <c r="AA22" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AB22" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AC22" s="3">
-        <v>0</v>
+      <c r="AC22" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="AD22" s="3">
         <v>0</v>
@@ -2377,246 +2417,255 @@
       <c r="AO22" s="3">
         <v>0</v>
       </c>
+      <c r="AP22" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="23" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="23" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C23" s="1" t="s">
         <v>18</v>
       </c>
       <c r="D23" s="3">
+        <v>19900</v>
+      </c>
+      <c r="E23" s="3">
         <v>19600</v>
       </c>
-      <c r="E23" s="3">
+      <c r="F23" s="3">
         <v>30800</v>
       </c>
-      <c r="F23" s="3">
+      <c r="G23" s="3">
         <v>39000</v>
       </c>
-      <c r="G23" s="3">
+      <c r="H23" s="3">
         <v>22400</v>
       </c>
-      <c r="H23" s="3">
+      <c r="I23" s="3">
         <v>20300</v>
       </c>
-      <c r="I23" s="3">
+      <c r="J23" s="3">
         <v>33000</v>
       </c>
-      <c r="J23" s="3">
+      <c r="K23" s="3">
         <v>38700</v>
       </c>
-      <c r="K23" s="3">
+      <c r="L23" s="3">
         <v>19300</v>
       </c>
-      <c r="L23" s="3">
+      <c r="M23" s="3">
         <v>18200</v>
       </c>
-      <c r="M23" s="3">
+      <c r="N23" s="3">
         <v>32000</v>
       </c>
-      <c r="N23" s="3">
+      <c r="O23" s="3">
         <v>31700</v>
       </c>
-      <c r="O23" s="3">
+      <c r="P23" s="3">
         <v>17500</v>
       </c>
-      <c r="P23" s="3">
+      <c r="Q23" s="3">
         <v>14200</v>
       </c>
-      <c r="Q23" s="3">
+      <c r="R23" s="3">
         <v>24700</v>
       </c>
-      <c r="R23" s="3">
+      <c r="S23" s="3">
         <v>26200</v>
       </c>
-      <c r="S23" s="3">
+      <c r="T23" s="3">
         <v>14400</v>
       </c>
-      <c r="T23" s="3">
+      <c r="U23" s="3">
         <v>14100</v>
       </c>
-      <c r="U23" s="3">
+      <c r="V23" s="3">
         <v>19500</v>
       </c>
-      <c r="V23" s="3">
+      <c r="W23" s="3">
         <v>22000</v>
       </c>
-      <c r="W23" s="3">
+      <c r="X23" s="3">
         <v>12700</v>
       </c>
-      <c r="X23" s="3">
+      <c r="Y23" s="3">
         <v>10600</v>
       </c>
-      <c r="Y23" s="3">
+      <c r="Z23" s="3">
         <v>16600</v>
       </c>
-      <c r="Z23" s="3">
+      <c r="AA23" s="3">
         <v>16000</v>
       </c>
-      <c r="AA23" s="3">
+      <c r="AB23" s="3">
         <v>6800</v>
       </c>
-      <c r="AB23" s="3">
+      <c r="AC23" s="3">
         <v>6300</v>
       </c>
-      <c r="AC23" s="3">
+      <c r="AD23" s="3">
         <v>12500</v>
       </c>
-      <c r="AD23" s="3">
+      <c r="AE23" s="3">
         <v>13300</v>
       </c>
-      <c r="AE23" s="3">
+      <c r="AF23" s="3">
         <v>5300</v>
       </c>
-      <c r="AF23" s="3">
+      <c r="AG23" s="3">
         <v>5600</v>
       </c>
-      <c r="AG23" s="3">
+      <c r="AH23" s="3">
         <v>10100</v>
       </c>
-      <c r="AH23" s="3">
+      <c r="AI23" s="3">
         <v>12500</v>
       </c>
-      <c r="AI23" s="3">
+      <c r="AJ23" s="3">
         <v>-36900</v>
       </c>
-      <c r="AJ23" s="3">
+      <c r="AK23" s="3">
         <v>3800</v>
       </c>
-      <c r="AK23" s="3">
+      <c r="AL23" s="3">
         <v>8500</v>
       </c>
-      <c r="AL23" s="3">
+      <c r="AM23" s="3">
         <v>9500</v>
       </c>
-      <c r="AM23" s="3">
+      <c r="AN23" s="3">
         <v>6800</v>
       </c>
-      <c r="AN23" s="3">
+      <c r="AO23" s="3">
         <v>5400</v>
       </c>
-      <c r="AO23" s="3">
+      <c r="AP23" s="3">
         <v>11500</v>
       </c>
     </row>
-    <row r="24" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="24" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C24" s="1" t="s">
         <v>19</v>
       </c>
       <c r="D24" s="3">
+        <v>4500</v>
+      </c>
+      <c r="E24" s="3">
         <v>5300</v>
       </c>
-      <c r="E24" s="3">
+      <c r="F24" s="3">
         <v>8200</v>
       </c>
-      <c r="F24" s="3">
+      <c r="G24" s="3">
         <v>9800</v>
       </c>
-      <c r="G24" s="3">
+      <c r="H24" s="3">
         <v>6100</v>
       </c>
-      <c r="H24" s="3">
+      <c r="I24" s="3">
         <v>5300</v>
       </c>
-      <c r="I24" s="3">
+      <c r="J24" s="3">
         <v>8900</v>
       </c>
-      <c r="J24" s="3">
+      <c r="K24" s="3">
         <v>9800</v>
       </c>
-      <c r="K24" s="3">
+      <c r="L24" s="3">
         <v>5500</v>
       </c>
-      <c r="L24" s="3">
+      <c r="M24" s="3">
         <v>3300</v>
       </c>
-      <c r="M24" s="3">
+      <c r="N24" s="3">
         <v>8800</v>
       </c>
-      <c r="N24" s="3">
+      <c r="O24" s="3">
         <v>8200</v>
       </c>
-      <c r="O24" s="3">
+      <c r="P24" s="3">
         <v>5900</v>
       </c>
-      <c r="P24" s="3">
+      <c r="Q24" s="3">
         <v>3500</v>
       </c>
-      <c r="Q24" s="3">
+      <c r="R24" s="3">
         <v>6700</v>
       </c>
-      <c r="R24" s="3">
+      <c r="S24" s="3">
         <v>6500</v>
-      </c>
-      <c r="S24" s="3">
-        <v>3900</v>
       </c>
       <c r="T24" s="3">
         <v>3900</v>
       </c>
       <c r="U24" s="3">
+        <v>3900</v>
+      </c>
+      <c r="V24" s="3">
         <v>5300</v>
       </c>
-      <c r="V24" s="3">
+      <c r="W24" s="3">
         <v>5400</v>
       </c>
-      <c r="W24" s="3">
+      <c r="X24" s="3">
         <v>3600</v>
       </c>
-      <c r="X24" s="3">
+      <c r="Y24" s="3">
         <v>2700</v>
       </c>
-      <c r="Y24" s="3">
+      <c r="Z24" s="3">
         <v>4400</v>
       </c>
-      <c r="Z24" s="3">
+      <c r="AA24" s="3">
         <v>4200</v>
       </c>
-      <c r="AA24" s="3">
+      <c r="AB24" s="3">
         <v>2000</v>
       </c>
-      <c r="AB24" s="3">
+      <c r="AC24" s="3">
         <v>1800</v>
       </c>
-      <c r="AC24" s="3">
+      <c r="AD24" s="3">
         <v>3300</v>
       </c>
-      <c r="AD24" s="3">
+      <c r="AE24" s="3">
         <v>3500</v>
-      </c>
-      <c r="AE24" s="3">
-        <v>1500</v>
       </c>
       <c r="AF24" s="3">
         <v>1500</v>
       </c>
       <c r="AG24" s="3">
+        <v>1500</v>
+      </c>
+      <c r="AH24" s="3">
         <v>2700</v>
       </c>
-      <c r="AH24" s="3">
+      <c r="AI24" s="3">
         <v>3400</v>
       </c>
-      <c r="AI24" s="3">
+      <c r="AJ24" s="3">
         <v>1200</v>
       </c>
-      <c r="AJ24" s="3">
+      <c r="AK24" s="3">
         <v>-100</v>
       </c>
-      <c r="AK24" s="3">
+      <c r="AL24" s="3">
         <v>3300</v>
       </c>
-      <c r="AL24" s="3">
+      <c r="AM24" s="3">
         <v>3700</v>
       </c>
-      <c r="AM24" s="3">
+      <c r="AN24" s="3">
         <v>2600</v>
       </c>
-      <c r="AN24" s="3">
+      <c r="AO24" s="3">
         <v>1800</v>
       </c>
-      <c r="AO24" s="3">
+      <c r="AP24" s="3">
         <v>4400</v>
       </c>
     </row>
-    <row r="25" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="25" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C25" s="1" t="s">
         <v>20</v>
       </c>
@@ -2734,246 +2783,255 @@
       <c r="AO25" s="3">
         <v>0</v>
       </c>
+      <c r="AP25" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="26" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="26" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E26" s="3">
         <v>14300</v>
       </c>
-      <c r="E26" s="3">
+      <c r="F26" s="3">
         <v>22600</v>
       </c>
-      <c r="F26" s="3">
+      <c r="G26" s="3">
         <v>29200</v>
       </c>
-      <c r="G26" s="3">
+      <c r="H26" s="3">
         <v>16300</v>
       </c>
-      <c r="H26" s="3">
+      <c r="I26" s="3">
         <v>15000</v>
       </c>
-      <c r="I26" s="3">
+      <c r="J26" s="3">
         <v>24100</v>
       </c>
-      <c r="J26" s="3">
+      <c r="K26" s="3">
         <v>28900</v>
       </c>
-      <c r="K26" s="3">
+      <c r="L26" s="3">
         <v>13800</v>
       </c>
-      <c r="L26" s="3">
+      <c r="M26" s="3">
         <v>14900</v>
       </c>
-      <c r="M26" s="3">
+      <c r="N26" s="3">
         <v>23200</v>
       </c>
-      <c r="N26" s="3">
+      <c r="O26" s="3">
         <v>23400</v>
       </c>
-      <c r="O26" s="3">
+      <c r="P26" s="3">
         <v>11600</v>
       </c>
-      <c r="P26" s="3">
+      <c r="Q26" s="3">
         <v>10700</v>
       </c>
-      <c r="Q26" s="3">
+      <c r="R26" s="3">
         <v>18000</v>
       </c>
-      <c r="R26" s="3">
+      <c r="S26" s="3">
         <v>19700</v>
       </c>
-      <c r="S26" s="3">
+      <c r="T26" s="3">
         <v>10600</v>
       </c>
-      <c r="T26" s="3">
+      <c r="U26" s="3">
         <v>10200</v>
       </c>
-      <c r="U26" s="3">
+      <c r="V26" s="3">
         <v>14100</v>
       </c>
-      <c r="V26" s="3">
+      <c r="W26" s="3">
         <v>16600</v>
       </c>
-      <c r="W26" s="3">
+      <c r="X26" s="3">
         <v>9100</v>
       </c>
-      <c r="X26" s="3">
+      <c r="Y26" s="3">
         <v>7900</v>
       </c>
-      <c r="Y26" s="3">
+      <c r="Z26" s="3">
         <v>12200</v>
       </c>
-      <c r="Z26" s="3">
+      <c r="AA26" s="3">
         <v>11800</v>
       </c>
-      <c r="AA26" s="3">
+      <c r="AB26" s="3">
         <v>4800</v>
       </c>
-      <c r="AB26" s="3">
+      <c r="AC26" s="3">
         <v>4500</v>
       </c>
-      <c r="AC26" s="3">
+      <c r="AD26" s="3">
         <v>9300</v>
       </c>
-      <c r="AD26" s="3">
+      <c r="AE26" s="3">
         <v>9800</v>
       </c>
-      <c r="AE26" s="3">
+      <c r="AF26" s="3">
         <v>3800</v>
       </c>
-      <c r="AF26" s="3">
+      <c r="AG26" s="3">
         <v>4100</v>
       </c>
-      <c r="AG26" s="3">
+      <c r="AH26" s="3">
         <v>7400</v>
       </c>
-      <c r="AH26" s="3">
+      <c r="AI26" s="3">
         <v>9100</v>
       </c>
-      <c r="AI26" s="3">
+      <c r="AJ26" s="3">
         <v>-38100</v>
       </c>
-      <c r="AJ26" s="3">
+      <c r="AK26" s="3">
         <v>3900</v>
       </c>
-      <c r="AK26" s="3">
+      <c r="AL26" s="3">
         <v>5200</v>
       </c>
-      <c r="AL26" s="3">
+      <c r="AM26" s="3">
         <v>5800</v>
       </c>
-      <c r="AM26" s="3">
+      <c r="AN26" s="3">
         <v>4200</v>
       </c>
-      <c r="AN26" s="3">
+      <c r="AO26" s="3">
         <v>3600</v>
       </c>
-      <c r="AO26" s="3">
+      <c r="AP26" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="27" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="27" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
       <c r="D27" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E27" s="3">
         <v>14300</v>
       </c>
-      <c r="E27" s="3">
+      <c r="F27" s="3">
         <v>22600</v>
       </c>
-      <c r="F27" s="3">
+      <c r="G27" s="3">
         <v>29200</v>
       </c>
-      <c r="G27" s="3">
+      <c r="H27" s="3">
         <v>16300</v>
       </c>
-      <c r="H27" s="3">
+      <c r="I27" s="3">
         <v>15000</v>
       </c>
-      <c r="I27" s="3">
+      <c r="J27" s="3">
         <v>24100</v>
       </c>
-      <c r="J27" s="3">
+      <c r="K27" s="3">
         <v>28900</v>
       </c>
-      <c r="K27" s="3">
+      <c r="L27" s="3">
         <v>13800</v>
       </c>
-      <c r="L27" s="3">
+      <c r="M27" s="3">
         <v>14900</v>
       </c>
-      <c r="M27" s="3">
+      <c r="N27" s="3">
         <v>23200</v>
       </c>
-      <c r="N27" s="3">
+      <c r="O27" s="3">
         <v>23400</v>
       </c>
-      <c r="O27" s="3">
+      <c r="P27" s="3">
         <v>11600</v>
       </c>
-      <c r="P27" s="3">
+      <c r="Q27" s="3">
         <v>10700</v>
       </c>
-      <c r="Q27" s="3">
+      <c r="R27" s="3">
         <v>18000</v>
       </c>
-      <c r="R27" s="3">
+      <c r="S27" s="3">
         <v>19700</v>
       </c>
-      <c r="S27" s="3">
+      <c r="T27" s="3">
         <v>10600</v>
       </c>
-      <c r="T27" s="3">
+      <c r="U27" s="3">
         <v>10200</v>
       </c>
-      <c r="U27" s="3">
+      <c r="V27" s="3">
         <v>14100</v>
       </c>
-      <c r="V27" s="3">
+      <c r="W27" s="3">
         <v>16600</v>
       </c>
-      <c r="W27" s="3">
+      <c r="X27" s="3">
         <v>9100</v>
       </c>
-      <c r="X27" s="3">
+      <c r="Y27" s="3">
         <v>7900</v>
       </c>
-      <c r="Y27" s="3">
+      <c r="Z27" s="3">
         <v>12200</v>
       </c>
-      <c r="Z27" s="3">
+      <c r="AA27" s="3">
         <v>11800</v>
       </c>
-      <c r="AA27" s="3">
+      <c r="AB27" s="3">
         <v>4800</v>
       </c>
-      <c r="AB27" s="3">
+      <c r="AC27" s="3">
         <v>4500</v>
       </c>
-      <c r="AC27" s="3">
+      <c r="AD27" s="3">
         <v>9300</v>
       </c>
-      <c r="AD27" s="3">
+      <c r="AE27" s="3">
         <v>9800</v>
       </c>
-      <c r="AE27" s="3">
+      <c r="AF27" s="3">
         <v>3800</v>
       </c>
-      <c r="AF27" s="3">
+      <c r="AG27" s="3">
         <v>4100</v>
       </c>
-      <c r="AG27" s="3">
+      <c r="AH27" s="3">
         <v>7400</v>
       </c>
-      <c r="AH27" s="3">
+      <c r="AI27" s="3">
         <v>9100</v>
       </c>
-      <c r="AI27" s="3">
+      <c r="AJ27" s="3">
         <v>-38100</v>
       </c>
-      <c r="AJ27" s="3">
+      <c r="AK27" s="3">
         <v>3900</v>
       </c>
-      <c r="AK27" s="3">
+      <c r="AL27" s="3">
         <v>5200</v>
       </c>
-      <c r="AL27" s="3">
+      <c r="AM27" s="3">
         <v>5800</v>
       </c>
-      <c r="AM27" s="3">
+      <c r="AN27" s="3">
         <v>4200</v>
       </c>
-      <c r="AN27" s="3">
+      <c r="AO27" s="3">
         <v>3600</v>
       </c>
-      <c r="AO27" s="3">
+      <c r="AP27" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="28" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="28" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C28" s="1" t="s">
         <v>23</v>
       </c>
@@ -3091,8 +3149,11 @@
       <c r="AO28" s="3">
         <v>0</v>
       </c>
+      <c r="AP28" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="29" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="29" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C29" s="1" t="s">
         <v>24</v>
       </c>
@@ -3171,17 +3232,17 @@
       <c r="AB29" s="3">
         <v>0</v>
       </c>
-      <c r="AC29" s="3" t="s">
-        <v>8</v>
+      <c r="AC29" s="3">
+        <v>0</v>
       </c>
       <c r="AD29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AE29" s="3">
-        <v>0</v>
-      </c>
-      <c r="AF29" s="3" t="s">
+      <c r="AE29" s="3" t="s">
         <v>8</v>
+      </c>
+      <c r="AF29" s="3">
+        <v>0</v>
       </c>
       <c r="AG29" s="3" t="s">
         <v>8</v>
@@ -3189,14 +3250,14 @@
       <c r="AH29" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="AI29" s="3">
+      <c r="AI29" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="AJ29" s="3">
         <v>700</v>
       </c>
-      <c r="AJ29" s="3">
+      <c r="AK29" s="3">
         <v>13200</v>
-      </c>
-      <c r="AK29" s="3" t="s">
-        <v>8</v>
       </c>
       <c r="AL29" s="3" t="s">
         <v>8</v>
@@ -3210,8 +3271,11 @@
       <c r="AO29" s="3" t="s">
         <v>8</v>
       </c>
+      <c r="AP29" s="3" t="s">
+        <v>8</v>
+      </c>
     </row>
-    <row r="30" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="30" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C30" s="1" t="s">
         <v>25</v>
       </c>
@@ -3329,8 +3393,11 @@
       <c r="AO30" s="3">
         <v>0</v>
       </c>
+      <c r="AP30" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="31" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="31" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C31" s="1" t="s">
         <v>26</v>
       </c>
@@ -3448,103 +3515,106 @@
       <c r="AO31" s="3">
         <v>0</v>
       </c>
+      <c r="AP31" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="32" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="32" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
       <c r="D32" s="3">
+        <v>-600</v>
+      </c>
+      <c r="E32" s="3">
         <v>500</v>
       </c>
-      <c r="E32" s="3">
+      <c r="F32" s="3">
         <v>700</v>
       </c>
-      <c r="F32" s="3">
+      <c r="G32" s="3">
         <v>900</v>
       </c>
-      <c r="G32" s="3">
+      <c r="H32" s="3">
         <v>-600</v>
       </c>
-      <c r="H32" s="3">
+      <c r="I32" s="3">
         <v>400</v>
       </c>
-      <c r="I32" s="3">
+      <c r="J32" s="3">
         <v>700</v>
       </c>
-      <c r="J32" s="3">
+      <c r="K32" s="3">
         <v>200</v>
       </c>
-      <c r="K32" s="3">
+      <c r="L32" s="3">
         <v>500</v>
       </c>
-      <c r="L32" s="3">
+      <c r="M32" s="3">
         <v>900</v>
       </c>
-      <c r="M32" s="3">
+      <c r="N32" s="3">
         <v>-300</v>
       </c>
-      <c r="N32" s="3">
+      <c r="O32" s="3">
         <v>300</v>
       </c>
-      <c r="O32" s="3">
+      <c r="P32" s="3">
         <v>400</v>
       </c>
-      <c r="P32" s="3">
+      <c r="Q32" s="3">
         <v>-500</v>
       </c>
-      <c r="Q32" s="3">
+      <c r="R32" s="3">
         <v>500</v>
       </c>
-      <c r="R32" s="3">
+      <c r="S32" s="3">
         <v>700</v>
       </c>
-      <c r="S32" s="3">
+      <c r="T32" s="3">
         <v>400</v>
       </c>
-      <c r="T32" s="3">
+      <c r="U32" s="3">
         <v>-100</v>
       </c>
-      <c r="U32" s="3">
+      <c r="V32" s="3">
         <v>-200</v>
       </c>
-      <c r="V32" s="3">
+      <c r="W32" s="3">
         <v>-300</v>
       </c>
-      <c r="W32" s="3">
+      <c r="X32" s="3">
         <v>-100</v>
       </c>
-      <c r="X32" s="3">
+      <c r="Y32" s="3">
         <v>-500</v>
       </c>
-      <c r="Y32" s="3">
+      <c r="Z32" s="3">
         <v>-300</v>
       </c>
-      <c r="Z32" s="3">
+      <c r="AA32" s="3">
         <v>-400</v>
       </c>
-      <c r="AA32" s="3">
+      <c r="AB32" s="3">
         <v>1000</v>
       </c>
-      <c r="AB32" s="3">
+      <c r="AC32" s="3">
         <v>400</v>
-      </c>
-      <c r="AC32" s="3">
-        <v>600</v>
       </c>
       <c r="AD32" s="3">
         <v>600</v>
       </c>
       <c r="AE32" s="3">
+        <v>600</v>
+      </c>
+      <c r="AF32" s="3">
         <v>500</v>
       </c>
-      <c r="AF32" s="3">
+      <c r="AG32" s="3">
         <v>1200</v>
       </c>
-      <c r="AG32" s="3">
+      <c r="AH32" s="3">
         <v>700</v>
-      </c>
-      <c r="AH32" s="3">
-        <v>900</v>
       </c>
       <c r="AI32" s="3">
         <v>900</v>
@@ -3553,141 +3623,147 @@
         <v>900</v>
       </c>
       <c r="AK32" s="3">
+        <v>900</v>
+      </c>
+      <c r="AL32" s="3">
         <v>800</v>
       </c>
-      <c r="AL32" s="3">
+      <c r="AM32" s="3">
         <v>700</v>
       </c>
-      <c r="AM32" s="3">
+      <c r="AN32" s="3">
         <v>600</v>
-      </c>
-      <c r="AN32" s="3">
-        <v>700</v>
       </c>
       <c r="AO32" s="3">
         <v>700</v>
       </c>
+      <c r="AP32" s="3">
+        <v>700</v>
+      </c>
     </row>
-    <row r="33" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="33" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D33" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E33" s="3">
         <v>14300</v>
       </c>
-      <c r="E33" s="3">
+      <c r="F33" s="3">
         <v>22600</v>
       </c>
-      <c r="F33" s="3">
+      <c r="G33" s="3">
         <v>29200</v>
       </c>
-      <c r="G33" s="3">
+      <c r="H33" s="3">
         <v>16300</v>
       </c>
-      <c r="H33" s="3">
+      <c r="I33" s="3">
         <v>15000</v>
       </c>
-      <c r="I33" s="3">
+      <c r="J33" s="3">
         <v>24100</v>
       </c>
-      <c r="J33" s="3">
+      <c r="K33" s="3">
         <v>28900</v>
       </c>
-      <c r="K33" s="3">
+      <c r="L33" s="3">
         <v>13800</v>
       </c>
-      <c r="L33" s="3">
+      <c r="M33" s="3">
         <v>14900</v>
       </c>
-      <c r="M33" s="3">
+      <c r="N33" s="3">
         <v>23200</v>
       </c>
-      <c r="N33" s="3">
+      <c r="O33" s="3">
         <v>23400</v>
       </c>
-      <c r="O33" s="3">
+      <c r="P33" s="3">
         <v>11600</v>
       </c>
-      <c r="P33" s="3">
+      <c r="Q33" s="3">
         <v>10700</v>
       </c>
-      <c r="Q33" s="3">
+      <c r="R33" s="3">
         <v>18000</v>
       </c>
-      <c r="R33" s="3">
+      <c r="S33" s="3">
         <v>19700</v>
       </c>
-      <c r="S33" s="3">
+      <c r="T33" s="3">
         <v>10600</v>
       </c>
-      <c r="T33" s="3">
+      <c r="U33" s="3">
         <v>10200</v>
       </c>
-      <c r="U33" s="3">
+      <c r="V33" s="3">
         <v>14100</v>
       </c>
-      <c r="V33" s="3">
+      <c r="W33" s="3">
         <v>16600</v>
       </c>
-      <c r="W33" s="3">
+      <c r="X33" s="3">
         <v>9100</v>
       </c>
-      <c r="X33" s="3">
+      <c r="Y33" s="3">
         <v>7900</v>
       </c>
-      <c r="Y33" s="3">
+      <c r="Z33" s="3">
         <v>12200</v>
       </c>
-      <c r="Z33" s="3">
+      <c r="AA33" s="3">
         <v>11800</v>
       </c>
-      <c r="AA33" s="3">
+      <c r="AB33" s="3">
         <v>4800</v>
       </c>
-      <c r="AB33" s="3">
+      <c r="AC33" s="3">
         <v>4500</v>
       </c>
-      <c r="AC33" s="3">
+      <c r="AD33" s="3">
         <v>9300</v>
       </c>
-      <c r="AD33" s="3">
+      <c r="AE33" s="3">
         <v>9800</v>
       </c>
-      <c r="AE33" s="3">
+      <c r="AF33" s="3">
         <v>3800</v>
       </c>
-      <c r="AF33" s="3">
+      <c r="AG33" s="3">
         <v>4100</v>
       </c>
-      <c r="AG33" s="3">
+      <c r="AH33" s="3">
         <v>7400</v>
       </c>
-      <c r="AH33" s="3">
+      <c r="AI33" s="3">
         <v>9100</v>
       </c>
-      <c r="AI33" s="3">
+      <c r="AJ33" s="3">
         <v>-37400</v>
       </c>
-      <c r="AJ33" s="3">
+      <c r="AK33" s="3">
         <v>17100</v>
       </c>
-      <c r="AK33" s="3">
+      <c r="AL33" s="3">
         <v>5200</v>
       </c>
-      <c r="AL33" s="3">
+      <c r="AM33" s="3">
         <v>5800</v>
       </c>
-      <c r="AM33" s="3">
+      <c r="AN33" s="3">
         <v>4200</v>
       </c>
-      <c r="AN33" s="3">
+      <c r="AO33" s="3">
         <v>3600</v>
       </c>
-      <c r="AO33" s="3">
+      <c r="AP33" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="34" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="34" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C34" s="1" t="s">
         <v>29</v>
       </c>
@@ -3805,251 +3881,260 @@
       <c r="AO34" s="3">
         <v>0</v>
       </c>
+      <c r="AP34" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="35" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="35" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
       <c r="D35" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E35" s="3">
         <v>14300</v>
       </c>
-      <c r="E35" s="3">
+      <c r="F35" s="3">
         <v>22600</v>
       </c>
-      <c r="F35" s="3">
+      <c r="G35" s="3">
         <v>29200</v>
       </c>
-      <c r="G35" s="3">
+      <c r="H35" s="3">
         <v>16300</v>
       </c>
-      <c r="H35" s="3">
+      <c r="I35" s="3">
         <v>15000</v>
       </c>
-      <c r="I35" s="3">
+      <c r="J35" s="3">
         <v>24100</v>
       </c>
-      <c r="J35" s="3">
+      <c r="K35" s="3">
         <v>28900</v>
       </c>
-      <c r="K35" s="3">
+      <c r="L35" s="3">
         <v>13800</v>
       </c>
-      <c r="L35" s="3">
+      <c r="M35" s="3">
         <v>14900</v>
       </c>
-      <c r="M35" s="3">
+      <c r="N35" s="3">
         <v>23200</v>
       </c>
-      <c r="N35" s="3">
+      <c r="O35" s="3">
         <v>23400</v>
       </c>
-      <c r="O35" s="3">
+      <c r="P35" s="3">
         <v>11600</v>
       </c>
-      <c r="P35" s="3">
+      <c r="Q35" s="3">
         <v>10700</v>
       </c>
-      <c r="Q35" s="3">
+      <c r="R35" s="3">
         <v>18000</v>
       </c>
-      <c r="R35" s="3">
+      <c r="S35" s="3">
         <v>19700</v>
       </c>
-      <c r="S35" s="3">
+      <c r="T35" s="3">
         <v>10600</v>
       </c>
-      <c r="T35" s="3">
+      <c r="U35" s="3">
         <v>10200</v>
       </c>
-      <c r="U35" s="3">
+      <c r="V35" s="3">
         <v>14100</v>
       </c>
-      <c r="V35" s="3">
+      <c r="W35" s="3">
         <v>16600</v>
       </c>
-      <c r="W35" s="3">
+      <c r="X35" s="3">
         <v>9100</v>
       </c>
-      <c r="X35" s="3">
+      <c r="Y35" s="3">
         <v>7900</v>
       </c>
-      <c r="Y35" s="3">
+      <c r="Z35" s="3">
         <v>12200</v>
       </c>
-      <c r="Z35" s="3">
+      <c r="AA35" s="3">
         <v>11800</v>
       </c>
-      <c r="AA35" s="3">
+      <c r="AB35" s="3">
         <v>4800</v>
       </c>
-      <c r="AB35" s="3">
+      <c r="AC35" s="3">
         <v>4500</v>
       </c>
-      <c r="AC35" s="3">
+      <c r="AD35" s="3">
         <v>9300</v>
       </c>
-      <c r="AD35" s="3">
+      <c r="AE35" s="3">
         <v>9800</v>
       </c>
-      <c r="AE35" s="3">
+      <c r="AF35" s="3">
         <v>3800</v>
       </c>
-      <c r="AF35" s="3">
+      <c r="AG35" s="3">
         <v>4100</v>
       </c>
-      <c r="AG35" s="3">
+      <c r="AH35" s="3">
         <v>7400</v>
       </c>
-      <c r="AH35" s="3">
+      <c r="AI35" s="3">
         <v>9100</v>
       </c>
-      <c r="AI35" s="3">
+      <c r="AJ35" s="3">
         <v>-37400</v>
       </c>
-      <c r="AJ35" s="3">
+      <c r="AK35" s="3">
         <v>17100</v>
       </c>
-      <c r="AK35" s="3">
+      <c r="AL35" s="3">
         <v>5200</v>
       </c>
-      <c r="AL35" s="3">
+      <c r="AM35" s="3">
         <v>5800</v>
       </c>
-      <c r="AM35" s="3">
+      <c r="AN35" s="3">
         <v>4200</v>
       </c>
-      <c r="AN35" s="3">
+      <c r="AO35" s="3">
         <v>3600</v>
       </c>
-      <c r="AO35" s="3">
+      <c r="AP35" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="37" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="37" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B37" s="1" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="38" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="38" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C38" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D38" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E38" s="2">
         <v>46019</v>
       </c>
-      <c r="E38" s="2">
+      <c r="F38" s="2">
         <v>45928</v>
       </c>
-      <c r="F38" s="2">
+      <c r="G38" s="2">
         <v>45837</v>
       </c>
-      <c r="G38" s="2">
+      <c r="H38" s="2">
         <v>45746</v>
       </c>
-      <c r="H38" s="2">
+      <c r="I38" s="2">
         <v>45655</v>
       </c>
-      <c r="I38" s="2">
+      <c r="J38" s="2">
         <v>45564</v>
       </c>
-      <c r="J38" s="2">
+      <c r="K38" s="2">
         <v>45473</v>
       </c>
-      <c r="K38" s="2">
+      <c r="L38" s="2">
         <v>45382</v>
       </c>
-      <c r="L38" s="2">
+      <c r="M38" s="2">
         <v>45291</v>
       </c>
-      <c r="M38" s="2">
+      <c r="N38" s="2">
         <v>45200</v>
       </c>
-      <c r="N38" s="2">
+      <c r="O38" s="2">
         <v>45109</v>
       </c>
-      <c r="O38" s="2">
+      <c r="P38" s="2">
         <v>45018</v>
       </c>
-      <c r="P38" s="2">
+      <c r="Q38" s="2">
         <v>44927</v>
       </c>
-      <c r="Q38" s="2">
+      <c r="R38" s="2">
         <v>44836</v>
       </c>
-      <c r="R38" s="2">
+      <c r="S38" s="2">
         <v>44745</v>
       </c>
-      <c r="S38" s="2">
+      <c r="T38" s="2">
         <v>44654</v>
       </c>
-      <c r="T38" s="2">
+      <c r="U38" s="2">
         <v>44556</v>
       </c>
-      <c r="U38" s="2">
+      <c r="V38" s="2">
         <v>44465</v>
       </c>
-      <c r="V38" s="2">
+      <c r="W38" s="2">
         <v>44374</v>
       </c>
-      <c r="W38" s="2">
+      <c r="X38" s="2">
         <v>44283</v>
       </c>
-      <c r="X38" s="2">
+      <c r="Y38" s="2">
         <v>44192</v>
       </c>
-      <c r="Y38" s="2">
+      <c r="Z38" s="2">
         <v>44101</v>
       </c>
-      <c r="Z38" s="2">
+      <c r="AA38" s="2">
         <v>44010</v>
       </c>
-      <c r="AA38" s="2">
+      <c r="AB38" s="2">
         <v>43919</v>
       </c>
-      <c r="AB38" s="2">
+      <c r="AC38" s="2">
         <v>43828</v>
       </c>
-      <c r="AC38" s="2">
+      <c r="AD38" s="2">
         <v>43737</v>
       </c>
-      <c r="AD38" s="2">
+      <c r="AE38" s="2">
         <v>43646</v>
       </c>
-      <c r="AE38" s="2">
+      <c r="AF38" s="2">
         <v>43555</v>
       </c>
-      <c r="AF38" s="2">
+      <c r="AG38" s="2">
         <v>43464</v>
       </c>
-      <c r="AG38" s="2">
+      <c r="AH38" s="2">
         <v>43373</v>
       </c>
-      <c r="AH38" s="2">
+      <c r="AI38" s="2">
         <v>43282</v>
       </c>
-      <c r="AI38" s="2">
+      <c r="AJ38" s="2">
         <v>43191</v>
       </c>
-      <c r="AJ38" s="2">
+      <c r="AK38" s="2">
         <v>43100</v>
       </c>
-      <c r="AK38" s="2">
+      <c r="AL38" s="2">
         <v>43009</v>
       </c>
-      <c r="AL38" s="2">
+      <c r="AM38" s="2">
         <v>42918</v>
       </c>
-      <c r="AM38" s="2">
+      <c r="AN38" s="2">
         <v>42827</v>
       </c>
-      <c r="AN38" s="2">
+      <c r="AO38" s="2">
         <v>42736</v>
       </c>
-      <c r="AO38" s="2">
+      <c r="AP38" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="39" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="39" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C39" s="1" t="s">
         <v>32</v>
       </c>
@@ -4091,8 +4176,9 @@
       <c r="AM39" s="3"/>
       <c r="AN39" s="3"/>
       <c r="AO39" s="3"/>
+      <c r="AP39" s="3"/>
     </row>
-    <row r="40" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="40" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C40" s="1" t="s">
         <v>33</v>
       </c>
@@ -4134,127 +4220,131 @@
       <c r="AM40" s="3"/>
       <c r="AN40" s="3"/>
       <c r="AO40" s="3"/>
+      <c r="AP40" s="3"/>
     </row>
-    <row r="41" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="41" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C41" s="1" t="s">
         <v>34</v>
       </c>
       <c r="D41" s="3">
+        <v>3900</v>
+      </c>
+      <c r="E41" s="3">
         <v>8200</v>
       </c>
-      <c r="E41" s="3">
+      <c r="F41" s="3">
         <v>10400</v>
       </c>
-      <c r="F41" s="3">
+      <c r="G41" s="3">
         <v>14500</v>
       </c>
-      <c r="G41" s="3">
+      <c r="H41" s="3">
         <v>5100</v>
       </c>
-      <c r="H41" s="3">
+      <c r="I41" s="3">
         <v>8300</v>
       </c>
-      <c r="I41" s="3">
+      <c r="J41" s="3">
         <v>7500</v>
       </c>
-      <c r="J41" s="3">
+      <c r="K41" s="3">
         <v>8900</v>
       </c>
-      <c r="K41" s="3">
+      <c r="L41" s="3">
         <v>7200</v>
       </c>
-      <c r="L41" s="3">
+      <c r="M41" s="3">
         <v>5700</v>
       </c>
-      <c r="M41" s="3">
+      <c r="N41" s="3">
         <v>11000</v>
       </c>
-      <c r="N41" s="3">
+      <c r="O41" s="3">
         <v>7100</v>
       </c>
-      <c r="O41" s="3">
+      <c r="P41" s="3">
         <v>7600</v>
       </c>
-      <c r="P41" s="3">
+      <c r="Q41" s="3">
         <v>6100</v>
       </c>
-      <c r="Q41" s="3">
+      <c r="R41" s="3">
         <v>3900</v>
       </c>
-      <c r="R41" s="3">
+      <c r="S41" s="3">
         <v>6000</v>
       </c>
-      <c r="S41" s="3">
+      <c r="T41" s="3">
         <v>3500</v>
       </c>
-      <c r="T41" s="3">
+      <c r="U41" s="3">
         <v>23400</v>
       </c>
-      <c r="U41" s="3">
+      <c r="V41" s="3">
         <v>6800</v>
       </c>
-      <c r="V41" s="3">
+      <c r="W41" s="3">
         <v>5200</v>
       </c>
-      <c r="W41" s="3">
+      <c r="X41" s="3">
         <v>3000</v>
       </c>
-      <c r="X41" s="3">
+      <c r="Y41" s="3">
         <v>8000</v>
       </c>
-      <c r="Y41" s="3">
+      <c r="Z41" s="3">
         <v>3200</v>
       </c>
-      <c r="Z41" s="3">
+      <c r="AA41" s="3">
         <v>4500</v>
       </c>
-      <c r="AA41" s="3">
+      <c r="AB41" s="3">
         <v>4300</v>
       </c>
-      <c r="AB41" s="3">
+      <c r="AC41" s="3">
         <v>7300</v>
       </c>
-      <c r="AC41" s="3">
+      <c r="AD41" s="3">
         <v>4100</v>
       </c>
-      <c r="AD41" s="3">
+      <c r="AE41" s="3">
         <v>5600</v>
       </c>
-      <c r="AE41" s="3">
+      <c r="AF41" s="3">
         <v>9200</v>
       </c>
-      <c r="AF41" s="3">
+      <c r="AG41" s="3">
         <v>7300</v>
       </c>
-      <c r="AG41" s="3">
+      <c r="AH41" s="3">
         <v>4000</v>
       </c>
-      <c r="AH41" s="3">
+      <c r="AI41" s="3">
         <v>5200</v>
       </c>
-      <c r="AI41" s="3">
+      <c r="AJ41" s="3">
         <v>5000</v>
       </c>
-      <c r="AJ41" s="3">
+      <c r="AK41" s="3">
         <v>7600</v>
       </c>
-      <c r="AK41" s="3">
+      <c r="AL41" s="3">
         <v>3800</v>
       </c>
-      <c r="AL41" s="3">
+      <c r="AM41" s="3">
         <v>2800</v>
       </c>
-      <c r="AM41" s="3">
+      <c r="AN41" s="3">
         <v>6900</v>
       </c>
-      <c r="AN41" s="3">
+      <c r="AO41" s="3">
         <v>8400</v>
       </c>
-      <c r="AO41" s="3">
+      <c r="AP41" s="3">
         <v>16700</v>
       </c>
     </row>
-    <row r="42" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="42" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C42" s="1" t="s">
         <v>35</v>
       </c>
@@ -4372,246 +4462,255 @@
       <c r="AO42" s="3">
         <v>0</v>
       </c>
+      <c r="AP42" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="43" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="43" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C43" s="1" t="s">
         <v>36</v>
       </c>
       <c r="D43" s="3">
+        <v>140700</v>
+      </c>
+      <c r="E43" s="3">
         <v>123700</v>
       </c>
-      <c r="E43" s="3">
+      <c r="F43" s="3">
         <v>131100</v>
       </c>
-      <c r="F43" s="3">
+      <c r="G43" s="3">
         <v>140100</v>
       </c>
-      <c r="G43" s="3">
+      <c r="H43" s="3">
         <v>134700</v>
       </c>
-      <c r="H43" s="3">
+      <c r="I43" s="3">
         <v>111500</v>
       </c>
-      <c r="I43" s="3">
+      <c r="J43" s="3">
         <v>115200</v>
       </c>
-      <c r="J43" s="3">
+      <c r="K43" s="3">
         <v>126400</v>
       </c>
-      <c r="K43" s="3">
+      <c r="L43" s="3">
         <v>114500</v>
       </c>
-      <c r="L43" s="3">
+      <c r="M43" s="3">
         <v>113000</v>
       </c>
-      <c r="M43" s="3">
+      <c r="N43" s="3">
         <v>124800</v>
       </c>
-      <c r="N43" s="3">
+      <c r="O43" s="3">
         <v>138300</v>
       </c>
-      <c r="O43" s="3">
+      <c r="P43" s="3">
         <v>129300</v>
       </c>
-      <c r="P43" s="3">
+      <c r="Q43" s="3">
         <v>125500</v>
       </c>
-      <c r="Q43" s="3">
+      <c r="R43" s="3">
         <v>131400</v>
       </c>
-      <c r="R43" s="3">
+      <c r="S43" s="3">
         <v>138800</v>
       </c>
-      <c r="S43" s="3">
+      <c r="T43" s="3">
         <v>122800</v>
       </c>
-      <c r="T43" s="3">
+      <c r="U43" s="3">
         <v>102800</v>
       </c>
-      <c r="U43" s="3">
+      <c r="V43" s="3">
         <v>90100</v>
       </c>
-      <c r="V43" s="3">
+      <c r="W43" s="3">
         <v>90900</v>
       </c>
-      <c r="W43" s="3">
+      <c r="X43" s="3">
         <v>90800</v>
       </c>
-      <c r="X43" s="3">
+      <c r="Y43" s="3">
         <v>77800</v>
       </c>
-      <c r="Y43" s="3">
+      <c r="Z43" s="3">
         <v>74500</v>
       </c>
-      <c r="Z43" s="3">
+      <c r="AA43" s="3">
         <v>69500</v>
       </c>
-      <c r="AA43" s="3">
+      <c r="AB43" s="3">
         <v>67400</v>
       </c>
-      <c r="AB43" s="3">
+      <c r="AC43" s="3">
         <v>56700</v>
       </c>
-      <c r="AC43" s="3">
+      <c r="AD43" s="3">
         <v>65400</v>
       </c>
-      <c r="AD43" s="3">
+      <c r="AE43" s="3">
         <v>69000</v>
       </c>
-      <c r="AE43" s="3">
+      <c r="AF43" s="3">
         <v>64500</v>
       </c>
-      <c r="AF43" s="3">
+      <c r="AG43" s="3">
         <v>61500</v>
       </c>
-      <c r="AG43" s="3">
+      <c r="AH43" s="3">
         <v>66400</v>
       </c>
-      <c r="AH43" s="3">
+      <c r="AI43" s="3">
         <v>67900</v>
       </c>
-      <c r="AI43" s="3">
+      <c r="AJ43" s="3">
         <v>66200</v>
       </c>
-      <c r="AJ43" s="3">
+      <c r="AK43" s="3">
         <v>57900</v>
       </c>
-      <c r="AK43" s="3">
+      <c r="AL43" s="3">
         <v>60000</v>
       </c>
-      <c r="AL43" s="3">
+      <c r="AM43" s="3">
         <v>62800</v>
       </c>
-      <c r="AM43" s="3">
+      <c r="AN43" s="3">
         <v>58600</v>
       </c>
-      <c r="AN43" s="3">
+      <c r="AO43" s="3">
         <v>53300</v>
       </c>
-      <c r="AO43" s="3">
+      <c r="AP43" s="3">
         <v>52800</v>
       </c>
     </row>
-    <row r="44" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="44" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C44" s="1" t="s">
         <v>37</v>
       </c>
       <c r="D44" s="3">
+        <v>78200</v>
+      </c>
+      <c r="E44" s="3">
         <v>85900</v>
       </c>
-      <c r="E44" s="3">
+      <c r="F44" s="3">
         <v>92900</v>
       </c>
-      <c r="F44" s="3">
+      <c r="G44" s="3">
         <v>95700</v>
       </c>
-      <c r="G44" s="3">
+      <c r="H44" s="3">
         <v>83500</v>
-      </c>
-      <c r="H44" s="3">
-        <v>81600</v>
       </c>
       <c r="I44" s="3">
         <v>81600</v>
       </c>
       <c r="J44" s="3">
+        <v>81600</v>
+      </c>
+      <c r="K44" s="3">
         <v>81200</v>
       </c>
-      <c r="K44" s="3">
+      <c r="L44" s="3">
         <v>74600</v>
       </c>
-      <c r="L44" s="3">
+      <c r="M44" s="3">
         <v>68800</v>
       </c>
-      <c r="M44" s="3">
+      <c r="N44" s="3">
         <v>68500</v>
       </c>
-      <c r="N44" s="3">
+      <c r="O44" s="3">
         <v>76900</v>
       </c>
-      <c r="O44" s="3">
+      <c r="P44" s="3">
         <v>88800</v>
       </c>
-      <c r="P44" s="3">
+      <c r="Q44" s="3">
         <v>101600</v>
       </c>
-      <c r="Q44" s="3">
+      <c r="R44" s="3">
         <v>113100</v>
       </c>
-      <c r="R44" s="3">
+      <c r="S44" s="3">
         <v>105000</v>
       </c>
-      <c r="S44" s="3">
+      <c r="T44" s="3">
         <v>95000</v>
       </c>
-      <c r="T44" s="3">
+      <c r="U44" s="3">
         <v>76200</v>
       </c>
-      <c r="U44" s="3">
+      <c r="V44" s="3">
         <v>70300</v>
       </c>
-      <c r="V44" s="3">
+      <c r="W44" s="3">
         <v>67900</v>
       </c>
-      <c r="W44" s="3">
+      <c r="X44" s="3">
         <v>63900</v>
       </c>
-      <c r="X44" s="3">
+      <c r="Y44" s="3">
         <v>64700</v>
       </c>
-      <c r="Y44" s="3">
+      <c r="Z44" s="3">
         <v>63200</v>
       </c>
-      <c r="Z44" s="3">
+      <c r="AA44" s="3">
         <v>63400</v>
       </c>
-      <c r="AA44" s="3">
+      <c r="AB44" s="3">
         <v>54400</v>
       </c>
-      <c r="AB44" s="3">
+      <c r="AC44" s="3">
         <v>57500</v>
       </c>
-      <c r="AC44" s="3">
+      <c r="AD44" s="3">
         <v>60800</v>
       </c>
-      <c r="AD44" s="3">
+      <c r="AE44" s="3">
         <v>58700</v>
       </c>
-      <c r="AE44" s="3">
+      <c r="AF44" s="3">
         <v>60500</v>
       </c>
-      <c r="AF44" s="3">
+      <c r="AG44" s="3">
         <v>67700</v>
       </c>
-      <c r="AG44" s="3">
+      <c r="AH44" s="3">
         <v>67800</v>
       </c>
-      <c r="AH44" s="3">
+      <c r="AI44" s="3">
         <v>66400</v>
       </c>
-      <c r="AI44" s="3">
+      <c r="AJ44" s="3">
         <v>59700</v>
       </c>
-      <c r="AJ44" s="3">
+      <c r="AK44" s="3">
         <v>62700</v>
       </c>
-      <c r="AK44" s="3">
+      <c r="AL44" s="3">
         <v>65900</v>
       </c>
-      <c r="AL44" s="3">
+      <c r="AM44" s="3">
         <v>65600</v>
       </c>
-      <c r="AM44" s="3">
+      <c r="AN44" s="3">
         <v>51200</v>
       </c>
-      <c r="AN44" s="3">
+      <c r="AO44" s="3">
         <v>50300</v>
       </c>
-      <c r="AO44" s="3">
+      <c r="AP44" s="3">
         <v>54400</v>
       </c>
     </row>
-    <row r="45" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="45" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C45" s="1" t="s">
         <v>38</v>
       </c>
@@ -4651,247 +4750,253 @@
       <c r="O45" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P45" s="3">
+      <c r="P45" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q45" s="3">
         <v>7100</v>
       </c>
-      <c r="Q45" s="3">
+      <c r="R45" s="3">
         <v>3200</v>
       </c>
-      <c r="R45" s="3">
+      <c r="S45" s="3">
         <v>3900</v>
       </c>
-      <c r="S45" s="3">
+      <c r="T45" s="3">
         <v>6400</v>
       </c>
-      <c r="T45" s="3">
+      <c r="U45" s="3">
         <v>7000</v>
       </c>
-      <c r="U45" s="3">
+      <c r="V45" s="3">
         <v>2500</v>
       </c>
-      <c r="V45" s="3">
+      <c r="W45" s="3">
         <v>3700</v>
       </c>
-      <c r="W45" s="3">
+      <c r="X45" s="3">
         <v>5400</v>
       </c>
-      <c r="X45" s="3">
+      <c r="Y45" s="3">
         <v>5100</v>
       </c>
-      <c r="Y45" s="3">
+      <c r="Z45" s="3">
         <v>1700</v>
       </c>
-      <c r="Z45" s="3">
+      <c r="AA45" s="3">
         <v>3100</v>
       </c>
-      <c r="AA45" s="3">
+      <c r="AB45" s="3">
         <v>4900</v>
       </c>
-      <c r="AB45" s="3">
+      <c r="AC45" s="3">
         <v>5600</v>
       </c>
-      <c r="AC45" s="3">
+      <c r="AD45" s="3">
         <v>2800</v>
       </c>
-      <c r="AD45" s="3">
+      <c r="AE45" s="3">
         <v>4800</v>
       </c>
-      <c r="AE45" s="3">
+      <c r="AF45" s="3">
         <v>5200</v>
       </c>
-      <c r="AF45" s="3">
+      <c r="AG45" s="3">
         <v>5700</v>
       </c>
-      <c r="AG45" s="3">
+      <c r="AH45" s="3">
         <v>1700</v>
       </c>
-      <c r="AH45" s="3">
+      <c r="AI45" s="3">
         <v>3500</v>
       </c>
-      <c r="AI45" s="3">
+      <c r="AJ45" s="3">
         <v>4100</v>
       </c>
-      <c r="AJ45" s="3">
+      <c r="AK45" s="3">
         <v>4800</v>
       </c>
-      <c r="AK45" s="3">
+      <c r="AL45" s="3">
         <v>2500</v>
       </c>
-      <c r="AL45" s="3">
+      <c r="AM45" s="3">
         <v>3300</v>
       </c>
-      <c r="AM45" s="3">
+      <c r="AN45" s="3">
         <v>4200</v>
       </c>
-      <c r="AN45" s="3">
+      <c r="AO45" s="3">
         <v>5100</v>
       </c>
-      <c r="AO45" s="3">
+      <c r="AP45" s="3">
         <v>2500</v>
       </c>
     </row>
-    <row r="46" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="46" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C46" s="1" t="s">
         <v>39</v>
       </c>
       <c r="D46" s="3">
+        <v>231500</v>
+      </c>
+      <c r="E46" s="3">
         <v>228200</v>
       </c>
-      <c r="E46" s="3">
+      <c r="F46" s="3">
         <v>239600</v>
       </c>
-      <c r="F46" s="3">
+      <c r="G46" s="3">
         <v>256400</v>
       </c>
-      <c r="G46" s="3">
+      <c r="H46" s="3">
         <v>230700</v>
       </c>
-      <c r="H46" s="3">
+      <c r="I46" s="3">
         <v>210400</v>
       </c>
-      <c r="I46" s="3">
+      <c r="J46" s="3">
         <v>209900</v>
       </c>
-      <c r="J46" s="3">
+      <c r="K46" s="3">
         <v>222000</v>
       </c>
-      <c r="K46" s="3">
+      <c r="L46" s="3">
         <v>202800</v>
       </c>
-      <c r="L46" s="3">
+      <c r="M46" s="3">
         <v>195000</v>
       </c>
-      <c r="M46" s="3">
+      <c r="N46" s="3">
         <v>207300</v>
       </c>
-      <c r="N46" s="3">
+      <c r="O46" s="3">
         <v>226500</v>
       </c>
-      <c r="O46" s="3">
+      <c r="P46" s="3">
         <v>232000</v>
       </c>
-      <c r="P46" s="3">
+      <c r="Q46" s="3">
         <v>240200</v>
       </c>
-      <c r="Q46" s="3">
+      <c r="R46" s="3">
         <v>251600</v>
       </c>
-      <c r="R46" s="3">
+      <c r="S46" s="3">
         <v>253600</v>
       </c>
-      <c r="S46" s="3">
+      <c r="T46" s="3">
         <v>227700</v>
       </c>
-      <c r="T46" s="3">
+      <c r="U46" s="3">
         <v>209500</v>
       </c>
-      <c r="U46" s="3">
+      <c r="V46" s="3">
         <v>169700</v>
       </c>
-      <c r="V46" s="3">
+      <c r="W46" s="3">
         <v>167800</v>
       </c>
-      <c r="W46" s="3">
+      <c r="X46" s="3">
         <v>163000</v>
       </c>
-      <c r="X46" s="3">
+      <c r="Y46" s="3">
         <v>155500</v>
       </c>
-      <c r="Y46" s="3">
+      <c r="Z46" s="3">
         <v>142600</v>
       </c>
-      <c r="Z46" s="3">
+      <c r="AA46" s="3">
         <v>140400</v>
       </c>
-      <c r="AA46" s="3">
+      <c r="AB46" s="3">
         <v>131000</v>
       </c>
-      <c r="AB46" s="3">
+      <c r="AC46" s="3">
         <v>127000</v>
       </c>
-      <c r="AC46" s="3">
+      <c r="AD46" s="3">
         <v>133100</v>
       </c>
-      <c r="AD46" s="3">
+      <c r="AE46" s="3">
         <v>138100</v>
       </c>
-      <c r="AE46" s="3">
+      <c r="AF46" s="3">
         <v>139400</v>
       </c>
-      <c r="AF46" s="3">
+      <c r="AG46" s="3">
         <v>142200</v>
       </c>
-      <c r="AG46" s="3">
+      <c r="AH46" s="3">
         <v>139900</v>
       </c>
-      <c r="AH46" s="3">
+      <c r="AI46" s="3">
         <v>142900</v>
       </c>
-      <c r="AI46" s="3">
+      <c r="AJ46" s="3">
         <v>135000</v>
       </c>
-      <c r="AJ46" s="3">
+      <c r="AK46" s="3">
         <v>133100</v>
       </c>
-      <c r="AK46" s="3">
+      <c r="AL46" s="3">
         <v>132200</v>
       </c>
-      <c r="AL46" s="3">
+      <c r="AM46" s="3">
         <v>134400</v>
       </c>
-      <c r="AM46" s="3">
+      <c r="AN46" s="3">
         <v>120900</v>
       </c>
-      <c r="AN46" s="3">
+      <c r="AO46" s="3">
         <v>117000</v>
       </c>
-      <c r="AO46" s="3">
+      <c r="AP46" s="3">
         <v>126400</v>
       </c>
     </row>
-    <row r="47" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="47" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C47" s="1" t="s">
         <v>40</v>
       </c>
-      <c r="D47" s="3">
+      <c r="D47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E47" s="3">
         <v>1300</v>
       </c>
-      <c r="E47" s="3">
+      <c r="F47" s="3">
         <v>1600</v>
       </c>
-      <c r="F47" s="3">
+      <c r="G47" s="3">
         <v>1900</v>
       </c>
-      <c r="G47" s="3">
-        <v>2400</v>
-      </c>
-      <c r="H47" s="3">
+      <c r="H47" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="I47" s="3">
         <v>3200</v>
       </c>
-      <c r="I47" s="3">
+      <c r="J47" s="3">
         <v>2300</v>
       </c>
-      <c r="J47" s="3">
+      <c r="K47" s="3">
         <v>4100</v>
       </c>
-      <c r="K47" s="3">
+      <c r="L47" s="3">
         <v>4300</v>
       </c>
-      <c r="L47" s="3">
+      <c r="M47" s="3">
         <v>3700</v>
       </c>
-      <c r="M47" s="3">
+      <c r="N47" s="3">
         <v>5500</v>
       </c>
-      <c r="N47" s="3">
+      <c r="O47" s="3">
         <v>5100</v>
       </c>
-      <c r="O47" s="3">
+      <c r="P47" s="3">
         <v>4000</v>
       </c>
-      <c r="P47" s="3">
-        <v>0</v>
-      </c>
       <c r="Q47" s="3">
         <v>0</v>
       </c>
@@ -4967,246 +5072,255 @@
       <c r="AO47" s="3">
         <v>0</v>
       </c>
+      <c r="AP47" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="48" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="48" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C48" s="1" t="s">
         <v>41</v>
       </c>
       <c r="D48" s="3">
+        <v>283100</v>
+      </c>
+      <c r="E48" s="3">
         <v>270600</v>
       </c>
-      <c r="E48" s="3">
+      <c r="F48" s="3">
         <v>264800</v>
       </c>
-      <c r="F48" s="3">
+      <c r="G48" s="3">
         <v>256500</v>
       </c>
-      <c r="G48" s="3">
+      <c r="H48" s="3">
         <v>238700</v>
       </c>
-      <c r="H48" s="3">
+      <c r="I48" s="3">
         <v>233500</v>
       </c>
-      <c r="I48" s="3">
+      <c r="J48" s="3">
         <v>229500</v>
       </c>
-      <c r="J48" s="3">
+      <c r="K48" s="3">
         <v>225800</v>
       </c>
-      <c r="K48" s="3">
+      <c r="L48" s="3">
         <v>220600</v>
       </c>
-      <c r="L48" s="3">
+      <c r="M48" s="3">
         <v>216900</v>
       </c>
-      <c r="M48" s="3">
+      <c r="N48" s="3">
         <v>204200</v>
       </c>
-      <c r="N48" s="3">
+      <c r="O48" s="3">
         <v>201900</v>
       </c>
-      <c r="O48" s="3">
+      <c r="P48" s="3">
         <v>196000</v>
       </c>
-      <c r="P48" s="3">
+      <c r="Q48" s="3">
         <v>188900</v>
       </c>
-      <c r="Q48" s="3">
+      <c r="R48" s="3">
         <v>181000</v>
       </c>
-      <c r="R48" s="3">
+      <c r="S48" s="3">
         <v>176400</v>
       </c>
-      <c r="S48" s="3">
+      <c r="T48" s="3">
         <v>172500</v>
       </c>
-      <c r="T48" s="3">
+      <c r="U48" s="3">
         <v>158400</v>
       </c>
-      <c r="U48" s="3">
+      <c r="V48" s="3">
         <v>154200</v>
       </c>
-      <c r="V48" s="3">
+      <c r="W48" s="3">
         <v>153700</v>
       </c>
-      <c r="W48" s="3">
+      <c r="X48" s="3">
         <v>156200</v>
       </c>
-      <c r="X48" s="3">
+      <c r="Y48" s="3">
         <v>147100</v>
       </c>
-      <c r="Y48" s="3">
+      <c r="Z48" s="3">
         <v>136000</v>
       </c>
-      <c r="Z48" s="3">
+      <c r="AA48" s="3">
         <v>135800</v>
       </c>
-      <c r="AA48" s="3">
+      <c r="AB48" s="3">
         <v>135400</v>
       </c>
-      <c r="AB48" s="3">
+      <c r="AC48" s="3">
         <v>134900</v>
       </c>
-      <c r="AC48" s="3">
+      <c r="AD48" s="3">
         <v>133900</v>
       </c>
-      <c r="AD48" s="3">
+      <c r="AE48" s="3">
         <v>133500</v>
       </c>
-      <c r="AE48" s="3">
+      <c r="AF48" s="3">
         <v>118600</v>
       </c>
-      <c r="AF48" s="3">
+      <c r="AG48" s="3">
         <v>117600</v>
       </c>
-      <c r="AG48" s="3">
+      <c r="AH48" s="3">
         <v>119400</v>
       </c>
-      <c r="AH48" s="3">
+      <c r="AI48" s="3">
         <v>121700</v>
       </c>
-      <c r="AI48" s="3">
+      <c r="AJ48" s="3">
         <v>123800</v>
       </c>
-      <c r="AJ48" s="3">
+      <c r="AK48" s="3">
         <v>125100</v>
       </c>
-      <c r="AK48" s="3">
+      <c r="AL48" s="3">
         <v>125900</v>
       </c>
-      <c r="AL48" s="3">
+      <c r="AM48" s="3">
         <v>123000</v>
       </c>
-      <c r="AM48" s="3">
+      <c r="AN48" s="3">
         <v>121500</v>
       </c>
-      <c r="AN48" s="3">
+      <c r="AO48" s="3">
         <v>120200</v>
       </c>
-      <c r="AO48" s="3">
+      <c r="AP48" s="3">
         <v>117900</v>
       </c>
     </row>
-    <row r="49" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="49" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C49" s="1" t="s">
         <v>42</v>
       </c>
       <c r="D49" s="3">
+        <v>455900</v>
+      </c>
+      <c r="E49" s="3">
         <v>461400</v>
       </c>
-      <c r="E49" s="3">
+      <c r="F49" s="3">
         <v>463200</v>
       </c>
-      <c r="F49" s="3">
+      <c r="G49" s="3">
         <v>458900</v>
       </c>
-      <c r="G49" s="3">
+      <c r="H49" s="3">
         <v>285500</v>
       </c>
-      <c r="H49" s="3">
+      <c r="I49" s="3">
         <v>247200</v>
       </c>
-      <c r="I49" s="3">
+      <c r="J49" s="3">
         <v>235500</v>
       </c>
-      <c r="J49" s="3">
+      <c r="K49" s="3">
         <v>238600</v>
       </c>
-      <c r="K49" s="3">
+      <c r="L49" s="3">
         <v>220000</v>
       </c>
-      <c r="L49" s="3">
+      <c r="M49" s="3">
         <v>218200</v>
       </c>
-      <c r="M49" s="3">
+      <c r="N49" s="3">
         <v>148900</v>
       </c>
-      <c r="N49" s="3">
+      <c r="O49" s="3">
         <v>148800</v>
       </c>
-      <c r="O49" s="3">
+      <c r="P49" s="3">
         <v>150500</v>
       </c>
-      <c r="P49" s="3">
+      <c r="Q49" s="3">
         <v>152300</v>
       </c>
-      <c r="Q49" s="3">
+      <c r="R49" s="3">
         <v>154100</v>
       </c>
-      <c r="R49" s="3">
+      <c r="S49" s="3">
         <v>155800</v>
       </c>
-      <c r="S49" s="3">
+      <c r="T49" s="3">
         <v>157600</v>
       </c>
-      <c r="T49" s="3">
+      <c r="U49" s="3">
         <v>145500</v>
       </c>
-      <c r="U49" s="3">
+      <c r="V49" s="3">
         <v>146100</v>
       </c>
-      <c r="V49" s="3">
+      <c r="W49" s="3">
         <v>145500</v>
       </c>
-      <c r="W49" s="3">
+      <c r="X49" s="3">
         <v>147100</v>
       </c>
-      <c r="X49" s="3">
+      <c r="Y49" s="3">
         <v>137400</v>
       </c>
-      <c r="Y49" s="3">
+      <c r="Z49" s="3">
         <v>138900</v>
       </c>
-      <c r="Z49" s="3">
+      <c r="AA49" s="3">
         <v>117800</v>
       </c>
-      <c r="AA49" s="3">
+      <c r="AB49" s="3">
         <v>119100</v>
       </c>
-      <c r="AB49" s="3">
+      <c r="AC49" s="3">
         <v>120400</v>
       </c>
-      <c r="AC49" s="3">
+      <c r="AD49" s="3">
         <v>121600</v>
       </c>
-      <c r="AD49" s="3">
+      <c r="AE49" s="3">
         <v>122900</v>
       </c>
-      <c r="AE49" s="3">
+      <c r="AF49" s="3">
         <v>124200</v>
       </c>
-      <c r="AF49" s="3">
+      <c r="AG49" s="3">
         <v>125400</v>
       </c>
-      <c r="AG49" s="3">
+      <c r="AH49" s="3">
         <v>126800</v>
       </c>
-      <c r="AH49" s="3">
+      <c r="AI49" s="3">
         <v>128200</v>
       </c>
-      <c r="AI49" s="3">
+      <c r="AJ49" s="3">
         <v>129600</v>
       </c>
-      <c r="AJ49" s="3">
+      <c r="AK49" s="3">
         <v>170200</v>
       </c>
-      <c r="AK49" s="3">
+      <c r="AL49" s="3">
         <v>171600</v>
       </c>
-      <c r="AL49" s="3">
+      <c r="AM49" s="3">
         <v>173000</v>
       </c>
-      <c r="AM49" s="3">
+      <c r="AN49" s="3">
         <v>174400</v>
       </c>
-      <c r="AN49" s="3">
+      <c r="AO49" s="3">
         <v>175900</v>
       </c>
-      <c r="AO49" s="3">
+      <c r="AP49" s="3">
         <v>177600</v>
       </c>
     </row>
-    <row r="50" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="50" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C50" s="1" t="s">
         <v>43</v>
       </c>
@@ -5324,8 +5438,11 @@
       <c r="AO50" s="3">
         <v>0</v>
       </c>
+      <c r="AP50" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="51" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="51" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C51" s="1" t="s">
         <v>44</v>
       </c>
@@ -5443,8 +5560,11 @@
       <c r="AO51" s="3">
         <v>0</v>
       </c>
+      <c r="AP51" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="52" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="52" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C52" s="1" t="s">
         <v>45</v>
       </c>
@@ -5452,118 +5572,121 @@
         <v>15000</v>
       </c>
       <c r="E52" s="3">
+        <v>15000</v>
+      </c>
+      <c r="F52" s="3">
         <v>14900</v>
       </c>
-      <c r="F52" s="3">
+      <c r="G52" s="3">
         <v>14500</v>
       </c>
-      <c r="G52" s="3">
-        <v>12500</v>
-      </c>
       <c r="H52" s="3">
+        <v>15100</v>
+      </c>
+      <c r="I52" s="3">
         <v>13000</v>
       </c>
-      <c r="I52" s="3">
+      <c r="J52" s="3">
         <v>12600</v>
       </c>
-      <c r="J52" s="3">
+      <c r="K52" s="3">
         <v>12200</v>
-      </c>
-      <c r="K52" s="3">
-        <v>10200</v>
       </c>
       <c r="L52" s="3">
         <v>10200</v>
       </c>
       <c r="M52" s="3">
+        <v>10200</v>
+      </c>
+      <c r="N52" s="3">
         <v>9500</v>
       </c>
-      <c r="N52" s="3">
+      <c r="O52" s="3">
         <v>9700</v>
       </c>
-      <c r="O52" s="3">
+      <c r="P52" s="3">
         <v>8000</v>
       </c>
-      <c r="P52" s="3">
+      <c r="Q52" s="3">
         <v>12500</v>
       </c>
-      <c r="Q52" s="3">
+      <c r="R52" s="3">
         <v>12600</v>
       </c>
-      <c r="R52" s="3">
+      <c r="S52" s="3">
         <v>10500</v>
       </c>
-      <c r="S52" s="3">
+      <c r="T52" s="3">
         <v>9500</v>
       </c>
-      <c r="T52" s="3">
+      <c r="U52" s="3">
         <v>7800</v>
       </c>
-      <c r="U52" s="3">
+      <c r="V52" s="3">
         <v>7900</v>
       </c>
-      <c r="V52" s="3">
+      <c r="W52" s="3">
         <v>8000</v>
       </c>
-      <c r="W52" s="3">
+      <c r="X52" s="3">
         <v>6200</v>
       </c>
-      <c r="X52" s="3">
+      <c r="Y52" s="3">
         <v>6000</v>
       </c>
-      <c r="Y52" s="3">
+      <c r="Z52" s="3">
         <v>5600</v>
       </c>
-      <c r="Z52" s="3">
+      <c r="AA52" s="3">
         <v>5400</v>
       </c>
-      <c r="AA52" s="3">
+      <c r="AB52" s="3">
         <v>3800</v>
       </c>
-      <c r="AB52" s="3">
+      <c r="AC52" s="3">
         <v>4300</v>
       </c>
-      <c r="AC52" s="3">
+      <c r="AD52" s="3">
         <v>4400</v>
       </c>
-      <c r="AD52" s="3">
+      <c r="AE52" s="3">
         <v>4500</v>
       </c>
-      <c r="AE52" s="3">
+      <c r="AF52" s="3">
         <v>3400</v>
       </c>
-      <c r="AF52" s="3">
+      <c r="AG52" s="3">
         <v>3200</v>
-      </c>
-      <c r="AG52" s="3">
-        <v>3800</v>
       </c>
       <c r="AH52" s="3">
         <v>3800</v>
       </c>
       <c r="AI52" s="3">
+        <v>3800</v>
+      </c>
+      <c r="AJ52" s="3">
         <v>2600</v>
       </c>
-      <c r="AJ52" s="3">
+      <c r="AK52" s="3">
         <v>2400</v>
       </c>
-      <c r="AK52" s="3">
+      <c r="AL52" s="3">
         <v>2200</v>
       </c>
-      <c r="AL52" s="3">
+      <c r="AM52" s="3">
         <v>3000</v>
       </c>
-      <c r="AM52" s="3">
+      <c r="AN52" s="3">
         <v>1700</v>
       </c>
-      <c r="AN52" s="3">
+      <c r="AO52" s="3">
         <v>1600</v>
       </c>
-      <c r="AO52" s="3">
+      <c r="AP52" s="3">
         <v>1100</v>
       </c>
     </row>
-    <row r="53" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="53" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C53" s="1" t="s">
         <v>46</v>
       </c>
@@ -5681,127 +5804,133 @@
       <c r="AO53" s="3">
         <v>0</v>
       </c>
+      <c r="AP53" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="54" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="54" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C54" s="1" t="s">
         <v>47</v>
       </c>
       <c r="D54" s="3">
+        <v>986300</v>
+      </c>
+      <c r="E54" s="3">
         <v>976500</v>
       </c>
-      <c r="E54" s="3">
+      <c r="F54" s="3">
         <v>984200</v>
       </c>
-      <c r="F54" s="3">
+      <c r="G54" s="3">
         <v>988300</v>
       </c>
-      <c r="G54" s="3">
-        <v>769900</v>
-      </c>
       <c r="H54" s="3">
+        <v>770000</v>
+      </c>
+      <c r="I54" s="3">
         <v>707200</v>
       </c>
-      <c r="I54" s="3">
+      <c r="J54" s="3">
         <v>689700</v>
       </c>
-      <c r="J54" s="3">
+      <c r="K54" s="3">
         <v>702700</v>
       </c>
-      <c r="K54" s="3">
+      <c r="L54" s="3">
         <v>657900</v>
       </c>
-      <c r="L54" s="3">
+      <c r="M54" s="3">
         <v>644000</v>
       </c>
-      <c r="M54" s="3">
+      <c r="N54" s="3">
         <v>575300</v>
       </c>
-      <c r="N54" s="3">
+      <c r="O54" s="3">
         <v>592000</v>
       </c>
-      <c r="O54" s="3">
+      <c r="P54" s="3">
         <v>590500</v>
       </c>
-      <c r="P54" s="3">
+      <c r="Q54" s="3">
         <v>594000</v>
       </c>
-      <c r="Q54" s="3">
+      <c r="R54" s="3">
         <v>599300</v>
       </c>
-      <c r="R54" s="3">
+      <c r="S54" s="3">
         <v>596400</v>
       </c>
-      <c r="S54" s="3">
+      <c r="T54" s="3">
         <v>567300</v>
       </c>
-      <c r="T54" s="3">
+      <c r="U54" s="3">
         <v>521100</v>
       </c>
-      <c r="U54" s="3">
+      <c r="V54" s="3">
         <v>477800</v>
       </c>
-      <c r="V54" s="3">
+      <c r="W54" s="3">
         <v>475000</v>
       </c>
-      <c r="W54" s="3">
+      <c r="X54" s="3">
         <v>472600</v>
       </c>
-      <c r="X54" s="3">
+      <c r="Y54" s="3">
         <v>446000</v>
       </c>
-      <c r="Y54" s="3">
+      <c r="Z54" s="3">
         <v>423100</v>
       </c>
-      <c r="Z54" s="3">
+      <c r="AA54" s="3">
         <v>399500</v>
       </c>
-      <c r="AA54" s="3">
+      <c r="AB54" s="3">
         <v>389300</v>
       </c>
-      <c r="AB54" s="3">
+      <c r="AC54" s="3">
         <v>386600</v>
       </c>
-      <c r="AC54" s="3">
+      <c r="AD54" s="3">
         <v>393000</v>
       </c>
-      <c r="AD54" s="3">
+      <c r="AE54" s="3">
         <v>399000</v>
       </c>
-      <c r="AE54" s="3">
+      <c r="AF54" s="3">
         <v>385600</v>
       </c>
-      <c r="AF54" s="3">
+      <c r="AG54" s="3">
         <v>388400</v>
       </c>
-      <c r="AG54" s="3">
+      <c r="AH54" s="3">
         <v>389800</v>
       </c>
-      <c r="AH54" s="3">
+      <c r="AI54" s="3">
         <v>396700</v>
       </c>
-      <c r="AI54" s="3">
+      <c r="AJ54" s="3">
         <v>391000</v>
       </c>
-      <c r="AJ54" s="3">
+      <c r="AK54" s="3">
         <v>430700</v>
       </c>
-      <c r="AK54" s="3">
+      <c r="AL54" s="3">
         <v>431900</v>
       </c>
-      <c r="AL54" s="3">
+      <c r="AM54" s="3">
         <v>433300</v>
       </c>
-      <c r="AM54" s="3">
+      <c r="AN54" s="3">
         <v>418600</v>
       </c>
-      <c r="AN54" s="3">
+      <c r="AO54" s="3">
         <v>414700</v>
       </c>
-      <c r="AO54" s="3">
+      <c r="AP54" s="3">
         <v>422900</v>
       </c>
     </row>
-    <row r="55" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="55" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C55" s="1" t="s">
         <v>48</v>
       </c>
@@ -5843,8 +5972,9 @@
       <c r="AM55" s="3"/>
       <c r="AN55" s="3"/>
       <c r="AO55" s="3"/>
+      <c r="AP55" s="3"/>
     </row>
-    <row r="56" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="56" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C56" s="1" t="s">
         <v>49</v>
       </c>
@@ -5886,132 +6016,136 @@
       <c r="AM56" s="3"/>
       <c r="AN56" s="3"/>
       <c r="AO56" s="3"/>
+      <c r="AP56" s="3"/>
     </row>
-    <row r="57" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="57" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C57" s="1" t="s">
         <v>50</v>
       </c>
       <c r="D57" s="3">
+        <v>59800</v>
+      </c>
+      <c r="E57" s="3">
         <v>46400</v>
       </c>
-      <c r="E57" s="3">
+      <c r="F57" s="3">
         <v>55300</v>
       </c>
-      <c r="F57" s="3">
+      <c r="G57" s="3">
         <v>62800</v>
       </c>
-      <c r="G57" s="3">
+      <c r="H57" s="3">
         <v>61200</v>
       </c>
-      <c r="H57" s="3">
+      <c r="I57" s="3">
         <v>39900</v>
       </c>
-      <c r="I57" s="3">
+      <c r="J57" s="3">
         <v>51000</v>
       </c>
-      <c r="J57" s="3">
+      <c r="K57" s="3">
         <v>47800</v>
       </c>
-      <c r="K57" s="3">
+      <c r="L57" s="3">
         <v>56400</v>
       </c>
-      <c r="L57" s="3">
+      <c r="M57" s="3">
         <v>42900</v>
       </c>
-      <c r="M57" s="3">
+      <c r="N57" s="3">
         <v>61200</v>
       </c>
-      <c r="N57" s="3">
+      <c r="O57" s="3">
         <v>55600</v>
       </c>
-      <c r="O57" s="3">
+      <c r="P57" s="3">
         <v>53700</v>
       </c>
-      <c r="P57" s="3">
+      <c r="Q57" s="3">
         <v>50600</v>
       </c>
-      <c r="Q57" s="3">
+      <c r="R57" s="3">
         <v>60900</v>
       </c>
-      <c r="R57" s="3">
+      <c r="S57" s="3">
         <v>56400</v>
       </c>
-      <c r="S57" s="3">
+      <c r="T57" s="3">
         <v>66700</v>
       </c>
-      <c r="T57" s="3">
+      <c r="U57" s="3">
         <v>44000</v>
       </c>
-      <c r="U57" s="3">
+      <c r="V57" s="3">
         <v>43000</v>
       </c>
-      <c r="V57" s="3">
+      <c r="W57" s="3">
         <v>38100</v>
       </c>
-      <c r="W57" s="3">
+      <c r="X57" s="3">
         <v>37300</v>
       </c>
-      <c r="X57" s="3">
+      <c r="Y57" s="3">
         <v>31200</v>
       </c>
-      <c r="Y57" s="3">
+      <c r="Z57" s="3">
         <v>32700</v>
       </c>
-      <c r="Z57" s="3">
+      <c r="AA57" s="3">
         <v>31100</v>
       </c>
-      <c r="AA57" s="3">
+      <c r="AB57" s="3">
         <v>34100</v>
       </c>
-      <c r="AB57" s="3">
+      <c r="AC57" s="3">
         <v>26700</v>
       </c>
-      <c r="AC57" s="3">
+      <c r="AD57" s="3">
         <v>29600</v>
       </c>
-      <c r="AD57" s="3">
+      <c r="AE57" s="3">
         <v>32000</v>
-      </c>
-      <c r="AE57" s="3">
-        <v>29300</v>
       </c>
       <c r="AF57" s="3">
         <v>29300</v>
       </c>
       <c r="AG57" s="3">
+        <v>29300</v>
+      </c>
+      <c r="AH57" s="3">
         <v>35500</v>
       </c>
-      <c r="AH57" s="3">
+      <c r="AI57" s="3">
         <v>36700</v>
       </c>
-      <c r="AI57" s="3">
+      <c r="AJ57" s="3">
         <v>33400</v>
       </c>
-      <c r="AJ57" s="3">
+      <c r="AK57" s="3">
         <v>28100</v>
       </c>
-      <c r="AK57" s="3">
+      <c r="AL57" s="3">
         <v>26800</v>
       </c>
-      <c r="AL57" s="3">
+      <c r="AM57" s="3">
         <v>27900</v>
       </c>
-      <c r="AM57" s="3">
+      <c r="AN57" s="3">
         <v>29800</v>
       </c>
-      <c r="AN57" s="3">
+      <c r="AO57" s="3">
         <v>21900</v>
       </c>
-      <c r="AO57" s="3">
+      <c r="AP57" s="3">
         <v>27700</v>
       </c>
     </row>
-    <row r="58" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="58" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C58" s="1" t="s">
         <v>51</v>
       </c>
       <c r="D58" s="3">
-        <v>9800</v>
+        <v>3000</v>
       </c>
       <c r="E58" s="3">
         <v>9800</v>
@@ -6020,10 +6154,10 @@
         <v>9800</v>
       </c>
       <c r="G58" s="3">
-        <v>12800</v>
+        <v>9800</v>
       </c>
       <c r="H58" s="3">
-        <v>9900</v>
+        <v>2900</v>
       </c>
       <c r="I58" s="3">
         <v>9900</v>
@@ -6110,498 +6244,513 @@
         <v>9900</v>
       </c>
       <c r="AK58" s="3">
+        <v>9900</v>
+      </c>
+      <c r="AL58" s="3">
         <v>9200</v>
       </c>
-      <c r="AL58" s="3">
+      <c r="AM58" s="3">
         <v>8600</v>
       </c>
-      <c r="AM58" s="3">
+      <c r="AN58" s="3">
         <v>8000</v>
       </c>
-      <c r="AN58" s="3">
+      <c r="AO58" s="3">
         <v>7400</v>
       </c>
-      <c r="AO58" s="3">
+      <c r="AP58" s="3">
         <v>6700</v>
       </c>
     </row>
-    <row r="59" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="59" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C59" s="1" t="s">
         <v>52</v>
       </c>
       <c r="D59" s="3">
+        <v>20700</v>
+      </c>
+      <c r="E59" s="3">
         <v>12400</v>
       </c>
-      <c r="E59" s="3">
+      <c r="F59" s="3">
         <v>11100</v>
       </c>
-      <c r="F59" s="3">
+      <c r="G59" s="3">
         <v>16200</v>
       </c>
-      <c r="G59" s="3">
-        <v>5800</v>
-      </c>
       <c r="H59" s="3">
+        <v>12400</v>
+      </c>
+      <c r="I59" s="3">
         <v>8400</v>
       </c>
-      <c r="I59" s="3">
+      <c r="J59" s="3">
         <v>11100</v>
       </c>
-      <c r="J59" s="3">
+      <c r="K59" s="3">
         <v>20100</v>
       </c>
-      <c r="K59" s="3">
+      <c r="L59" s="3">
         <v>9800</v>
       </c>
-      <c r="L59" s="3">
+      <c r="M59" s="3">
         <v>9200</v>
       </c>
-      <c r="M59" s="3">
+      <c r="N59" s="3">
         <v>10900</v>
       </c>
-      <c r="N59" s="3">
+      <c r="O59" s="3">
         <v>18100</v>
       </c>
-      <c r="O59" s="3">
+      <c r="P59" s="3">
         <v>10000</v>
       </c>
-      <c r="P59" s="3">
+      <c r="Q59" s="3">
         <v>24400</v>
       </c>
-      <c r="Q59" s="3">
+      <c r="R59" s="3">
         <v>20100</v>
       </c>
-      <c r="R59" s="3">
+      <c r="S59" s="3">
         <v>21900</v>
       </c>
-      <c r="S59" s="3">
+      <c r="T59" s="3">
         <v>24900</v>
       </c>
-      <c r="T59" s="3">
+      <c r="U59" s="3">
         <v>21600</v>
-      </c>
-      <c r="U59" s="3">
-        <v>18600</v>
       </c>
       <c r="V59" s="3">
         <v>18600</v>
       </c>
       <c r="W59" s="3">
+        <v>18600</v>
+      </c>
+      <c r="X59" s="3">
         <v>23200</v>
       </c>
-      <c r="X59" s="3">
+      <c r="Y59" s="3">
         <v>18000</v>
       </c>
-      <c r="Y59" s="3">
+      <c r="Z59" s="3">
         <v>16100</v>
       </c>
-      <c r="Z59" s="3">
+      <c r="AA59" s="3">
         <v>15700</v>
       </c>
-      <c r="AA59" s="3">
+      <c r="AB59" s="3">
         <v>18200</v>
       </c>
-      <c r="AB59" s="3">
+      <c r="AC59" s="3">
         <v>14600</v>
       </c>
-      <c r="AC59" s="3">
+      <c r="AD59" s="3">
         <v>14300</v>
       </c>
-      <c r="AD59" s="3">
+      <c r="AE59" s="3">
         <v>13800</v>
       </c>
-      <c r="AE59" s="3">
+      <c r="AF59" s="3">
         <v>16200</v>
       </c>
-      <c r="AF59" s="3">
+      <c r="AG59" s="3">
         <v>13900</v>
       </c>
-      <c r="AG59" s="3">
+      <c r="AH59" s="3">
         <v>13500</v>
       </c>
-      <c r="AH59" s="3">
+      <c r="AI59" s="3">
         <v>10000</v>
       </c>
-      <c r="AI59" s="3">
+      <c r="AJ59" s="3">
         <v>17300</v>
       </c>
-      <c r="AJ59" s="3">
+      <c r="AK59" s="3">
         <v>10600</v>
       </c>
-      <c r="AK59" s="3">
+      <c r="AL59" s="3">
         <v>16400</v>
       </c>
-      <c r="AL59" s="3">
+      <c r="AM59" s="3">
         <v>8500</v>
       </c>
-      <c r="AM59" s="3">
+      <c r="AN59" s="3">
         <v>17900</v>
       </c>
-      <c r="AN59" s="3">
+      <c r="AO59" s="3">
         <v>12700</v>
       </c>
-      <c r="AO59" s="3">
+      <c r="AP59" s="3">
         <v>18700</v>
       </c>
     </row>
-    <row r="60" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="60" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C60" s="1" t="s">
         <v>53</v>
       </c>
       <c r="D60" s="3">
+        <v>104800</v>
+      </c>
+      <c r="E60" s="3">
         <v>97200</v>
       </c>
-      <c r="E60" s="3">
+      <c r="F60" s="3">
         <v>98600</v>
       </c>
-      <c r="F60" s="3">
+      <c r="G60" s="3">
         <v>110900</v>
       </c>
-      <c r="G60" s="3">
-        <v>107100</v>
-      </c>
       <c r="H60" s="3">
+        <v>97200</v>
+      </c>
+      <c r="I60" s="3">
         <v>84300</v>
       </c>
-      <c r="I60" s="3">
+      <c r="J60" s="3">
         <v>92300</v>
       </c>
-      <c r="J60" s="3">
+      <c r="K60" s="3">
         <v>98000</v>
       </c>
-      <c r="K60" s="3">
+      <c r="L60" s="3">
         <v>103300</v>
       </c>
-      <c r="L60" s="3">
+      <c r="M60" s="3">
         <v>79700</v>
       </c>
-      <c r="M60" s="3">
+      <c r="N60" s="3">
         <v>94500</v>
       </c>
-      <c r="N60" s="3">
+      <c r="O60" s="3">
         <v>94300</v>
       </c>
-      <c r="O60" s="3">
+      <c r="P60" s="3">
         <v>90900</v>
       </c>
-      <c r="P60" s="3">
+      <c r="Q60" s="3">
         <v>84900</v>
       </c>
-      <c r="Q60" s="3">
+      <c r="R60" s="3">
         <v>90900</v>
       </c>
-      <c r="R60" s="3">
+      <c r="S60" s="3">
         <v>88200</v>
       </c>
-      <c r="S60" s="3">
+      <c r="T60" s="3">
         <v>101500</v>
       </c>
-      <c r="T60" s="3">
+      <c r="U60" s="3">
         <v>75500</v>
       </c>
-      <c r="U60" s="3">
+      <c r="V60" s="3">
         <v>71500</v>
       </c>
-      <c r="V60" s="3">
+      <c r="W60" s="3">
         <v>66500</v>
       </c>
-      <c r="W60" s="3">
+      <c r="X60" s="3">
         <v>70500</v>
       </c>
-      <c r="X60" s="3">
+      <c r="Y60" s="3">
         <v>59000</v>
       </c>
-      <c r="Y60" s="3">
+      <c r="Z60" s="3">
         <v>58800</v>
       </c>
-      <c r="Z60" s="3">
+      <c r="AA60" s="3">
         <v>56700</v>
       </c>
-      <c r="AA60" s="3">
+      <c r="AB60" s="3">
         <v>62200</v>
       </c>
-      <c r="AB60" s="3">
+      <c r="AC60" s="3">
         <v>51300</v>
       </c>
-      <c r="AC60" s="3">
+      <c r="AD60" s="3">
         <v>53900</v>
       </c>
-      <c r="AD60" s="3">
+      <c r="AE60" s="3">
         <v>55700</v>
       </c>
-      <c r="AE60" s="3">
+      <c r="AF60" s="3">
         <v>55400</v>
       </c>
-      <c r="AF60" s="3">
+      <c r="AG60" s="3">
         <v>53100</v>
       </c>
-      <c r="AG60" s="3">
+      <c r="AH60" s="3">
         <v>58800</v>
       </c>
-      <c r="AH60" s="3">
+      <c r="AI60" s="3">
         <v>56500</v>
       </c>
-      <c r="AI60" s="3">
+      <c r="AJ60" s="3">
         <v>60600</v>
       </c>
-      <c r="AJ60" s="3">
+      <c r="AK60" s="3">
         <v>48500</v>
       </c>
-      <c r="AK60" s="3">
+      <c r="AL60" s="3">
         <v>52500</v>
       </c>
-      <c r="AL60" s="3">
+      <c r="AM60" s="3">
         <v>45000</v>
       </c>
-      <c r="AM60" s="3">
+      <c r="AN60" s="3">
         <v>55700</v>
       </c>
-      <c r="AN60" s="3">
+      <c r="AO60" s="3">
         <v>41900</v>
       </c>
-      <c r="AO60" s="3">
+      <c r="AP60" s="3">
         <v>53100</v>
       </c>
     </row>
-    <row r="61" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="61" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C61" s="1" t="s">
         <v>54</v>
       </c>
       <c r="D61" s="3">
+        <v>258500</v>
+      </c>
+      <c r="E61" s="3">
         <v>268500</v>
       </c>
-      <c r="E61" s="3">
+      <c r="F61" s="3">
         <v>283400</v>
       </c>
-      <c r="F61" s="3">
+      <c r="G61" s="3">
         <v>298900</v>
       </c>
-      <c r="G61" s="3">
-        <v>149800</v>
-      </c>
       <c r="H61" s="3">
+        <v>159900</v>
+      </c>
+      <c r="I61" s="3">
         <v>114500</v>
       </c>
-      <c r="I61" s="3">
+      <c r="J61" s="3">
         <v>103500</v>
       </c>
-      <c r="J61" s="3">
+      <c r="K61" s="3">
         <v>133700</v>
       </c>
-      <c r="K61" s="3">
+      <c r="L61" s="3">
         <v>98300</v>
       </c>
-      <c r="L61" s="3">
+      <c r="M61" s="3">
         <v>120900</v>
       </c>
-      <c r="M61" s="3">
+      <c r="N61" s="3">
         <v>59300</v>
       </c>
-      <c r="N61" s="3">
+      <c r="O61" s="3">
         <v>88000</v>
       </c>
-      <c r="O61" s="3">
+      <c r="P61" s="3">
         <v>110400</v>
       </c>
-      <c r="P61" s="3">
+      <c r="Q61" s="3">
         <v>120700</v>
       </c>
-      <c r="Q61" s="3">
+      <c r="R61" s="3">
         <v>130700</v>
       </c>
-      <c r="R61" s="3">
+      <c r="S61" s="3">
         <v>149200</v>
       </c>
-      <c r="S61" s="3">
+      <c r="T61" s="3">
         <v>115600</v>
       </c>
-      <c r="T61" s="3">
+      <c r="U61" s="3">
         <v>105900</v>
       </c>
-      <c r="U61" s="3">
+      <c r="V61" s="3">
         <v>73900</v>
       </c>
-      <c r="V61" s="3">
+      <c r="W61" s="3">
         <v>85900</v>
       </c>
-      <c r="W61" s="3">
+      <c r="X61" s="3">
         <v>88800</v>
       </c>
-      <c r="X61" s="3">
+      <c r="Y61" s="3">
         <v>85800</v>
       </c>
-      <c r="Y61" s="3">
+      <c r="Z61" s="3">
         <v>65800</v>
       </c>
-      <c r="Z61" s="3">
+      <c r="AA61" s="3">
         <v>55800</v>
       </c>
-      <c r="AA61" s="3">
+      <c r="AB61" s="3">
         <v>49800</v>
       </c>
-      <c r="AB61" s="3">
+      <c r="AC61" s="3">
         <v>57700</v>
       </c>
-      <c r="AC61" s="3">
+      <c r="AD61" s="3">
         <v>64700</v>
-      </c>
-      <c r="AD61" s="3">
-        <v>74700</v>
       </c>
       <c r="AE61" s="3">
         <v>74700</v>
       </c>
       <c r="AF61" s="3">
+        <v>74700</v>
+      </c>
+      <c r="AG61" s="3">
         <v>80600</v>
       </c>
-      <c r="AG61" s="3">
+      <c r="AH61" s="3">
         <v>75800</v>
-      </c>
-      <c r="AH61" s="3">
-        <v>90800</v>
       </c>
       <c r="AI61" s="3">
         <v>90800</v>
       </c>
       <c r="AJ61" s="3">
+        <v>90800</v>
+      </c>
+      <c r="AK61" s="3">
         <v>104200</v>
       </c>
-      <c r="AK61" s="3">
+      <c r="AL61" s="3">
         <v>102700</v>
       </c>
-      <c r="AL61" s="3">
+      <c r="AM61" s="3">
         <v>112200</v>
       </c>
-      <c r="AM61" s="3">
+      <c r="AN61" s="3">
         <v>94600</v>
       </c>
-      <c r="AN61" s="3">
+      <c r="AO61" s="3">
         <v>105100</v>
       </c>
-      <c r="AO61" s="3">
+      <c r="AP61" s="3">
         <v>106900</v>
       </c>
     </row>
-    <row r="62" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="62" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C62" s="1" t="s">
         <v>55</v>
       </c>
       <c r="D62" s="3">
+        <v>61100</v>
+      </c>
+      <c r="E62" s="3">
         <v>67100</v>
       </c>
-      <c r="E62" s="3">
+      <c r="F62" s="3">
         <v>70100</v>
       </c>
-      <c r="F62" s="3">
+      <c r="G62" s="3">
         <v>68600</v>
       </c>
-      <c r="G62" s="3">
+      <c r="H62" s="3">
         <v>27100</v>
       </c>
-      <c r="H62" s="3">
+      <c r="I62" s="3">
         <v>26100</v>
       </c>
-      <c r="I62" s="3">
+      <c r="J62" s="3">
         <v>25200</v>
       </c>
-      <c r="J62" s="3">
+      <c r="K62" s="3">
         <v>24100</v>
       </c>
-      <c r="K62" s="3">
+      <c r="L62" s="3">
         <v>24300</v>
       </c>
-      <c r="L62" s="3">
+      <c r="M62" s="3">
         <v>22400</v>
       </c>
-      <c r="M62" s="3">
+      <c r="N62" s="3">
         <v>11000</v>
       </c>
-      <c r="N62" s="3">
+      <c r="O62" s="3">
         <v>10800</v>
       </c>
-      <c r="O62" s="3">
+      <c r="P62" s="3">
         <v>11500</v>
       </c>
-      <c r="P62" s="3">
+      <c r="Q62" s="3">
         <v>47300</v>
       </c>
-      <c r="Q62" s="3">
+      <c r="R62" s="3">
         <v>46300</v>
       </c>
-      <c r="R62" s="3">
+      <c r="S62" s="3">
         <v>45800</v>
       </c>
-      <c r="S62" s="3">
+      <c r="T62" s="3">
         <v>47600</v>
       </c>
-      <c r="T62" s="3">
+      <c r="U62" s="3">
         <v>48000</v>
       </c>
-      <c r="U62" s="3">
+      <c r="V62" s="3">
         <v>48100</v>
       </c>
-      <c r="V62" s="3">
+      <c r="W62" s="3">
         <v>47400</v>
       </c>
-      <c r="W62" s="3">
+      <c r="X62" s="3">
         <v>48000</v>
       </c>
-      <c r="X62" s="3">
+      <c r="Y62" s="3">
         <v>44200</v>
       </c>
-      <c r="Y62" s="3">
+      <c r="Z62" s="3">
         <v>43900</v>
       </c>
-      <c r="Z62" s="3">
+      <c r="AA62" s="3">
         <v>43600</v>
       </c>
-      <c r="AA62" s="3">
+      <c r="AB62" s="3">
         <v>43900</v>
       </c>
-      <c r="AB62" s="3">
+      <c r="AC62" s="3">
         <v>45400</v>
       </c>
-      <c r="AC62" s="3">
+      <c r="AD62" s="3">
         <v>45000</v>
       </c>
-      <c r="AD62" s="3">
+      <c r="AE62" s="3">
         <v>45200</v>
       </c>
-      <c r="AE62" s="3">
+      <c r="AF62" s="3">
         <v>37700</v>
       </c>
-      <c r="AF62" s="3">
+      <c r="AG62" s="3">
         <v>37200</v>
       </c>
-      <c r="AG62" s="3">
+      <c r="AH62" s="3">
         <v>37400</v>
       </c>
-      <c r="AH62" s="3">
+      <c r="AI62" s="3">
         <v>37100</v>
       </c>
-      <c r="AI62" s="3">
+      <c r="AJ62" s="3">
         <v>37400</v>
       </c>
-      <c r="AJ62" s="3">
+      <c r="AK62" s="3">
         <v>34700</v>
       </c>
-      <c r="AK62" s="3">
+      <c r="AL62" s="3">
         <v>51100</v>
       </c>
-      <c r="AL62" s="3">
+      <c r="AM62" s="3">
         <v>51500</v>
       </c>
-      <c r="AM62" s="3">
+      <c r="AN62" s="3">
         <v>50500</v>
       </c>
-      <c r="AN62" s="3">
+      <c r="AO62" s="3">
         <v>50400</v>
       </c>
-      <c r="AO62" s="3">
+      <c r="AP62" s="3">
         <v>50100</v>
       </c>
     </row>
-    <row r="63" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="63" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C63" s="1" t="s">
         <v>56</v>
       </c>
@@ -6719,8 +6868,11 @@
       <c r="AO63" s="3">
         <v>0</v>
       </c>
+      <c r="AP63" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="64" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="64" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C64" s="1" t="s">
         <v>20</v>
       </c>
@@ -6838,8 +6990,11 @@
       <c r="AO64" s="3">
         <v>0</v>
       </c>
+      <c r="AP64" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="65" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="65" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C65" s="1" t="s">
         <v>57</v>
       </c>
@@ -6957,127 +7112,133 @@
       <c r="AO65" s="3">
         <v>0</v>
       </c>
+      <c r="AP65" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="66" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="66" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C66" s="1" t="s">
         <v>58</v>
       </c>
       <c r="D66" s="3">
+        <v>452300</v>
+      </c>
+      <c r="E66" s="3">
         <v>457600</v>
       </c>
-      <c r="E66" s="3">
+      <c r="F66" s="3">
         <v>477200</v>
       </c>
-      <c r="F66" s="3">
+      <c r="G66" s="3">
         <v>503700</v>
       </c>
-      <c r="G66" s="3">
-        <v>309600</v>
-      </c>
       <c r="H66" s="3">
+        <v>309800</v>
+      </c>
+      <c r="I66" s="3">
         <v>250300</v>
       </c>
-      <c r="I66" s="3">
+      <c r="J66" s="3">
         <v>246300</v>
       </c>
-      <c r="J66" s="3">
+      <c r="K66" s="3">
         <v>281500</v>
       </c>
-      <c r="K66" s="3">
+      <c r="L66" s="3">
         <v>251900</v>
       </c>
-      <c r="L66" s="3">
+      <c r="M66" s="3">
         <v>250300</v>
       </c>
-      <c r="M66" s="3">
+      <c r="N66" s="3">
         <v>192600</v>
       </c>
-      <c r="N66" s="3">
+      <c r="O66" s="3">
         <v>221000</v>
       </c>
-      <c r="O66" s="3">
+      <c r="P66" s="3">
         <v>240500</v>
       </c>
-      <c r="P66" s="3">
+      <c r="Q66" s="3">
         <v>252800</v>
       </c>
-      <c r="Q66" s="3">
+      <c r="R66" s="3">
         <v>267900</v>
       </c>
-      <c r="R66" s="3">
+      <c r="S66" s="3">
         <v>283100</v>
       </c>
-      <c r="S66" s="3">
+      <c r="T66" s="3">
         <v>264700</v>
       </c>
-      <c r="T66" s="3">
+      <c r="U66" s="3">
         <v>229500</v>
       </c>
-      <c r="U66" s="3">
+      <c r="V66" s="3">
         <v>193500</v>
       </c>
-      <c r="V66" s="3">
+      <c r="W66" s="3">
         <v>199800</v>
       </c>
-      <c r="W66" s="3">
+      <c r="X66" s="3">
         <v>207300</v>
       </c>
-      <c r="X66" s="3">
+      <c r="Y66" s="3">
         <v>189100</v>
       </c>
-      <c r="Y66" s="3">
+      <c r="Z66" s="3">
         <v>168400</v>
       </c>
-      <c r="Z66" s="3">
+      <c r="AA66" s="3">
         <v>156000</v>
       </c>
-      <c r="AA66" s="3">
+      <c r="AB66" s="3">
         <v>155800</v>
       </c>
-      <c r="AB66" s="3">
+      <c r="AC66" s="3">
         <v>154400</v>
       </c>
-      <c r="AC66" s="3">
+      <c r="AD66" s="3">
         <v>163600</v>
       </c>
-      <c r="AD66" s="3">
+      <c r="AE66" s="3">
         <v>175600</v>
       </c>
-      <c r="AE66" s="3">
+      <c r="AF66" s="3">
         <v>167700</v>
       </c>
-      <c r="AF66" s="3">
+      <c r="AG66" s="3">
         <v>170900</v>
       </c>
-      <c r="AG66" s="3">
+      <c r="AH66" s="3">
         <v>172000</v>
       </c>
-      <c r="AH66" s="3">
+      <c r="AI66" s="3">
         <v>184400</v>
       </c>
-      <c r="AI66" s="3">
+      <c r="AJ66" s="3">
         <v>188700</v>
       </c>
-      <c r="AJ66" s="3">
+      <c r="AK66" s="3">
         <v>187500</v>
       </c>
-      <c r="AK66" s="3">
+      <c r="AL66" s="3">
         <v>206200</v>
       </c>
-      <c r="AL66" s="3">
+      <c r="AM66" s="3">
         <v>208600</v>
       </c>
-      <c r="AM66" s="3">
+      <c r="AN66" s="3">
         <v>200800</v>
       </c>
-      <c r="AN66" s="3">
+      <c r="AO66" s="3">
         <v>197400</v>
       </c>
-      <c r="AO66" s="3">
+      <c r="AP66" s="3">
         <v>210100</v>
       </c>
     </row>
-    <row r="67" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="67" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C67" s="1" t="s">
         <v>59</v>
       </c>
@@ -7119,8 +7280,9 @@
       <c r="AM67" s="3"/>
       <c r="AN67" s="3"/>
       <c r="AO67" s="3"/>
+      <c r="AP67" s="3"/>
     </row>
-    <row r="68" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="68" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C68" s="1" t="s">
         <v>60</v>
       </c>
@@ -7238,8 +7400,11 @@
       <c r="AO68" s="3">
         <v>0</v>
       </c>
+      <c r="AP68" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="69" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="69" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C69" s="1" t="s">
         <v>61</v>
       </c>
@@ -7357,8 +7522,11 @@
       <c r="AO69" s="3">
         <v>0</v>
       </c>
+      <c r="AP69" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="70" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="70" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C70" s="1" t="s">
         <v>62</v>
       </c>
@@ -7476,8 +7644,11 @@
       <c r="AO70" s="3">
         <v>0</v>
       </c>
+      <c r="AP70" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="71" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="71" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C71" s="1" t="s">
         <v>63</v>
       </c>
@@ -7595,127 +7766,133 @@
       <c r="AO71" s="3">
         <v>0</v>
       </c>
+      <c r="AP71" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="72" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="72" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C72" s="1" t="s">
         <v>64</v>
       </c>
       <c r="D72" s="3">
+        <v>500100</v>
+      </c>
+      <c r="E72" s="3">
         <v>488700</v>
       </c>
-      <c r="E72" s="3">
+      <c r="F72" s="3">
         <v>478300</v>
       </c>
-      <c r="F72" s="3">
+      <c r="G72" s="3">
         <v>459700</v>
       </c>
-      <c r="G72" s="3">
+      <c r="H72" s="3">
         <v>434300</v>
       </c>
-      <c r="H72" s="3">
+      <c r="I72" s="3">
         <v>421700</v>
       </c>
-      <c r="I72" s="3">
+      <c r="J72" s="3">
         <v>410400</v>
       </c>
-      <c r="J72" s="3">
+      <c r="K72" s="3">
         <v>390100</v>
       </c>
-      <c r="K72" s="3">
+      <c r="L72" s="3">
         <v>364500</v>
       </c>
-      <c r="L72" s="3">
+      <c r="M72" s="3">
         <v>354100</v>
       </c>
-      <c r="M72" s="3">
+      <c r="N72" s="3">
         <v>342500</v>
       </c>
-      <c r="N72" s="3">
+      <c r="O72" s="3">
         <v>322700</v>
       </c>
-      <c r="O72" s="3">
+      <c r="P72" s="3">
         <v>302400</v>
       </c>
-      <c r="P72" s="3">
+      <c r="Q72" s="3">
         <v>294000</v>
       </c>
-      <c r="Q72" s="3">
+      <c r="R72" s="3">
         <v>286200</v>
       </c>
-      <c r="R72" s="3">
+      <c r="S72" s="3">
         <v>271100</v>
       </c>
-      <c r="S72" s="3">
+      <c r="T72" s="3">
         <v>254400</v>
       </c>
-      <c r="T72" s="3">
+      <c r="U72" s="3">
         <v>246800</v>
       </c>
-      <c r="U72" s="3">
+      <c r="V72" s="3">
         <v>239300</v>
       </c>
-      <c r="V72" s="3">
+      <c r="W72" s="3">
         <v>227900</v>
       </c>
-      <c r="W72" s="3">
+      <c r="X72" s="3">
         <v>213900</v>
       </c>
-      <c r="X72" s="3">
+      <c r="Y72" s="3">
         <v>207400</v>
       </c>
-      <c r="Y72" s="3">
+      <c r="Z72" s="3">
         <v>202000</v>
       </c>
-      <c r="Z72" s="3">
+      <c r="AA72" s="3">
         <v>192300</v>
       </c>
-      <c r="AA72" s="3">
+      <c r="AB72" s="3">
         <v>182900</v>
       </c>
-      <c r="AB72" s="3">
+      <c r="AC72" s="3">
         <v>180700</v>
       </c>
-      <c r="AC72" s="3">
+      <c r="AD72" s="3">
         <v>178600</v>
       </c>
-      <c r="AD72" s="3">
+      <c r="AE72" s="3">
         <v>171800</v>
       </c>
-      <c r="AE72" s="3">
+      <c r="AF72" s="3">
         <v>164400</v>
       </c>
-      <c r="AF72" s="3">
+      <c r="AG72" s="3">
         <v>163100</v>
       </c>
-      <c r="AG72" s="3">
+      <c r="AH72" s="3">
         <v>161400</v>
       </c>
-      <c r="AH72" s="3">
+      <c r="AI72" s="3">
         <v>156400</v>
       </c>
-      <c r="AI72" s="3">
+      <c r="AJ72" s="3">
         <v>147200</v>
       </c>
-      <c r="AJ72" s="3">
+      <c r="AK72" s="3">
         <v>189400</v>
       </c>
-      <c r="AK72" s="3">
+      <c r="AL72" s="3">
         <v>172200</v>
       </c>
-      <c r="AL72" s="3">
+      <c r="AM72" s="3">
         <v>171700</v>
       </c>
-      <c r="AM72" s="3">
+      <c r="AN72" s="3">
         <v>165900</v>
       </c>
-      <c r="AN72" s="3">
+      <c r="AO72" s="3">
         <v>166200</v>
       </c>
-      <c r="AO72" s="3">
+      <c r="AP72" s="3">
         <v>162600</v>
       </c>
     </row>
-    <row r="73" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="73" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C73" s="1" t="s">
         <v>65</v>
       </c>
@@ -7833,8 +8010,11 @@
       <c r="AO73" s="3">
         <v>0</v>
       </c>
+      <c r="AP73" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="74" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="74" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C74" s="1" t="s">
         <v>66</v>
       </c>
@@ -7952,8 +8132,11 @@
       <c r="AO74" s="3">
         <v>0</v>
       </c>
+      <c r="AP74" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="75" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="75" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C75" s="1" t="s">
         <v>67</v>
       </c>
@@ -8071,127 +8254,133 @@
       <c r="AO75" s="3">
         <v>0</v>
       </c>
+      <c r="AP75" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="76" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="76" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C76" s="1" t="s">
         <v>68</v>
       </c>
       <c r="D76" s="3">
+        <v>534000</v>
+      </c>
+      <c r="E76" s="3">
         <v>518900</v>
       </c>
-      <c r="E76" s="3">
+      <c r="F76" s="3">
         <v>507000</v>
       </c>
-      <c r="F76" s="3">
+      <c r="G76" s="3">
         <v>484600</v>
       </c>
-      <c r="G76" s="3">
+      <c r="H76" s="3">
         <v>460300</v>
       </c>
-      <c r="H76" s="3">
+      <c r="I76" s="3">
         <v>457000</v>
       </c>
-      <c r="I76" s="3">
+      <c r="J76" s="3">
         <v>443400</v>
       </c>
-      <c r="J76" s="3">
+      <c r="K76" s="3">
         <v>421200</v>
       </c>
-      <c r="K76" s="3">
+      <c r="L76" s="3">
         <v>406000</v>
       </c>
-      <c r="L76" s="3">
+      <c r="M76" s="3">
         <v>393800</v>
       </c>
-      <c r="M76" s="3">
+      <c r="N76" s="3">
         <v>382700</v>
       </c>
-      <c r="N76" s="3">
+      <c r="O76" s="3">
         <v>371000</v>
       </c>
-      <c r="O76" s="3">
+      <c r="P76" s="3">
         <v>350000</v>
       </c>
-      <c r="P76" s="3">
+      <c r="Q76" s="3">
         <v>341200</v>
       </c>
-      <c r="Q76" s="3">
+      <c r="R76" s="3">
         <v>331400</v>
       </c>
-      <c r="R76" s="3">
+      <c r="S76" s="3">
         <v>313300</v>
       </c>
-      <c r="S76" s="3">
+      <c r="T76" s="3">
         <v>302600</v>
       </c>
-      <c r="T76" s="3">
+      <c r="U76" s="3">
         <v>291700</v>
       </c>
-      <c r="U76" s="3">
+      <c r="V76" s="3">
         <v>284300</v>
       </c>
-      <c r="V76" s="3">
+      <c r="W76" s="3">
         <v>275200</v>
       </c>
-      <c r="W76" s="3">
+      <c r="X76" s="3">
         <v>265200</v>
       </c>
-      <c r="X76" s="3">
+      <c r="Y76" s="3">
         <v>256900</v>
       </c>
-      <c r="Y76" s="3">
+      <c r="Z76" s="3">
         <v>254600</v>
       </c>
-      <c r="Z76" s="3">
+      <c r="AA76" s="3">
         <v>243400</v>
       </c>
-      <c r="AA76" s="3">
+      <c r="AB76" s="3">
         <v>233500</v>
       </c>
-      <c r="AB76" s="3">
+      <c r="AC76" s="3">
         <v>232200</v>
       </c>
-      <c r="AC76" s="3">
+      <c r="AD76" s="3">
         <v>229400</v>
       </c>
-      <c r="AD76" s="3">
+      <c r="AE76" s="3">
         <v>223400</v>
       </c>
-      <c r="AE76" s="3">
+      <c r="AF76" s="3">
         <v>217900</v>
       </c>
-      <c r="AF76" s="3">
+      <c r="AG76" s="3">
         <v>217500</v>
       </c>
-      <c r="AG76" s="3">
+      <c r="AH76" s="3">
         <v>217800</v>
       </c>
-      <c r="AH76" s="3">
+      <c r="AI76" s="3">
         <v>212300</v>
       </c>
-      <c r="AI76" s="3">
+      <c r="AJ76" s="3">
         <v>202200</v>
       </c>
-      <c r="AJ76" s="3">
+      <c r="AK76" s="3">
         <v>243300</v>
       </c>
-      <c r="AK76" s="3">
+      <c r="AL76" s="3">
         <v>225700</v>
       </c>
-      <c r="AL76" s="3">
+      <c r="AM76" s="3">
         <v>224700</v>
       </c>
-      <c r="AM76" s="3">
+      <c r="AN76" s="3">
         <v>217800</v>
       </c>
-      <c r="AN76" s="3">
+      <c r="AO76" s="3">
         <v>217300</v>
       </c>
-      <c r="AO76" s="3">
+      <c r="AP76" s="3">
         <v>212800</v>
       </c>
     </row>
-    <row r="77" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="77" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C77" s="1" t="s">
         <v>69</v>
       </c>
@@ -8309,251 +8498,260 @@
       <c r="AO77" s="3">
         <v>0</v>
       </c>
+      <c r="AP77" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="79" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="79" spans="2:42" x14ac:dyDescent="0.2">
       <c r="B79" s="1" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="80" spans="2:41" x14ac:dyDescent="0.2">
+    <row r="80" spans="2:42" x14ac:dyDescent="0.2">
       <c r="C80" s="1" t="s">
         <v>2</v>
       </c>
       <c r="D80" s="2">
+        <v>46110</v>
+      </c>
+      <c r="E80" s="2">
         <v>46019</v>
       </c>
-      <c r="E80" s="2">
+      <c r="F80" s="2">
         <v>45928</v>
       </c>
-      <c r="F80" s="2">
+      <c r="G80" s="2">
         <v>45837</v>
       </c>
-      <c r="G80" s="2">
+      <c r="H80" s="2">
         <v>45746</v>
       </c>
-      <c r="H80" s="2">
+      <c r="I80" s="2">
         <v>45655</v>
       </c>
-      <c r="I80" s="2">
+      <c r="J80" s="2">
         <v>45564</v>
       </c>
-      <c r="J80" s="2">
+      <c r="K80" s="2">
         <v>45473</v>
       </c>
-      <c r="K80" s="2">
+      <c r="L80" s="2">
         <v>45382</v>
       </c>
-      <c r="L80" s="2">
+      <c r="M80" s="2">
         <v>45291</v>
       </c>
-      <c r="M80" s="2">
+      <c r="N80" s="2">
         <v>45200</v>
       </c>
-      <c r="N80" s="2">
+      <c r="O80" s="2">
         <v>45109</v>
       </c>
-      <c r="O80" s="2">
+      <c r="P80" s="2">
         <v>45018</v>
       </c>
-      <c r="P80" s="2">
+      <c r="Q80" s="2">
         <v>44927</v>
       </c>
-      <c r="Q80" s="2">
+      <c r="R80" s="2">
         <v>44836</v>
       </c>
-      <c r="R80" s="2">
+      <c r="S80" s="2">
         <v>44745</v>
       </c>
-      <c r="S80" s="2">
+      <c r="T80" s="2">
         <v>44654</v>
       </c>
-      <c r="T80" s="2">
+      <c r="U80" s="2">
         <v>44556</v>
       </c>
-      <c r="U80" s="2">
+      <c r="V80" s="2">
         <v>44465</v>
       </c>
-      <c r="V80" s="2">
+      <c r="W80" s="2">
         <v>44374</v>
       </c>
-      <c r="W80" s="2">
+      <c r="X80" s="2">
         <v>44283</v>
       </c>
-      <c r="X80" s="2">
+      <c r="Y80" s="2">
         <v>44192</v>
       </c>
-      <c r="Y80" s="2">
+      <c r="Z80" s="2">
         <v>44101</v>
       </c>
-      <c r="Z80" s="2">
+      <c r="AA80" s="2">
         <v>44010</v>
       </c>
-      <c r="AA80" s="2">
+      <c r="AB80" s="2">
         <v>43919</v>
       </c>
-      <c r="AB80" s="2">
+      <c r="AC80" s="2">
         <v>43828</v>
       </c>
-      <c r="AC80" s="2">
+      <c r="AD80" s="2">
         <v>43737</v>
       </c>
-      <c r="AD80" s="2">
+      <c r="AE80" s="2">
         <v>43646</v>
       </c>
-      <c r="AE80" s="2">
+      <c r="AF80" s="2">
         <v>43555</v>
       </c>
-      <c r="AF80" s="2">
+      <c r="AG80" s="2">
         <v>43464</v>
       </c>
-      <c r="AG80" s="2">
+      <c r="AH80" s="2">
         <v>43373</v>
       </c>
-      <c r="AH80" s="2">
+      <c r="AI80" s="2">
         <v>43282</v>
       </c>
-      <c r="AI80" s="2">
+      <c r="AJ80" s="2">
         <v>43191</v>
       </c>
-      <c r="AJ80" s="2">
+      <c r="AK80" s="2">
         <v>43100</v>
       </c>
-      <c r="AK80" s="2">
+      <c r="AL80" s="2">
         <v>43009</v>
       </c>
-      <c r="AL80" s="2">
+      <c r="AM80" s="2">
         <v>42918</v>
       </c>
-      <c r="AM80" s="2">
+      <c r="AN80" s="2">
         <v>42827</v>
       </c>
-      <c r="AN80" s="2">
+      <c r="AO80" s="2">
         <v>42736</v>
       </c>
-      <c r="AO80" s="2">
+      <c r="AP80" s="2">
         <v>42645</v>
       </c>
     </row>
-    <row r="81" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="81" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
       <c r="D81" s="3">
+        <v>15500</v>
+      </c>
+      <c r="E81" s="3">
         <v>14300</v>
       </c>
-      <c r="E81" s="3">
+      <c r="F81" s="3">
         <v>22600</v>
       </c>
-      <c r="F81" s="3">
+      <c r="G81" s="3">
         <v>29200</v>
       </c>
-      <c r="G81" s="3">
+      <c r="H81" s="3">
         <v>16300</v>
       </c>
-      <c r="H81" s="3">
+      <c r="I81" s="3">
         <v>15000</v>
       </c>
-      <c r="I81" s="3">
+      <c r="J81" s="3">
         <v>24100</v>
       </c>
-      <c r="J81" s="3">
+      <c r="K81" s="3">
         <v>28900</v>
       </c>
-      <c r="K81" s="3">
+      <c r="L81" s="3">
         <v>13800</v>
       </c>
-      <c r="L81" s="3">
+      <c r="M81" s="3">
         <v>14900</v>
       </c>
-      <c r="M81" s="3">
+      <c r="N81" s="3">
         <v>23200</v>
       </c>
-      <c r="N81" s="3">
+      <c r="O81" s="3">
         <v>23400</v>
       </c>
-      <c r="O81" s="3">
+      <c r="P81" s="3">
         <v>11600</v>
       </c>
-      <c r="P81" s="3">
+      <c r="Q81" s="3">
         <v>10700</v>
       </c>
-      <c r="Q81" s="3">
+      <c r="R81" s="3">
         <v>18000</v>
       </c>
-      <c r="R81" s="3">
+      <c r="S81" s="3">
         <v>19700</v>
       </c>
-      <c r="S81" s="3">
+      <c r="T81" s="3">
         <v>10600</v>
       </c>
-      <c r="T81" s="3">
+      <c r="U81" s="3">
         <v>10200</v>
       </c>
-      <c r="U81" s="3">
+      <c r="V81" s="3">
         <v>14100</v>
       </c>
-      <c r="V81" s="3">
+      <c r="W81" s="3">
         <v>16600</v>
       </c>
-      <c r="W81" s="3">
+      <c r="X81" s="3">
         <v>9100</v>
       </c>
-      <c r="X81" s="3">
+      <c r="Y81" s="3">
         <v>7900</v>
       </c>
-      <c r="Y81" s="3">
+      <c r="Z81" s="3">
         <v>12200</v>
       </c>
-      <c r="Z81" s="3">
+      <c r="AA81" s="3">
         <v>11800</v>
       </c>
-      <c r="AA81" s="3">
+      <c r="AB81" s="3">
         <v>4800</v>
       </c>
-      <c r="AB81" s="3">
+      <c r="AC81" s="3">
         <v>4500</v>
       </c>
-      <c r="AC81" s="3">
+      <c r="AD81" s="3">
         <v>9300</v>
       </c>
-      <c r="AD81" s="3">
+      <c r="AE81" s="3">
         <v>9800</v>
       </c>
-      <c r="AE81" s="3">
+      <c r="AF81" s="3">
         <v>3800</v>
       </c>
-      <c r="AF81" s="3">
+      <c r="AG81" s="3">
         <v>4100</v>
       </c>
-      <c r="AG81" s="3">
+      <c r="AH81" s="3">
         <v>7400</v>
       </c>
-      <c r="AH81" s="3">
+      <c r="AI81" s="3">
         <v>9100</v>
       </c>
-      <c r="AI81" s="3">
+      <c r="AJ81" s="3">
         <v>-37400</v>
       </c>
-      <c r="AJ81" s="3">
+      <c r="AK81" s="3">
         <v>17100</v>
       </c>
-      <c r="AK81" s="3">
+      <c r="AL81" s="3">
         <v>5200</v>
       </c>
-      <c r="AL81" s="3">
+      <c r="AM81" s="3">
         <v>5800</v>
       </c>
-      <c r="AM81" s="3">
+      <c r="AN81" s="3">
         <v>4200</v>
       </c>
-      <c r="AN81" s="3">
+      <c r="AO81" s="3">
         <v>3600</v>
       </c>
-      <c r="AO81" s="3">
+      <c r="AP81" s="3">
         <v>7200</v>
       </c>
     </row>
-    <row r="82" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="82" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C82" s="1" t="s">
         <v>71</v>
       </c>
@@ -8595,82 +8793,83 @@
       <c r="AM82" s="3"/>
       <c r="AN82" s="3"/>
       <c r="AO82" s="3"/>
+      <c r="AP82" s="3"/>
     </row>
-    <row r="83" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="83" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C83" s="1" t="s">
         <v>72</v>
       </c>
       <c r="D83" s="3">
+        <v>10600</v>
+      </c>
+      <c r="E83" s="3">
         <v>10100</v>
       </c>
-      <c r="E83" s="3">
+      <c r="F83" s="3">
         <v>9900</v>
       </c>
-      <c r="F83" s="3">
+      <c r="G83" s="3">
         <v>9300</v>
       </c>
-      <c r="G83" s="3">
+      <c r="H83" s="3">
         <v>500</v>
       </c>
-      <c r="H83" s="3">
+      <c r="I83" s="3">
         <v>8300</v>
       </c>
-      <c r="I83" s="3">
+      <c r="J83" s="3">
         <v>7400</v>
       </c>
-      <c r="J83" s="3">
+      <c r="K83" s="3">
         <v>7100</v>
       </c>
-      <c r="K83" s="3">
+      <c r="L83" s="3">
         <v>200</v>
       </c>
-      <c r="L83" s="3">
+      <c r="M83" s="3">
         <v>7000</v>
       </c>
-      <c r="M83" s="3">
+      <c r="N83" s="3">
         <v>6800</v>
       </c>
-      <c r="N83" s="3">
+      <c r="O83" s="3">
         <v>6600</v>
       </c>
-      <c r="O83" s="3">
+      <c r="P83" s="3">
         <v>6300</v>
       </c>
-      <c r="P83" s="3">
+      <c r="Q83" s="3">
         <v>7000</v>
       </c>
-      <c r="Q83" s="3">
+      <c r="R83" s="3">
         <v>6800</v>
       </c>
-      <c r="R83" s="3">
+      <c r="S83" s="3">
         <v>6600</v>
       </c>
-      <c r="S83" s="3">
+      <c r="T83" s="3">
         <v>6300</v>
-      </c>
-      <c r="T83" s="3">
-        <v>6000</v>
       </c>
       <c r="U83" s="3">
         <v>6000</v>
       </c>
       <c r="V83" s="3">
-        <v>5900</v>
+        <v>6000</v>
       </c>
       <c r="W83" s="3">
         <v>5900</v>
       </c>
       <c r="X83" s="3">
+        <v>5900</v>
+      </c>
+      <c r="Y83" s="3">
         <v>5700</v>
       </c>
-      <c r="Y83" s="3">
+      <c r="Z83" s="3">
         <v>5600</v>
       </c>
-      <c r="Z83" s="3">
+      <c r="AA83" s="3">
         <v>5500</v>
-      </c>
-      <c r="AA83" s="3">
-        <v>5400</v>
       </c>
       <c r="AB83" s="3">
         <v>5400</v>
@@ -8688,34 +8887,37 @@
         <v>5400</v>
       </c>
       <c r="AG83" s="3">
-        <v>5500</v>
+        <v>5400</v>
       </c>
       <c r="AH83" s="3">
         <v>5500</v>
       </c>
       <c r="AI83" s="3">
+        <v>5500</v>
+      </c>
+      <c r="AJ83" s="3">
         <v>5600</v>
       </c>
-      <c r="AJ83" s="3">
+      <c r="AK83" s="3">
         <v>5400</v>
       </c>
-      <c r="AK83" s="3">
+      <c r="AL83" s="3">
         <v>5500</v>
       </c>
-      <c r="AL83" s="3">
+      <c r="AM83" s="3">
         <v>5800</v>
       </c>
-      <c r="AM83" s="3">
+      <c r="AN83" s="3">
         <v>5400</v>
-      </c>
-      <c r="AN83" s="3">
-        <v>5200</v>
       </c>
       <c r="AO83" s="3">
         <v>5200</v>
       </c>
+      <c r="AP83" s="3">
+        <v>5200</v>
+      </c>
     </row>
-    <row r="84" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="84" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C84" s="1" t="s">
         <v>73</v>
       </c>
@@ -8833,8 +9035,11 @@
       <c r="AO84" s="3">
         <v>0</v>
       </c>
+      <c r="AP84" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="85" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="85" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C85" s="1" t="s">
         <v>74</v>
       </c>
@@ -8952,8 +9157,11 @@
       <c r="AO85" s="3">
         <v>0</v>
       </c>
+      <c r="AP85" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="86" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="86" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C86" s="1" t="s">
         <v>75</v>
       </c>
@@ -9071,8 +9279,11 @@
       <c r="AO86" s="3">
         <v>0</v>
       </c>
+      <c r="AP86" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="87" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="87" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C87" s="1" t="s">
         <v>76</v>
       </c>
@@ -9190,8 +9401,11 @@
       <c r="AO87" s="3">
         <v>0</v>
       </c>
+      <c r="AP87" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="88" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="88" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C88" s="1" t="s">
         <v>77</v>
       </c>
@@ -9309,127 +9523,133 @@
       <c r="AO88" s="3">
         <v>0</v>
       </c>
+      <c r="AP88" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="89" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="89" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C89" s="1" t="s">
         <v>78</v>
       </c>
       <c r="D89" s="3">
+        <v>37700</v>
+      </c>
+      <c r="E89" s="3">
         <v>35600</v>
       </c>
-      <c r="E89" s="3">
+      <c r="F89" s="3">
         <v>39500</v>
       </c>
-      <c r="F89" s="3">
+      <c r="G89" s="3">
         <v>31500</v>
       </c>
-      <c r="G89" s="3">
+      <c r="H89" s="3">
         <v>30800</v>
       </c>
-      <c r="H89" s="3">
+      <c r="I89" s="3">
         <v>21000</v>
       </c>
-      <c r="I89" s="3">
+      <c r="J89" s="3">
         <v>41600</v>
       </c>
-      <c r="J89" s="3">
+      <c r="K89" s="3">
         <v>17600</v>
       </c>
-      <c r="K89" s="3">
+      <c r="L89" s="3">
         <v>41900</v>
       </c>
-      <c r="L89" s="3">
+      <c r="M89" s="3">
         <v>25000</v>
       </c>
-      <c r="M89" s="3">
+      <c r="N89" s="3">
         <v>57800</v>
       </c>
-      <c r="N89" s="3">
+      <c r="O89" s="3">
         <v>34900</v>
       </c>
-      <c r="O89" s="3">
+      <c r="P89" s="3">
         <v>32900</v>
       </c>
-      <c r="P89" s="3">
+      <c r="Q89" s="3">
         <v>25700</v>
       </c>
-      <c r="Q89" s="3">
+      <c r="R89" s="3">
         <v>28200</v>
       </c>
-      <c r="R89" s="3">
+      <c r="S89" s="3">
         <v>-9400</v>
       </c>
-      <c r="S89" s="3">
+      <c r="T89" s="3">
         <v>4100</v>
       </c>
-      <c r="T89" s="3">
+      <c r="U89" s="3">
         <v>-1400</v>
       </c>
-      <c r="U89" s="3">
+      <c r="V89" s="3">
         <v>25300</v>
       </c>
-      <c r="V89" s="3">
+      <c r="W89" s="3">
         <v>14800</v>
       </c>
-      <c r="W89" s="3">
+      <c r="X89" s="3">
         <v>17200</v>
       </c>
-      <c r="X89" s="3">
+      <c r="Y89" s="3">
         <v>6500</v>
       </c>
-      <c r="Y89" s="3">
+      <c r="Z89" s="3">
         <v>18600</v>
       </c>
-      <c r="Z89" s="3">
+      <c r="AA89" s="3">
         <v>1600</v>
       </c>
-      <c r="AA89" s="3">
+      <c r="AB89" s="3">
         <v>13900</v>
       </c>
-      <c r="AB89" s="3">
+      <c r="AC89" s="3">
         <v>17900</v>
       </c>
-      <c r="AC89" s="3">
+      <c r="AD89" s="3">
         <v>17000</v>
       </c>
-      <c r="AD89" s="3">
+      <c r="AE89" s="3">
         <v>10100</v>
       </c>
-      <c r="AE89" s="3">
+      <c r="AF89" s="3">
         <v>17000</v>
       </c>
-      <c r="AF89" s="3">
+      <c r="AG89" s="3">
         <v>6200</v>
       </c>
-      <c r="AG89" s="3">
+      <c r="AH89" s="3">
         <v>18000</v>
       </c>
-      <c r="AH89" s="3">
+      <c r="AI89" s="3">
         <v>6800</v>
       </c>
-      <c r="AI89" s="3">
+      <c r="AJ89" s="3">
         <v>12800</v>
       </c>
-      <c r="AJ89" s="3">
+      <c r="AK89" s="3">
         <v>10100</v>
       </c>
-      <c r="AK89" s="3">
+      <c r="AL89" s="3">
         <v>16400</v>
       </c>
-      <c r="AL89" s="3">
+      <c r="AM89" s="3">
         <v>-11900</v>
       </c>
-      <c r="AM89" s="3">
+      <c r="AN89" s="3">
         <v>13900</v>
       </c>
-      <c r="AN89" s="3">
+      <c r="AO89" s="3">
         <v>2900</v>
       </c>
-      <c r="AO89" s="3">
+      <c r="AP89" s="3">
         <v>13600</v>
       </c>
     </row>
-    <row r="90" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="90" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C90" s="1" t="s">
         <v>79</v>
       </c>
@@ -9471,127 +9691,131 @@
       <c r="AM90" s="3"/>
       <c r="AN90" s="3"/>
       <c r="AO90" s="3"/>
+      <c r="AP90" s="3"/>
     </row>
-    <row r="91" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="91" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C91" s="1" t="s">
         <v>80</v>
       </c>
       <c r="D91" s="3">
+        <v>-19600</v>
+      </c>
+      <c r="E91" s="3">
         <v>-14300</v>
       </c>
-      <c r="E91" s="3">
+      <c r="F91" s="3">
         <v>-10800</v>
       </c>
-      <c r="F91" s="3">
+      <c r="G91" s="3">
         <v>-13500</v>
       </c>
-      <c r="G91" s="3">
+      <c r="H91" s="3">
         <v>-11100</v>
       </c>
-      <c r="H91" s="3">
+      <c r="I91" s="3">
         <v>-8700</v>
-      </c>
-      <c r="I91" s="3">
-        <v>-10600</v>
       </c>
       <c r="J91" s="3">
         <v>-10600</v>
       </c>
       <c r="K91" s="3">
+        <v>-10600</v>
+      </c>
+      <c r="L91" s="3">
         <v>-11900</v>
       </c>
-      <c r="L91" s="3">
+      <c r="M91" s="3">
         <v>-11300</v>
       </c>
-      <c r="M91" s="3">
+      <c r="N91" s="3">
         <v>-9000</v>
       </c>
-      <c r="N91" s="3">
+      <c r="O91" s="3">
         <v>-7900</v>
       </c>
-      <c r="O91" s="3">
+      <c r="P91" s="3">
         <v>-16000</v>
       </c>
-      <c r="P91" s="3">
+      <c r="Q91" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q91" s="3">
+      <c r="R91" s="3">
         <v>-9000</v>
       </c>
-      <c r="R91" s="3">
+      <c r="S91" s="3">
         <v>-11600</v>
       </c>
-      <c r="S91" s="3">
+      <c r="T91" s="3">
         <v>-12800</v>
       </c>
-      <c r="T91" s="3">
+      <c r="U91" s="3">
         <v>-8800</v>
       </c>
-      <c r="U91" s="3">
+      <c r="V91" s="3">
         <v>-4700</v>
       </c>
-      <c r="V91" s="3">
+      <c r="W91" s="3">
         <v>-2200</v>
       </c>
-      <c r="W91" s="3">
+      <c r="X91" s="3">
         <v>-7600</v>
       </c>
-      <c r="X91" s="3">
+      <c r="Y91" s="3">
         <v>-5100</v>
       </c>
-      <c r="Y91" s="3">
+      <c r="Z91" s="3">
         <v>-3300</v>
       </c>
-      <c r="Z91" s="3">
+      <c r="AA91" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA91" s="3">
+      <c r="AB91" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB91" s="3">
+      <c r="AC91" s="3">
         <v>-5300</v>
       </c>
-      <c r="AC91" s="3">
+      <c r="AD91" s="3">
         <v>-4900</v>
       </c>
-      <c r="AD91" s="3">
+      <c r="AE91" s="3">
         <v>-9200</v>
       </c>
-      <c r="AE91" s="3">
+      <c r="AF91" s="3">
         <v>-5400</v>
       </c>
-      <c r="AF91" s="3">
+      <c r="AG91" s="3">
         <v>-3000</v>
       </c>
-      <c r="AG91" s="3">
+      <c r="AH91" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH91" s="3">
+      <c r="AI91" s="3">
         <v>-2400</v>
       </c>
-      <c r="AI91" s="3">
+      <c r="AJ91" s="3">
         <v>-2700</v>
       </c>
-      <c r="AJ91" s="3">
+      <c r="AK91" s="3">
         <v>-3800</v>
-      </c>
-      <c r="AK91" s="3">
-        <v>-6600</v>
       </c>
       <c r="AL91" s="3">
         <v>-6600</v>
       </c>
       <c r="AM91" s="3">
+        <v>-6600</v>
+      </c>
+      <c r="AN91" s="3">
         <v>-5800</v>
       </c>
-      <c r="AN91" s="3">
+      <c r="AO91" s="3">
         <v>-5600</v>
       </c>
-      <c r="AO91" s="3">
+      <c r="AP91" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="92" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="92" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C92" s="1" t="s">
         <v>81</v>
       </c>
@@ -9709,8 +9933,11 @@
       <c r="AO92" s="3">
         <v>0</v>
       </c>
+      <c r="AP92" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="93" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="93" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C93" s="1" t="s">
         <v>82</v>
       </c>
@@ -9828,127 +10055,133 @@
       <c r="AO93" s="3">
         <v>0</v>
       </c>
+      <c r="AP93" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="94" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="94" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C94" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D94" s="3">
+        <v>-19500</v>
+      </c>
+      <c r="E94" s="3">
         <v>-18800</v>
       </c>
-      <c r="E94" s="3">
+      <c r="F94" s="3">
         <v>-21300</v>
       </c>
-      <c r="F94" s="3">
+      <c r="G94" s="3">
         <v>-164500</v>
       </c>
-      <c r="G94" s="3">
+      <c r="H94" s="3">
         <v>-55100</v>
       </c>
-      <c r="H94" s="3">
+      <c r="I94" s="3">
         <v>-26500</v>
       </c>
-      <c r="I94" s="3">
+      <c r="J94" s="3">
         <v>-10500</v>
       </c>
-      <c r="J94" s="3">
+      <c r="K94" s="3">
         <v>-35800</v>
       </c>
-      <c r="K94" s="3">
+      <c r="L94" s="3">
         <v>-16100</v>
       </c>
-      <c r="L94" s="3">
+      <c r="M94" s="3">
         <v>-86400</v>
       </c>
-      <c r="M94" s="3">
+      <c r="N94" s="3">
         <v>-12100</v>
       </c>
-      <c r="N94" s="3">
+      <c r="O94" s="3">
         <v>-7800</v>
       </c>
-      <c r="O94" s="3">
+      <c r="P94" s="3">
         <v>-9300</v>
       </c>
-      <c r="P94" s="3">
+      <c r="Q94" s="3">
         <v>-11600</v>
       </c>
-      <c r="Q94" s="3">
+      <c r="R94" s="3">
         <v>-8800</v>
       </c>
-      <c r="R94" s="3">
+      <c r="S94" s="3">
         <v>-11500</v>
       </c>
-      <c r="S94" s="3">
+      <c r="T94" s="3">
         <v>-31700</v>
       </c>
-      <c r="T94" s="3">
+      <c r="U94" s="3">
         <v>-10100</v>
       </c>
-      <c r="U94" s="3">
+      <c r="V94" s="3">
         <v>-5800</v>
       </c>
-      <c r="V94" s="3">
+      <c r="W94" s="3">
         <v>-2100</v>
       </c>
-      <c r="W94" s="3">
+      <c r="X94" s="3">
         <v>-23400</v>
       </c>
-      <c r="X94" s="3">
+      <c r="Y94" s="3">
         <v>-15000</v>
       </c>
-      <c r="Y94" s="3">
+      <c r="Z94" s="3">
         <v>-28200</v>
       </c>
-      <c r="Z94" s="3">
+      <c r="AA94" s="3">
         <v>-4800</v>
       </c>
-      <c r="AA94" s="3">
+      <c r="AB94" s="3">
         <v>-5100</v>
       </c>
-      <c r="AB94" s="3">
+      <c r="AC94" s="3">
         <v>-5200</v>
       </c>
-      <c r="AC94" s="3">
+      <c r="AD94" s="3">
         <v>-4800</v>
       </c>
-      <c r="AD94" s="3">
+      <c r="AE94" s="3">
         <v>-9100</v>
       </c>
-      <c r="AE94" s="3">
+      <c r="AF94" s="3">
         <v>-5300</v>
       </c>
-      <c r="AF94" s="3">
+      <c r="AG94" s="3">
         <v>-2900</v>
       </c>
-      <c r="AG94" s="3">
+      <c r="AH94" s="3">
         <v>-1800</v>
       </c>
-      <c r="AH94" s="3">
+      <c r="AI94" s="3">
         <v>-2300</v>
       </c>
-      <c r="AI94" s="3">
+      <c r="AJ94" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ94" s="3">
+      <c r="AK94" s="3">
         <v>-3700</v>
-      </c>
-      <c r="AK94" s="3">
-        <v>-6500</v>
       </c>
       <c r="AL94" s="3">
         <v>-6500</v>
       </c>
       <c r="AM94" s="3">
+        <v>-6500</v>
+      </c>
+      <c r="AN94" s="3">
         <v>-5700</v>
       </c>
-      <c r="AN94" s="3">
+      <c r="AO94" s="3">
         <v>-5500</v>
       </c>
-      <c r="AO94" s="3">
+      <c r="AP94" s="3">
         <v>-4000</v>
       </c>
     </row>
-    <row r="95" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="95" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C95" s="1" t="s">
         <v>84</v>
       </c>
@@ -9990,8 +10223,9 @@
       <c r="AM95" s="3"/>
       <c r="AN95" s="3"/>
       <c r="AO95" s="3"/>
+      <c r="AP95" s="3"/>
     </row>
-    <row r="96" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="96" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C96" s="1" t="s">
         <v>85</v>
       </c>
@@ -10002,7 +10236,7 @@
         <v>4000</v>
       </c>
       <c r="F96" s="3">
-        <v>3800</v>
+        <v>4000</v>
       </c>
       <c r="G96" s="3">
         <v>3800</v>
@@ -10014,7 +10248,7 @@
         <v>3800</v>
       </c>
       <c r="J96" s="3">
-        <v>3400</v>
+        <v>3800</v>
       </c>
       <c r="K96" s="3">
         <v>3400</v>
@@ -10026,37 +10260,37 @@
         <v>3400</v>
       </c>
       <c r="N96" s="3">
-        <v>3200</v>
+        <v>3400</v>
       </c>
       <c r="O96" s="3">
         <v>3200</v>
       </c>
       <c r="P96" s="3">
-        <v>-2900</v>
+        <v>3200</v>
       </c>
       <c r="Q96" s="3">
         <v>-2900</v>
       </c>
       <c r="R96" s="3">
-        <v>-3000</v>
+        <v>-2900</v>
       </c>
       <c r="S96" s="3">
         <v>-3000</v>
       </c>
       <c r="T96" s="3">
+        <v>-3000</v>
+      </c>
+      <c r="U96" s="3">
         <v>-2700</v>
       </c>
-      <c r="U96" s="3">
+      <c r="V96" s="3">
         <v>-2800</v>
-      </c>
-      <c r="V96" s="3">
-        <v>-2600</v>
       </c>
       <c r="W96" s="3">
         <v>-2600</v>
       </c>
       <c r="X96" s="3">
-        <v>-2500</v>
+        <v>-2600</v>
       </c>
       <c r="Y96" s="3">
         <v>-2500</v>
@@ -10068,49 +10302,52 @@
         <v>-2500</v>
       </c>
       <c r="AB96" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="AC96" s="3">
         <v>-2400</v>
       </c>
       <c r="AD96" s="3">
-        <v>-2500</v>
+        <v>-2400</v>
       </c>
       <c r="AE96" s="3">
         <v>-2500</v>
       </c>
       <c r="AF96" s="3">
-        <v>-2400</v>
+        <v>-2500</v>
       </c>
       <c r="AG96" s="3">
         <v>-2400</v>
       </c>
       <c r="AH96" s="3">
+        <v>-2400</v>
+      </c>
+      <c r="AI96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AI96" s="3">
-        <v>0</v>
-      </c>
       <c r="AJ96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AK96" s="3">
         <v>-4700</v>
       </c>
-      <c r="AK96" s="3">
-        <v>0</v>
-      </c>
       <c r="AL96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AM96" s="3">
         <v>-4500</v>
       </c>
-      <c r="AM96" s="3">
-        <v>0</v>
-      </c>
       <c r="AN96" s="3">
+        <v>0</v>
+      </c>
+      <c r="AO96" s="3">
         <v>-4500</v>
       </c>
-      <c r="AO96" s="3">
+      <c r="AP96" s="3">
         <v>0</v>
       </c>
     </row>
-    <row r="97" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="97" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C97" s="1" t="s">
         <v>86</v>
       </c>
@@ -10228,8 +10465,11 @@
       <c r="AO97" s="3">
         <v>0</v>
       </c>
+      <c r="AP97" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="98" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="98" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C98" s="1" t="s">
         <v>87</v>
       </c>
@@ -10347,8 +10587,11 @@
       <c r="AO98" s="3">
         <v>0</v>
       </c>
+      <c r="AP98" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="99" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="99" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C99" s="1" t="s">
         <v>88</v>
       </c>
@@ -10466,127 +10709,133 @@
       <c r="AO99" s="3">
         <v>0</v>
       </c>
+      <c r="AP99" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="100" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="100" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C100" s="1" t="s">
         <v>89</v>
       </c>
       <c r="D100" s="3">
+        <v>-22500</v>
+      </c>
+      <c r="E100" s="3">
         <v>-19000</v>
       </c>
-      <c r="E100" s="3">
+      <c r="F100" s="3">
         <v>-22400</v>
       </c>
-      <c r="F100" s="3">
+      <c r="G100" s="3">
         <v>142500</v>
       </c>
-      <c r="G100" s="3">
+      <c r="H100" s="3">
         <v>21100</v>
       </c>
-      <c r="H100" s="3">
+      <c r="I100" s="3">
         <v>6200</v>
       </c>
-      <c r="I100" s="3">
+      <c r="J100" s="3">
         <v>-32500</v>
       </c>
-      <c r="J100" s="3">
+      <c r="K100" s="3">
         <v>20000</v>
       </c>
-      <c r="K100" s="3">
+      <c r="L100" s="3">
         <v>-24400</v>
       </c>
-      <c r="L100" s="3">
+      <c r="M100" s="3">
         <v>56200</v>
       </c>
-      <c r="M100" s="3">
+      <c r="N100" s="3">
         <v>-41700</v>
       </c>
-      <c r="N100" s="3">
+      <c r="O100" s="3">
         <v>-27600</v>
       </c>
-      <c r="O100" s="3">
+      <c r="P100" s="3">
         <v>-22200</v>
       </c>
-      <c r="P100" s="3">
+      <c r="Q100" s="3">
         <v>-11900</v>
       </c>
-      <c r="Q100" s="3">
+      <c r="R100" s="3">
         <v>-21400</v>
       </c>
-      <c r="R100" s="3">
+      <c r="S100" s="3">
         <v>23400</v>
       </c>
-      <c r="S100" s="3">
+      <c r="T100" s="3">
         <v>7600</v>
       </c>
-      <c r="T100" s="3">
+      <c r="U100" s="3">
         <v>28100</v>
       </c>
-      <c r="U100" s="3">
+      <c r="V100" s="3">
         <v>-17900</v>
       </c>
-      <c r="V100" s="3">
+      <c r="W100" s="3">
         <v>-10500</v>
       </c>
-      <c r="W100" s="3">
+      <c r="X100" s="3">
         <v>1200</v>
       </c>
-      <c r="X100" s="3">
+      <c r="Y100" s="3">
         <v>13400</v>
       </c>
-      <c r="Y100" s="3">
+      <c r="Z100" s="3">
         <v>8300</v>
       </c>
-      <c r="Z100" s="3">
+      <c r="AA100" s="3">
         <v>3500</v>
       </c>
-      <c r="AA100" s="3">
+      <c r="AB100" s="3">
         <v>-11800</v>
       </c>
-      <c r="AB100" s="3">
+      <c r="AC100" s="3">
         <v>-9400</v>
       </c>
-      <c r="AC100" s="3">
+      <c r="AD100" s="3">
         <v>-13800</v>
       </c>
-      <c r="AD100" s="3">
+      <c r="AE100" s="3">
         <v>-4600</v>
       </c>
-      <c r="AE100" s="3">
+      <c r="AF100" s="3">
         <v>-9800</v>
       </c>
-      <c r="AF100" s="3">
-        <v>0</v>
-      </c>
       <c r="AG100" s="3">
+        <v>0</v>
+      </c>
+      <c r="AH100" s="3">
         <v>-17400</v>
       </c>
-      <c r="AH100" s="3">
+      <c r="AI100" s="3">
         <v>-4300</v>
       </c>
-      <c r="AI100" s="3">
+      <c r="AJ100" s="3">
         <v>-12800</v>
       </c>
-      <c r="AJ100" s="3">
+      <c r="AK100" s="3">
         <v>-2600</v>
       </c>
-      <c r="AK100" s="3">
+      <c r="AL100" s="3">
         <v>-8900</v>
       </c>
-      <c r="AL100" s="3">
+      <c r="AM100" s="3">
         <v>14400</v>
       </c>
-      <c r="AM100" s="3">
+      <c r="AN100" s="3">
         <v>-9600</v>
       </c>
-      <c r="AN100" s="3">
+      <c r="AO100" s="3">
         <v>-5700</v>
       </c>
-      <c r="AO100" s="3">
+      <c r="AP100" s="3">
         <v>-14300</v>
       </c>
     </row>
-    <row r="101" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="101" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C101" s="1" t="s">
         <v>90</v>
       </c>
@@ -10626,8 +10875,8 @@
       <c r="O101" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="P101" s="3">
-        <v>0</v>
+      <c r="P101" s="3" t="s">
+        <v>8</v>
       </c>
       <c r="Q101" s="3">
         <v>0</v>
@@ -10704,123 +10953,129 @@
       <c r="AO101" s="3">
         <v>0</v>
       </c>
+      <c r="AP101" s="3">
+        <v>0</v>
+      </c>
     </row>
-    <row r="102" spans="3:41" x14ac:dyDescent="0.2">
+    <row r="102" spans="3:42" x14ac:dyDescent="0.2">
       <c r="C102" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D102" s="3">
+        <v>-4300</v>
+      </c>
+      <c r="E102" s="3">
         <v>-2200</v>
       </c>
-      <c r="E102" s="3">
+      <c r="F102" s="3">
         <v>-4100</v>
       </c>
-      <c r="F102" s="3">
+      <c r="G102" s="3">
         <v>9400</v>
       </c>
-      <c r="G102" s="3">
+      <c r="H102" s="3">
         <v>-3200</v>
       </c>
-      <c r="H102" s="3">
+      <c r="I102" s="3">
         <v>800</v>
       </c>
-      <c r="I102" s="3">
+      <c r="J102" s="3">
         <v>-1400</v>
       </c>
-      <c r="J102" s="3">
+      <c r="K102" s="3">
         <v>1700</v>
       </c>
-      <c r="K102" s="3">
+      <c r="L102" s="3">
         <v>1400</v>
       </c>
-      <c r="L102" s="3">
+      <c r="M102" s="3">
         <v>-5200</v>
       </c>
-      <c r="M102" s="3">
+      <c r="N102" s="3">
         <v>3900</v>
       </c>
-      <c r="N102" s="3">
+      <c r="O102" s="3">
         <v>-500</v>
       </c>
-      <c r="O102" s="3">
+      <c r="P102" s="3">
         <v>1400</v>
       </c>
-      <c r="P102" s="3">
+      <c r="Q102" s="3">
         <v>2200</v>
       </c>
-      <c r="Q102" s="3">
+      <c r="R102" s="3">
         <v>-2100</v>
       </c>
-      <c r="R102" s="3">
+      <c r="S102" s="3">
         <v>2500</v>
       </c>
-      <c r="S102" s="3">
+      <c r="T102" s="3">
         <v>-19900</v>
       </c>
-      <c r="T102" s="3">
+      <c r="U102" s="3">
         <v>16600</v>
       </c>
-      <c r="U102" s="3">
+      <c r="V102" s="3">
         <v>1600</v>
       </c>
-      <c r="V102" s="3">
+      <c r="W102" s="3">
         <v>2200</v>
       </c>
-      <c r="W102" s="3">
+      <c r="X102" s="3">
         <v>-5000</v>
       </c>
-      <c r="X102" s="3">
+      <c r="Y102" s="3">
         <v>4800</v>
       </c>
-      <c r="Y102" s="3">
+      <c r="Z102" s="3">
         <v>-1400</v>
       </c>
-      <c r="Z102" s="3">
+      <c r="AA102" s="3">
         <v>200</v>
       </c>
-      <c r="AA102" s="3">
+      <c r="AB102" s="3">
         <v>-3000</v>
       </c>
-      <c r="AB102" s="3">
+      <c r="AC102" s="3">
         <v>3200</v>
       </c>
-      <c r="AC102" s="3">
+      <c r="AD102" s="3">
         <v>-1600</v>
       </c>
-      <c r="AD102" s="3">
+      <c r="AE102" s="3">
         <v>-3600</v>
       </c>
-      <c r="AE102" s="3">
+      <c r="AF102" s="3">
         <v>1900</v>
       </c>
-      <c r="AF102" s="3">
+      <c r="AG102" s="3">
         <v>3300</v>
       </c>
-      <c r="AG102" s="3">
+      <c r="AH102" s="3">
         <v>-1100</v>
       </c>
-      <c r="AH102" s="3">
+      <c r="AI102" s="3">
         <v>200</v>
       </c>
-      <c r="AI102" s="3">
+      <c r="AJ102" s="3">
         <v>-2600</v>
       </c>
-      <c r="AJ102" s="3">
+      <c r="AK102" s="3">
         <v>3900</v>
       </c>
-      <c r="AK102" s="3">
+      <c r="AL102" s="3">
         <v>1000</v>
       </c>
-      <c r="AL102" s="3">
+      <c r="AM102" s="3">
         <v>-4100</v>
       </c>
-      <c r="AM102" s="3">
+      <c r="AN102" s="3">
         <v>-1500</v>
       </c>
-      <c r="AN102" s="3">
+      <c r="AO102" s="3">
         <v>-8300</v>
       </c>
-      <c r="AO102" s="3">
+      <c r="AP102" s="3">
         <v>-4600</v>
       </c>
     </row>
